--- a/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="77">
+  <fonts count="79">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -466,6 +466,16 @@
       <color rgb="001B3A6B"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="47">
     <fill>
@@ -700,7 +710,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="274">
+  <borders count="292">
     <border>
       <left/>
       <right/>
@@ -3637,11 +3647,196 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="339">
+  <cellXfs count="408">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4414,6 +4609,176 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="268" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="279" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="280" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="281" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="276" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="275" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="276" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="275" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="276" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="7" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="288" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="286" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="285" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="286" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="285" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="288" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4488,72 +4853,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5238750" cy="1514475"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>0</row>
-      <rowOff>257175</rowOff>
-    </from>
-    <ext cx="1552575" cy="438150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4865,717 +5164,1988 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="327" t="inlineStr">
+      <c r="A1" s="339" t="inlineStr">
         <is>
           <t>Gage Verification Log</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="285" t="n"/>
-      <c r="H1" s="285" t="n"/>
-      <c r="I1" s="285" t="n"/>
-      <c r="J1" s="285" t="n"/>
-      <c r="K1" s="286" t="n"/>
+      <c r="B1" s="402" t="n"/>
+      <c r="C1" s="402" t="n"/>
+      <c r="D1" s="402" t="n"/>
+      <c r="E1" s="402" t="n"/>
+      <c r="F1" s="402" t="n"/>
+      <c r="G1" s="402" t="n"/>
+      <c r="H1" s="402" t="n"/>
+      <c r="I1" s="402" t="n"/>
+      <c r="J1" s="402" t="n"/>
+      <c r="K1" s="403" t="n"/>
+      <c r="L1" s="342" t="n"/>
+      <c r="M1" s="342" t="n"/>
+      <c r="N1" s="342" t="n"/>
+      <c r="O1" s="342" t="n"/>
+      <c r="P1" s="342" t="n"/>
+      <c r="Q1" s="342" t="n"/>
+      <c r="R1" s="342" t="n"/>
+      <c r="S1" s="342" t="n"/>
+      <c r="T1" s="342" t="n"/>
+      <c r="U1" s="342" t="n"/>
+      <c r="V1" s="342" t="n"/>
+      <c r="W1" s="342" t="n"/>
+      <c r="X1" s="342" t="n"/>
+      <c r="Y1" s="342" t="n"/>
+      <c r="Z1" s="342" t="n"/>
+      <c r="AA1" s="342" t="n"/>
+      <c r="AB1" s="342" t="n"/>
+      <c r="AC1" s="342" t="n"/>
+      <c r="AD1" s="342" t="n"/>
+      <c r="AE1" s="342" t="n"/>
+      <c r="AF1" s="342" t="n"/>
+      <c r="AG1" s="342" t="n"/>
+      <c r="AH1" s="342" t="n"/>
+      <c r="AI1" s="342" t="n"/>
+      <c r="AJ1" s="342" t="n"/>
+      <c r="AK1" s="342" t="n"/>
+      <c r="AL1" s="342" t="n"/>
+      <c r="AM1" s="342" t="n"/>
+      <c r="AN1" s="342" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="328" t="inlineStr">
+      <c r="A2" s="343" t="inlineStr">
         <is>
           <t>Operational Data Sheet · FRM-602 · Owner: QA</t>
         </is>
       </c>
-      <c r="B2" s="285" t="n"/>
-      <c r="C2" s="285" t="n"/>
-      <c r="D2" s="285" t="n"/>
-      <c r="E2" s="285" t="n"/>
-      <c r="F2" s="285" t="n"/>
-      <c r="G2" s="285" t="n"/>
-      <c r="H2" s="285" t="n"/>
-      <c r="I2" s="285" t="n"/>
-      <c r="J2" s="285" t="n"/>
-      <c r="K2" s="286" t="n"/>
+      <c r="B2" s="402" t="n"/>
+      <c r="C2" s="402" t="n"/>
+      <c r="D2" s="402" t="n"/>
+      <c r="E2" s="402" t="n"/>
+      <c r="F2" s="402" t="n"/>
+      <c r="G2" s="402" t="n"/>
+      <c r="H2" s="402" t="n"/>
+      <c r="I2" s="402" t="n"/>
+      <c r="J2" s="402" t="n"/>
+      <c r="K2" s="403" t="n"/>
+      <c r="L2" s="342" t="n"/>
+      <c r="M2" s="342" t="n"/>
+      <c r="N2" s="342" t="n"/>
+      <c r="O2" s="342" t="n"/>
+      <c r="P2" s="342" t="n"/>
+      <c r="Q2" s="342" t="n"/>
+      <c r="R2" s="342" t="n"/>
+      <c r="S2" s="342" t="n"/>
+      <c r="T2" s="342" t="n"/>
+      <c r="U2" s="342" t="n"/>
+      <c r="V2" s="342" t="n"/>
+      <c r="W2" s="342" t="n"/>
+      <c r="X2" s="342" t="n"/>
+      <c r="Y2" s="342" t="n"/>
+      <c r="Z2" s="342" t="n"/>
+      <c r="AA2" s="342" t="n"/>
+      <c r="AB2" s="342" t="n"/>
+      <c r="AC2" s="342" t="n"/>
+      <c r="AD2" s="342" t="n"/>
+      <c r="AE2" s="342" t="n"/>
+      <c r="AF2" s="342" t="n"/>
+      <c r="AG2" s="342" t="n"/>
+      <c r="AH2" s="342" t="n"/>
+      <c r="AI2" s="342" t="n"/>
+      <c r="AJ2" s="342" t="n"/>
+      <c r="AK2" s="342" t="n"/>
+      <c r="AL2" s="342" t="n"/>
+      <c r="AM2" s="342" t="n"/>
+      <c r="AN2" s="342" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="329" t="inlineStr">
+      <c r="A3" s="344" t="inlineStr">
         <is>
           <t>Controlled row-level entry. Use approved dropdowns only. Do not delete history. Refer to the FACE sheet for review context and sign-off.</t>
         </is>
       </c>
-      <c r="B3" s="285" t="n"/>
-      <c r="C3" s="285" t="n"/>
-      <c r="D3" s="285" t="n"/>
-      <c r="E3" s="285" t="n"/>
-      <c r="F3" s="285" t="n"/>
-      <c r="G3" s="285" t="n"/>
-      <c r="H3" s="285" t="n"/>
-      <c r="I3" s="285" t="n"/>
-      <c r="J3" s="285" t="n"/>
-      <c r="K3" s="286" t="n"/>
+      <c r="B3" s="402" t="n"/>
+      <c r="C3" s="402" t="n"/>
+      <c r="D3" s="402" t="n"/>
+      <c r="E3" s="402" t="n"/>
+      <c r="F3" s="402" t="n"/>
+      <c r="G3" s="402" t="n"/>
+      <c r="H3" s="402" t="n"/>
+      <c r="I3" s="402" t="n"/>
+      <c r="J3" s="402" t="n"/>
+      <c r="K3" s="403" t="n"/>
+      <c r="L3" s="342" t="n"/>
+      <c r="M3" s="342" t="n"/>
+      <c r="N3" s="342" t="n"/>
+      <c r="O3" s="342" t="n"/>
+      <c r="P3" s="342" t="n"/>
+      <c r="Q3" s="342" t="n"/>
+      <c r="R3" s="342" t="n"/>
+      <c r="S3" s="342" t="n"/>
+      <c r="T3" s="342" t="n"/>
+      <c r="U3" s="342" t="n"/>
+      <c r="V3" s="342" t="n"/>
+      <c r="W3" s="342" t="n"/>
+      <c r="X3" s="342" t="n"/>
+      <c r="Y3" s="342" t="n"/>
+      <c r="Z3" s="342" t="n"/>
+      <c r="AA3" s="342" t="n"/>
+      <c r="AB3" s="342" t="n"/>
+      <c r="AC3" s="342" t="n"/>
+      <c r="AD3" s="342" t="n"/>
+      <c r="AE3" s="342" t="n"/>
+      <c r="AF3" s="342" t="n"/>
+      <c r="AG3" s="342" t="n"/>
+      <c r="AH3" s="342" t="n"/>
+      <c r="AI3" s="342" t="n"/>
+      <c r="AJ3" s="342" t="n"/>
+      <c r="AK3" s="342" t="n"/>
+      <c r="AL3" s="342" t="n"/>
+      <c r="AM3" s="342" t="n"/>
+      <c r="AN3" s="342" t="n"/>
     </row>
     <row r="4" ht="4" customHeight="1">
-      <c r="A4" s="330" t="n"/>
-      <c r="B4" s="330" t="n"/>
-      <c r="C4" s="330" t="n"/>
-      <c r="D4" s="330" t="n"/>
-      <c r="E4" s="330" t="n"/>
-      <c r="F4" s="330" t="n"/>
-      <c r="G4" s="330" t="n"/>
-      <c r="H4" s="330" t="n"/>
-      <c r="I4" s="330" t="n"/>
-      <c r="J4" s="330" t="n"/>
-      <c r="K4" s="330" t="n"/>
+      <c r="A4" s="345" t="n"/>
+      <c r="B4" s="345" t="n"/>
+      <c r="C4" s="345" t="n"/>
+      <c r="D4" s="345" t="n"/>
+      <c r="E4" s="345" t="n"/>
+      <c r="F4" s="345" t="n"/>
+      <c r="G4" s="345" t="n"/>
+      <c r="H4" s="345" t="n"/>
+      <c r="I4" s="345" t="n"/>
+      <c r="J4" s="345" t="n"/>
+      <c r="K4" s="345" t="n"/>
+      <c r="L4" s="345" t="n"/>
+      <c r="M4" s="345" t="n"/>
+      <c r="N4" s="345" t="n"/>
+      <c r="O4" s="345" t="n"/>
+      <c r="P4" s="345" t="n"/>
+      <c r="Q4" s="345" t="n"/>
+      <c r="R4" s="345" t="n"/>
+      <c r="S4" s="345" t="n"/>
+      <c r="T4" s="345" t="n"/>
+      <c r="U4" s="345" t="n"/>
+      <c r="V4" s="345" t="n"/>
+      <c r="W4" s="345" t="n"/>
+      <c r="X4" s="345" t="n"/>
+      <c r="Y4" s="345" t="n"/>
+      <c r="Z4" s="345" t="n"/>
+      <c r="AA4" s="345" t="n"/>
+      <c r="AB4" s="345" t="n"/>
+      <c r="AC4" s="345" t="n"/>
+      <c r="AD4" s="345" t="n"/>
+      <c r="AE4" s="345" t="n"/>
+      <c r="AF4" s="345" t="n"/>
+      <c r="AG4" s="345" t="n"/>
+      <c r="AH4" s="345" t="n"/>
+      <c r="AI4" s="345" t="n"/>
+      <c r="AJ4" s="345" t="n"/>
+      <c r="AK4" s="345" t="n"/>
+      <c r="AL4" s="345" t="n"/>
+      <c r="AM4" s="345" t="n"/>
+      <c r="AN4" s="345" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="331" t="inlineStr">
+      <c r="A5" s="346" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. ACTIVE LOG TABLE</t>
         </is>
       </c>
-      <c r="B5" s="285" t="n"/>
-      <c r="C5" s="285" t="n"/>
-      <c r="D5" s="285" t="n"/>
-      <c r="E5" s="285" t="n"/>
-      <c r="F5" s="285" t="n"/>
-      <c r="G5" s="285" t="n"/>
-      <c r="H5" s="285" t="n"/>
-      <c r="I5" s="285" t="n"/>
-      <c r="J5" s="285" t="n"/>
-      <c r="K5" s="286" t="n"/>
+      <c r="B5" s="402" t="n"/>
+      <c r="C5" s="402" t="n"/>
+      <c r="D5" s="402" t="n"/>
+      <c r="E5" s="402" t="n"/>
+      <c r="F5" s="402" t="n"/>
+      <c r="G5" s="402" t="n"/>
+      <c r="H5" s="402" t="n"/>
+      <c r="I5" s="402" t="n"/>
+      <c r="J5" s="402" t="n"/>
+      <c r="K5" s="403" t="n"/>
+      <c r="L5" s="342" t="n"/>
+      <c r="M5" s="342" t="n"/>
+      <c r="N5" s="342" t="n"/>
+      <c r="O5" s="342" t="n"/>
+      <c r="P5" s="342" t="n"/>
+      <c r="Q5" s="342" t="n"/>
+      <c r="R5" s="342" t="n"/>
+      <c r="S5" s="342" t="n"/>
+      <c r="T5" s="342" t="n"/>
+      <c r="U5" s="342" t="n"/>
+      <c r="V5" s="342" t="n"/>
+      <c r="W5" s="342" t="n"/>
+      <c r="X5" s="342" t="n"/>
+      <c r="Y5" s="342" t="n"/>
+      <c r="Z5" s="342" t="n"/>
+      <c r="AA5" s="342" t="n"/>
+      <c r="AB5" s="342" t="n"/>
+      <c r="AC5" s="342" t="n"/>
+      <c r="AD5" s="342" t="n"/>
+      <c r="AE5" s="342" t="n"/>
+      <c r="AF5" s="342" t="n"/>
+      <c r="AG5" s="342" t="n"/>
+      <c r="AH5" s="342" t="n"/>
+      <c r="AI5" s="342" t="n"/>
+      <c r="AJ5" s="342" t="n"/>
+      <c r="AK5" s="342" t="n"/>
+      <c r="AL5" s="342" t="n"/>
+      <c r="AM5" s="342" t="n"/>
+      <c r="AN5" s="342" t="n"/>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="291" t="inlineStr">
+      <c r="A6" s="347" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B6" s="291" t="inlineStr">
+      <c r="B6" s="347" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C6" s="291" t="inlineStr">
+      <c r="C6" s="347" t="inlineStr">
         <is>
           <t>Gage ID</t>
         </is>
       </c>
-      <c r="D6" s="291" t="inlineStr">
+      <c r="D6" s="347" t="inlineStr">
         <is>
           <t>Verification Type</t>
         </is>
       </c>
-      <c r="E6" s="291" t="inlineStr">
+      <c r="E6" s="347" t="inlineStr">
         <is>
           <t>Check Artifact / Master</t>
         </is>
       </c>
-      <c r="F6" s="291" t="inlineStr">
+      <c r="F6" s="347" t="inlineStr">
         <is>
           <t>Criteria</t>
         </is>
       </c>
-      <c r="G6" s="291" t="inlineStr">
+      <c r="G6" s="347" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="H6" s="291" t="inlineStr">
+      <c r="H6" s="347" t="inlineStr">
         <is>
           <t>CAL Status</t>
         </is>
       </c>
-      <c r="I6" s="291" t="inlineStr">
+      <c r="I6" s="347" t="inlineStr">
         <is>
           <t>Use Stop (Y/N)</t>
         </is>
       </c>
-      <c r="J6" s="291" t="inlineStr">
+      <c r="J6" s="347" t="inlineStr">
         <is>
           <t>Owner Dept</t>
         </is>
       </c>
-      <c r="K6" s="291" t="inlineStr">
+      <c r="K6" s="347" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="L6" s="342" t="n"/>
+      <c r="M6" s="342" t="n"/>
+      <c r="N6" s="342" t="n"/>
+      <c r="O6" s="342" t="n"/>
+      <c r="P6" s="342" t="n"/>
+      <c r="Q6" s="342" t="n"/>
+      <c r="R6" s="342" t="n"/>
+      <c r="S6" s="342" t="n"/>
+      <c r="T6" s="342" t="n"/>
+      <c r="U6" s="342" t="n"/>
+      <c r="V6" s="342" t="n"/>
+      <c r="W6" s="342" t="n"/>
+      <c r="X6" s="342" t="n"/>
+      <c r="Y6" s="342" t="n"/>
+      <c r="Z6" s="342" t="n"/>
+      <c r="AA6" s="342" t="n"/>
+      <c r="AB6" s="342" t="n"/>
+      <c r="AC6" s="342" t="n"/>
+      <c r="AD6" s="342" t="n"/>
+      <c r="AE6" s="342" t="n"/>
+      <c r="AF6" s="342" t="n"/>
+      <c r="AG6" s="342" t="n"/>
+      <c r="AH6" s="342" t="n"/>
+      <c r="AI6" s="342" t="n"/>
+      <c r="AJ6" s="342" t="n"/>
+      <c r="AK6" s="342" t="n"/>
+      <c r="AL6" s="342" t="n"/>
+      <c r="AM6" s="342" t="n"/>
+      <c r="AN6" s="342" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="338">
+      <c r="A7" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B7" s="333" t="n"/>
-      <c r="C7" s="333" t="n"/>
-      <c r="D7" s="333" t="n"/>
-      <c r="E7" s="333" t="n"/>
-      <c r="F7" s="333" t="n"/>
-      <c r="G7" s="333" t="n"/>
-      <c r="H7" s="333" t="n"/>
-      <c r="I7" s="333" t="n"/>
-      <c r="J7" s="333" t="n"/>
-      <c r="K7" s="333" t="n"/>
+      <c r="B7" s="349" t="n"/>
+      <c r="C7" s="349" t="n"/>
+      <c r="D7" s="349" t="n"/>
+      <c r="E7" s="349" t="n"/>
+      <c r="F7" s="349" t="n"/>
+      <c r="G7" s="349" t="n"/>
+      <c r="H7" s="349" t="n"/>
+      <c r="I7" s="349" t="n"/>
+      <c r="J7" s="349" t="n"/>
+      <c r="K7" s="349" t="n"/>
+      <c r="L7" s="342" t="n"/>
+      <c r="M7" s="342" t="n"/>
+      <c r="N7" s="342" t="n"/>
+      <c r="O7" s="342" t="n"/>
+      <c r="P7" s="342" t="n"/>
+      <c r="Q7" s="342" t="n"/>
+      <c r="R7" s="342" t="n"/>
+      <c r="S7" s="342" t="n"/>
+      <c r="T7" s="342" t="n"/>
+      <c r="U7" s="342" t="n"/>
+      <c r="V7" s="342" t="n"/>
+      <c r="W7" s="342" t="n"/>
+      <c r="X7" s="342" t="n"/>
+      <c r="Y7" s="342" t="n"/>
+      <c r="Z7" s="342" t="n"/>
+      <c r="AA7" s="342" t="n"/>
+      <c r="AB7" s="342" t="n"/>
+      <c r="AC7" s="342" t="n"/>
+      <c r="AD7" s="342" t="n"/>
+      <c r="AE7" s="342" t="n"/>
+      <c r="AF7" s="342" t="n"/>
+      <c r="AG7" s="342" t="n"/>
+      <c r="AH7" s="342" t="n"/>
+      <c r="AI7" s="342" t="n"/>
+      <c r="AJ7" s="342" t="n"/>
+      <c r="AK7" s="342" t="n"/>
+      <c r="AL7" s="342" t="n"/>
+      <c r="AM7" s="342" t="n"/>
+      <c r="AN7" s="342" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="338">
+      <c r="A8" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B8" s="333" t="n"/>
-      <c r="C8" s="333" t="n"/>
-      <c r="D8" s="333" t="n"/>
-      <c r="E8" s="333" t="n"/>
-      <c r="F8" s="333" t="n"/>
-      <c r="G8" s="333" t="n"/>
-      <c r="H8" s="333" t="n"/>
-      <c r="I8" s="333" t="n"/>
-      <c r="J8" s="333" t="n"/>
-      <c r="K8" s="333" t="n"/>
+      <c r="B8" s="349" t="n"/>
+      <c r="C8" s="349" t="n"/>
+      <c r="D8" s="349" t="n"/>
+      <c r="E8" s="349" t="n"/>
+      <c r="F8" s="349" t="n"/>
+      <c r="G8" s="349" t="n"/>
+      <c r="H8" s="349" t="n"/>
+      <c r="I8" s="349" t="n"/>
+      <c r="J8" s="349" t="n"/>
+      <c r="K8" s="349" t="n"/>
+      <c r="L8" s="350" t="n"/>
+      <c r="M8" s="350" t="n"/>
+      <c r="N8" s="350" t="n"/>
+      <c r="O8" s="350" t="n"/>
+      <c r="P8" s="350" t="n"/>
+      <c r="Q8" s="350" t="n"/>
+      <c r="R8" s="350" t="n"/>
+      <c r="S8" s="350" t="n"/>
+      <c r="T8" s="350" t="n"/>
+      <c r="U8" s="350" t="n"/>
+      <c r="V8" s="350" t="n"/>
+      <c r="W8" s="350" t="n"/>
+      <c r="X8" s="350" t="n"/>
+      <c r="Y8" s="350" t="n"/>
+      <c r="Z8" s="350" t="n"/>
+      <c r="AA8" s="350" t="n"/>
+      <c r="AB8" s="350" t="n"/>
+      <c r="AC8" s="350" t="n"/>
+      <c r="AD8" s="350" t="n"/>
+      <c r="AE8" s="350" t="n"/>
+      <c r="AF8" s="350" t="n"/>
+      <c r="AG8" s="350" t="n"/>
+      <c r="AH8" s="350" t="n"/>
+      <c r="AI8" s="350" t="n"/>
+      <c r="AJ8" s="350" t="n"/>
+      <c r="AK8" s="350" t="n"/>
+      <c r="AL8" s="350" t="n"/>
+      <c r="AM8" s="350" t="n"/>
+      <c r="AN8" s="350" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="338">
+      <c r="A9" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B9" s="333" t="n"/>
-      <c r="C9" s="333" t="n"/>
-      <c r="D9" s="333" t="n"/>
-      <c r="E9" s="333" t="n"/>
-      <c r="F9" s="333" t="n"/>
-      <c r="G9" s="333" t="n"/>
-      <c r="H9" s="333" t="n"/>
-      <c r="I9" s="333" t="n"/>
-      <c r="J9" s="333" t="n"/>
-      <c r="K9" s="333" t="n"/>
+      <c r="B9" s="349" t="n"/>
+      <c r="C9" s="349" t="n"/>
+      <c r="D9" s="349" t="n"/>
+      <c r="E9" s="349" t="n"/>
+      <c r="F9" s="349" t="n"/>
+      <c r="G9" s="349" t="n"/>
+      <c r="H9" s="349" t="n"/>
+      <c r="I9" s="349" t="n"/>
+      <c r="J9" s="349" t="n"/>
+      <c r="K9" s="349" t="n"/>
+      <c r="L9" s="350" t="n"/>
+      <c r="M9" s="350" t="n"/>
+      <c r="N9" s="350" t="n"/>
+      <c r="O9" s="350" t="n"/>
+      <c r="P9" s="350" t="n"/>
+      <c r="Q9" s="350" t="n"/>
+      <c r="R9" s="350" t="n"/>
+      <c r="S9" s="350" t="n"/>
+      <c r="T9" s="350" t="n"/>
+      <c r="U9" s="350" t="n"/>
+      <c r="V9" s="350" t="n"/>
+      <c r="W9" s="350" t="n"/>
+      <c r="X9" s="350" t="n"/>
+      <c r="Y9" s="350" t="n"/>
+      <c r="Z9" s="350" t="n"/>
+      <c r="AA9" s="350" t="n"/>
+      <c r="AB9" s="350" t="n"/>
+      <c r="AC9" s="350" t="n"/>
+      <c r="AD9" s="350" t="n"/>
+      <c r="AE9" s="350" t="n"/>
+      <c r="AF9" s="350" t="n"/>
+      <c r="AG9" s="350" t="n"/>
+      <c r="AH9" s="350" t="n"/>
+      <c r="AI9" s="350" t="n"/>
+      <c r="AJ9" s="350" t="n"/>
+      <c r="AK9" s="350" t="n"/>
+      <c r="AL9" s="350" t="n"/>
+      <c r="AM9" s="350" t="n"/>
+      <c r="AN9" s="350" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="338">
+      <c r="A10" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B10" s="333" t="n"/>
-      <c r="C10" s="333" t="n"/>
-      <c r="D10" s="333" t="n"/>
-      <c r="E10" s="333" t="n"/>
-      <c r="F10" s="333" t="n"/>
-      <c r="G10" s="333" t="n"/>
-      <c r="H10" s="333" t="n"/>
-      <c r="I10" s="333" t="n"/>
-      <c r="J10" s="333" t="n"/>
-      <c r="K10" s="333" t="n"/>
+      <c r="B10" s="349" t="n"/>
+      <c r="C10" s="349" t="n"/>
+      <c r="D10" s="349" t="n"/>
+      <c r="E10" s="349" t="n"/>
+      <c r="F10" s="349" t="n"/>
+      <c r="G10" s="349" t="n"/>
+      <c r="H10" s="349" t="n"/>
+      <c r="I10" s="349" t="n"/>
+      <c r="J10" s="349" t="n"/>
+      <c r="K10" s="349" t="n"/>
+      <c r="L10" s="350" t="n"/>
+      <c r="M10" s="350" t="n"/>
+      <c r="N10" s="350" t="n"/>
+      <c r="O10" s="350" t="n"/>
+      <c r="P10" s="350" t="n"/>
+      <c r="Q10" s="350" t="n"/>
+      <c r="R10" s="350" t="n"/>
+      <c r="S10" s="350" t="n"/>
+      <c r="T10" s="350" t="n"/>
+      <c r="U10" s="350" t="n"/>
+      <c r="V10" s="350" t="n"/>
+      <c r="W10" s="350" t="n"/>
+      <c r="X10" s="350" t="n"/>
+      <c r="Y10" s="350" t="n"/>
+      <c r="Z10" s="350" t="n"/>
+      <c r="AA10" s="350" t="n"/>
+      <c r="AB10" s="350" t="n"/>
+      <c r="AC10" s="350" t="n"/>
+      <c r="AD10" s="350" t="n"/>
+      <c r="AE10" s="350" t="n"/>
+      <c r="AF10" s="350" t="n"/>
+      <c r="AG10" s="350" t="n"/>
+      <c r="AH10" s="350" t="n"/>
+      <c r="AI10" s="350" t="n"/>
+      <c r="AJ10" s="350" t="n"/>
+      <c r="AK10" s="350" t="n"/>
+      <c r="AL10" s="350" t="n"/>
+      <c r="AM10" s="350" t="n"/>
+      <c r="AN10" s="350" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="338">
+      <c r="A11" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B11" s="333" t="n"/>
-      <c r="C11" s="333" t="n"/>
-      <c r="D11" s="333" t="n"/>
-      <c r="E11" s="333" t="n"/>
-      <c r="F11" s="333" t="n"/>
-      <c r="G11" s="333" t="n"/>
-      <c r="H11" s="333" t="n"/>
-      <c r="I11" s="333" t="n"/>
-      <c r="J11" s="333" t="n"/>
-      <c r="K11" s="333" t="n"/>
+      <c r="B11" s="349" t="n"/>
+      <c r="C11" s="349" t="n"/>
+      <c r="D11" s="349" t="n"/>
+      <c r="E11" s="349" t="n"/>
+      <c r="F11" s="349" t="n"/>
+      <c r="G11" s="349" t="n"/>
+      <c r="H11" s="349" t="n"/>
+      <c r="I11" s="349" t="n"/>
+      <c r="J11" s="349" t="n"/>
+      <c r="K11" s="349" t="n"/>
+      <c r="L11" s="350" t="n"/>
+      <c r="M11" s="350" t="n"/>
+      <c r="N11" s="350" t="n"/>
+      <c r="O11" s="350" t="n"/>
+      <c r="P11" s="350" t="n"/>
+      <c r="Q11" s="350" t="n"/>
+      <c r="R11" s="350" t="n"/>
+      <c r="S11" s="350" t="n"/>
+      <c r="T11" s="350" t="n"/>
+      <c r="U11" s="350" t="n"/>
+      <c r="V11" s="350" t="n"/>
+      <c r="W11" s="350" t="n"/>
+      <c r="X11" s="350" t="n"/>
+      <c r="Y11" s="350" t="n"/>
+      <c r="Z11" s="350" t="n"/>
+      <c r="AA11" s="350" t="n"/>
+      <c r="AB11" s="350" t="n"/>
+      <c r="AC11" s="350" t="n"/>
+      <c r="AD11" s="350" t="n"/>
+      <c r="AE11" s="350" t="n"/>
+      <c r="AF11" s="350" t="n"/>
+      <c r="AG11" s="350" t="n"/>
+      <c r="AH11" s="350" t="n"/>
+      <c r="AI11" s="350" t="n"/>
+      <c r="AJ11" s="350" t="n"/>
+      <c r="AK11" s="350" t="n"/>
+      <c r="AL11" s="350" t="n"/>
+      <c r="AM11" s="350" t="n"/>
+      <c r="AN11" s="350" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="338">
+      <c r="A12" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B12" s="333" t="n"/>
-      <c r="C12" s="333" t="n"/>
-      <c r="D12" s="333" t="n"/>
-      <c r="E12" s="333" t="n"/>
-      <c r="F12" s="333" t="n"/>
-      <c r="G12" s="333" t="n"/>
-      <c r="H12" s="333" t="n"/>
-      <c r="I12" s="333" t="n"/>
-      <c r="J12" s="333" t="n"/>
-      <c r="K12" s="333" t="n"/>
+      <c r="B12" s="349" t="n"/>
+      <c r="C12" s="349" t="n"/>
+      <c r="D12" s="349" t="n"/>
+      <c r="E12" s="349" t="n"/>
+      <c r="F12" s="349" t="n"/>
+      <c r="G12" s="349" t="n"/>
+      <c r="H12" s="349" t="n"/>
+      <c r="I12" s="349" t="n"/>
+      <c r="J12" s="349" t="n"/>
+      <c r="K12" s="349" t="n"/>
+      <c r="L12" s="350" t="n"/>
+      <c r="M12" s="350" t="n"/>
+      <c r="N12" s="350" t="n"/>
+      <c r="O12" s="350" t="n"/>
+      <c r="P12" s="350" t="n"/>
+      <c r="Q12" s="350" t="n"/>
+      <c r="R12" s="350" t="n"/>
+      <c r="S12" s="350" t="n"/>
+      <c r="T12" s="350" t="n"/>
+      <c r="U12" s="350" t="n"/>
+      <c r="V12" s="350" t="n"/>
+      <c r="W12" s="350" t="n"/>
+      <c r="X12" s="350" t="n"/>
+      <c r="Y12" s="350" t="n"/>
+      <c r="Z12" s="350" t="n"/>
+      <c r="AA12" s="350" t="n"/>
+      <c r="AB12" s="350" t="n"/>
+      <c r="AC12" s="350" t="n"/>
+      <c r="AD12" s="350" t="n"/>
+      <c r="AE12" s="350" t="n"/>
+      <c r="AF12" s="350" t="n"/>
+      <c r="AG12" s="350" t="n"/>
+      <c r="AH12" s="350" t="n"/>
+      <c r="AI12" s="350" t="n"/>
+      <c r="AJ12" s="350" t="n"/>
+      <c r="AK12" s="350" t="n"/>
+      <c r="AL12" s="350" t="n"/>
+      <c r="AM12" s="350" t="n"/>
+      <c r="AN12" s="350" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="338">
+      <c r="A13" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B13" s="333" t="n"/>
-      <c r="C13" s="333" t="n"/>
-      <c r="D13" s="333" t="n"/>
-      <c r="E13" s="333" t="n"/>
-      <c r="F13" s="333" t="n"/>
-      <c r="G13" s="333" t="n"/>
-      <c r="H13" s="333" t="n"/>
-      <c r="I13" s="333" t="n"/>
-      <c r="J13" s="333" t="n"/>
-      <c r="K13" s="333" t="n"/>
+      <c r="B13" s="349" t="n"/>
+      <c r="C13" s="349" t="n"/>
+      <c r="D13" s="349" t="n"/>
+      <c r="E13" s="349" t="n"/>
+      <c r="F13" s="349" t="n"/>
+      <c r="G13" s="349" t="n"/>
+      <c r="H13" s="349" t="n"/>
+      <c r="I13" s="349" t="n"/>
+      <c r="J13" s="349" t="n"/>
+      <c r="K13" s="349" t="n"/>
+      <c r="L13" s="350" t="n"/>
+      <c r="M13" s="350" t="n"/>
+      <c r="N13" s="350" t="n"/>
+      <c r="O13" s="350" t="n"/>
+      <c r="P13" s="350" t="n"/>
+      <c r="Q13" s="350" t="n"/>
+      <c r="R13" s="350" t="n"/>
+      <c r="S13" s="350" t="n"/>
+      <c r="T13" s="350" t="n"/>
+      <c r="U13" s="350" t="n"/>
+      <c r="V13" s="350" t="n"/>
+      <c r="W13" s="350" t="n"/>
+      <c r="X13" s="350" t="n"/>
+      <c r="Y13" s="350" t="n"/>
+      <c r="Z13" s="350" t="n"/>
+      <c r="AA13" s="350" t="n"/>
+      <c r="AB13" s="350" t="n"/>
+      <c r="AC13" s="350" t="n"/>
+      <c r="AD13" s="350" t="n"/>
+      <c r="AE13" s="350" t="n"/>
+      <c r="AF13" s="350" t="n"/>
+      <c r="AG13" s="350" t="n"/>
+      <c r="AH13" s="350" t="n"/>
+      <c r="AI13" s="350" t="n"/>
+      <c r="AJ13" s="350" t="n"/>
+      <c r="AK13" s="350" t="n"/>
+      <c r="AL13" s="350" t="n"/>
+      <c r="AM13" s="350" t="n"/>
+      <c r="AN13" s="350" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="338">
+      <c r="A14" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B14" s="333" t="n"/>
-      <c r="C14" s="333" t="n"/>
-      <c r="D14" s="333" t="n"/>
-      <c r="E14" s="333" t="n"/>
-      <c r="F14" s="333" t="n"/>
-      <c r="G14" s="333" t="n"/>
-      <c r="H14" s="333" t="n"/>
-      <c r="I14" s="333" t="n"/>
-      <c r="J14" s="333" t="n"/>
-      <c r="K14" s="333" t="n"/>
+      <c r="B14" s="349" t="n"/>
+      <c r="C14" s="349" t="n"/>
+      <c r="D14" s="349" t="n"/>
+      <c r="E14" s="349" t="n"/>
+      <c r="F14" s="349" t="n"/>
+      <c r="G14" s="349" t="n"/>
+      <c r="H14" s="349" t="n"/>
+      <c r="I14" s="349" t="n"/>
+      <c r="J14" s="349" t="n"/>
+      <c r="K14" s="349" t="n"/>
+      <c r="L14" s="350" t="n"/>
+      <c r="M14" s="350" t="n"/>
+      <c r="N14" s="350" t="n"/>
+      <c r="O14" s="350" t="n"/>
+      <c r="P14" s="350" t="n"/>
+      <c r="Q14" s="350" t="n"/>
+      <c r="R14" s="350" t="n"/>
+      <c r="S14" s="350" t="n"/>
+      <c r="T14" s="350" t="n"/>
+      <c r="U14" s="350" t="n"/>
+      <c r="V14" s="350" t="n"/>
+      <c r="W14" s="350" t="n"/>
+      <c r="X14" s="350" t="n"/>
+      <c r="Y14" s="350" t="n"/>
+      <c r="Z14" s="350" t="n"/>
+      <c r="AA14" s="350" t="n"/>
+      <c r="AB14" s="350" t="n"/>
+      <c r="AC14" s="350" t="n"/>
+      <c r="AD14" s="350" t="n"/>
+      <c r="AE14" s="350" t="n"/>
+      <c r="AF14" s="350" t="n"/>
+      <c r="AG14" s="350" t="n"/>
+      <c r="AH14" s="350" t="n"/>
+      <c r="AI14" s="350" t="n"/>
+      <c r="AJ14" s="350" t="n"/>
+      <c r="AK14" s="350" t="n"/>
+      <c r="AL14" s="350" t="n"/>
+      <c r="AM14" s="350" t="n"/>
+      <c r="AN14" s="350" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="338">
+      <c r="A15" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B15" s="333" t="n"/>
-      <c r="C15" s="333" t="n"/>
-      <c r="D15" s="333" t="n"/>
-      <c r="E15" s="333" t="n"/>
-      <c r="F15" s="333" t="n"/>
-      <c r="G15" s="333" t="n"/>
-      <c r="H15" s="333" t="n"/>
-      <c r="I15" s="333" t="n"/>
-      <c r="J15" s="333" t="n"/>
-      <c r="K15" s="333" t="n"/>
+      <c r="B15" s="349" t="n"/>
+      <c r="C15" s="349" t="n"/>
+      <c r="D15" s="349" t="n"/>
+      <c r="E15" s="349" t="n"/>
+      <c r="F15" s="349" t="n"/>
+      <c r="G15" s="349" t="n"/>
+      <c r="H15" s="349" t="n"/>
+      <c r="I15" s="349" t="n"/>
+      <c r="J15" s="349" t="n"/>
+      <c r="K15" s="349" t="n"/>
+      <c r="L15" s="350" t="n"/>
+      <c r="M15" s="350" t="n"/>
+      <c r="N15" s="350" t="n"/>
+      <c r="O15" s="350" t="n"/>
+      <c r="P15" s="350" t="n"/>
+      <c r="Q15" s="350" t="n"/>
+      <c r="R15" s="350" t="n"/>
+      <c r="S15" s="350" t="n"/>
+      <c r="T15" s="350" t="n"/>
+      <c r="U15" s="350" t="n"/>
+      <c r="V15" s="350" t="n"/>
+      <c r="W15" s="350" t="n"/>
+      <c r="X15" s="350" t="n"/>
+      <c r="Y15" s="350" t="n"/>
+      <c r="Z15" s="350" t="n"/>
+      <c r="AA15" s="350" t="n"/>
+      <c r="AB15" s="350" t="n"/>
+      <c r="AC15" s="350" t="n"/>
+      <c r="AD15" s="350" t="n"/>
+      <c r="AE15" s="350" t="n"/>
+      <c r="AF15" s="350" t="n"/>
+      <c r="AG15" s="350" t="n"/>
+      <c r="AH15" s="350" t="n"/>
+      <c r="AI15" s="350" t="n"/>
+      <c r="AJ15" s="350" t="n"/>
+      <c r="AK15" s="350" t="n"/>
+      <c r="AL15" s="350" t="n"/>
+      <c r="AM15" s="350" t="n"/>
+      <c r="AN15" s="350" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="338">
+      <c r="A16" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B16" s="333" t="n"/>
-      <c r="C16" s="333" t="n"/>
-      <c r="D16" s="333" t="n"/>
-      <c r="E16" s="333" t="n"/>
-      <c r="F16" s="333" t="n"/>
-      <c r="G16" s="333" t="n"/>
-      <c r="H16" s="333" t="n"/>
-      <c r="I16" s="333" t="n"/>
-      <c r="J16" s="333" t="n"/>
-      <c r="K16" s="333" t="n"/>
+      <c r="B16" s="349" t="n"/>
+      <c r="C16" s="349" t="n"/>
+      <c r="D16" s="349" t="n"/>
+      <c r="E16" s="349" t="n"/>
+      <c r="F16" s="349" t="n"/>
+      <c r="G16" s="349" t="n"/>
+      <c r="H16" s="349" t="n"/>
+      <c r="I16" s="349" t="n"/>
+      <c r="J16" s="349" t="n"/>
+      <c r="K16" s="349" t="n"/>
+      <c r="L16" s="350" t="n"/>
+      <c r="M16" s="350" t="n"/>
+      <c r="N16" s="350" t="n"/>
+      <c r="O16" s="350" t="n"/>
+      <c r="P16" s="350" t="n"/>
+      <c r="Q16" s="350" t="n"/>
+      <c r="R16" s="350" t="n"/>
+      <c r="S16" s="350" t="n"/>
+      <c r="T16" s="350" t="n"/>
+      <c r="U16" s="350" t="n"/>
+      <c r="V16" s="350" t="n"/>
+      <c r="W16" s="350" t="n"/>
+      <c r="X16" s="350" t="n"/>
+      <c r="Y16" s="350" t="n"/>
+      <c r="Z16" s="350" t="n"/>
+      <c r="AA16" s="350" t="n"/>
+      <c r="AB16" s="350" t="n"/>
+      <c r="AC16" s="350" t="n"/>
+      <c r="AD16" s="350" t="n"/>
+      <c r="AE16" s="350" t="n"/>
+      <c r="AF16" s="350" t="n"/>
+      <c r="AG16" s="350" t="n"/>
+      <c r="AH16" s="350" t="n"/>
+      <c r="AI16" s="350" t="n"/>
+      <c r="AJ16" s="350" t="n"/>
+      <c r="AK16" s="350" t="n"/>
+      <c r="AL16" s="350" t="n"/>
+      <c r="AM16" s="350" t="n"/>
+      <c r="AN16" s="350" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="338">
+      <c r="A17" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B17" s="333" t="n"/>
-      <c r="C17" s="333" t="n"/>
-      <c r="D17" s="333" t="n"/>
-      <c r="E17" s="333" t="n"/>
-      <c r="F17" s="333" t="n"/>
-      <c r="G17" s="333" t="n"/>
-      <c r="H17" s="333" t="n"/>
-      <c r="I17" s="333" t="n"/>
-      <c r="J17" s="333" t="n"/>
-      <c r="K17" s="333" t="n"/>
+      <c r="B17" s="349" t="n"/>
+      <c r="C17" s="349" t="n"/>
+      <c r="D17" s="349" t="n"/>
+      <c r="E17" s="349" t="n"/>
+      <c r="F17" s="349" t="n"/>
+      <c r="G17" s="349" t="n"/>
+      <c r="H17" s="349" t="n"/>
+      <c r="I17" s="349" t="n"/>
+      <c r="J17" s="349" t="n"/>
+      <c r="K17" s="349" t="n"/>
+      <c r="L17" s="350" t="n"/>
+      <c r="M17" s="350" t="n"/>
+      <c r="N17" s="350" t="n"/>
+      <c r="O17" s="350" t="n"/>
+      <c r="P17" s="350" t="n"/>
+      <c r="Q17" s="350" t="n"/>
+      <c r="R17" s="350" t="n"/>
+      <c r="S17" s="350" t="n"/>
+      <c r="T17" s="350" t="n"/>
+      <c r="U17" s="350" t="n"/>
+      <c r="V17" s="350" t="n"/>
+      <c r="W17" s="350" t="n"/>
+      <c r="X17" s="350" t="n"/>
+      <c r="Y17" s="350" t="n"/>
+      <c r="Z17" s="350" t="n"/>
+      <c r="AA17" s="350" t="n"/>
+      <c r="AB17" s="350" t="n"/>
+      <c r="AC17" s="350" t="n"/>
+      <c r="AD17" s="350" t="n"/>
+      <c r="AE17" s="350" t="n"/>
+      <c r="AF17" s="350" t="n"/>
+      <c r="AG17" s="350" t="n"/>
+      <c r="AH17" s="350" t="n"/>
+      <c r="AI17" s="350" t="n"/>
+      <c r="AJ17" s="350" t="n"/>
+      <c r="AK17" s="350" t="n"/>
+      <c r="AL17" s="350" t="n"/>
+      <c r="AM17" s="350" t="n"/>
+      <c r="AN17" s="350" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="338">
+      <c r="A18" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B18" s="333" t="n"/>
-      <c r="C18" s="333" t="n"/>
-      <c r="D18" s="333" t="n"/>
-      <c r="E18" s="333" t="n"/>
-      <c r="F18" s="333" t="n"/>
-      <c r="G18" s="333" t="n"/>
-      <c r="H18" s="333" t="n"/>
-      <c r="I18" s="333" t="n"/>
-      <c r="J18" s="333" t="n"/>
-      <c r="K18" s="333" t="n"/>
+      <c r="B18" s="349" t="n"/>
+      <c r="C18" s="349" t="n"/>
+      <c r="D18" s="349" t="n"/>
+      <c r="E18" s="349" t="n"/>
+      <c r="F18" s="349" t="n"/>
+      <c r="G18" s="349" t="n"/>
+      <c r="H18" s="349" t="n"/>
+      <c r="I18" s="349" t="n"/>
+      <c r="J18" s="349" t="n"/>
+      <c r="K18" s="349" t="n"/>
+      <c r="L18" s="350" t="n"/>
+      <c r="M18" s="350" t="n"/>
+      <c r="N18" s="350" t="n"/>
+      <c r="O18" s="350" t="n"/>
+      <c r="P18" s="350" t="n"/>
+      <c r="Q18" s="350" t="n"/>
+      <c r="R18" s="350" t="n"/>
+      <c r="S18" s="350" t="n"/>
+      <c r="T18" s="350" t="n"/>
+      <c r="U18" s="350" t="n"/>
+      <c r="V18" s="350" t="n"/>
+      <c r="W18" s="350" t="n"/>
+      <c r="X18" s="350" t="n"/>
+      <c r="Y18" s="350" t="n"/>
+      <c r="Z18" s="350" t="n"/>
+      <c r="AA18" s="350" t="n"/>
+      <c r="AB18" s="350" t="n"/>
+      <c r="AC18" s="350" t="n"/>
+      <c r="AD18" s="350" t="n"/>
+      <c r="AE18" s="350" t="n"/>
+      <c r="AF18" s="350" t="n"/>
+      <c r="AG18" s="350" t="n"/>
+      <c r="AH18" s="350" t="n"/>
+      <c r="AI18" s="350" t="n"/>
+      <c r="AJ18" s="350" t="n"/>
+      <c r="AK18" s="350" t="n"/>
+      <c r="AL18" s="350" t="n"/>
+      <c r="AM18" s="350" t="n"/>
+      <c r="AN18" s="350" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="338">
+      <c r="A19" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B19" s="333" t="n"/>
-      <c r="C19" s="333" t="n"/>
-      <c r="D19" s="333" t="n"/>
-      <c r="E19" s="333" t="n"/>
-      <c r="F19" s="333" t="n"/>
-      <c r="G19" s="333" t="n"/>
-      <c r="H19" s="333" t="n"/>
-      <c r="I19" s="333" t="n"/>
-      <c r="J19" s="333" t="n"/>
-      <c r="K19" s="333" t="n"/>
+      <c r="B19" s="349" t="n"/>
+      <c r="C19" s="349" t="n"/>
+      <c r="D19" s="349" t="n"/>
+      <c r="E19" s="349" t="n"/>
+      <c r="F19" s="349" t="n"/>
+      <c r="G19" s="349" t="n"/>
+      <c r="H19" s="349" t="n"/>
+      <c r="I19" s="349" t="n"/>
+      <c r="J19" s="349" t="n"/>
+      <c r="K19" s="349" t="n"/>
+      <c r="L19" s="350" t="n"/>
+      <c r="M19" s="350" t="n"/>
+      <c r="N19" s="350" t="n"/>
+      <c r="O19" s="350" t="n"/>
+      <c r="P19" s="350" t="n"/>
+      <c r="Q19" s="350" t="n"/>
+      <c r="R19" s="350" t="n"/>
+      <c r="S19" s="350" t="n"/>
+      <c r="T19" s="350" t="n"/>
+      <c r="U19" s="350" t="n"/>
+      <c r="V19" s="350" t="n"/>
+      <c r="W19" s="350" t="n"/>
+      <c r="X19" s="350" t="n"/>
+      <c r="Y19" s="350" t="n"/>
+      <c r="Z19" s="350" t="n"/>
+      <c r="AA19" s="350" t="n"/>
+      <c r="AB19" s="350" t="n"/>
+      <c r="AC19" s="350" t="n"/>
+      <c r="AD19" s="350" t="n"/>
+      <c r="AE19" s="350" t="n"/>
+      <c r="AF19" s="350" t="n"/>
+      <c r="AG19" s="350" t="n"/>
+      <c r="AH19" s="350" t="n"/>
+      <c r="AI19" s="350" t="n"/>
+      <c r="AJ19" s="350" t="n"/>
+      <c r="AK19" s="350" t="n"/>
+      <c r="AL19" s="350" t="n"/>
+      <c r="AM19" s="350" t="n"/>
+      <c r="AN19" s="350" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="338">
+      <c r="A20" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B20" s="333" t="n"/>
-      <c r="C20" s="333" t="n"/>
-      <c r="D20" s="333" t="n"/>
-      <c r="E20" s="333" t="n"/>
-      <c r="F20" s="333" t="n"/>
-      <c r="G20" s="333" t="n"/>
-      <c r="H20" s="333" t="n"/>
-      <c r="I20" s="333" t="n"/>
-      <c r="J20" s="333" t="n"/>
-      <c r="K20" s="333" t="n"/>
+      <c r="B20" s="349" t="n"/>
+      <c r="C20" s="349" t="n"/>
+      <c r="D20" s="349" t="n"/>
+      <c r="E20" s="349" t="n"/>
+      <c r="F20" s="349" t="n"/>
+      <c r="G20" s="349" t="n"/>
+      <c r="H20" s="349" t="n"/>
+      <c r="I20" s="349" t="n"/>
+      <c r="J20" s="349" t="n"/>
+      <c r="K20" s="349" t="n"/>
+      <c r="L20" s="350" t="n"/>
+      <c r="M20" s="350" t="n"/>
+      <c r="N20" s="350" t="n"/>
+      <c r="O20" s="350" t="n"/>
+      <c r="P20" s="350" t="n"/>
+      <c r="Q20" s="350" t="n"/>
+      <c r="R20" s="350" t="n"/>
+      <c r="S20" s="350" t="n"/>
+      <c r="T20" s="350" t="n"/>
+      <c r="U20" s="350" t="n"/>
+      <c r="V20" s="350" t="n"/>
+      <c r="W20" s="350" t="n"/>
+      <c r="X20" s="350" t="n"/>
+      <c r="Y20" s="350" t="n"/>
+      <c r="Z20" s="350" t="n"/>
+      <c r="AA20" s="350" t="n"/>
+      <c r="AB20" s="350" t="n"/>
+      <c r="AC20" s="350" t="n"/>
+      <c r="AD20" s="350" t="n"/>
+      <c r="AE20" s="350" t="n"/>
+      <c r="AF20" s="350" t="n"/>
+      <c r="AG20" s="350" t="n"/>
+      <c r="AH20" s="350" t="n"/>
+      <c r="AI20" s="350" t="n"/>
+      <c r="AJ20" s="350" t="n"/>
+      <c r="AK20" s="350" t="n"/>
+      <c r="AL20" s="350" t="n"/>
+      <c r="AM20" s="350" t="n"/>
+      <c r="AN20" s="350" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="338">
+      <c r="A21" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B21" s="333" t="n"/>
-      <c r="C21" s="333" t="n"/>
-      <c r="D21" s="333" t="n"/>
-      <c r="E21" s="333" t="n"/>
-      <c r="F21" s="333" t="n"/>
-      <c r="G21" s="333" t="n"/>
-      <c r="H21" s="333" t="n"/>
-      <c r="I21" s="333" t="n"/>
-      <c r="J21" s="333" t="n"/>
-      <c r="K21" s="333" t="n"/>
+      <c r="B21" s="349" t="n"/>
+      <c r="C21" s="349" t="n"/>
+      <c r="D21" s="349" t="n"/>
+      <c r="E21" s="349" t="n"/>
+      <c r="F21" s="349" t="n"/>
+      <c r="G21" s="349" t="n"/>
+      <c r="H21" s="349" t="n"/>
+      <c r="I21" s="349" t="n"/>
+      <c r="J21" s="349" t="n"/>
+      <c r="K21" s="349" t="n"/>
+      <c r="L21" s="350" t="n"/>
+      <c r="M21" s="350" t="n"/>
+      <c r="N21" s="350" t="n"/>
+      <c r="O21" s="350" t="n"/>
+      <c r="P21" s="350" t="n"/>
+      <c r="Q21" s="350" t="n"/>
+      <c r="R21" s="350" t="n"/>
+      <c r="S21" s="350" t="n"/>
+      <c r="T21" s="350" t="n"/>
+      <c r="U21" s="350" t="n"/>
+      <c r="V21" s="350" t="n"/>
+      <c r="W21" s="350" t="n"/>
+      <c r="X21" s="350" t="n"/>
+      <c r="Y21" s="350" t="n"/>
+      <c r="Z21" s="350" t="n"/>
+      <c r="AA21" s="350" t="n"/>
+      <c r="AB21" s="350" t="n"/>
+      <c r="AC21" s="350" t="n"/>
+      <c r="AD21" s="350" t="n"/>
+      <c r="AE21" s="350" t="n"/>
+      <c r="AF21" s="350" t="n"/>
+      <c r="AG21" s="350" t="n"/>
+      <c r="AH21" s="350" t="n"/>
+      <c r="AI21" s="350" t="n"/>
+      <c r="AJ21" s="350" t="n"/>
+      <c r="AK21" s="350" t="n"/>
+      <c r="AL21" s="350" t="n"/>
+      <c r="AM21" s="350" t="n"/>
+      <c r="AN21" s="350" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="338">
+      <c r="A22" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B22" s="333" t="n"/>
-      <c r="C22" s="333" t="n"/>
-      <c r="D22" s="333" t="n"/>
-      <c r="E22" s="333" t="n"/>
-      <c r="F22" s="333" t="n"/>
-      <c r="G22" s="333" t="n"/>
-      <c r="H22" s="333" t="n"/>
-      <c r="I22" s="333" t="n"/>
-      <c r="J22" s="333" t="n"/>
-      <c r="K22" s="333" t="n"/>
+      <c r="B22" s="349" t="n"/>
+      <c r="C22" s="349" t="n"/>
+      <c r="D22" s="349" t="n"/>
+      <c r="E22" s="349" t="n"/>
+      <c r="F22" s="349" t="n"/>
+      <c r="G22" s="349" t="n"/>
+      <c r="H22" s="349" t="n"/>
+      <c r="I22" s="349" t="n"/>
+      <c r="J22" s="349" t="n"/>
+      <c r="K22" s="349" t="n"/>
+      <c r="L22" s="350" t="n"/>
+      <c r="M22" s="350" t="n"/>
+      <c r="N22" s="350" t="n"/>
+      <c r="O22" s="350" t="n"/>
+      <c r="P22" s="350" t="n"/>
+      <c r="Q22" s="350" t="n"/>
+      <c r="R22" s="350" t="n"/>
+      <c r="S22" s="350" t="n"/>
+      <c r="T22" s="350" t="n"/>
+      <c r="U22" s="350" t="n"/>
+      <c r="V22" s="350" t="n"/>
+      <c r="W22" s="350" t="n"/>
+      <c r="X22" s="350" t="n"/>
+      <c r="Y22" s="350" t="n"/>
+      <c r="Z22" s="350" t="n"/>
+      <c r="AA22" s="350" t="n"/>
+      <c r="AB22" s="350" t="n"/>
+      <c r="AC22" s="350" t="n"/>
+      <c r="AD22" s="350" t="n"/>
+      <c r="AE22" s="350" t="n"/>
+      <c r="AF22" s="350" t="n"/>
+      <c r="AG22" s="350" t="n"/>
+      <c r="AH22" s="350" t="n"/>
+      <c r="AI22" s="350" t="n"/>
+      <c r="AJ22" s="350" t="n"/>
+      <c r="AK22" s="350" t="n"/>
+      <c r="AL22" s="350" t="n"/>
+      <c r="AM22" s="350" t="n"/>
+      <c r="AN22" s="350" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="338">
+      <c r="A23" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B23" s="333" t="n"/>
-      <c r="C23" s="333" t="n"/>
-      <c r="D23" s="333" t="n"/>
-      <c r="E23" s="333" t="n"/>
-      <c r="F23" s="333" t="n"/>
-      <c r="G23" s="333" t="n"/>
-      <c r="H23" s="333" t="n"/>
-      <c r="I23" s="333" t="n"/>
-      <c r="J23" s="333" t="n"/>
-      <c r="K23" s="333" t="n"/>
+      <c r="B23" s="349" t="n"/>
+      <c r="C23" s="349" t="n"/>
+      <c r="D23" s="349" t="n"/>
+      <c r="E23" s="349" t="n"/>
+      <c r="F23" s="349" t="n"/>
+      <c r="G23" s="349" t="n"/>
+      <c r="H23" s="349" t="n"/>
+      <c r="I23" s="349" t="n"/>
+      <c r="J23" s="349" t="n"/>
+      <c r="K23" s="349" t="n"/>
+      <c r="L23" s="350" t="n"/>
+      <c r="M23" s="350" t="n"/>
+      <c r="N23" s="350" t="n"/>
+      <c r="O23" s="350" t="n"/>
+      <c r="P23" s="350" t="n"/>
+      <c r="Q23" s="350" t="n"/>
+      <c r="R23" s="350" t="n"/>
+      <c r="S23" s="350" t="n"/>
+      <c r="T23" s="350" t="n"/>
+      <c r="U23" s="350" t="n"/>
+      <c r="V23" s="350" t="n"/>
+      <c r="W23" s="350" t="n"/>
+      <c r="X23" s="350" t="n"/>
+      <c r="Y23" s="350" t="n"/>
+      <c r="Z23" s="350" t="n"/>
+      <c r="AA23" s="350" t="n"/>
+      <c r="AB23" s="350" t="n"/>
+      <c r="AC23" s="350" t="n"/>
+      <c r="AD23" s="350" t="n"/>
+      <c r="AE23" s="350" t="n"/>
+      <c r="AF23" s="350" t="n"/>
+      <c r="AG23" s="350" t="n"/>
+      <c r="AH23" s="350" t="n"/>
+      <c r="AI23" s="350" t="n"/>
+      <c r="AJ23" s="350" t="n"/>
+      <c r="AK23" s="350" t="n"/>
+      <c r="AL23" s="350" t="n"/>
+      <c r="AM23" s="350" t="n"/>
+      <c r="AN23" s="350" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="338">
+      <c r="A24" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B24" s="333" t="n"/>
-      <c r="C24" s="333" t="n"/>
-      <c r="D24" s="333" t="n"/>
-      <c r="E24" s="333" t="n"/>
-      <c r="F24" s="333" t="n"/>
-      <c r="G24" s="333" t="n"/>
-      <c r="H24" s="333" t="n"/>
-      <c r="I24" s="333" t="n"/>
-      <c r="J24" s="333" t="n"/>
-      <c r="K24" s="333" t="n"/>
+      <c r="B24" s="349" t="n"/>
+      <c r="C24" s="349" t="n"/>
+      <c r="D24" s="349" t="n"/>
+      <c r="E24" s="349" t="n"/>
+      <c r="F24" s="349" t="n"/>
+      <c r="G24" s="349" t="n"/>
+      <c r="H24" s="349" t="n"/>
+      <c r="I24" s="349" t="n"/>
+      <c r="J24" s="349" t="n"/>
+      <c r="K24" s="349" t="n"/>
+      <c r="L24" s="350" t="n"/>
+      <c r="M24" s="350" t="n"/>
+      <c r="N24" s="350" t="n"/>
+      <c r="O24" s="350" t="n"/>
+      <c r="P24" s="350" t="n"/>
+      <c r="Q24" s="350" t="n"/>
+      <c r="R24" s="350" t="n"/>
+      <c r="S24" s="350" t="n"/>
+      <c r="T24" s="350" t="n"/>
+      <c r="U24" s="350" t="n"/>
+      <c r="V24" s="350" t="n"/>
+      <c r="W24" s="350" t="n"/>
+      <c r="X24" s="350" t="n"/>
+      <c r="Y24" s="350" t="n"/>
+      <c r="Z24" s="350" t="n"/>
+      <c r="AA24" s="350" t="n"/>
+      <c r="AB24" s="350" t="n"/>
+      <c r="AC24" s="350" t="n"/>
+      <c r="AD24" s="350" t="n"/>
+      <c r="AE24" s="350" t="n"/>
+      <c r="AF24" s="350" t="n"/>
+      <c r="AG24" s="350" t="n"/>
+      <c r="AH24" s="350" t="n"/>
+      <c r="AI24" s="350" t="n"/>
+      <c r="AJ24" s="350" t="n"/>
+      <c r="AK24" s="350" t="n"/>
+      <c r="AL24" s="350" t="n"/>
+      <c r="AM24" s="350" t="n"/>
+      <c r="AN24" s="350" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="338">
+      <c r="A25" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B25" s="333" t="n"/>
-      <c r="C25" s="333" t="n"/>
-      <c r="D25" s="333" t="n"/>
-      <c r="E25" s="333" t="n"/>
-      <c r="F25" s="333" t="n"/>
-      <c r="G25" s="333" t="n"/>
-      <c r="H25" s="333" t="n"/>
-      <c r="I25" s="333" t="n"/>
-      <c r="J25" s="333" t="n"/>
-      <c r="K25" s="333" t="n"/>
+      <c r="B25" s="349" t="n"/>
+      <c r="C25" s="349" t="n"/>
+      <c r="D25" s="349" t="n"/>
+      <c r="E25" s="349" t="n"/>
+      <c r="F25" s="349" t="n"/>
+      <c r="G25" s="349" t="n"/>
+      <c r="H25" s="349" t="n"/>
+      <c r="I25" s="349" t="n"/>
+      <c r="J25" s="349" t="n"/>
+      <c r="K25" s="349" t="n"/>
+      <c r="L25" s="350" t="n"/>
+      <c r="M25" s="350" t="n"/>
+      <c r="N25" s="350" t="n"/>
+      <c r="O25" s="350" t="n"/>
+      <c r="P25" s="350" t="n"/>
+      <c r="Q25" s="350" t="n"/>
+      <c r="R25" s="350" t="n"/>
+      <c r="S25" s="350" t="n"/>
+      <c r="T25" s="350" t="n"/>
+      <c r="U25" s="350" t="n"/>
+      <c r="V25" s="350" t="n"/>
+      <c r="W25" s="350" t="n"/>
+      <c r="X25" s="350" t="n"/>
+      <c r="Y25" s="350" t="n"/>
+      <c r="Z25" s="350" t="n"/>
+      <c r="AA25" s="350" t="n"/>
+      <c r="AB25" s="350" t="n"/>
+      <c r="AC25" s="350" t="n"/>
+      <c r="AD25" s="350" t="n"/>
+      <c r="AE25" s="350" t="n"/>
+      <c r="AF25" s="350" t="n"/>
+      <c r="AG25" s="350" t="n"/>
+      <c r="AH25" s="350" t="n"/>
+      <c r="AI25" s="350" t="n"/>
+      <c r="AJ25" s="350" t="n"/>
+      <c r="AK25" s="350" t="n"/>
+      <c r="AL25" s="350" t="n"/>
+      <c r="AM25" s="350" t="n"/>
+      <c r="AN25" s="350" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="338">
+      <c r="A26" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B26" s="333" t="n"/>
-      <c r="C26" s="333" t="n"/>
-      <c r="D26" s="333" t="n"/>
-      <c r="E26" s="333" t="n"/>
-      <c r="F26" s="333" t="n"/>
-      <c r="G26" s="333" t="n"/>
-      <c r="H26" s="333" t="n"/>
-      <c r="I26" s="333" t="n"/>
-      <c r="J26" s="333" t="n"/>
-      <c r="K26" s="333" t="n"/>
+      <c r="B26" s="349" t="n"/>
+      <c r="C26" s="349" t="n"/>
+      <c r="D26" s="349" t="n"/>
+      <c r="E26" s="349" t="n"/>
+      <c r="F26" s="349" t="n"/>
+      <c r="G26" s="349" t="n"/>
+      <c r="H26" s="349" t="n"/>
+      <c r="I26" s="349" t="n"/>
+      <c r="J26" s="349" t="n"/>
+      <c r="K26" s="349" t="n"/>
+      <c r="L26" s="350" t="n"/>
+      <c r="M26" s="350" t="n"/>
+      <c r="N26" s="350" t="n"/>
+      <c r="O26" s="350" t="n"/>
+      <c r="P26" s="350" t="n"/>
+      <c r="Q26" s="350" t="n"/>
+      <c r="R26" s="350" t="n"/>
+      <c r="S26" s="350" t="n"/>
+      <c r="T26" s="350" t="n"/>
+      <c r="U26" s="350" t="n"/>
+      <c r="V26" s="350" t="n"/>
+      <c r="W26" s="350" t="n"/>
+      <c r="X26" s="350" t="n"/>
+      <c r="Y26" s="350" t="n"/>
+      <c r="Z26" s="350" t="n"/>
+      <c r="AA26" s="350" t="n"/>
+      <c r="AB26" s="350" t="n"/>
+      <c r="AC26" s="350" t="n"/>
+      <c r="AD26" s="350" t="n"/>
+      <c r="AE26" s="350" t="n"/>
+      <c r="AF26" s="350" t="n"/>
+      <c r="AG26" s="350" t="n"/>
+      <c r="AH26" s="350" t="n"/>
+      <c r="AI26" s="350" t="n"/>
+      <c r="AJ26" s="350" t="n"/>
+      <c r="AK26" s="350" t="n"/>
+      <c r="AL26" s="350" t="n"/>
+      <c r="AM26" s="350" t="n"/>
+      <c r="AN26" s="350" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="338">
+      <c r="A27" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B27" s="333" t="n"/>
-      <c r="C27" s="333" t="n"/>
-      <c r="D27" s="333" t="n"/>
-      <c r="E27" s="333" t="n"/>
-      <c r="F27" s="333" t="n"/>
-      <c r="G27" s="333" t="n"/>
-      <c r="H27" s="333" t="n"/>
-      <c r="I27" s="333" t="n"/>
-      <c r="J27" s="333" t="n"/>
-      <c r="K27" s="333" t="n"/>
+      <c r="B27" s="349" t="n"/>
+      <c r="C27" s="349" t="n"/>
+      <c r="D27" s="349" t="n"/>
+      <c r="E27" s="349" t="n"/>
+      <c r="F27" s="349" t="n"/>
+      <c r="G27" s="349" t="n"/>
+      <c r="H27" s="349" t="n"/>
+      <c r="I27" s="349" t="n"/>
+      <c r="J27" s="349" t="n"/>
+      <c r="K27" s="349" t="n"/>
+      <c r="L27" s="350" t="n"/>
+      <c r="M27" s="350" t="n"/>
+      <c r="N27" s="350" t="n"/>
+      <c r="O27" s="350" t="n"/>
+      <c r="P27" s="350" t="n"/>
+      <c r="Q27" s="350" t="n"/>
+      <c r="R27" s="350" t="n"/>
+      <c r="S27" s="350" t="n"/>
+      <c r="T27" s="350" t="n"/>
+      <c r="U27" s="350" t="n"/>
+      <c r="V27" s="350" t="n"/>
+      <c r="W27" s="350" t="n"/>
+      <c r="X27" s="350" t="n"/>
+      <c r="Y27" s="350" t="n"/>
+      <c r="Z27" s="350" t="n"/>
+      <c r="AA27" s="350" t="n"/>
+      <c r="AB27" s="350" t="n"/>
+      <c r="AC27" s="350" t="n"/>
+      <c r="AD27" s="350" t="n"/>
+      <c r="AE27" s="350" t="n"/>
+      <c r="AF27" s="350" t="n"/>
+      <c r="AG27" s="350" t="n"/>
+      <c r="AH27" s="350" t="n"/>
+      <c r="AI27" s="350" t="n"/>
+      <c r="AJ27" s="350" t="n"/>
+      <c r="AK27" s="350" t="n"/>
+      <c r="AL27" s="350" t="n"/>
+      <c r="AM27" s="350" t="n"/>
+      <c r="AN27" s="350" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="338">
+      <c r="A28" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B28" s="333" t="n"/>
-      <c r="C28" s="333" t="n"/>
-      <c r="D28" s="333" t="n"/>
-      <c r="E28" s="333" t="n"/>
-      <c r="F28" s="333" t="n"/>
-      <c r="G28" s="333" t="n"/>
-      <c r="H28" s="333" t="n"/>
-      <c r="I28" s="333" t="n"/>
-      <c r="J28" s="333" t="n"/>
-      <c r="K28" s="333" t="n"/>
+      <c r="B28" s="349" t="n"/>
+      <c r="C28" s="349" t="n"/>
+      <c r="D28" s="349" t="n"/>
+      <c r="E28" s="349" t="n"/>
+      <c r="F28" s="349" t="n"/>
+      <c r="G28" s="349" t="n"/>
+      <c r="H28" s="349" t="n"/>
+      <c r="I28" s="349" t="n"/>
+      <c r="J28" s="349" t="n"/>
+      <c r="K28" s="349" t="n"/>
+      <c r="L28" s="350" t="n"/>
+      <c r="M28" s="350" t="n"/>
+      <c r="N28" s="350" t="n"/>
+      <c r="O28" s="350" t="n"/>
+      <c r="P28" s="350" t="n"/>
+      <c r="Q28" s="350" t="n"/>
+      <c r="R28" s="350" t="n"/>
+      <c r="S28" s="350" t="n"/>
+      <c r="T28" s="350" t="n"/>
+      <c r="U28" s="350" t="n"/>
+      <c r="V28" s="350" t="n"/>
+      <c r="W28" s="350" t="n"/>
+      <c r="X28" s="350" t="n"/>
+      <c r="Y28" s="350" t="n"/>
+      <c r="Z28" s="350" t="n"/>
+      <c r="AA28" s="350" t="n"/>
+      <c r="AB28" s="350" t="n"/>
+      <c r="AC28" s="350" t="n"/>
+      <c r="AD28" s="350" t="n"/>
+      <c r="AE28" s="350" t="n"/>
+      <c r="AF28" s="350" t="n"/>
+      <c r="AG28" s="350" t="n"/>
+      <c r="AH28" s="350" t="n"/>
+      <c r="AI28" s="350" t="n"/>
+      <c r="AJ28" s="350" t="n"/>
+      <c r="AK28" s="350" t="n"/>
+      <c r="AL28" s="350" t="n"/>
+      <c r="AM28" s="350" t="n"/>
+      <c r="AN28" s="350" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="338">
+      <c r="A29" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B29" s="333" t="n"/>
-      <c r="C29" s="333" t="n"/>
-      <c r="D29" s="333" t="n"/>
-      <c r="E29" s="333" t="n"/>
-      <c r="F29" s="333" t="n"/>
-      <c r="G29" s="333" t="n"/>
-      <c r="H29" s="333" t="n"/>
-      <c r="I29" s="333" t="n"/>
-      <c r="J29" s="333" t="n"/>
-      <c r="K29" s="333" t="n"/>
+      <c r="B29" s="349" t="n"/>
+      <c r="C29" s="349" t="n"/>
+      <c r="D29" s="349" t="n"/>
+      <c r="E29" s="349" t="n"/>
+      <c r="F29" s="349" t="n"/>
+      <c r="G29" s="349" t="n"/>
+      <c r="H29" s="349" t="n"/>
+      <c r="I29" s="349" t="n"/>
+      <c r="J29" s="349" t="n"/>
+      <c r="K29" s="349" t="n"/>
+      <c r="L29" s="350" t="n"/>
+      <c r="M29" s="350" t="n"/>
+      <c r="N29" s="350" t="n"/>
+      <c r="O29" s="350" t="n"/>
+      <c r="P29" s="350" t="n"/>
+      <c r="Q29" s="350" t="n"/>
+      <c r="R29" s="350" t="n"/>
+      <c r="S29" s="350" t="n"/>
+      <c r="T29" s="350" t="n"/>
+      <c r="U29" s="350" t="n"/>
+      <c r="V29" s="350" t="n"/>
+      <c r="W29" s="350" t="n"/>
+      <c r="X29" s="350" t="n"/>
+      <c r="Y29" s="350" t="n"/>
+      <c r="Z29" s="350" t="n"/>
+      <c r="AA29" s="350" t="n"/>
+      <c r="AB29" s="350" t="n"/>
+      <c r="AC29" s="350" t="n"/>
+      <c r="AD29" s="350" t="n"/>
+      <c r="AE29" s="350" t="n"/>
+      <c r="AF29" s="350" t="n"/>
+      <c r="AG29" s="350" t="n"/>
+      <c r="AH29" s="350" t="n"/>
+      <c r="AI29" s="350" t="n"/>
+      <c r="AJ29" s="350" t="n"/>
+      <c r="AK29" s="350" t="n"/>
+      <c r="AL29" s="350" t="n"/>
+      <c r="AM29" s="350" t="n"/>
+      <c r="AN29" s="350" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="338">
+      <c r="A30" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B30" s="333" t="n"/>
-      <c r="C30" s="333" t="n"/>
-      <c r="D30" s="333" t="n"/>
-      <c r="E30" s="333" t="n"/>
-      <c r="F30" s="333" t="n"/>
-      <c r="G30" s="333" t="n"/>
-      <c r="H30" s="333" t="n"/>
-      <c r="I30" s="333" t="n"/>
-      <c r="J30" s="333" t="n"/>
-      <c r="K30" s="333" t="n"/>
+      <c r="B30" s="349" t="n"/>
+      <c r="C30" s="349" t="n"/>
+      <c r="D30" s="349" t="n"/>
+      <c r="E30" s="349" t="n"/>
+      <c r="F30" s="349" t="n"/>
+      <c r="G30" s="349" t="n"/>
+      <c r="H30" s="349" t="n"/>
+      <c r="I30" s="349" t="n"/>
+      <c r="J30" s="349" t="n"/>
+      <c r="K30" s="349" t="n"/>
+      <c r="L30" s="350" t="n"/>
+      <c r="M30" s="350" t="n"/>
+      <c r="N30" s="350" t="n"/>
+      <c r="O30" s="350" t="n"/>
+      <c r="P30" s="350" t="n"/>
+      <c r="Q30" s="350" t="n"/>
+      <c r="R30" s="350" t="n"/>
+      <c r="S30" s="350" t="n"/>
+      <c r="T30" s="350" t="n"/>
+      <c r="U30" s="350" t="n"/>
+      <c r="V30" s="350" t="n"/>
+      <c r="W30" s="350" t="n"/>
+      <c r="X30" s="350" t="n"/>
+      <c r="Y30" s="350" t="n"/>
+      <c r="Z30" s="350" t="n"/>
+      <c r="AA30" s="350" t="n"/>
+      <c r="AB30" s="350" t="n"/>
+      <c r="AC30" s="350" t="n"/>
+      <c r="AD30" s="350" t="n"/>
+      <c r="AE30" s="350" t="n"/>
+      <c r="AF30" s="350" t="n"/>
+      <c r="AG30" s="350" t="n"/>
+      <c r="AH30" s="350" t="n"/>
+      <c r="AI30" s="350" t="n"/>
+      <c r="AJ30" s="350" t="n"/>
+      <c r="AK30" s="350" t="n"/>
+      <c r="AL30" s="350" t="n"/>
+      <c r="AM30" s="350" t="n"/>
+      <c r="AN30" s="350" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="338">
+      <c r="A31" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B31" s="333" t="n"/>
-      <c r="C31" s="333" t="n"/>
-      <c r="D31" s="333" t="n"/>
-      <c r="E31" s="333" t="n"/>
-      <c r="F31" s="333" t="n"/>
-      <c r="G31" s="333" t="n"/>
-      <c r="H31" s="333" t="n"/>
-      <c r="I31" s="333" t="n"/>
-      <c r="J31" s="333" t="n"/>
-      <c r="K31" s="333" t="n"/>
+      <c r="B31" s="349" t="n"/>
+      <c r="C31" s="349" t="n"/>
+      <c r="D31" s="349" t="n"/>
+      <c r="E31" s="349" t="n"/>
+      <c r="F31" s="349" t="n"/>
+      <c r="G31" s="349" t="n"/>
+      <c r="H31" s="349" t="n"/>
+      <c r="I31" s="349" t="n"/>
+      <c r="J31" s="349" t="n"/>
+      <c r="K31" s="349" t="n"/>
+      <c r="L31" s="350" t="n"/>
+      <c r="M31" s="350" t="n"/>
+      <c r="N31" s="350" t="n"/>
+      <c r="O31" s="350" t="n"/>
+      <c r="P31" s="350" t="n"/>
+      <c r="Q31" s="350" t="n"/>
+      <c r="R31" s="350" t="n"/>
+      <c r="S31" s="350" t="n"/>
+      <c r="T31" s="350" t="n"/>
+      <c r="U31" s="350" t="n"/>
+      <c r="V31" s="350" t="n"/>
+      <c r="W31" s="350" t="n"/>
+      <c r="X31" s="350" t="n"/>
+      <c r="Y31" s="350" t="n"/>
+      <c r="Z31" s="350" t="n"/>
+      <c r="AA31" s="350" t="n"/>
+      <c r="AB31" s="350" t="n"/>
+      <c r="AC31" s="350" t="n"/>
+      <c r="AD31" s="350" t="n"/>
+      <c r="AE31" s="350" t="n"/>
+      <c r="AF31" s="350" t="n"/>
+      <c r="AG31" s="350" t="n"/>
+      <c r="AH31" s="350" t="n"/>
+      <c r="AI31" s="350" t="n"/>
+      <c r="AJ31" s="350" t="n"/>
+      <c r="AK31" s="350" t="n"/>
+      <c r="AL31" s="350" t="n"/>
+      <c r="AM31" s="350" t="n"/>
+      <c r="AN31" s="350" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="338">
+      <c r="A32" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B32" s="333" t="n"/>
-      <c r="C32" s="333" t="n"/>
-      <c r="D32" s="333" t="n"/>
-      <c r="E32" s="333" t="n"/>
-      <c r="F32" s="333" t="n"/>
-      <c r="G32" s="333" t="n"/>
-      <c r="H32" s="333" t="n"/>
-      <c r="I32" s="333" t="n"/>
-      <c r="J32" s="333" t="n"/>
-      <c r="K32" s="333" t="n"/>
+      <c r="B32" s="349" t="n"/>
+      <c r="C32" s="349" t="n"/>
+      <c r="D32" s="349" t="n"/>
+      <c r="E32" s="349" t="n"/>
+      <c r="F32" s="349" t="n"/>
+      <c r="G32" s="349" t="n"/>
+      <c r="H32" s="349" t="n"/>
+      <c r="I32" s="349" t="n"/>
+      <c r="J32" s="349" t="n"/>
+      <c r="K32" s="349" t="n"/>
+      <c r="L32" s="350" t="n"/>
+      <c r="M32" s="350" t="n"/>
+      <c r="N32" s="350" t="n"/>
+      <c r="O32" s="350" t="n"/>
+      <c r="P32" s="350" t="n"/>
+      <c r="Q32" s="350" t="n"/>
+      <c r="R32" s="350" t="n"/>
+      <c r="S32" s="350" t="n"/>
+      <c r="T32" s="350" t="n"/>
+      <c r="U32" s="350" t="n"/>
+      <c r="V32" s="350" t="n"/>
+      <c r="W32" s="350" t="n"/>
+      <c r="X32" s="350" t="n"/>
+      <c r="Y32" s="350" t="n"/>
+      <c r="Z32" s="350" t="n"/>
+      <c r="AA32" s="350" t="n"/>
+      <c r="AB32" s="350" t="n"/>
+      <c r="AC32" s="350" t="n"/>
+      <c r="AD32" s="350" t="n"/>
+      <c r="AE32" s="350" t="n"/>
+      <c r="AF32" s="350" t="n"/>
+      <c r="AG32" s="350" t="n"/>
+      <c r="AH32" s="350" t="n"/>
+      <c r="AI32" s="350" t="n"/>
+      <c r="AJ32" s="350" t="n"/>
+      <c r="AK32" s="350" t="n"/>
+      <c r="AL32" s="350" t="n"/>
+      <c r="AM32" s="350" t="n"/>
+      <c r="AN32" s="350" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="338">
+      <c r="A33" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B33" s="333" t="n"/>
-      <c r="C33" s="333" t="n"/>
-      <c r="D33" s="333" t="n"/>
-      <c r="E33" s="333" t="n"/>
-      <c r="F33" s="333" t="n"/>
-      <c r="G33" s="333" t="n"/>
-      <c r="H33" s="333" t="n"/>
-      <c r="I33" s="333" t="n"/>
-      <c r="J33" s="333" t="n"/>
-      <c r="K33" s="333" t="n"/>
+      <c r="B33" s="349" t="n"/>
+      <c r="C33" s="349" t="n"/>
+      <c r="D33" s="349" t="n"/>
+      <c r="E33" s="349" t="n"/>
+      <c r="F33" s="349" t="n"/>
+      <c r="G33" s="349" t="n"/>
+      <c r="H33" s="349" t="n"/>
+      <c r="I33" s="349" t="n"/>
+      <c r="J33" s="349" t="n"/>
+      <c r="K33" s="349" t="n"/>
+      <c r="L33" s="350" t="n"/>
+      <c r="M33" s="350" t="n"/>
+      <c r="N33" s="350" t="n"/>
+      <c r="O33" s="350" t="n"/>
+      <c r="P33" s="350" t="n"/>
+      <c r="Q33" s="350" t="n"/>
+      <c r="R33" s="350" t="n"/>
+      <c r="S33" s="350" t="n"/>
+      <c r="T33" s="350" t="n"/>
+      <c r="U33" s="350" t="n"/>
+      <c r="V33" s="350" t="n"/>
+      <c r="W33" s="350" t="n"/>
+      <c r="X33" s="350" t="n"/>
+      <c r="Y33" s="350" t="n"/>
+      <c r="Z33" s="350" t="n"/>
+      <c r="AA33" s="350" t="n"/>
+      <c r="AB33" s="350" t="n"/>
+      <c r="AC33" s="350" t="n"/>
+      <c r="AD33" s="350" t="n"/>
+      <c r="AE33" s="350" t="n"/>
+      <c r="AF33" s="350" t="n"/>
+      <c r="AG33" s="350" t="n"/>
+      <c r="AH33" s="350" t="n"/>
+      <c r="AI33" s="350" t="n"/>
+      <c r="AJ33" s="350" t="n"/>
+      <c r="AK33" s="350" t="n"/>
+      <c r="AL33" s="350" t="n"/>
+      <c r="AM33" s="350" t="n"/>
+      <c r="AN33" s="350" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="338">
+      <c r="A34" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B34" s="333" t="n"/>
-      <c r="C34" s="333" t="n"/>
-      <c r="D34" s="333" t="n"/>
-      <c r="E34" s="333" t="n"/>
-      <c r="F34" s="333" t="n"/>
-      <c r="G34" s="333" t="n"/>
-      <c r="H34" s="333" t="n"/>
-      <c r="I34" s="333" t="n"/>
-      <c r="J34" s="333" t="n"/>
-      <c r="K34" s="333" t="n"/>
+      <c r="B34" s="349" t="n"/>
+      <c r="C34" s="349" t="n"/>
+      <c r="D34" s="349" t="n"/>
+      <c r="E34" s="349" t="n"/>
+      <c r="F34" s="349" t="n"/>
+      <c r="G34" s="349" t="n"/>
+      <c r="H34" s="349" t="n"/>
+      <c r="I34" s="349" t="n"/>
+      <c r="J34" s="349" t="n"/>
+      <c r="K34" s="349" t="n"/>
+      <c r="L34" s="350" t="n"/>
+      <c r="M34" s="350" t="n"/>
+      <c r="N34" s="350" t="n"/>
+      <c r="O34" s="350" t="n"/>
+      <c r="P34" s="350" t="n"/>
+      <c r="Q34" s="350" t="n"/>
+      <c r="R34" s="350" t="n"/>
+      <c r="S34" s="350" t="n"/>
+      <c r="T34" s="350" t="n"/>
+      <c r="U34" s="350" t="n"/>
+      <c r="V34" s="350" t="n"/>
+      <c r="W34" s="350" t="n"/>
+      <c r="X34" s="350" t="n"/>
+      <c r="Y34" s="350" t="n"/>
+      <c r="Z34" s="350" t="n"/>
+      <c r="AA34" s="350" t="n"/>
+      <c r="AB34" s="350" t="n"/>
+      <c r="AC34" s="350" t="n"/>
+      <c r="AD34" s="350" t="n"/>
+      <c r="AE34" s="350" t="n"/>
+      <c r="AF34" s="350" t="n"/>
+      <c r="AG34" s="350" t="n"/>
+      <c r="AH34" s="350" t="n"/>
+      <c r="AI34" s="350" t="n"/>
+      <c r="AJ34" s="350" t="n"/>
+      <c r="AK34" s="350" t="n"/>
+      <c r="AL34" s="350" t="n"/>
+      <c r="AM34" s="350" t="n"/>
+      <c r="AN34" s="350" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="338">
+      <c r="A35" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B35" s="333" t="n"/>
-      <c r="C35" s="333" t="n"/>
-      <c r="D35" s="333" t="n"/>
-      <c r="E35" s="333" t="n"/>
-      <c r="F35" s="333" t="n"/>
-      <c r="G35" s="333" t="n"/>
-      <c r="H35" s="333" t="n"/>
-      <c r="I35" s="333" t="n"/>
-      <c r="J35" s="333" t="n"/>
-      <c r="K35" s="333" t="n"/>
+      <c r="B35" s="349" t="n"/>
+      <c r="C35" s="349" t="n"/>
+      <c r="D35" s="349" t="n"/>
+      <c r="E35" s="349" t="n"/>
+      <c r="F35" s="349" t="n"/>
+      <c r="G35" s="349" t="n"/>
+      <c r="H35" s="349" t="n"/>
+      <c r="I35" s="349" t="n"/>
+      <c r="J35" s="349" t="n"/>
+      <c r="K35" s="349" t="n"/>
+      <c r="L35" s="350" t="n"/>
+      <c r="M35" s="350" t="n"/>
+      <c r="N35" s="350" t="n"/>
+      <c r="O35" s="350" t="n"/>
+      <c r="P35" s="350" t="n"/>
+      <c r="Q35" s="350" t="n"/>
+      <c r="R35" s="350" t="n"/>
+      <c r="S35" s="350" t="n"/>
+      <c r="T35" s="350" t="n"/>
+      <c r="U35" s="350" t="n"/>
+      <c r="V35" s="350" t="n"/>
+      <c r="W35" s="350" t="n"/>
+      <c r="X35" s="350" t="n"/>
+      <c r="Y35" s="350" t="n"/>
+      <c r="Z35" s="350" t="n"/>
+      <c r="AA35" s="350" t="n"/>
+      <c r="AB35" s="350" t="n"/>
+      <c r="AC35" s="350" t="n"/>
+      <c r="AD35" s="350" t="n"/>
+      <c r="AE35" s="350" t="n"/>
+      <c r="AF35" s="350" t="n"/>
+      <c r="AG35" s="350" t="n"/>
+      <c r="AH35" s="350" t="n"/>
+      <c r="AI35" s="350" t="n"/>
+      <c r="AJ35" s="350" t="n"/>
+      <c r="AK35" s="350" t="n"/>
+      <c r="AL35" s="350" t="n"/>
+      <c r="AM35" s="350" t="n"/>
+      <c r="AN35" s="350" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="338">
+      <c r="A36" s="348">
         <f>ROW()-ROW($A$7)+1</f>
         <v/>
       </c>
-      <c r="B36" s="333" t="n"/>
-      <c r="C36" s="333" t="n"/>
-      <c r="D36" s="333" t="n"/>
-      <c r="E36" s="333" t="n"/>
-      <c r="F36" s="333" t="n"/>
-      <c r="G36" s="333" t="n"/>
-      <c r="H36" s="333" t="n"/>
-      <c r="I36" s="333" t="n"/>
-      <c r="J36" s="333" t="n"/>
-      <c r="K36" s="333" t="n"/>
-    </row>
-    <row r="37"/>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="331" t="inlineStr">
+      <c r="B36" s="349" t="n"/>
+      <c r="C36" s="349" t="n"/>
+      <c r="D36" s="349" t="n"/>
+      <c r="E36" s="349" t="n"/>
+      <c r="F36" s="349" t="n"/>
+      <c r="G36" s="349" t="n"/>
+      <c r="H36" s="349" t="n"/>
+      <c r="I36" s="349" t="n"/>
+      <c r="J36" s="349" t="n"/>
+      <c r="K36" s="349" t="n"/>
+      <c r="L36" s="350" t="n"/>
+      <c r="M36" s="350" t="n"/>
+      <c r="N36" s="350" t="n"/>
+      <c r="O36" s="350" t="n"/>
+      <c r="P36" s="350" t="n"/>
+      <c r="Q36" s="350" t="n"/>
+      <c r="R36" s="350" t="n"/>
+      <c r="S36" s="350" t="n"/>
+      <c r="T36" s="350" t="n"/>
+      <c r="U36" s="350" t="n"/>
+      <c r="V36" s="350" t="n"/>
+      <c r="W36" s="350" t="n"/>
+      <c r="X36" s="350" t="n"/>
+      <c r="Y36" s="350" t="n"/>
+      <c r="Z36" s="350" t="n"/>
+      <c r="AA36" s="350" t="n"/>
+      <c r="AB36" s="350" t="n"/>
+      <c r="AC36" s="350" t="n"/>
+      <c r="AD36" s="350" t="n"/>
+      <c r="AE36" s="350" t="n"/>
+      <c r="AF36" s="350" t="n"/>
+      <c r="AG36" s="350" t="n"/>
+      <c r="AH36" s="350" t="n"/>
+      <c r="AI36" s="350" t="n"/>
+      <c r="AJ36" s="350" t="n"/>
+      <c r="AK36" s="350" t="n"/>
+      <c r="AL36" s="350" t="n"/>
+      <c r="AM36" s="350" t="n"/>
+      <c r="AN36" s="350" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="350" t="n"/>
+      <c r="B37" s="350" t="n"/>
+      <c r="C37" s="350" t="n"/>
+      <c r="D37" s="350" t="n"/>
+      <c r="E37" s="350" t="n"/>
+      <c r="F37" s="350" t="n"/>
+      <c r="G37" s="350" t="n"/>
+      <c r="H37" s="350" t="n"/>
+      <c r="I37" s="350" t="n"/>
+      <c r="J37" s="350" t="n"/>
+      <c r="K37" s="350" t="n"/>
+      <c r="L37" s="350" t="n"/>
+      <c r="M37" s="350" t="n"/>
+      <c r="N37" s="350" t="n"/>
+      <c r="O37" s="350" t="n"/>
+      <c r="P37" s="350" t="n"/>
+      <c r="Q37" s="350" t="n"/>
+      <c r="R37" s="350" t="n"/>
+      <c r="S37" s="350" t="n"/>
+      <c r="T37" s="350" t="n"/>
+      <c r="U37" s="350" t="n"/>
+      <c r="V37" s="350" t="n"/>
+      <c r="W37" s="350" t="n"/>
+      <c r="X37" s="350" t="n"/>
+      <c r="Y37" s="350" t="n"/>
+      <c r="Z37" s="350" t="n"/>
+      <c r="AA37" s="350" t="n"/>
+      <c r="AB37" s="350" t="n"/>
+      <c r="AC37" s="350" t="n"/>
+      <c r="AD37" s="350" t="n"/>
+      <c r="AE37" s="350" t="n"/>
+      <c r="AF37" s="350" t="n"/>
+      <c r="AG37" s="350" t="n"/>
+      <c r="AH37" s="350" t="n"/>
+      <c r="AI37" s="350" t="n"/>
+      <c r="AJ37" s="350" t="n"/>
+      <c r="AK37" s="350" t="n"/>
+      <c r="AL37" s="350" t="n"/>
+      <c r="AM37" s="350" t="n"/>
+      <c r="AN37" s="350" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="346" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. PERIODIC REVIEW / CLOSEOUT</t>
         </is>
       </c>
-      <c r="B38" s="285" t="n"/>
-      <c r="C38" s="285" t="n"/>
-      <c r="D38" s="285" t="n"/>
-      <c r="E38" s="285" t="n"/>
-      <c r="F38" s="285" t="n"/>
-      <c r="G38" s="285" t="n"/>
-      <c r="H38" s="285" t="n"/>
-      <c r="I38" s="285" t="n"/>
-      <c r="J38" s="285" t="n"/>
-      <c r="K38" s="286" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="334" t="inlineStr">
+      <c r="B38" s="389" t="n"/>
+      <c r="C38" s="389" t="n"/>
+      <c r="D38" s="389" t="n"/>
+      <c r="E38" s="389" t="n"/>
+      <c r="F38" s="389" t="n"/>
+      <c r="G38" s="389" t="n"/>
+      <c r="H38" s="389" t="n"/>
+      <c r="I38" s="389" t="n"/>
+      <c r="J38" s="389" t="n"/>
+      <c r="K38" s="390" t="n"/>
+      <c r="L38" s="350" t="n"/>
+      <c r="M38" s="350" t="n"/>
+      <c r="N38" s="350" t="n"/>
+      <c r="O38" s="350" t="n"/>
+      <c r="P38" s="350" t="n"/>
+      <c r="Q38" s="350" t="n"/>
+      <c r="R38" s="350" t="n"/>
+      <c r="S38" s="350" t="n"/>
+      <c r="T38" s="350" t="n"/>
+      <c r="U38" s="350" t="n"/>
+      <c r="V38" s="350" t="n"/>
+      <c r="W38" s="350" t="n"/>
+      <c r="X38" s="350" t="n"/>
+      <c r="Y38" s="350" t="n"/>
+      <c r="Z38" s="350" t="n"/>
+      <c r="AA38" s="350" t="n"/>
+      <c r="AB38" s="350" t="n"/>
+      <c r="AC38" s="350" t="n"/>
+      <c r="AD38" s="350" t="n"/>
+      <c r="AE38" s="350" t="n"/>
+      <c r="AF38" s="350" t="n"/>
+      <c r="AG38" s="350" t="n"/>
+      <c r="AH38" s="350" t="n"/>
+      <c r="AI38" s="350" t="n"/>
+      <c r="AJ38" s="350" t="n"/>
+      <c r="AK38" s="350" t="n"/>
+      <c r="AL38" s="350" t="n"/>
+      <c r="AM38" s="350" t="n"/>
+      <c r="AN38" s="350" t="n"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="353" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="B39" s="286" t="n"/>
-      <c r="C39" s="335" t="inlineStr"/>
-      <c r="D39" s="285" t="n"/>
-      <c r="E39" s="286" t="n"/>
-      <c r="F39" s="334" t="inlineStr">
+      <c r="B39" s="388" t="n"/>
+      <c r="C39" s="354" t="inlineStr"/>
+      <c r="D39" s="387" t="n"/>
+      <c r="E39" s="388" t="n"/>
+      <c r="F39" s="353" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="G39" s="286" t="n"/>
-      <c r="H39" s="335" t="inlineStr"/>
-      <c r="I39" s="285" t="n"/>
-      <c r="J39" s="285" t="n"/>
-      <c r="K39" s="286" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="334" t="inlineStr">
+      <c r="G39" s="388" t="n"/>
+      <c r="H39" s="354" t="inlineStr"/>
+      <c r="I39" s="387" t="n"/>
+      <c r="J39" s="387" t="n"/>
+      <c r="K39" s="388" t="n"/>
+      <c r="L39" s="342" t="n"/>
+      <c r="M39" s="342" t="n"/>
+      <c r="N39" s="342" t="n"/>
+      <c r="O39" s="342" t="n"/>
+      <c r="P39" s="342" t="n"/>
+      <c r="Q39" s="342" t="n"/>
+      <c r="R39" s="342" t="n"/>
+      <c r="S39" s="342" t="n"/>
+      <c r="T39" s="342" t="n"/>
+      <c r="U39" s="342" t="n"/>
+      <c r="V39" s="342" t="n"/>
+      <c r="W39" s="342" t="n"/>
+      <c r="X39" s="342" t="n"/>
+      <c r="Y39" s="342" t="n"/>
+      <c r="Z39" s="342" t="n"/>
+      <c r="AA39" s="342" t="n"/>
+      <c r="AB39" s="342" t="n"/>
+      <c r="AC39" s="342" t="n"/>
+      <c r="AD39" s="342" t="n"/>
+      <c r="AE39" s="342" t="n"/>
+      <c r="AF39" s="342" t="n"/>
+      <c r="AG39" s="342" t="n"/>
+      <c r="AH39" s="342" t="n"/>
+      <c r="AI39" s="342" t="n"/>
+      <c r="AJ39" s="342" t="n"/>
+      <c r="AK39" s="342" t="n"/>
+      <c r="AL39" s="342" t="n"/>
+      <c r="AM39" s="342" t="n"/>
+      <c r="AN39" s="342" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="353" t="inlineStr">
         <is>
           <t>Open Items / Exceptions</t>
         </is>
       </c>
-      <c r="B40" s="286" t="n"/>
-      <c r="C40" s="335" t="inlineStr"/>
-      <c r="D40" s="285" t="n"/>
-      <c r="E40" s="286" t="n"/>
-      <c r="F40" s="334" t="inlineStr">
+      <c r="B40" s="390" t="n"/>
+      <c r="C40" s="354" t="inlineStr"/>
+      <c r="D40" s="389" t="n"/>
+      <c r="E40" s="390" t="n"/>
+      <c r="F40" s="353" t="inlineStr">
         <is>
           <t>Final Status</t>
         </is>
       </c>
-      <c r="G40" s="286" t="n"/>
-      <c r="H40" s="335" t="inlineStr"/>
-      <c r="I40" s="285" t="n"/>
-      <c r="J40" s="285" t="n"/>
-      <c r="K40" s="286" t="n"/>
-    </row>
-    <row r="41"/>
+      <c r="G40" s="390" t="n"/>
+      <c r="H40" s="354" t="inlineStr"/>
+      <c r="I40" s="389" t="n"/>
+      <c r="J40" s="389" t="n"/>
+      <c r="K40" s="390" t="n"/>
+      <c r="L40" s="350" t="n"/>
+      <c r="M40" s="350" t="n"/>
+      <c r="N40" s="350" t="n"/>
+      <c r="O40" s="350" t="n"/>
+      <c r="P40" s="350" t="n"/>
+      <c r="Q40" s="350" t="n"/>
+      <c r="R40" s="350" t="n"/>
+      <c r="S40" s="350" t="n"/>
+      <c r="T40" s="350" t="n"/>
+      <c r="U40" s="350" t="n"/>
+      <c r="V40" s="350" t="n"/>
+      <c r="W40" s="350" t="n"/>
+      <c r="X40" s="350" t="n"/>
+      <c r="Y40" s="350" t="n"/>
+      <c r="Z40" s="350" t="n"/>
+      <c r="AA40" s="350" t="n"/>
+      <c r="AB40" s="350" t="n"/>
+      <c r="AC40" s="350" t="n"/>
+      <c r="AD40" s="350" t="n"/>
+      <c r="AE40" s="350" t="n"/>
+      <c r="AF40" s="350" t="n"/>
+      <c r="AG40" s="350" t="n"/>
+      <c r="AH40" s="350" t="n"/>
+      <c r="AI40" s="350" t="n"/>
+      <c r="AJ40" s="350" t="n"/>
+      <c r="AK40" s="350" t="n"/>
+      <c r="AL40" s="350" t="n"/>
+      <c r="AM40" s="350" t="n"/>
+      <c r="AN40" s="350" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="350" t="n"/>
+      <c r="B41" s="350" t="n"/>
+      <c r="C41" s="350" t="n"/>
+      <c r="D41" s="350" t="n"/>
+      <c r="E41" s="350" t="n"/>
+      <c r="F41" s="350" t="n"/>
+      <c r="G41" s="350" t="n"/>
+      <c r="H41" s="350" t="n"/>
+      <c r="I41" s="350" t="n"/>
+      <c r="J41" s="350" t="n"/>
+      <c r="K41" s="350" t="n"/>
+      <c r="L41" s="350" t="n"/>
+      <c r="M41" s="350" t="n"/>
+      <c r="N41" s="350" t="n"/>
+      <c r="O41" s="350" t="n"/>
+      <c r="P41" s="350" t="n"/>
+      <c r="Q41" s="350" t="n"/>
+      <c r="R41" s="350" t="n"/>
+      <c r="S41" s="350" t="n"/>
+      <c r="T41" s="350" t="n"/>
+      <c r="U41" s="350" t="n"/>
+      <c r="V41" s="350" t="n"/>
+      <c r="W41" s="350" t="n"/>
+      <c r="X41" s="350" t="n"/>
+      <c r="Y41" s="350" t="n"/>
+      <c r="Z41" s="350" t="n"/>
+      <c r="AA41" s="350" t="n"/>
+      <c r="AB41" s="350" t="n"/>
+      <c r="AC41" s="350" t="n"/>
+      <c r="AD41" s="350" t="n"/>
+      <c r="AE41" s="350" t="n"/>
+      <c r="AF41" s="350" t="n"/>
+      <c r="AG41" s="350" t="n"/>
+      <c r="AH41" s="350" t="n"/>
+      <c r="AI41" s="350" t="n"/>
+      <c r="AJ41" s="350" t="n"/>
+      <c r="AK41" s="350" t="n"/>
+      <c r="AL41" s="350" t="n"/>
+      <c r="AM41" s="350" t="n"/>
+      <c r="AN41" s="350" t="n"/>
+    </row>
     <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="336" t="inlineStr">
+      <c r="A42" s="355" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. Do not back-date, delete history, or overwrite a closed row without a controlled supplemental entry. Review / sign-off context remains on sheet GAGE_VERIFY_LOG.</t>
         </is>
       </c>
-      <c r="B42" s="285" t="n"/>
-      <c r="C42" s="285" t="n"/>
-      <c r="D42" s="285" t="n"/>
-      <c r="E42" s="285" t="n"/>
-      <c r="F42" s="285" t="n"/>
-      <c r="G42" s="285" t="n"/>
-      <c r="H42" s="285" t="n"/>
-      <c r="I42" s="285" t="n"/>
-      <c r="J42" s="285" t="n"/>
-      <c r="K42" s="286" t="n"/>
+      <c r="B42" s="387" t="n"/>
+      <c r="C42" s="387" t="n"/>
+      <c r="D42" s="387" t="n"/>
+      <c r="E42" s="387" t="n"/>
+      <c r="F42" s="387" t="n"/>
+      <c r="G42" s="387" t="n"/>
+      <c r="H42" s="387" t="n"/>
+      <c r="I42" s="387" t="n"/>
+      <c r="J42" s="387" t="n"/>
+      <c r="K42" s="388" t="n"/>
+      <c r="L42" s="342" t="n"/>
+      <c r="M42" s="342" t="n"/>
+      <c r="N42" s="342" t="n"/>
+      <c r="O42" s="342" t="n"/>
+      <c r="P42" s="342" t="n"/>
+      <c r="Q42" s="342" t="n"/>
+      <c r="R42" s="342" t="n"/>
+      <c r="S42" s="342" t="n"/>
+      <c r="T42" s="342" t="n"/>
+      <c r="U42" s="342" t="n"/>
+      <c r="V42" s="342" t="n"/>
+      <c r="W42" s="342" t="n"/>
+      <c r="X42" s="342" t="n"/>
+      <c r="Y42" s="342" t="n"/>
+      <c r="Z42" s="342" t="n"/>
+      <c r="AA42" s="342" t="n"/>
+      <c r="AB42" s="342" t="n"/>
+      <c r="AC42" s="342" t="n"/>
+      <c r="AD42" s="342" t="n"/>
+      <c r="AE42" s="342" t="n"/>
+      <c r="AF42" s="342" t="n"/>
+      <c r="AG42" s="342" t="n"/>
+      <c r="AH42" s="342" t="n"/>
+      <c r="AI42" s="342" t="n"/>
+      <c r="AJ42" s="342" t="n"/>
+      <c r="AK42" s="342" t="n"/>
+      <c r="AL42" s="342" t="n"/>
+      <c r="AM42" s="342" t="n"/>
+      <c r="AN42" s="342" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -5611,9 +7181,8 @@
   <printOptions horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5686,1782 +7255,1996 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="267" t="inlineStr"/>
-      <c r="B1" s="268" t="n"/>
-      <c r="C1" s="268" t="n"/>
-      <c r="D1" s="268" t="n"/>
-      <c r="E1" s="268" t="n"/>
-      <c r="F1" s="268" t="n"/>
-      <c r="G1" s="268" t="n"/>
-      <c r="H1" s="268" t="n"/>
-      <c r="I1" s="268" t="n"/>
-      <c r="J1" s="268" t="n"/>
-      <c r="K1" s="268" t="n"/>
-      <c r="L1" s="269" t="inlineStr">
+      <c r="A1" s="356" t="inlineStr"/>
+      <c r="B1" s="404" t="n"/>
+      <c r="C1" s="404" t="n"/>
+      <c r="D1" s="404" t="n"/>
+      <c r="E1" s="404" t="n"/>
+      <c r="F1" s="404" t="n"/>
+      <c r="G1" s="404" t="n"/>
+      <c r="H1" s="404" t="n"/>
+      <c r="I1" s="404" t="n"/>
+      <c r="J1" s="404" t="n"/>
+      <c r="K1" s="404" t="n"/>
+      <c r="L1" s="358" t="inlineStr">
         <is>
           <t>Gage Verification Log</t>
         </is>
       </c>
-      <c r="M1" s="268" t="n"/>
-      <c r="N1" s="268" t="n"/>
-      <c r="O1" s="268" t="n"/>
-      <c r="P1" s="268" t="n"/>
-      <c r="Q1" s="268" t="n"/>
-      <c r="R1" s="268" t="n"/>
-      <c r="S1" s="268" t="n"/>
-      <c r="T1" s="268" t="n"/>
-      <c r="U1" s="268" t="n"/>
-      <c r="V1" s="268" t="n"/>
-      <c r="W1" s="268" t="n"/>
-      <c r="X1" s="268" t="n"/>
-      <c r="Y1" s="268" t="n"/>
-      <c r="Z1" s="268" t="n"/>
-      <c r="AA1" s="268" t="n"/>
-      <c r="AB1" s="268" t="n"/>
-      <c r="AC1" s="268" t="n"/>
-      <c r="AD1" s="268" t="n"/>
-      <c r="AE1" s="268" t="n"/>
-      <c r="AF1" s="268" t="n"/>
-      <c r="AG1" s="268" t="n"/>
-      <c r="AH1" s="268" t="n"/>
-      <c r="AI1" s="268" t="n"/>
-      <c r="AJ1" s="268" t="n"/>
-      <c r="AK1" s="268" t="n"/>
-      <c r="AL1" s="268" t="n"/>
-      <c r="AM1" s="268" t="n"/>
-      <c r="AN1" s="268" t="n"/>
-      <c r="AO1" s="268" t="n"/>
-      <c r="AP1" s="268" t="n"/>
-      <c r="AQ1" s="270" t="inlineStr">
+      <c r="M1" s="404" t="n"/>
+      <c r="N1" s="404" t="n"/>
+      <c r="O1" s="404" t="n"/>
+      <c r="P1" s="404" t="n"/>
+      <c r="Q1" s="404" t="n"/>
+      <c r="R1" s="404" t="n"/>
+      <c r="S1" s="404" t="n"/>
+      <c r="T1" s="404" t="n"/>
+      <c r="U1" s="404" t="n"/>
+      <c r="V1" s="404" t="n"/>
+      <c r="W1" s="404" t="n"/>
+      <c r="X1" s="404" t="n"/>
+      <c r="Y1" s="404" t="n"/>
+      <c r="Z1" s="404" t="n"/>
+      <c r="AA1" s="404" t="n"/>
+      <c r="AB1" s="404" t="n"/>
+      <c r="AC1" s="404" t="n"/>
+      <c r="AD1" s="404" t="n"/>
+      <c r="AE1" s="404" t="n"/>
+      <c r="AF1" s="404" t="n"/>
+      <c r="AG1" s="404" t="n"/>
+      <c r="AH1" s="404" t="n"/>
+      <c r="AI1" s="404" t="n"/>
+      <c r="AJ1" s="404" t="n"/>
+      <c r="AK1" s="404" t="n"/>
+      <c r="AL1" s="404" t="n"/>
+      <c r="AM1" s="404" t="n"/>
+      <c r="AN1" s="404" t="n"/>
+      <c r="AO1" s="404" t="n"/>
+      <c r="AP1" s="404" t="n"/>
+      <c r="AQ1" s="359" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="271" t="n"/>
-      <c r="AS1" s="271" t="n"/>
-      <c r="AT1" s="271" t="n"/>
-      <c r="AU1" s="271" t="n"/>
-      <c r="AV1" s="272" t="n"/>
-      <c r="AW1" s="273" t="inlineStr">
+      <c r="AR1" s="402" t="n"/>
+      <c r="AS1" s="402" t="n"/>
+      <c r="AT1" s="402" t="n"/>
+      <c r="AU1" s="402" t="n"/>
+      <c r="AV1" s="403" t="n"/>
+      <c r="AW1" s="360" t="inlineStr">
         <is>
           <t>FRM-602</t>
         </is>
       </c>
-      <c r="AX1" s="271" t="n"/>
-      <c r="AY1" s="271" t="n"/>
-      <c r="AZ1" s="271" t="n"/>
-      <c r="BA1" s="271" t="n"/>
-      <c r="BB1" s="271" t="n"/>
-      <c r="BC1" s="271" t="n"/>
-      <c r="BD1" s="274" t="n"/>
+      <c r="AX1" s="402" t="n"/>
+      <c r="AY1" s="402" t="n"/>
+      <c r="AZ1" s="402" t="n"/>
+      <c r="BA1" s="402" t="n"/>
+      <c r="BB1" s="402" t="n"/>
+      <c r="BC1" s="402" t="n"/>
+      <c r="BD1" s="403" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="L2" s="275" t="n"/>
-      <c r="AQ2" s="270" t="inlineStr">
+      <c r="A2" s="405" t="n"/>
+      <c r="L2" s="405" t="n"/>
+      <c r="AQ2" s="359" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="271" t="n"/>
-      <c r="AS2" s="271" t="n"/>
-      <c r="AT2" s="271" t="n"/>
-      <c r="AU2" s="271" t="n"/>
-      <c r="AV2" s="272" t="n"/>
-      <c r="AW2" s="273" t="inlineStr">
+      <c r="AR2" s="402" t="n"/>
+      <c r="AS2" s="402" t="n"/>
+      <c r="AT2" s="402" t="n"/>
+      <c r="AU2" s="402" t="n"/>
+      <c r="AV2" s="403" t="n"/>
+      <c r="AW2" s="360" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="271" t="n"/>
-      <c r="AY2" s="271" t="n"/>
-      <c r="AZ2" s="271" t="n"/>
-      <c r="BA2" s="271" t="n"/>
-      <c r="BB2" s="271" t="n"/>
-      <c r="BC2" s="271" t="n"/>
-      <c r="BD2" s="274" t="n"/>
+      <c r="AX2" s="402" t="n"/>
+      <c r="AY2" s="402" t="n"/>
+      <c r="AZ2" s="402" t="n"/>
+      <c r="BA2" s="402" t="n"/>
+      <c r="BB2" s="402" t="n"/>
+      <c r="BC2" s="402" t="n"/>
+      <c r="BD2" s="403" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="L3" s="279" t="n"/>
-      <c r="M3" s="276" t="n"/>
-      <c r="N3" s="276" t="n"/>
-      <c r="O3" s="276" t="n"/>
-      <c r="P3" s="276" t="n"/>
-      <c r="Q3" s="276" t="n"/>
-      <c r="R3" s="276" t="n"/>
-      <c r="S3" s="276" t="n"/>
-      <c r="T3" s="276" t="n"/>
-      <c r="U3" s="276" t="n"/>
-      <c r="V3" s="276" t="n"/>
-      <c r="W3" s="276" t="n"/>
-      <c r="X3" s="276" t="n"/>
-      <c r="Y3" s="276" t="n"/>
-      <c r="Z3" s="276" t="n"/>
-      <c r="AA3" s="276" t="n"/>
-      <c r="AB3" s="276" t="n"/>
-      <c r="AC3" s="276" t="n"/>
-      <c r="AD3" s="276" t="n"/>
-      <c r="AE3" s="276" t="n"/>
-      <c r="AF3" s="276" t="n"/>
-      <c r="AG3" s="276" t="n"/>
-      <c r="AH3" s="276" t="n"/>
-      <c r="AI3" s="276" t="n"/>
-      <c r="AJ3" s="276" t="n"/>
-      <c r="AK3" s="276" t="n"/>
-      <c r="AL3" s="276" t="n"/>
-      <c r="AM3" s="276" t="n"/>
-      <c r="AN3" s="276" t="n"/>
-      <c r="AO3" s="276" t="n"/>
-      <c r="AP3" s="276" t="n"/>
-      <c r="AQ3" s="270" t="inlineStr">
+      <c r="A3" s="405" t="n"/>
+      <c r="L3" s="406" t="n"/>
+      <c r="M3" s="407" t="n"/>
+      <c r="N3" s="407" t="n"/>
+      <c r="O3" s="407" t="n"/>
+      <c r="P3" s="407" t="n"/>
+      <c r="Q3" s="407" t="n"/>
+      <c r="R3" s="407" t="n"/>
+      <c r="S3" s="407" t="n"/>
+      <c r="T3" s="407" t="n"/>
+      <c r="U3" s="407" t="n"/>
+      <c r="V3" s="407" t="n"/>
+      <c r="W3" s="407" t="n"/>
+      <c r="X3" s="407" t="n"/>
+      <c r="Y3" s="407" t="n"/>
+      <c r="Z3" s="407" t="n"/>
+      <c r="AA3" s="407" t="n"/>
+      <c r="AB3" s="407" t="n"/>
+      <c r="AC3" s="407" t="n"/>
+      <c r="AD3" s="407" t="n"/>
+      <c r="AE3" s="407" t="n"/>
+      <c r="AF3" s="407" t="n"/>
+      <c r="AG3" s="407" t="n"/>
+      <c r="AH3" s="407" t="n"/>
+      <c r="AI3" s="407" t="n"/>
+      <c r="AJ3" s="407" t="n"/>
+      <c r="AK3" s="407" t="n"/>
+      <c r="AL3" s="407" t="n"/>
+      <c r="AM3" s="407" t="n"/>
+      <c r="AN3" s="407" t="n"/>
+      <c r="AO3" s="407" t="n"/>
+      <c r="AP3" s="407" t="n"/>
+      <c r="AQ3" s="359" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="271" t="n"/>
-      <c r="AS3" s="271" t="n"/>
-      <c r="AT3" s="271" t="n"/>
-      <c r="AU3" s="271" t="n"/>
-      <c r="AV3" s="272" t="n"/>
-      <c r="AW3" s="273" t="inlineStr">
+      <c r="AR3" s="402" t="n"/>
+      <c r="AS3" s="402" t="n"/>
+      <c r="AT3" s="402" t="n"/>
+      <c r="AU3" s="402" t="n"/>
+      <c r="AV3" s="403" t="n"/>
+      <c r="AW3" s="360" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="271" t="n"/>
-      <c r="AY3" s="271" t="n"/>
-      <c r="AZ3" s="271" t="n"/>
-      <c r="BA3" s="271" t="n"/>
-      <c r="BB3" s="271" t="n"/>
-      <c r="BC3" s="271" t="n"/>
-      <c r="BD3" s="274" t="n"/>
+      <c r="AX3" s="402" t="n"/>
+      <c r="AY3" s="402" t="n"/>
+      <c r="AZ3" s="402" t="n"/>
+      <c r="BA3" s="402" t="n"/>
+      <c r="BB3" s="402" t="n"/>
+      <c r="BC3" s="402" t="n"/>
+      <c r="BD3" s="403" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="A4" s="405" t="n"/>
+      <c r="L4" s="364" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="270" t="inlineStr">
+      <c r="AQ4" s="359" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="271" t="n"/>
-      <c r="AS4" s="271" t="n"/>
-      <c r="AT4" s="271" t="n"/>
-      <c r="AU4" s="271" t="n"/>
-      <c r="AV4" s="272" t="n"/>
-      <c r="AW4" s="273" t="inlineStr">
+      <c r="AR4" s="402" t="n"/>
+      <c r="AS4" s="402" t="n"/>
+      <c r="AT4" s="402" t="n"/>
+      <c r="AU4" s="402" t="n"/>
+      <c r="AV4" s="403" t="n"/>
+      <c r="AW4" s="360" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="271" t="n"/>
-      <c r="AY4" s="271" t="n"/>
-      <c r="AZ4" s="271" t="n"/>
-      <c r="BA4" s="271" t="n"/>
-      <c r="BB4" s="271" t="n"/>
-      <c r="BC4" s="271" t="n"/>
-      <c r="BD4" s="274" t="n"/>
+      <c r="AX4" s="402" t="n"/>
+      <c r="AY4" s="402" t="n"/>
+      <c r="AZ4" s="402" t="n"/>
+      <c r="BA4" s="402" t="n"/>
+      <c r="BB4" s="402" t="n"/>
+      <c r="BC4" s="402" t="n"/>
+      <c r="BD4" s="403" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="280" t="n"/>
-      <c r="B5" s="281" t="n"/>
-      <c r="C5" s="281" t="n"/>
-      <c r="D5" s="281" t="n"/>
-      <c r="E5" s="281" t="n"/>
-      <c r="F5" s="281" t="n"/>
-      <c r="G5" s="281" t="n"/>
-      <c r="H5" s="281" t="n"/>
-      <c r="I5" s="281" t="n"/>
-      <c r="J5" s="281" t="n"/>
-      <c r="K5" s="281" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="A5" s="406" t="n"/>
+      <c r="B5" s="407" t="n"/>
+      <c r="C5" s="407" t="n"/>
+      <c r="D5" s="407" t="n"/>
+      <c r="E5" s="407" t="n"/>
+      <c r="F5" s="407" t="n"/>
+      <c r="G5" s="407" t="n"/>
+      <c r="H5" s="407" t="n"/>
+      <c r="I5" s="407" t="n"/>
+      <c r="J5" s="407" t="n"/>
+      <c r="K5" s="407" t="n"/>
+      <c r="L5" s="365" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="281" t="n"/>
-      <c r="N5" s="281" t="n"/>
-      <c r="O5" s="281" t="n"/>
-      <c r="P5" s="281" t="n"/>
-      <c r="Q5" s="281" t="n"/>
-      <c r="R5" s="281" t="n"/>
-      <c r="S5" s="281" t="n"/>
-      <c r="T5" s="281" t="n"/>
-      <c r="U5" s="281" t="n"/>
-      <c r="V5" s="281" t="n"/>
-      <c r="W5" s="281" t="n"/>
-      <c r="X5" s="281" t="n"/>
-      <c r="Y5" s="281" t="n"/>
-      <c r="Z5" s="281" t="n"/>
-      <c r="AA5" s="281" t="n"/>
-      <c r="AB5" s="281" t="n"/>
-      <c r="AC5" s="281" t="n"/>
-      <c r="AD5" s="281" t="n"/>
-      <c r="AE5" s="281" t="n"/>
-      <c r="AF5" s="281" t="n"/>
-      <c r="AG5" s="281" t="n"/>
-      <c r="AH5" s="281" t="n"/>
-      <c r="AI5" s="281" t="n"/>
-      <c r="AJ5" s="281" t="n"/>
-      <c r="AK5" s="281" t="n"/>
-      <c r="AL5" s="281" t="n"/>
-      <c r="AM5" s="281" t="n"/>
-      <c r="AN5" s="281" t="n"/>
-      <c r="AO5" s="281" t="n"/>
-      <c r="AP5" s="281" t="n"/>
-      <c r="AQ5" s="270" t="inlineStr">
+      <c r="M5" s="407" t="n"/>
+      <c r="N5" s="407" t="n"/>
+      <c r="O5" s="407" t="n"/>
+      <c r="P5" s="407" t="n"/>
+      <c r="Q5" s="407" t="n"/>
+      <c r="R5" s="407" t="n"/>
+      <c r="S5" s="407" t="n"/>
+      <c r="T5" s="407" t="n"/>
+      <c r="U5" s="407" t="n"/>
+      <c r="V5" s="407" t="n"/>
+      <c r="W5" s="407" t="n"/>
+      <c r="X5" s="407" t="n"/>
+      <c r="Y5" s="407" t="n"/>
+      <c r="Z5" s="407" t="n"/>
+      <c r="AA5" s="407" t="n"/>
+      <c r="AB5" s="407" t="n"/>
+      <c r="AC5" s="407" t="n"/>
+      <c r="AD5" s="407" t="n"/>
+      <c r="AE5" s="407" t="n"/>
+      <c r="AF5" s="407" t="n"/>
+      <c r="AG5" s="407" t="n"/>
+      <c r="AH5" s="407" t="n"/>
+      <c r="AI5" s="407" t="n"/>
+      <c r="AJ5" s="407" t="n"/>
+      <c r="AK5" s="407" t="n"/>
+      <c r="AL5" s="407" t="n"/>
+      <c r="AM5" s="407" t="n"/>
+      <c r="AN5" s="407" t="n"/>
+      <c r="AO5" s="407" t="n"/>
+      <c r="AP5" s="407" t="n"/>
+      <c r="AQ5" s="359" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="271" t="n"/>
-      <c r="AS5" s="271" t="n"/>
-      <c r="AT5" s="271" t="n"/>
-      <c r="AU5" s="271" t="n"/>
-      <c r="AV5" s="272" t="n"/>
-      <c r="AW5" s="273" t="inlineStr">
+      <c r="AR5" s="402" t="n"/>
+      <c r="AS5" s="402" t="n"/>
+      <c r="AT5" s="402" t="n"/>
+      <c r="AU5" s="402" t="n"/>
+      <c r="AV5" s="403" t="n"/>
+      <c r="AW5" s="360" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="271" t="n"/>
-      <c r="AY5" s="271" t="n"/>
-      <c r="AZ5" s="271" t="n"/>
-      <c r="BA5" s="271" t="n"/>
-      <c r="BB5" s="271" t="n"/>
-      <c r="BC5" s="271" t="n"/>
-      <c r="BD5" s="274" t="n"/>
+      <c r="AX5" s="402" t="n"/>
+      <c r="AY5" s="402" t="n"/>
+      <c r="AZ5" s="402" t="n"/>
+      <c r="BA5" s="402" t="n"/>
+      <c r="BB5" s="402" t="n"/>
+      <c r="BC5" s="402" t="n"/>
+      <c r="BD5" s="403" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="25" t="inlineStr"/>
+      <c r="A6" s="345" t="inlineStr"/>
+      <c r="B6" s="401" t="n"/>
+      <c r="C6" s="401" t="n"/>
+      <c r="D6" s="401" t="n"/>
+      <c r="E6" s="401" t="n"/>
+      <c r="F6" s="401" t="n"/>
+      <c r="G6" s="401" t="n"/>
+      <c r="H6" s="401" t="n"/>
+      <c r="I6" s="401" t="n"/>
+      <c r="J6" s="401" t="n"/>
+      <c r="K6" s="401" t="n"/>
+      <c r="L6" s="401" t="n"/>
+      <c r="M6" s="401" t="n"/>
+      <c r="N6" s="401" t="n"/>
+      <c r="O6" s="401" t="n"/>
+      <c r="P6" s="401" t="n"/>
+      <c r="Q6" s="401" t="n"/>
+      <c r="R6" s="401" t="n"/>
+      <c r="S6" s="401" t="n"/>
+      <c r="T6" s="401" t="n"/>
+      <c r="U6" s="401" t="n"/>
+      <c r="V6" s="401" t="n"/>
+      <c r="W6" s="401" t="n"/>
+      <c r="X6" s="401" t="n"/>
+      <c r="Y6" s="401" t="n"/>
+      <c r="Z6" s="401" t="n"/>
+      <c r="AA6" s="401" t="n"/>
+      <c r="AB6" s="401" t="n"/>
+      <c r="AC6" s="401" t="n"/>
+      <c r="AD6" s="401" t="n"/>
+      <c r="AE6" s="401" t="n"/>
+      <c r="AF6" s="401" t="n"/>
+      <c r="AG6" s="401" t="n"/>
+      <c r="AH6" s="401" t="n"/>
+      <c r="AI6" s="401" t="n"/>
+      <c r="AJ6" s="401" t="n"/>
+      <c r="AK6" s="401" t="n"/>
+      <c r="AL6" s="401" t="n"/>
+      <c r="AM6" s="401" t="n"/>
+      <c r="AN6" s="401" t="n"/>
+      <c r="AO6" s="401" t="n"/>
+      <c r="AP6" s="401" t="n"/>
+      <c r="AQ6" s="401" t="n"/>
+      <c r="AR6" s="401" t="n"/>
+      <c r="AS6" s="401" t="n"/>
+      <c r="AT6" s="401" t="n"/>
+      <c r="AU6" s="401" t="n"/>
+      <c r="AV6" s="401" t="n"/>
+      <c r="AW6" s="401" t="n"/>
+      <c r="AX6" s="401" t="n"/>
+      <c r="AY6" s="401" t="n"/>
+      <c r="AZ6" s="401" t="n"/>
+      <c r="BA6" s="401" t="n"/>
+      <c r="BB6" s="401" t="n"/>
+      <c r="BC6" s="401" t="n"/>
+      <c r="BD6" s="401" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="284" t="inlineStr">
+      <c r="A7" s="366" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. SCOPE / REVIEW CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="285" t="n"/>
-      <c r="C7" s="285" t="n"/>
-      <c r="D7" s="285" t="n"/>
-      <c r="E7" s="285" t="n"/>
-      <c r="F7" s="285" t="n"/>
-      <c r="G7" s="285" t="n"/>
-      <c r="H7" s="285" t="n"/>
-      <c r="I7" s="285" t="n"/>
-      <c r="J7" s="285" t="n"/>
-      <c r="K7" s="285" t="n"/>
-      <c r="L7" s="285" t="n"/>
-      <c r="M7" s="285" t="n"/>
-      <c r="N7" s="285" t="n"/>
-      <c r="O7" s="285" t="n"/>
-      <c r="P7" s="285" t="n"/>
-      <c r="Q7" s="285" t="n"/>
-      <c r="R7" s="285" t="n"/>
-      <c r="S7" s="285" t="n"/>
-      <c r="T7" s="285" t="n"/>
-      <c r="U7" s="285" t="n"/>
-      <c r="V7" s="285" t="n"/>
-      <c r="W7" s="285" t="n"/>
-      <c r="X7" s="285" t="n"/>
-      <c r="Y7" s="285" t="n"/>
-      <c r="Z7" s="285" t="n"/>
-      <c r="AA7" s="285" t="n"/>
-      <c r="AB7" s="285" t="n"/>
-      <c r="AC7" s="285" t="n"/>
-      <c r="AD7" s="285" t="n"/>
-      <c r="AE7" s="285" t="n"/>
-      <c r="AF7" s="285" t="n"/>
-      <c r="AG7" s="285" t="n"/>
-      <c r="AH7" s="285" t="n"/>
-      <c r="AI7" s="285" t="n"/>
-      <c r="AJ7" s="285" t="n"/>
-      <c r="AK7" s="285" t="n"/>
-      <c r="AL7" s="285" t="n"/>
-      <c r="AM7" s="285" t="n"/>
-      <c r="AN7" s="285" t="n"/>
-      <c r="AO7" s="285" t="n"/>
-      <c r="AP7" s="285" t="n"/>
-      <c r="AQ7" s="285" t="n"/>
-      <c r="AR7" s="285" t="n"/>
-      <c r="AS7" s="285" t="n"/>
-      <c r="AT7" s="285" t="n"/>
-      <c r="AU7" s="285" t="n"/>
-      <c r="AV7" s="285" t="n"/>
-      <c r="AW7" s="285" t="n"/>
-      <c r="AX7" s="285" t="n"/>
-      <c r="AY7" s="285" t="n"/>
-      <c r="AZ7" s="285" t="n"/>
-      <c r="BA7" s="285" t="n"/>
-      <c r="BB7" s="285" t="n"/>
-      <c r="BC7" s="285" t="n"/>
-      <c r="BD7" s="286" t="n"/>
+      <c r="B7" s="402" t="n"/>
+      <c r="C7" s="402" t="n"/>
+      <c r="D7" s="402" t="n"/>
+      <c r="E7" s="402" t="n"/>
+      <c r="F7" s="402" t="n"/>
+      <c r="G7" s="402" t="n"/>
+      <c r="H7" s="402" t="n"/>
+      <c r="I7" s="402" t="n"/>
+      <c r="J7" s="402" t="n"/>
+      <c r="K7" s="402" t="n"/>
+      <c r="L7" s="402" t="n"/>
+      <c r="M7" s="402" t="n"/>
+      <c r="N7" s="402" t="n"/>
+      <c r="O7" s="402" t="n"/>
+      <c r="P7" s="402" t="n"/>
+      <c r="Q7" s="402" t="n"/>
+      <c r="R7" s="402" t="n"/>
+      <c r="S7" s="402" t="n"/>
+      <c r="T7" s="402" t="n"/>
+      <c r="U7" s="402" t="n"/>
+      <c r="V7" s="402" t="n"/>
+      <c r="W7" s="402" t="n"/>
+      <c r="X7" s="402" t="n"/>
+      <c r="Y7" s="402" t="n"/>
+      <c r="Z7" s="402" t="n"/>
+      <c r="AA7" s="402" t="n"/>
+      <c r="AB7" s="402" t="n"/>
+      <c r="AC7" s="402" t="n"/>
+      <c r="AD7" s="402" t="n"/>
+      <c r="AE7" s="402" t="n"/>
+      <c r="AF7" s="402" t="n"/>
+      <c r="AG7" s="402" t="n"/>
+      <c r="AH7" s="402" t="n"/>
+      <c r="AI7" s="402" t="n"/>
+      <c r="AJ7" s="402" t="n"/>
+      <c r="AK7" s="402" t="n"/>
+      <c r="AL7" s="402" t="n"/>
+      <c r="AM7" s="402" t="n"/>
+      <c r="AN7" s="402" t="n"/>
+      <c r="AO7" s="402" t="n"/>
+      <c r="AP7" s="402" t="n"/>
+      <c r="AQ7" s="402" t="n"/>
+      <c r="AR7" s="402" t="n"/>
+      <c r="AS7" s="402" t="n"/>
+      <c r="AT7" s="402" t="n"/>
+      <c r="AU7" s="402" t="n"/>
+      <c r="AV7" s="402" t="n"/>
+      <c r="AW7" s="402" t="n"/>
+      <c r="AX7" s="402" t="n"/>
+      <c r="AY7" s="402" t="n"/>
+      <c r="AZ7" s="402" t="n"/>
+      <c r="BA7" s="402" t="n"/>
+      <c r="BB7" s="402" t="n"/>
+      <c r="BC7" s="402" t="n"/>
+      <c r="BD7" s="403" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="287" t="inlineStr">
+      <c r="A8" s="353" t="inlineStr">
         <is>
           <t>Verification ID</t>
         </is>
       </c>
-      <c r="B8" s="271" t="n"/>
-      <c r="C8" s="271" t="n"/>
-      <c r="D8" s="271" t="n"/>
-      <c r="E8" s="271" t="n"/>
-      <c r="F8" s="271" t="n"/>
-      <c r="G8" s="271" t="n"/>
-      <c r="H8" s="271" t="n"/>
-      <c r="I8" s="271" t="n"/>
-      <c r="J8" s="272" t="n"/>
-      <c r="K8" s="288" t="n"/>
-      <c r="L8" s="319" t="n"/>
-      <c r="M8" s="319" t="n"/>
-      <c r="N8" s="319" t="n"/>
-      <c r="O8" s="319" t="n"/>
-      <c r="P8" s="319" t="n"/>
-      <c r="Q8" s="319" t="n"/>
-      <c r="R8" s="319" t="n"/>
-      <c r="S8" s="319" t="n"/>
-      <c r="T8" s="319" t="n"/>
-      <c r="U8" s="319" t="n"/>
-      <c r="V8" s="319" t="n"/>
-      <c r="W8" s="319" t="n"/>
-      <c r="X8" s="319" t="n"/>
-      <c r="Y8" s="319" t="n"/>
-      <c r="Z8" s="319" t="n"/>
-      <c r="AA8" s="319" t="n"/>
-      <c r="AB8" s="320" t="n"/>
-      <c r="AC8" s="289" t="inlineStr">
+      <c r="B8" s="389" t="n"/>
+      <c r="C8" s="389" t="n"/>
+      <c r="D8" s="389" t="n"/>
+      <c r="E8" s="389" t="n"/>
+      <c r="F8" s="389" t="n"/>
+      <c r="G8" s="389" t="n"/>
+      <c r="H8" s="389" t="n"/>
+      <c r="I8" s="389" t="n"/>
+      <c r="J8" s="390" t="n"/>
+      <c r="K8" s="367" t="n"/>
+      <c r="L8" s="395" t="n"/>
+      <c r="M8" s="395" t="n"/>
+      <c r="N8" s="395" t="n"/>
+      <c r="O8" s="395" t="n"/>
+      <c r="P8" s="395" t="n"/>
+      <c r="Q8" s="395" t="n"/>
+      <c r="R8" s="395" t="n"/>
+      <c r="S8" s="395" t="n"/>
+      <c r="T8" s="395" t="n"/>
+      <c r="U8" s="395" t="n"/>
+      <c r="V8" s="395" t="n"/>
+      <c r="W8" s="395" t="n"/>
+      <c r="X8" s="395" t="n"/>
+      <c r="Y8" s="395" t="n"/>
+      <c r="Z8" s="395" t="n"/>
+      <c r="AA8" s="395" t="n"/>
+      <c r="AB8" s="396" t="n"/>
+      <c r="AC8" s="370" t="inlineStr">
         <is>
           <t>Verification Result</t>
         </is>
       </c>
-      <c r="AD8" s="271" t="n"/>
-      <c r="AE8" s="271" t="n"/>
-      <c r="AF8" s="271" t="n"/>
-      <c r="AG8" s="271" t="n"/>
-      <c r="AH8" s="271" t="n"/>
-      <c r="AI8" s="271" t="n"/>
-      <c r="AJ8" s="271" t="n"/>
-      <c r="AK8" s="271" t="n"/>
-      <c r="AL8" s="272" t="n"/>
-      <c r="AM8" s="290" t="n"/>
-      <c r="AN8" s="319" t="n"/>
-      <c r="AO8" s="319" t="n"/>
-      <c r="AP8" s="319" t="n"/>
-      <c r="AQ8" s="319" t="n"/>
-      <c r="AR8" s="319" t="n"/>
-      <c r="AS8" s="319" t="n"/>
-      <c r="AT8" s="319" t="n"/>
-      <c r="AU8" s="319" t="n"/>
-      <c r="AV8" s="319" t="n"/>
-      <c r="AW8" s="319" t="n"/>
-      <c r="AX8" s="319" t="n"/>
-      <c r="AY8" s="319" t="n"/>
-      <c r="AZ8" s="319" t="n"/>
-      <c r="BA8" s="319" t="n"/>
-      <c r="BB8" s="319" t="n"/>
-      <c r="BC8" s="319" t="n"/>
-      <c r="BD8" s="321" t="n"/>
+      <c r="AD8" s="389" t="n"/>
+      <c r="AE8" s="389" t="n"/>
+      <c r="AF8" s="389" t="n"/>
+      <c r="AG8" s="389" t="n"/>
+      <c r="AH8" s="389" t="n"/>
+      <c r="AI8" s="389" t="n"/>
+      <c r="AJ8" s="389" t="n"/>
+      <c r="AK8" s="389" t="n"/>
+      <c r="AL8" s="390" t="n"/>
+      <c r="AM8" s="367" t="n"/>
+      <c r="AN8" s="395" t="n"/>
+      <c r="AO8" s="395" t="n"/>
+      <c r="AP8" s="395" t="n"/>
+      <c r="AQ8" s="395" t="n"/>
+      <c r="AR8" s="395" t="n"/>
+      <c r="AS8" s="395" t="n"/>
+      <c r="AT8" s="395" t="n"/>
+      <c r="AU8" s="395" t="n"/>
+      <c r="AV8" s="395" t="n"/>
+      <c r="AW8" s="395" t="n"/>
+      <c r="AX8" s="395" t="n"/>
+      <c r="AY8" s="395" t="n"/>
+      <c r="AZ8" s="395" t="n"/>
+      <c r="BA8" s="395" t="n"/>
+      <c r="BB8" s="395" t="n"/>
+      <c r="BC8" s="395" t="n"/>
+      <c r="BD8" s="396" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="287" t="inlineStr">
+      <c r="A9" s="353" t="inlineStr">
         <is>
           <t>Equipment ID / Description</t>
         </is>
       </c>
-      <c r="B9" s="271" t="n"/>
-      <c r="C9" s="271" t="n"/>
-      <c r="D9" s="271" t="n"/>
-      <c r="E9" s="271" t="n"/>
-      <c r="F9" s="271" t="n"/>
-      <c r="G9" s="271" t="n"/>
-      <c r="H9" s="271" t="n"/>
-      <c r="I9" s="271" t="n"/>
-      <c r="J9" s="272" t="n"/>
-      <c r="K9" s="288" t="n"/>
-      <c r="L9" s="319" t="n"/>
-      <c r="M9" s="319" t="n"/>
-      <c r="N9" s="319" t="n"/>
-      <c r="O9" s="319" t="n"/>
-      <c r="P9" s="319" t="n"/>
-      <c r="Q9" s="319" t="n"/>
-      <c r="R9" s="319" t="n"/>
-      <c r="S9" s="319" t="n"/>
-      <c r="T9" s="319" t="n"/>
-      <c r="U9" s="319" t="n"/>
-      <c r="V9" s="319" t="n"/>
-      <c r="W9" s="319" t="n"/>
-      <c r="X9" s="319" t="n"/>
-      <c r="Y9" s="319" t="n"/>
-      <c r="Z9" s="319" t="n"/>
-      <c r="AA9" s="319" t="n"/>
-      <c r="AB9" s="320" t="n"/>
-      <c r="AC9" s="289" t="inlineStr">
+      <c r="B9" s="389" t="n"/>
+      <c r="C9" s="389" t="n"/>
+      <c r="D9" s="389" t="n"/>
+      <c r="E9" s="389" t="n"/>
+      <c r="F9" s="389" t="n"/>
+      <c r="G9" s="389" t="n"/>
+      <c r="H9" s="389" t="n"/>
+      <c r="I9" s="389" t="n"/>
+      <c r="J9" s="390" t="n"/>
+      <c r="K9" s="367" t="n"/>
+      <c r="L9" s="395" t="n"/>
+      <c r="M9" s="395" t="n"/>
+      <c r="N9" s="395" t="n"/>
+      <c r="O9" s="395" t="n"/>
+      <c r="P9" s="395" t="n"/>
+      <c r="Q9" s="395" t="n"/>
+      <c r="R9" s="395" t="n"/>
+      <c r="S9" s="395" t="n"/>
+      <c r="T9" s="395" t="n"/>
+      <c r="U9" s="395" t="n"/>
+      <c r="V9" s="395" t="n"/>
+      <c r="W9" s="395" t="n"/>
+      <c r="X9" s="395" t="n"/>
+      <c r="Y9" s="395" t="n"/>
+      <c r="Z9" s="395" t="n"/>
+      <c r="AA9" s="395" t="n"/>
+      <c r="AB9" s="396" t="n"/>
+      <c r="AC9" s="370" t="inlineStr">
         <is>
           <t>User / Area</t>
         </is>
       </c>
-      <c r="AD9" s="271" t="n"/>
-      <c r="AE9" s="271" t="n"/>
-      <c r="AF9" s="271" t="n"/>
-      <c r="AG9" s="271" t="n"/>
-      <c r="AH9" s="271" t="n"/>
-      <c r="AI9" s="271" t="n"/>
-      <c r="AJ9" s="271" t="n"/>
-      <c r="AK9" s="271" t="n"/>
-      <c r="AL9" s="272" t="n"/>
-      <c r="AM9" s="290" t="n"/>
-      <c r="AN9" s="319" t="n"/>
-      <c r="AO9" s="319" t="n"/>
-      <c r="AP9" s="319" t="n"/>
-      <c r="AQ9" s="319" t="n"/>
-      <c r="AR9" s="319" t="n"/>
-      <c r="AS9" s="319" t="n"/>
-      <c r="AT9" s="319" t="n"/>
-      <c r="AU9" s="319" t="n"/>
-      <c r="AV9" s="319" t="n"/>
-      <c r="AW9" s="319" t="n"/>
-      <c r="AX9" s="319" t="n"/>
-      <c r="AY9" s="319" t="n"/>
-      <c r="AZ9" s="319" t="n"/>
-      <c r="BA9" s="319" t="n"/>
-      <c r="BB9" s="319" t="n"/>
-      <c r="BC9" s="319" t="n"/>
-      <c r="BD9" s="321" t="n"/>
+      <c r="AD9" s="389" t="n"/>
+      <c r="AE9" s="389" t="n"/>
+      <c r="AF9" s="389" t="n"/>
+      <c r="AG9" s="389" t="n"/>
+      <c r="AH9" s="389" t="n"/>
+      <c r="AI9" s="389" t="n"/>
+      <c r="AJ9" s="389" t="n"/>
+      <c r="AK9" s="389" t="n"/>
+      <c r="AL9" s="390" t="n"/>
+      <c r="AM9" s="367" t="n"/>
+      <c r="AN9" s="395" t="n"/>
+      <c r="AO9" s="395" t="n"/>
+      <c r="AP9" s="395" t="n"/>
+      <c r="AQ9" s="395" t="n"/>
+      <c r="AR9" s="395" t="n"/>
+      <c r="AS9" s="395" t="n"/>
+      <c r="AT9" s="395" t="n"/>
+      <c r="AU9" s="395" t="n"/>
+      <c r="AV9" s="395" t="n"/>
+      <c r="AW9" s="395" t="n"/>
+      <c r="AX9" s="395" t="n"/>
+      <c r="AY9" s="395" t="n"/>
+      <c r="AZ9" s="395" t="n"/>
+      <c r="BA9" s="395" t="n"/>
+      <c r="BB9" s="395" t="n"/>
+      <c r="BC9" s="395" t="n"/>
+      <c r="BD9" s="396" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="287" t="inlineStr">
+      <c r="A10" s="353" t="inlineStr">
         <is>
           <t>Verification Type</t>
         </is>
       </c>
-      <c r="B10" s="271" t="n"/>
-      <c r="C10" s="271" t="n"/>
-      <c r="D10" s="271" t="n"/>
-      <c r="E10" s="271" t="n"/>
-      <c r="F10" s="271" t="n"/>
-      <c r="G10" s="271" t="n"/>
-      <c r="H10" s="271" t="n"/>
-      <c r="I10" s="271" t="n"/>
-      <c r="J10" s="272" t="n"/>
-      <c r="K10" s="288" t="n"/>
-      <c r="L10" s="319" t="n"/>
-      <c r="M10" s="319" t="n"/>
-      <c r="N10" s="319" t="n"/>
-      <c r="O10" s="319" t="n"/>
-      <c r="P10" s="319" t="n"/>
-      <c r="Q10" s="319" t="n"/>
-      <c r="R10" s="319" t="n"/>
-      <c r="S10" s="319" t="n"/>
-      <c r="T10" s="319" t="n"/>
-      <c r="U10" s="319" t="n"/>
-      <c r="V10" s="319" t="n"/>
-      <c r="W10" s="319" t="n"/>
-      <c r="X10" s="319" t="n"/>
-      <c r="Y10" s="319" t="n"/>
-      <c r="Z10" s="319" t="n"/>
-      <c r="AA10" s="319" t="n"/>
-      <c r="AB10" s="320" t="n"/>
-      <c r="AC10" s="289" t="inlineStr">
+      <c r="B10" s="389" t="n"/>
+      <c r="C10" s="389" t="n"/>
+      <c r="D10" s="389" t="n"/>
+      <c r="E10" s="389" t="n"/>
+      <c r="F10" s="389" t="n"/>
+      <c r="G10" s="389" t="n"/>
+      <c r="H10" s="389" t="n"/>
+      <c r="I10" s="389" t="n"/>
+      <c r="J10" s="390" t="n"/>
+      <c r="K10" s="367" t="n"/>
+      <c r="L10" s="395" t="n"/>
+      <c r="M10" s="395" t="n"/>
+      <c r="N10" s="395" t="n"/>
+      <c r="O10" s="395" t="n"/>
+      <c r="P10" s="395" t="n"/>
+      <c r="Q10" s="395" t="n"/>
+      <c r="R10" s="395" t="n"/>
+      <c r="S10" s="395" t="n"/>
+      <c r="T10" s="395" t="n"/>
+      <c r="U10" s="395" t="n"/>
+      <c r="V10" s="395" t="n"/>
+      <c r="W10" s="395" t="n"/>
+      <c r="X10" s="395" t="n"/>
+      <c r="Y10" s="395" t="n"/>
+      <c r="Z10" s="395" t="n"/>
+      <c r="AA10" s="395" t="n"/>
+      <c r="AB10" s="396" t="n"/>
+      <c r="AC10" s="370" t="inlineStr">
         <is>
           <t>CAL Status</t>
         </is>
       </c>
-      <c r="AD10" s="271" t="n"/>
-      <c r="AE10" s="271" t="n"/>
-      <c r="AF10" s="271" t="n"/>
-      <c r="AG10" s="271" t="n"/>
-      <c r="AH10" s="271" t="n"/>
-      <c r="AI10" s="271" t="n"/>
-      <c r="AJ10" s="271" t="n"/>
-      <c r="AK10" s="271" t="n"/>
-      <c r="AL10" s="272" t="n"/>
-      <c r="AM10" s="290" t="n"/>
-      <c r="AN10" s="319" t="n"/>
-      <c r="AO10" s="319" t="n"/>
-      <c r="AP10" s="319" t="n"/>
-      <c r="AQ10" s="319" t="n"/>
-      <c r="AR10" s="319" t="n"/>
-      <c r="AS10" s="319" t="n"/>
-      <c r="AT10" s="319" t="n"/>
-      <c r="AU10" s="319" t="n"/>
-      <c r="AV10" s="319" t="n"/>
-      <c r="AW10" s="319" t="n"/>
-      <c r="AX10" s="319" t="n"/>
-      <c r="AY10" s="319" t="n"/>
-      <c r="AZ10" s="319" t="n"/>
-      <c r="BA10" s="319" t="n"/>
-      <c r="BB10" s="319" t="n"/>
-      <c r="BC10" s="319" t="n"/>
-      <c r="BD10" s="321" t="n"/>
+      <c r="AD10" s="389" t="n"/>
+      <c r="AE10" s="389" t="n"/>
+      <c r="AF10" s="389" t="n"/>
+      <c r="AG10" s="389" t="n"/>
+      <c r="AH10" s="389" t="n"/>
+      <c r="AI10" s="389" t="n"/>
+      <c r="AJ10" s="389" t="n"/>
+      <c r="AK10" s="389" t="n"/>
+      <c r="AL10" s="390" t="n"/>
+      <c r="AM10" s="367" t="n"/>
+      <c r="AN10" s="395" t="n"/>
+      <c r="AO10" s="395" t="n"/>
+      <c r="AP10" s="395" t="n"/>
+      <c r="AQ10" s="395" t="n"/>
+      <c r="AR10" s="395" t="n"/>
+      <c r="AS10" s="395" t="n"/>
+      <c r="AT10" s="395" t="n"/>
+      <c r="AU10" s="395" t="n"/>
+      <c r="AV10" s="395" t="n"/>
+      <c r="AW10" s="395" t="n"/>
+      <c r="AX10" s="395" t="n"/>
+      <c r="AY10" s="395" t="n"/>
+      <c r="AZ10" s="395" t="n"/>
+      <c r="BA10" s="395" t="n"/>
+      <c r="BB10" s="395" t="n"/>
+      <c r="BC10" s="395" t="n"/>
+      <c r="BD10" s="396" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="287" t="inlineStr">
+      <c r="A11" s="353" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="271" t="n"/>
-      <c r="C11" s="271" t="n"/>
-      <c r="D11" s="271" t="n"/>
-      <c r="E11" s="271" t="n"/>
-      <c r="F11" s="271" t="n"/>
-      <c r="G11" s="271" t="n"/>
-      <c r="H11" s="271" t="n"/>
-      <c r="I11" s="271" t="n"/>
-      <c r="J11" s="272" t="n"/>
-      <c r="K11" s="288" t="n"/>
-      <c r="L11" s="319" t="n"/>
-      <c r="M11" s="319" t="n"/>
-      <c r="N11" s="319" t="n"/>
-      <c r="O11" s="319" t="n"/>
-      <c r="P11" s="319" t="n"/>
-      <c r="Q11" s="319" t="n"/>
-      <c r="R11" s="319" t="n"/>
-      <c r="S11" s="319" t="n"/>
-      <c r="T11" s="319" t="n"/>
-      <c r="U11" s="319" t="n"/>
-      <c r="V11" s="319" t="n"/>
-      <c r="W11" s="319" t="n"/>
-      <c r="X11" s="319" t="n"/>
-      <c r="Y11" s="319" t="n"/>
-      <c r="Z11" s="319" t="n"/>
-      <c r="AA11" s="319" t="n"/>
-      <c r="AB11" s="320" t="n"/>
-      <c r="AC11" s="289" t="inlineStr">
+      <c r="B11" s="387" t="n"/>
+      <c r="C11" s="387" t="n"/>
+      <c r="D11" s="387" t="n"/>
+      <c r="E11" s="387" t="n"/>
+      <c r="F11" s="387" t="n"/>
+      <c r="G11" s="387" t="n"/>
+      <c r="H11" s="387" t="n"/>
+      <c r="I11" s="387" t="n"/>
+      <c r="J11" s="388" t="n"/>
+      <c r="K11" s="367" t="n"/>
+      <c r="L11" s="397" t="n"/>
+      <c r="M11" s="397" t="n"/>
+      <c r="N11" s="397" t="n"/>
+      <c r="O11" s="397" t="n"/>
+      <c r="P11" s="397" t="n"/>
+      <c r="Q11" s="397" t="n"/>
+      <c r="R11" s="397" t="n"/>
+      <c r="S11" s="397" t="n"/>
+      <c r="T11" s="397" t="n"/>
+      <c r="U11" s="397" t="n"/>
+      <c r="V11" s="397" t="n"/>
+      <c r="W11" s="397" t="n"/>
+      <c r="X11" s="397" t="n"/>
+      <c r="Y11" s="397" t="n"/>
+      <c r="Z11" s="397" t="n"/>
+      <c r="AA11" s="397" t="n"/>
+      <c r="AB11" s="398" t="n"/>
+      <c r="AC11" s="370" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="AD11" s="271" t="n"/>
-      <c r="AE11" s="271" t="n"/>
-      <c r="AF11" s="271" t="n"/>
-      <c r="AG11" s="271" t="n"/>
-      <c r="AH11" s="271" t="n"/>
-      <c r="AI11" s="271" t="n"/>
-      <c r="AJ11" s="271" t="n"/>
-      <c r="AK11" s="271" t="n"/>
-      <c r="AL11" s="272" t="n"/>
-      <c r="AM11" s="290" t="n"/>
-      <c r="AN11" s="319" t="n"/>
-      <c r="AO11" s="319" t="n"/>
-      <c r="AP11" s="319" t="n"/>
-      <c r="AQ11" s="319" t="n"/>
-      <c r="AR11" s="319" t="n"/>
-      <c r="AS11" s="319" t="n"/>
-      <c r="AT11" s="319" t="n"/>
-      <c r="AU11" s="319" t="n"/>
-      <c r="AV11" s="319" t="n"/>
-      <c r="AW11" s="319" t="n"/>
-      <c r="AX11" s="319" t="n"/>
-      <c r="AY11" s="319" t="n"/>
-      <c r="AZ11" s="319" t="n"/>
-      <c r="BA11" s="319" t="n"/>
-      <c r="BB11" s="319" t="n"/>
-      <c r="BC11" s="319" t="n"/>
-      <c r="BD11" s="321" t="n"/>
+      <c r="AD11" s="387" t="n"/>
+      <c r="AE11" s="387" t="n"/>
+      <c r="AF11" s="387" t="n"/>
+      <c r="AG11" s="387" t="n"/>
+      <c r="AH11" s="387" t="n"/>
+      <c r="AI11" s="387" t="n"/>
+      <c r="AJ11" s="387" t="n"/>
+      <c r="AK11" s="387" t="n"/>
+      <c r="AL11" s="388" t="n"/>
+      <c r="AM11" s="367" t="n"/>
+      <c r="AN11" s="397" t="n"/>
+      <c r="AO11" s="397" t="n"/>
+      <c r="AP11" s="397" t="n"/>
+      <c r="AQ11" s="397" t="n"/>
+      <c r="AR11" s="397" t="n"/>
+      <c r="AS11" s="397" t="n"/>
+      <c r="AT11" s="397" t="n"/>
+      <c r="AU11" s="397" t="n"/>
+      <c r="AV11" s="397" t="n"/>
+      <c r="AW11" s="397" t="n"/>
+      <c r="AX11" s="397" t="n"/>
+      <c r="AY11" s="397" t="n"/>
+      <c r="AZ11" s="397" t="n"/>
+      <c r="BA11" s="397" t="n"/>
+      <c r="BB11" s="397" t="n"/>
+      <c r="BC11" s="397" t="n"/>
+      <c r="BD11" s="398" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="287" t="inlineStr">
+      <c r="A12" s="353" t="inlineStr">
         <is>
           <t>Method / Acceptance Ref</t>
         </is>
       </c>
-      <c r="B12" s="271" t="n"/>
-      <c r="C12" s="271" t="n"/>
-      <c r="D12" s="271" t="n"/>
-      <c r="E12" s="271" t="n"/>
-      <c r="F12" s="271" t="n"/>
-      <c r="G12" s="271" t="n"/>
-      <c r="H12" s="271" t="n"/>
-      <c r="I12" s="271" t="n"/>
-      <c r="J12" s="272" t="n"/>
-      <c r="K12" s="288" t="n"/>
-      <c r="L12" s="319" t="n"/>
-      <c r="M12" s="319" t="n"/>
-      <c r="N12" s="319" t="n"/>
-      <c r="O12" s="319" t="n"/>
-      <c r="P12" s="319" t="n"/>
-      <c r="Q12" s="319" t="n"/>
-      <c r="R12" s="319" t="n"/>
-      <c r="S12" s="319" t="n"/>
-      <c r="T12" s="319" t="n"/>
-      <c r="U12" s="319" t="n"/>
-      <c r="V12" s="319" t="n"/>
-      <c r="W12" s="319" t="n"/>
-      <c r="X12" s="319" t="n"/>
-      <c r="Y12" s="319" t="n"/>
-      <c r="Z12" s="319" t="n"/>
-      <c r="AA12" s="319" t="n"/>
-      <c r="AB12" s="320" t="n"/>
-      <c r="AC12" s="289" t="inlineStr">
+      <c r="B12" s="389" t="n"/>
+      <c r="C12" s="389" t="n"/>
+      <c r="D12" s="389" t="n"/>
+      <c r="E12" s="389" t="n"/>
+      <c r="F12" s="389" t="n"/>
+      <c r="G12" s="389" t="n"/>
+      <c r="H12" s="389" t="n"/>
+      <c r="I12" s="389" t="n"/>
+      <c r="J12" s="390" t="n"/>
+      <c r="K12" s="367" t="n"/>
+      <c r="L12" s="395" t="n"/>
+      <c r="M12" s="395" t="n"/>
+      <c r="N12" s="395" t="n"/>
+      <c r="O12" s="395" t="n"/>
+      <c r="P12" s="395" t="n"/>
+      <c r="Q12" s="395" t="n"/>
+      <c r="R12" s="395" t="n"/>
+      <c r="S12" s="395" t="n"/>
+      <c r="T12" s="395" t="n"/>
+      <c r="U12" s="395" t="n"/>
+      <c r="V12" s="395" t="n"/>
+      <c r="W12" s="395" t="n"/>
+      <c r="X12" s="395" t="n"/>
+      <c r="Y12" s="395" t="n"/>
+      <c r="Z12" s="395" t="n"/>
+      <c r="AA12" s="395" t="n"/>
+      <c r="AB12" s="396" t="n"/>
+      <c r="AC12" s="370" t="inlineStr">
         <is>
           <t>Affected Job Ref</t>
         </is>
       </c>
-      <c r="AD12" s="271" t="n"/>
-      <c r="AE12" s="271" t="n"/>
-      <c r="AF12" s="271" t="n"/>
-      <c r="AG12" s="271" t="n"/>
-      <c r="AH12" s="271" t="n"/>
-      <c r="AI12" s="271" t="n"/>
-      <c r="AJ12" s="271" t="n"/>
-      <c r="AK12" s="271" t="n"/>
-      <c r="AL12" s="272" t="n"/>
-      <c r="AM12" s="290" t="n"/>
-      <c r="AN12" s="319" t="n"/>
-      <c r="AO12" s="319" t="n"/>
-      <c r="AP12" s="319" t="n"/>
-      <c r="AQ12" s="319" t="n"/>
-      <c r="AR12" s="319" t="n"/>
-      <c r="AS12" s="319" t="n"/>
-      <c r="AT12" s="319" t="n"/>
-      <c r="AU12" s="319" t="n"/>
-      <c r="AV12" s="319" t="n"/>
-      <c r="AW12" s="319" t="n"/>
-      <c r="AX12" s="319" t="n"/>
-      <c r="AY12" s="319" t="n"/>
-      <c r="AZ12" s="319" t="n"/>
-      <c r="BA12" s="319" t="n"/>
-      <c r="BB12" s="319" t="n"/>
-      <c r="BC12" s="319" t="n"/>
-      <c r="BD12" s="321" t="n"/>
+      <c r="AD12" s="389" t="n"/>
+      <c r="AE12" s="389" t="n"/>
+      <c r="AF12" s="389" t="n"/>
+      <c r="AG12" s="389" t="n"/>
+      <c r="AH12" s="389" t="n"/>
+      <c r="AI12" s="389" t="n"/>
+      <c r="AJ12" s="389" t="n"/>
+      <c r="AK12" s="389" t="n"/>
+      <c r="AL12" s="390" t="n"/>
+      <c r="AM12" s="367" t="n"/>
+      <c r="AN12" s="395" t="n"/>
+      <c r="AO12" s="395" t="n"/>
+      <c r="AP12" s="395" t="n"/>
+      <c r="AQ12" s="395" t="n"/>
+      <c r="AR12" s="395" t="n"/>
+      <c r="AS12" s="395" t="n"/>
+      <c r="AT12" s="395" t="n"/>
+      <c r="AU12" s="395" t="n"/>
+      <c r="AV12" s="395" t="n"/>
+      <c r="AW12" s="395" t="n"/>
+      <c r="AX12" s="395" t="n"/>
+      <c r="AY12" s="395" t="n"/>
+      <c r="AZ12" s="395" t="n"/>
+      <c r="BA12" s="395" t="n"/>
+      <c r="BB12" s="395" t="n"/>
+      <c r="BC12" s="395" t="n"/>
+      <c r="BD12" s="396" t="n"/>
     </row>
     <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="25" t="n"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="284" t="inlineStr">
+      <c r="A13" s="345" t="n"/>
+      <c r="B13" s="345" t="n"/>
+      <c r="C13" s="345" t="n"/>
+      <c r="D13" s="345" t="n"/>
+      <c r="E13" s="345" t="n"/>
+      <c r="F13" s="345" t="n"/>
+      <c r="G13" s="345" t="n"/>
+      <c r="H13" s="345" t="n"/>
+      <c r="I13" s="345" t="n"/>
+      <c r="J13" s="345" t="n"/>
+      <c r="K13" s="345" t="n"/>
+      <c r="L13" s="345" t="n"/>
+      <c r="M13" s="345" t="n"/>
+      <c r="N13" s="345" t="n"/>
+      <c r="O13" s="345" t="n"/>
+      <c r="P13" s="345" t="n"/>
+      <c r="Q13" s="345" t="n"/>
+      <c r="R13" s="345" t="n"/>
+      <c r="S13" s="345" t="n"/>
+      <c r="T13" s="345" t="n"/>
+      <c r="U13" s="345" t="n"/>
+      <c r="V13" s="345" t="n"/>
+      <c r="W13" s="345" t="n"/>
+      <c r="X13" s="345" t="n"/>
+      <c r="Y13" s="345" t="n"/>
+      <c r="Z13" s="345" t="n"/>
+      <c r="AA13" s="345" t="n"/>
+      <c r="AB13" s="345" t="n"/>
+      <c r="AC13" s="345" t="n"/>
+      <c r="AD13" s="345" t="n"/>
+      <c r="AE13" s="345" t="n"/>
+      <c r="AF13" s="345" t="n"/>
+      <c r="AG13" s="345" t="n"/>
+      <c r="AH13" s="345" t="n"/>
+      <c r="AI13" s="345" t="n"/>
+      <c r="AJ13" s="345" t="n"/>
+      <c r="AK13" s="345" t="n"/>
+      <c r="AL13" s="345" t="n"/>
+      <c r="AM13" s="345" t="n"/>
+      <c r="AN13" s="345" t="n"/>
+      <c r="AO13" s="345" t="n"/>
+      <c r="AP13" s="345" t="n"/>
+      <c r="AQ13" s="345" t="n"/>
+      <c r="AR13" s="345" t="n"/>
+      <c r="AS13" s="345" t="n"/>
+      <c r="AT13" s="345" t="n"/>
+      <c r="AU13" s="345" t="n"/>
+      <c r="AV13" s="345" t="n"/>
+      <c r="AW13" s="345" t="n"/>
+      <c r="AX13" s="345" t="n"/>
+      <c r="AY13" s="345" t="n"/>
+      <c r="AZ13" s="345" t="n"/>
+      <c r="BA13" s="345" t="n"/>
+      <c r="BB13" s="345" t="n"/>
+      <c r="BC13" s="345" t="n"/>
+      <c r="BD13" s="345" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="366" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. REVIEW SNAPSHOT / LIVE ENTRY ON GAGE_DATA_LOG</t>
         </is>
       </c>
-      <c r="B14" s="285" t="n"/>
-      <c r="C14" s="285" t="n"/>
-      <c r="D14" s="285" t="n"/>
-      <c r="E14" s="285" t="n"/>
-      <c r="F14" s="285" t="n"/>
-      <c r="G14" s="285" t="n"/>
-      <c r="H14" s="285" t="n"/>
-      <c r="I14" s="285" t="n"/>
-      <c r="J14" s="285" t="n"/>
-      <c r="K14" s="285" t="n"/>
-      <c r="L14" s="285" t="n"/>
-      <c r="M14" s="285" t="n"/>
-      <c r="N14" s="285" t="n"/>
-      <c r="O14" s="285" t="n"/>
-      <c r="P14" s="285" t="n"/>
-      <c r="Q14" s="285" t="n"/>
-      <c r="R14" s="285" t="n"/>
-      <c r="S14" s="285" t="n"/>
-      <c r="T14" s="285" t="n"/>
-      <c r="U14" s="285" t="n"/>
-      <c r="V14" s="285" t="n"/>
-      <c r="W14" s="285" t="n"/>
-      <c r="X14" s="285" t="n"/>
-      <c r="Y14" s="285" t="n"/>
-      <c r="Z14" s="285" t="n"/>
-      <c r="AA14" s="285" t="n"/>
-      <c r="AB14" s="285" t="n"/>
-      <c r="AC14" s="285" t="n"/>
-      <c r="AD14" s="285" t="n"/>
-      <c r="AE14" s="285" t="n"/>
-      <c r="AF14" s="285" t="n"/>
-      <c r="AG14" s="285" t="n"/>
-      <c r="AH14" s="285" t="n"/>
-      <c r="AI14" s="285" t="n"/>
-      <c r="AJ14" s="285" t="n"/>
-      <c r="AK14" s="285" t="n"/>
-      <c r="AL14" s="285" t="n"/>
-      <c r="AM14" s="285" t="n"/>
-      <c r="AN14" s="285" t="n"/>
-      <c r="AO14" s="285" t="n"/>
-      <c r="AP14" s="285" t="n"/>
-      <c r="AQ14" s="285" t="n"/>
-      <c r="AR14" s="285" t="n"/>
-      <c r="AS14" s="285" t="n"/>
-      <c r="AT14" s="285" t="n"/>
-      <c r="AU14" s="285" t="n"/>
-      <c r="AV14" s="285" t="n"/>
-      <c r="AW14" s="285" t="n"/>
-      <c r="AX14" s="285" t="n"/>
-      <c r="AY14" s="285" t="n"/>
-      <c r="AZ14" s="285" t="n"/>
-      <c r="BA14" s="285" t="n"/>
-      <c r="BB14" s="285" t="n"/>
-      <c r="BC14" s="285" t="n"/>
-      <c r="BD14" s="286" t="n"/>
+      <c r="B14" s="389" t="n"/>
+      <c r="C14" s="389" t="n"/>
+      <c r="D14" s="389" t="n"/>
+      <c r="E14" s="389" t="n"/>
+      <c r="F14" s="389" t="n"/>
+      <c r="G14" s="389" t="n"/>
+      <c r="H14" s="389" t="n"/>
+      <c r="I14" s="389" t="n"/>
+      <c r="J14" s="389" t="n"/>
+      <c r="K14" s="389" t="n"/>
+      <c r="L14" s="389" t="n"/>
+      <c r="M14" s="389" t="n"/>
+      <c r="N14" s="389" t="n"/>
+      <c r="O14" s="389" t="n"/>
+      <c r="P14" s="389" t="n"/>
+      <c r="Q14" s="389" t="n"/>
+      <c r="R14" s="389" t="n"/>
+      <c r="S14" s="389" t="n"/>
+      <c r="T14" s="389" t="n"/>
+      <c r="U14" s="389" t="n"/>
+      <c r="V14" s="389" t="n"/>
+      <c r="W14" s="389" t="n"/>
+      <c r="X14" s="389" t="n"/>
+      <c r="Y14" s="389" t="n"/>
+      <c r="Z14" s="389" t="n"/>
+      <c r="AA14" s="389" t="n"/>
+      <c r="AB14" s="389" t="n"/>
+      <c r="AC14" s="389" t="n"/>
+      <c r="AD14" s="389" t="n"/>
+      <c r="AE14" s="389" t="n"/>
+      <c r="AF14" s="389" t="n"/>
+      <c r="AG14" s="389" t="n"/>
+      <c r="AH14" s="389" t="n"/>
+      <c r="AI14" s="389" t="n"/>
+      <c r="AJ14" s="389" t="n"/>
+      <c r="AK14" s="389" t="n"/>
+      <c r="AL14" s="389" t="n"/>
+      <c r="AM14" s="389" t="n"/>
+      <c r="AN14" s="389" t="n"/>
+      <c r="AO14" s="389" t="n"/>
+      <c r="AP14" s="389" t="n"/>
+      <c r="AQ14" s="389" t="n"/>
+      <c r="AR14" s="389" t="n"/>
+      <c r="AS14" s="389" t="n"/>
+      <c r="AT14" s="389" t="n"/>
+      <c r="AU14" s="389" t="n"/>
+      <c r="AV14" s="389" t="n"/>
+      <c r="AW14" s="389" t="n"/>
+      <c r="AX14" s="389" t="n"/>
+      <c r="AY14" s="389" t="n"/>
+      <c r="AZ14" s="389" t="n"/>
+      <c r="BA14" s="389" t="n"/>
+      <c r="BB14" s="389" t="n"/>
+      <c r="BC14" s="389" t="n"/>
+      <c r="BD14" s="390" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="291" t="inlineStr">
+      <c r="A15" s="347" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="285" t="n"/>
-      <c r="C15" s="286" t="n"/>
-      <c r="D15" s="291" t="inlineStr">
+      <c r="B15" s="389" t="n"/>
+      <c r="C15" s="390" t="n"/>
+      <c r="D15" s="347" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E15" s="285" t="n"/>
-      <c r="F15" s="285" t="n"/>
-      <c r="G15" s="285" t="n"/>
-      <c r="H15" s="286" t="n"/>
-      <c r="I15" s="291" t="inlineStr">
+      <c r="E15" s="389" t="n"/>
+      <c r="F15" s="389" t="n"/>
+      <c r="G15" s="389" t="n"/>
+      <c r="H15" s="390" t="n"/>
+      <c r="I15" s="347" t="inlineStr">
         <is>
           <t>Gage ID</t>
         </is>
       </c>
-      <c r="J15" s="285" t="n"/>
-      <c r="K15" s="285" t="n"/>
-      <c r="L15" s="285" t="n"/>
-      <c r="M15" s="286" t="n"/>
-      <c r="N15" s="291" t="inlineStr">
+      <c r="J15" s="389" t="n"/>
+      <c r="K15" s="389" t="n"/>
+      <c r="L15" s="389" t="n"/>
+      <c r="M15" s="390" t="n"/>
+      <c r="N15" s="347" t="inlineStr">
         <is>
           <t>Verification Type</t>
         </is>
       </c>
-      <c r="O15" s="285" t="n"/>
-      <c r="P15" s="285" t="n"/>
-      <c r="Q15" s="285" t="n"/>
-      <c r="R15" s="285" t="n"/>
-      <c r="S15" s="285" t="n"/>
-      <c r="T15" s="286" t="n"/>
-      <c r="U15" s="291" t="inlineStr">
+      <c r="O15" s="389" t="n"/>
+      <c r="P15" s="389" t="n"/>
+      <c r="Q15" s="389" t="n"/>
+      <c r="R15" s="389" t="n"/>
+      <c r="S15" s="389" t="n"/>
+      <c r="T15" s="390" t="n"/>
+      <c r="U15" s="347" t="inlineStr">
         <is>
           <t>Check Artifact / Master</t>
         </is>
       </c>
-      <c r="V15" s="285" t="n"/>
-      <c r="W15" s="285" t="n"/>
-      <c r="X15" s="285" t="n"/>
-      <c r="Y15" s="285" t="n"/>
-      <c r="Z15" s="286" t="n"/>
-      <c r="AA15" s="291" t="inlineStr">
+      <c r="V15" s="389" t="n"/>
+      <c r="W15" s="389" t="n"/>
+      <c r="X15" s="389" t="n"/>
+      <c r="Y15" s="389" t="n"/>
+      <c r="Z15" s="390" t="n"/>
+      <c r="AA15" s="347" t="inlineStr">
         <is>
           <t>Criteria</t>
         </is>
       </c>
-      <c r="AB15" s="285" t="n"/>
-      <c r="AC15" s="285" t="n"/>
-      <c r="AD15" s="285" t="n"/>
-      <c r="AE15" s="285" t="n"/>
-      <c r="AF15" s="285" t="n"/>
-      <c r="AG15" s="286" t="n"/>
-      <c r="AH15" s="291" t="inlineStr">
+      <c r="AB15" s="389" t="n"/>
+      <c r="AC15" s="389" t="n"/>
+      <c r="AD15" s="389" t="n"/>
+      <c r="AE15" s="389" t="n"/>
+      <c r="AF15" s="389" t="n"/>
+      <c r="AG15" s="390" t="n"/>
+      <c r="AH15" s="347" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AI15" s="285" t="n"/>
-      <c r="AJ15" s="285" t="n"/>
-      <c r="AK15" s="286" t="n"/>
-      <c r="AL15" s="291" t="inlineStr">
+      <c r="AI15" s="389" t="n"/>
+      <c r="AJ15" s="389" t="n"/>
+      <c r="AK15" s="390" t="n"/>
+      <c r="AL15" s="347" t="inlineStr">
         <is>
           <t>CAL Status</t>
         </is>
       </c>
-      <c r="AM15" s="285" t="n"/>
-      <c r="AN15" s="285" t="n"/>
-      <c r="AO15" s="286" t="n"/>
-      <c r="AP15" s="291" t="inlineStr">
+      <c r="AM15" s="389" t="n"/>
+      <c r="AN15" s="389" t="n"/>
+      <c r="AO15" s="390" t="n"/>
+      <c r="AP15" s="347" t="inlineStr">
         <is>
           <t>Use Stop (Y/N)</t>
         </is>
       </c>
-      <c r="AQ15" s="285" t="n"/>
-      <c r="AR15" s="285" t="n"/>
-      <c r="AS15" s="286" t="n"/>
-      <c r="AT15" s="291" t="inlineStr">
+      <c r="AQ15" s="389" t="n"/>
+      <c r="AR15" s="389" t="n"/>
+      <c r="AS15" s="390" t="n"/>
+      <c r="AT15" s="347" t="inlineStr">
         <is>
           <t>Owner Dept</t>
         </is>
       </c>
-      <c r="AU15" s="285" t="n"/>
-      <c r="AV15" s="285" t="n"/>
-      <c r="AW15" s="286" t="n"/>
-      <c r="AX15" s="291" t="inlineStr">
+      <c r="AU15" s="389" t="n"/>
+      <c r="AV15" s="389" t="n"/>
+      <c r="AW15" s="390" t="n"/>
+      <c r="AX15" s="347" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AY15" s="285" t="n"/>
-      <c r="AZ15" s="285" t="n"/>
-      <c r="BA15" s="285" t="n"/>
-      <c r="BB15" s="285" t="n"/>
-      <c r="BC15" s="285" t="n"/>
-      <c r="BD15" s="286" t="n"/>
+      <c r="AY15" s="389" t="n"/>
+      <c r="AZ15" s="389" t="n"/>
+      <c r="BA15" s="389" t="n"/>
+      <c r="BB15" s="389" t="n"/>
+      <c r="BC15" s="389" t="n"/>
+      <c r="BD15" s="390" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="293" t="n"/>
-      <c r="B16" s="322" t="n"/>
-      <c r="C16" s="323" t="n"/>
-      <c r="D16" s="294" t="n"/>
-      <c r="E16" s="324" t="n"/>
-      <c r="F16" s="324" t="n"/>
-      <c r="G16" s="324" t="n"/>
-      <c r="H16" s="325" t="n"/>
-      <c r="I16" s="294" t="n"/>
-      <c r="J16" s="324" t="n"/>
-      <c r="K16" s="324" t="n"/>
-      <c r="L16" s="324" t="n"/>
-      <c r="M16" s="325" t="n"/>
-      <c r="N16" s="294" t="n"/>
-      <c r="O16" s="324" t="n"/>
-      <c r="P16" s="324" t="n"/>
-      <c r="Q16" s="324" t="n"/>
-      <c r="R16" s="324" t="n"/>
-      <c r="S16" s="324" t="n"/>
-      <c r="T16" s="325" t="n"/>
-      <c r="U16" s="294" t="n"/>
-      <c r="V16" s="324" t="n"/>
-      <c r="W16" s="324" t="n"/>
-      <c r="X16" s="324" t="n"/>
-      <c r="Y16" s="324" t="n"/>
-      <c r="Z16" s="325" t="n"/>
-      <c r="AA16" s="294" t="n"/>
-      <c r="AB16" s="324" t="n"/>
-      <c r="AC16" s="324" t="n"/>
-      <c r="AD16" s="324" t="n"/>
-      <c r="AE16" s="324" t="n"/>
-      <c r="AF16" s="324" t="n"/>
-      <c r="AG16" s="325" t="n"/>
-      <c r="AH16" s="294" t="n"/>
-      <c r="AI16" s="324" t="n"/>
-      <c r="AJ16" s="324" t="n"/>
-      <c r="AK16" s="325" t="n"/>
-      <c r="AL16" s="294" t="n"/>
-      <c r="AM16" s="324" t="n"/>
-      <c r="AN16" s="324" t="n"/>
-      <c r="AO16" s="325" t="n"/>
-      <c r="AP16" s="294" t="n"/>
-      <c r="AQ16" s="324" t="n"/>
-      <c r="AR16" s="324" t="n"/>
-      <c r="AS16" s="325" t="n"/>
-      <c r="AT16" s="294" t="n"/>
-      <c r="AU16" s="324" t="n"/>
-      <c r="AV16" s="324" t="n"/>
-      <c r="AW16" s="325" t="n"/>
-      <c r="AX16" s="294" t="n"/>
-      <c r="AY16" s="324" t="n"/>
-      <c r="AZ16" s="324" t="n"/>
-      <c r="BA16" s="324" t="n"/>
-      <c r="BB16" s="324" t="n"/>
-      <c r="BC16" s="324" t="n"/>
-      <c r="BD16" s="325" t="n"/>
+      <c r="A16" s="373" t="n"/>
+      <c r="B16" s="389" t="n"/>
+      <c r="C16" s="390" t="n"/>
+      <c r="D16" s="374" t="n"/>
+      <c r="E16" s="395" t="n"/>
+      <c r="F16" s="395" t="n"/>
+      <c r="G16" s="395" t="n"/>
+      <c r="H16" s="396" t="n"/>
+      <c r="I16" s="374" t="n"/>
+      <c r="J16" s="395" t="n"/>
+      <c r="K16" s="395" t="n"/>
+      <c r="L16" s="395" t="n"/>
+      <c r="M16" s="396" t="n"/>
+      <c r="N16" s="374" t="n"/>
+      <c r="O16" s="395" t="n"/>
+      <c r="P16" s="395" t="n"/>
+      <c r="Q16" s="395" t="n"/>
+      <c r="R16" s="395" t="n"/>
+      <c r="S16" s="395" t="n"/>
+      <c r="T16" s="396" t="n"/>
+      <c r="U16" s="374" t="n"/>
+      <c r="V16" s="395" t="n"/>
+      <c r="W16" s="395" t="n"/>
+      <c r="X16" s="395" t="n"/>
+      <c r="Y16" s="395" t="n"/>
+      <c r="Z16" s="396" t="n"/>
+      <c r="AA16" s="374" t="n"/>
+      <c r="AB16" s="395" t="n"/>
+      <c r="AC16" s="395" t="n"/>
+      <c r="AD16" s="395" t="n"/>
+      <c r="AE16" s="395" t="n"/>
+      <c r="AF16" s="395" t="n"/>
+      <c r="AG16" s="396" t="n"/>
+      <c r="AH16" s="374" t="n"/>
+      <c r="AI16" s="395" t="n"/>
+      <c r="AJ16" s="395" t="n"/>
+      <c r="AK16" s="396" t="n"/>
+      <c r="AL16" s="374" t="n"/>
+      <c r="AM16" s="395" t="n"/>
+      <c r="AN16" s="395" t="n"/>
+      <c r="AO16" s="396" t="n"/>
+      <c r="AP16" s="374" t="n"/>
+      <c r="AQ16" s="395" t="n"/>
+      <c r="AR16" s="395" t="n"/>
+      <c r="AS16" s="396" t="n"/>
+      <c r="AT16" s="374" t="n"/>
+      <c r="AU16" s="395" t="n"/>
+      <c r="AV16" s="395" t="n"/>
+      <c r="AW16" s="396" t="n"/>
+      <c r="AX16" s="374" t="n"/>
+      <c r="AY16" s="395" t="n"/>
+      <c r="AZ16" s="395" t="n"/>
+      <c r="BA16" s="395" t="n"/>
+      <c r="BB16" s="395" t="n"/>
+      <c r="BC16" s="395" t="n"/>
+      <c r="BD16" s="396" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="293" t="n"/>
-      <c r="B17" s="322" t="n"/>
-      <c r="C17" s="323" t="n"/>
-      <c r="D17" s="294" t="n"/>
-      <c r="E17" s="324" t="n"/>
-      <c r="F17" s="324" t="n"/>
-      <c r="G17" s="324" t="n"/>
-      <c r="H17" s="325" t="n"/>
-      <c r="I17" s="294" t="n"/>
-      <c r="J17" s="324" t="n"/>
-      <c r="K17" s="324" t="n"/>
-      <c r="L17" s="324" t="n"/>
-      <c r="M17" s="325" t="n"/>
-      <c r="N17" s="294" t="n"/>
-      <c r="O17" s="324" t="n"/>
-      <c r="P17" s="324" t="n"/>
-      <c r="Q17" s="324" t="n"/>
-      <c r="R17" s="324" t="n"/>
-      <c r="S17" s="324" t="n"/>
-      <c r="T17" s="325" t="n"/>
-      <c r="U17" s="294" t="n"/>
-      <c r="V17" s="324" t="n"/>
-      <c r="W17" s="324" t="n"/>
-      <c r="X17" s="324" t="n"/>
-      <c r="Y17" s="324" t="n"/>
-      <c r="Z17" s="325" t="n"/>
-      <c r="AA17" s="294" t="n"/>
-      <c r="AB17" s="324" t="n"/>
-      <c r="AC17" s="324" t="n"/>
-      <c r="AD17" s="324" t="n"/>
-      <c r="AE17" s="324" t="n"/>
-      <c r="AF17" s="324" t="n"/>
-      <c r="AG17" s="325" t="n"/>
-      <c r="AH17" s="294" t="n"/>
-      <c r="AI17" s="324" t="n"/>
-      <c r="AJ17" s="324" t="n"/>
-      <c r="AK17" s="325" t="n"/>
-      <c r="AL17" s="294" t="n"/>
-      <c r="AM17" s="324" t="n"/>
-      <c r="AN17" s="324" t="n"/>
-      <c r="AO17" s="325" t="n"/>
-      <c r="AP17" s="294" t="n"/>
-      <c r="AQ17" s="324" t="n"/>
-      <c r="AR17" s="324" t="n"/>
-      <c r="AS17" s="325" t="n"/>
-      <c r="AT17" s="294" t="n"/>
-      <c r="AU17" s="324" t="n"/>
-      <c r="AV17" s="324" t="n"/>
-      <c r="AW17" s="325" t="n"/>
-      <c r="AX17" s="294" t="n"/>
-      <c r="AY17" s="324" t="n"/>
-      <c r="AZ17" s="324" t="n"/>
-      <c r="BA17" s="324" t="n"/>
-      <c r="BB17" s="324" t="n"/>
-      <c r="BC17" s="324" t="n"/>
-      <c r="BD17" s="325" t="n"/>
+      <c r="A17" s="373" t="n"/>
+      <c r="B17" s="389" t="n"/>
+      <c r="C17" s="390" t="n"/>
+      <c r="D17" s="374" t="n"/>
+      <c r="E17" s="395" t="n"/>
+      <c r="F17" s="395" t="n"/>
+      <c r="G17" s="395" t="n"/>
+      <c r="H17" s="396" t="n"/>
+      <c r="I17" s="374" t="n"/>
+      <c r="J17" s="395" t="n"/>
+      <c r="K17" s="395" t="n"/>
+      <c r="L17" s="395" t="n"/>
+      <c r="M17" s="396" t="n"/>
+      <c r="N17" s="374" t="n"/>
+      <c r="O17" s="395" t="n"/>
+      <c r="P17" s="395" t="n"/>
+      <c r="Q17" s="395" t="n"/>
+      <c r="R17" s="395" t="n"/>
+      <c r="S17" s="395" t="n"/>
+      <c r="T17" s="396" t="n"/>
+      <c r="U17" s="374" t="n"/>
+      <c r="V17" s="395" t="n"/>
+      <c r="W17" s="395" t="n"/>
+      <c r="X17" s="395" t="n"/>
+      <c r="Y17" s="395" t="n"/>
+      <c r="Z17" s="396" t="n"/>
+      <c r="AA17" s="374" t="n"/>
+      <c r="AB17" s="395" t="n"/>
+      <c r="AC17" s="395" t="n"/>
+      <c r="AD17" s="395" t="n"/>
+      <c r="AE17" s="395" t="n"/>
+      <c r="AF17" s="395" t="n"/>
+      <c r="AG17" s="396" t="n"/>
+      <c r="AH17" s="374" t="n"/>
+      <c r="AI17" s="395" t="n"/>
+      <c r="AJ17" s="395" t="n"/>
+      <c r="AK17" s="396" t="n"/>
+      <c r="AL17" s="374" t="n"/>
+      <c r="AM17" s="395" t="n"/>
+      <c r="AN17" s="395" t="n"/>
+      <c r="AO17" s="396" t="n"/>
+      <c r="AP17" s="374" t="n"/>
+      <c r="AQ17" s="395" t="n"/>
+      <c r="AR17" s="395" t="n"/>
+      <c r="AS17" s="396" t="n"/>
+      <c r="AT17" s="374" t="n"/>
+      <c r="AU17" s="395" t="n"/>
+      <c r="AV17" s="395" t="n"/>
+      <c r="AW17" s="396" t="n"/>
+      <c r="AX17" s="374" t="n"/>
+      <c r="AY17" s="395" t="n"/>
+      <c r="AZ17" s="395" t="n"/>
+      <c r="BA17" s="395" t="n"/>
+      <c r="BB17" s="395" t="n"/>
+      <c r="BC17" s="395" t="n"/>
+      <c r="BD17" s="396" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="293" t="n"/>
-      <c r="B18" s="322" t="n"/>
-      <c r="C18" s="323" t="n"/>
-      <c r="D18" s="294" t="n"/>
-      <c r="E18" s="324" t="n"/>
-      <c r="F18" s="324" t="n"/>
-      <c r="G18" s="324" t="n"/>
-      <c r="H18" s="325" t="n"/>
-      <c r="I18" s="294" t="n"/>
-      <c r="J18" s="324" t="n"/>
-      <c r="K18" s="324" t="n"/>
-      <c r="L18" s="324" t="n"/>
-      <c r="M18" s="325" t="n"/>
-      <c r="N18" s="294" t="n"/>
-      <c r="O18" s="324" t="n"/>
-      <c r="P18" s="324" t="n"/>
-      <c r="Q18" s="324" t="n"/>
-      <c r="R18" s="324" t="n"/>
-      <c r="S18" s="324" t="n"/>
-      <c r="T18" s="325" t="n"/>
-      <c r="U18" s="294" t="n"/>
-      <c r="V18" s="324" t="n"/>
-      <c r="W18" s="324" t="n"/>
-      <c r="X18" s="324" t="n"/>
-      <c r="Y18" s="324" t="n"/>
-      <c r="Z18" s="325" t="n"/>
-      <c r="AA18" s="294" t="n"/>
-      <c r="AB18" s="324" t="n"/>
-      <c r="AC18" s="324" t="n"/>
-      <c r="AD18" s="324" t="n"/>
-      <c r="AE18" s="324" t="n"/>
-      <c r="AF18" s="324" t="n"/>
-      <c r="AG18" s="325" t="n"/>
-      <c r="AH18" s="294" t="n"/>
-      <c r="AI18" s="324" t="n"/>
-      <c r="AJ18" s="324" t="n"/>
-      <c r="AK18" s="325" t="n"/>
-      <c r="AL18" s="294" t="n"/>
-      <c r="AM18" s="324" t="n"/>
-      <c r="AN18" s="324" t="n"/>
-      <c r="AO18" s="325" t="n"/>
-      <c r="AP18" s="294" t="n"/>
-      <c r="AQ18" s="324" t="n"/>
-      <c r="AR18" s="324" t="n"/>
-      <c r="AS18" s="325" t="n"/>
-      <c r="AT18" s="294" t="n"/>
-      <c r="AU18" s="324" t="n"/>
-      <c r="AV18" s="324" t="n"/>
-      <c r="AW18" s="325" t="n"/>
-      <c r="AX18" s="294" t="n"/>
-      <c r="AY18" s="324" t="n"/>
-      <c r="AZ18" s="324" t="n"/>
-      <c r="BA18" s="324" t="n"/>
-      <c r="BB18" s="324" t="n"/>
-      <c r="BC18" s="324" t="n"/>
-      <c r="BD18" s="325" t="n"/>
+      <c r="A18" s="373" t="n"/>
+      <c r="B18" s="389" t="n"/>
+      <c r="C18" s="390" t="n"/>
+      <c r="D18" s="374" t="n"/>
+      <c r="E18" s="395" t="n"/>
+      <c r="F18" s="395" t="n"/>
+      <c r="G18" s="395" t="n"/>
+      <c r="H18" s="396" t="n"/>
+      <c r="I18" s="374" t="n"/>
+      <c r="J18" s="395" t="n"/>
+      <c r="K18" s="395" t="n"/>
+      <c r="L18" s="395" t="n"/>
+      <c r="M18" s="396" t="n"/>
+      <c r="N18" s="374" t="n"/>
+      <c r="O18" s="395" t="n"/>
+      <c r="P18" s="395" t="n"/>
+      <c r="Q18" s="395" t="n"/>
+      <c r="R18" s="395" t="n"/>
+      <c r="S18" s="395" t="n"/>
+      <c r="T18" s="396" t="n"/>
+      <c r="U18" s="374" t="n"/>
+      <c r="V18" s="395" t="n"/>
+      <c r="W18" s="395" t="n"/>
+      <c r="X18" s="395" t="n"/>
+      <c r="Y18" s="395" t="n"/>
+      <c r="Z18" s="396" t="n"/>
+      <c r="AA18" s="374" t="n"/>
+      <c r="AB18" s="395" t="n"/>
+      <c r="AC18" s="395" t="n"/>
+      <c r="AD18" s="395" t="n"/>
+      <c r="AE18" s="395" t="n"/>
+      <c r="AF18" s="395" t="n"/>
+      <c r="AG18" s="396" t="n"/>
+      <c r="AH18" s="374" t="n"/>
+      <c r="AI18" s="395" t="n"/>
+      <c r="AJ18" s="395" t="n"/>
+      <c r="AK18" s="396" t="n"/>
+      <c r="AL18" s="374" t="n"/>
+      <c r="AM18" s="395" t="n"/>
+      <c r="AN18" s="395" t="n"/>
+      <c r="AO18" s="396" t="n"/>
+      <c r="AP18" s="374" t="n"/>
+      <c r="AQ18" s="395" t="n"/>
+      <c r="AR18" s="395" t="n"/>
+      <c r="AS18" s="396" t="n"/>
+      <c r="AT18" s="374" t="n"/>
+      <c r="AU18" s="395" t="n"/>
+      <c r="AV18" s="395" t="n"/>
+      <c r="AW18" s="396" t="n"/>
+      <c r="AX18" s="374" t="n"/>
+      <c r="AY18" s="395" t="n"/>
+      <c r="AZ18" s="395" t="n"/>
+      <c r="BA18" s="395" t="n"/>
+      <c r="BB18" s="395" t="n"/>
+      <c r="BC18" s="395" t="n"/>
+      <c r="BD18" s="396" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="293" t="n"/>
-      <c r="B19" s="322" t="n"/>
-      <c r="C19" s="323" t="n"/>
-      <c r="D19" s="294" t="n"/>
-      <c r="E19" s="324" t="n"/>
-      <c r="F19" s="324" t="n"/>
-      <c r="G19" s="324" t="n"/>
-      <c r="H19" s="325" t="n"/>
-      <c r="I19" s="294" t="n"/>
-      <c r="J19" s="324" t="n"/>
-      <c r="K19" s="324" t="n"/>
-      <c r="L19" s="324" t="n"/>
-      <c r="M19" s="325" t="n"/>
-      <c r="N19" s="294" t="n"/>
-      <c r="O19" s="324" t="n"/>
-      <c r="P19" s="324" t="n"/>
-      <c r="Q19" s="324" t="n"/>
-      <c r="R19" s="324" t="n"/>
-      <c r="S19" s="324" t="n"/>
-      <c r="T19" s="325" t="n"/>
-      <c r="U19" s="294" t="n"/>
-      <c r="V19" s="324" t="n"/>
-      <c r="W19" s="324" t="n"/>
-      <c r="X19" s="324" t="n"/>
-      <c r="Y19" s="324" t="n"/>
-      <c r="Z19" s="325" t="n"/>
-      <c r="AA19" s="294" t="n"/>
-      <c r="AB19" s="324" t="n"/>
-      <c r="AC19" s="324" t="n"/>
-      <c r="AD19" s="324" t="n"/>
-      <c r="AE19" s="324" t="n"/>
-      <c r="AF19" s="324" t="n"/>
-      <c r="AG19" s="325" t="n"/>
-      <c r="AH19" s="294" t="n"/>
-      <c r="AI19" s="324" t="n"/>
-      <c r="AJ19" s="324" t="n"/>
-      <c r="AK19" s="325" t="n"/>
-      <c r="AL19" s="294" t="n"/>
-      <c r="AM19" s="324" t="n"/>
-      <c r="AN19" s="324" t="n"/>
-      <c r="AO19" s="325" t="n"/>
-      <c r="AP19" s="294" t="n"/>
-      <c r="AQ19" s="324" t="n"/>
-      <c r="AR19" s="324" t="n"/>
-      <c r="AS19" s="325" t="n"/>
-      <c r="AT19" s="294" t="n"/>
-      <c r="AU19" s="324" t="n"/>
-      <c r="AV19" s="324" t="n"/>
-      <c r="AW19" s="325" t="n"/>
-      <c r="AX19" s="294" t="n"/>
-      <c r="AY19" s="324" t="n"/>
-      <c r="AZ19" s="324" t="n"/>
-      <c r="BA19" s="324" t="n"/>
-      <c r="BB19" s="324" t="n"/>
-      <c r="BC19" s="324" t="n"/>
-      <c r="BD19" s="325" t="n"/>
+      <c r="A19" s="373" t="n"/>
+      <c r="B19" s="389" t="n"/>
+      <c r="C19" s="390" t="n"/>
+      <c r="D19" s="374" t="n"/>
+      <c r="E19" s="395" t="n"/>
+      <c r="F19" s="395" t="n"/>
+      <c r="G19" s="395" t="n"/>
+      <c r="H19" s="396" t="n"/>
+      <c r="I19" s="374" t="n"/>
+      <c r="J19" s="395" t="n"/>
+      <c r="K19" s="395" t="n"/>
+      <c r="L19" s="395" t="n"/>
+      <c r="M19" s="396" t="n"/>
+      <c r="N19" s="374" t="n"/>
+      <c r="O19" s="395" t="n"/>
+      <c r="P19" s="395" t="n"/>
+      <c r="Q19" s="395" t="n"/>
+      <c r="R19" s="395" t="n"/>
+      <c r="S19" s="395" t="n"/>
+      <c r="T19" s="396" t="n"/>
+      <c r="U19" s="374" t="n"/>
+      <c r="V19" s="395" t="n"/>
+      <c r="W19" s="395" t="n"/>
+      <c r="X19" s="395" t="n"/>
+      <c r="Y19" s="395" t="n"/>
+      <c r="Z19" s="396" t="n"/>
+      <c r="AA19" s="374" t="n"/>
+      <c r="AB19" s="395" t="n"/>
+      <c r="AC19" s="395" t="n"/>
+      <c r="AD19" s="395" t="n"/>
+      <c r="AE19" s="395" t="n"/>
+      <c r="AF19" s="395" t="n"/>
+      <c r="AG19" s="396" t="n"/>
+      <c r="AH19" s="374" t="n"/>
+      <c r="AI19" s="395" t="n"/>
+      <c r="AJ19" s="395" t="n"/>
+      <c r="AK19" s="396" t="n"/>
+      <c r="AL19" s="374" t="n"/>
+      <c r="AM19" s="395" t="n"/>
+      <c r="AN19" s="395" t="n"/>
+      <c r="AO19" s="396" t="n"/>
+      <c r="AP19" s="374" t="n"/>
+      <c r="AQ19" s="395" t="n"/>
+      <c r="AR19" s="395" t="n"/>
+      <c r="AS19" s="396" t="n"/>
+      <c r="AT19" s="374" t="n"/>
+      <c r="AU19" s="395" t="n"/>
+      <c r="AV19" s="395" t="n"/>
+      <c r="AW19" s="396" t="n"/>
+      <c r="AX19" s="374" t="n"/>
+      <c r="AY19" s="395" t="n"/>
+      <c r="AZ19" s="395" t="n"/>
+      <c r="BA19" s="395" t="n"/>
+      <c r="BB19" s="395" t="n"/>
+      <c r="BC19" s="395" t="n"/>
+      <c r="BD19" s="396" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="293" t="n"/>
-      <c r="B20" s="322" t="n"/>
-      <c r="C20" s="323" t="n"/>
-      <c r="D20" s="294" t="n"/>
-      <c r="E20" s="324" t="n"/>
-      <c r="F20" s="324" t="n"/>
-      <c r="G20" s="324" t="n"/>
-      <c r="H20" s="325" t="n"/>
-      <c r="I20" s="294" t="n"/>
-      <c r="J20" s="324" t="n"/>
-      <c r="K20" s="324" t="n"/>
-      <c r="L20" s="324" t="n"/>
-      <c r="M20" s="325" t="n"/>
-      <c r="N20" s="294" t="n"/>
-      <c r="O20" s="324" t="n"/>
-      <c r="P20" s="324" t="n"/>
-      <c r="Q20" s="324" t="n"/>
-      <c r="R20" s="324" t="n"/>
-      <c r="S20" s="324" t="n"/>
-      <c r="T20" s="325" t="n"/>
-      <c r="U20" s="294" t="n"/>
-      <c r="V20" s="324" t="n"/>
-      <c r="W20" s="324" t="n"/>
-      <c r="X20" s="324" t="n"/>
-      <c r="Y20" s="324" t="n"/>
-      <c r="Z20" s="325" t="n"/>
-      <c r="AA20" s="294" t="n"/>
-      <c r="AB20" s="324" t="n"/>
-      <c r="AC20" s="324" t="n"/>
-      <c r="AD20" s="324" t="n"/>
-      <c r="AE20" s="324" t="n"/>
-      <c r="AF20" s="324" t="n"/>
-      <c r="AG20" s="325" t="n"/>
-      <c r="AH20" s="294" t="n"/>
-      <c r="AI20" s="324" t="n"/>
-      <c r="AJ20" s="324" t="n"/>
-      <c r="AK20" s="325" t="n"/>
-      <c r="AL20" s="294" t="n"/>
-      <c r="AM20" s="324" t="n"/>
-      <c r="AN20" s="324" t="n"/>
-      <c r="AO20" s="325" t="n"/>
-      <c r="AP20" s="294" t="n"/>
-      <c r="AQ20" s="324" t="n"/>
-      <c r="AR20" s="324" t="n"/>
-      <c r="AS20" s="325" t="n"/>
-      <c r="AT20" s="294" t="n"/>
-      <c r="AU20" s="324" t="n"/>
-      <c r="AV20" s="324" t="n"/>
-      <c r="AW20" s="325" t="n"/>
-      <c r="AX20" s="294" t="n"/>
-      <c r="AY20" s="324" t="n"/>
-      <c r="AZ20" s="324" t="n"/>
-      <c r="BA20" s="324" t="n"/>
-      <c r="BB20" s="324" t="n"/>
-      <c r="BC20" s="324" t="n"/>
-      <c r="BD20" s="325" t="n"/>
+      <c r="A20" s="373" t="n"/>
+      <c r="B20" s="389" t="n"/>
+      <c r="C20" s="390" t="n"/>
+      <c r="D20" s="374" t="n"/>
+      <c r="E20" s="395" t="n"/>
+      <c r="F20" s="395" t="n"/>
+      <c r="G20" s="395" t="n"/>
+      <c r="H20" s="396" t="n"/>
+      <c r="I20" s="374" t="n"/>
+      <c r="J20" s="395" t="n"/>
+      <c r="K20" s="395" t="n"/>
+      <c r="L20" s="395" t="n"/>
+      <c r="M20" s="396" t="n"/>
+      <c r="N20" s="374" t="n"/>
+      <c r="O20" s="395" t="n"/>
+      <c r="P20" s="395" t="n"/>
+      <c r="Q20" s="395" t="n"/>
+      <c r="R20" s="395" t="n"/>
+      <c r="S20" s="395" t="n"/>
+      <c r="T20" s="396" t="n"/>
+      <c r="U20" s="374" t="n"/>
+      <c r="V20" s="395" t="n"/>
+      <c r="W20" s="395" t="n"/>
+      <c r="X20" s="395" t="n"/>
+      <c r="Y20" s="395" t="n"/>
+      <c r="Z20" s="396" t="n"/>
+      <c r="AA20" s="374" t="n"/>
+      <c r="AB20" s="395" t="n"/>
+      <c r="AC20" s="395" t="n"/>
+      <c r="AD20" s="395" t="n"/>
+      <c r="AE20" s="395" t="n"/>
+      <c r="AF20" s="395" t="n"/>
+      <c r="AG20" s="396" t="n"/>
+      <c r="AH20" s="374" t="n"/>
+      <c r="AI20" s="395" t="n"/>
+      <c r="AJ20" s="395" t="n"/>
+      <c r="AK20" s="396" t="n"/>
+      <c r="AL20" s="374" t="n"/>
+      <c r="AM20" s="395" t="n"/>
+      <c r="AN20" s="395" t="n"/>
+      <c r="AO20" s="396" t="n"/>
+      <c r="AP20" s="374" t="n"/>
+      <c r="AQ20" s="395" t="n"/>
+      <c r="AR20" s="395" t="n"/>
+      <c r="AS20" s="396" t="n"/>
+      <c r="AT20" s="374" t="n"/>
+      <c r="AU20" s="395" t="n"/>
+      <c r="AV20" s="395" t="n"/>
+      <c r="AW20" s="396" t="n"/>
+      <c r="AX20" s="374" t="n"/>
+      <c r="AY20" s="395" t="n"/>
+      <c r="AZ20" s="395" t="n"/>
+      <c r="BA20" s="395" t="n"/>
+      <c r="BB20" s="395" t="n"/>
+      <c r="BC20" s="395" t="n"/>
+      <c r="BD20" s="396" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="293" t="n"/>
-      <c r="B21" s="322" t="n"/>
-      <c r="C21" s="323" t="n"/>
-      <c r="D21" s="294" t="n"/>
-      <c r="E21" s="324" t="n"/>
-      <c r="F21" s="324" t="n"/>
-      <c r="G21" s="324" t="n"/>
-      <c r="H21" s="325" t="n"/>
-      <c r="I21" s="294" t="n"/>
-      <c r="J21" s="324" t="n"/>
-      <c r="K21" s="324" t="n"/>
-      <c r="L21" s="324" t="n"/>
-      <c r="M21" s="325" t="n"/>
-      <c r="N21" s="294" t="n"/>
-      <c r="O21" s="324" t="n"/>
-      <c r="P21" s="324" t="n"/>
-      <c r="Q21" s="324" t="n"/>
-      <c r="R21" s="324" t="n"/>
-      <c r="S21" s="324" t="n"/>
-      <c r="T21" s="325" t="n"/>
-      <c r="U21" s="294" t="n"/>
-      <c r="V21" s="324" t="n"/>
-      <c r="W21" s="324" t="n"/>
-      <c r="X21" s="324" t="n"/>
-      <c r="Y21" s="324" t="n"/>
-      <c r="Z21" s="325" t="n"/>
-      <c r="AA21" s="294" t="n"/>
-      <c r="AB21" s="324" t="n"/>
-      <c r="AC21" s="324" t="n"/>
-      <c r="AD21" s="324" t="n"/>
-      <c r="AE21" s="324" t="n"/>
-      <c r="AF21" s="324" t="n"/>
-      <c r="AG21" s="325" t="n"/>
-      <c r="AH21" s="294" t="n"/>
-      <c r="AI21" s="324" t="n"/>
-      <c r="AJ21" s="324" t="n"/>
-      <c r="AK21" s="325" t="n"/>
-      <c r="AL21" s="294" t="n"/>
-      <c r="AM21" s="324" t="n"/>
-      <c r="AN21" s="324" t="n"/>
-      <c r="AO21" s="325" t="n"/>
-      <c r="AP21" s="294" t="n"/>
-      <c r="AQ21" s="324" t="n"/>
-      <c r="AR21" s="324" t="n"/>
-      <c r="AS21" s="325" t="n"/>
-      <c r="AT21" s="294" t="n"/>
-      <c r="AU21" s="324" t="n"/>
-      <c r="AV21" s="324" t="n"/>
-      <c r="AW21" s="325" t="n"/>
-      <c r="AX21" s="294" t="n"/>
-      <c r="AY21" s="324" t="n"/>
-      <c r="AZ21" s="324" t="n"/>
-      <c r="BA21" s="324" t="n"/>
-      <c r="BB21" s="324" t="n"/>
-      <c r="BC21" s="324" t="n"/>
-      <c r="BD21" s="325" t="n"/>
+      <c r="A21" s="373" t="n"/>
+      <c r="B21" s="389" t="n"/>
+      <c r="C21" s="390" t="n"/>
+      <c r="D21" s="374" t="n"/>
+      <c r="E21" s="395" t="n"/>
+      <c r="F21" s="395" t="n"/>
+      <c r="G21" s="395" t="n"/>
+      <c r="H21" s="396" t="n"/>
+      <c r="I21" s="374" t="n"/>
+      <c r="J21" s="395" t="n"/>
+      <c r="K21" s="395" t="n"/>
+      <c r="L21" s="395" t="n"/>
+      <c r="M21" s="396" t="n"/>
+      <c r="N21" s="374" t="n"/>
+      <c r="O21" s="395" t="n"/>
+      <c r="P21" s="395" t="n"/>
+      <c r="Q21" s="395" t="n"/>
+      <c r="R21" s="395" t="n"/>
+      <c r="S21" s="395" t="n"/>
+      <c r="T21" s="396" t="n"/>
+      <c r="U21" s="374" t="n"/>
+      <c r="V21" s="395" t="n"/>
+      <c r="W21" s="395" t="n"/>
+      <c r="X21" s="395" t="n"/>
+      <c r="Y21" s="395" t="n"/>
+      <c r="Z21" s="396" t="n"/>
+      <c r="AA21" s="374" t="n"/>
+      <c r="AB21" s="395" t="n"/>
+      <c r="AC21" s="395" t="n"/>
+      <c r="AD21" s="395" t="n"/>
+      <c r="AE21" s="395" t="n"/>
+      <c r="AF21" s="395" t="n"/>
+      <c r="AG21" s="396" t="n"/>
+      <c r="AH21" s="374" t="n"/>
+      <c r="AI21" s="395" t="n"/>
+      <c r="AJ21" s="395" t="n"/>
+      <c r="AK21" s="396" t="n"/>
+      <c r="AL21" s="374" t="n"/>
+      <c r="AM21" s="395" t="n"/>
+      <c r="AN21" s="395" t="n"/>
+      <c r="AO21" s="396" t="n"/>
+      <c r="AP21" s="374" t="n"/>
+      <c r="AQ21" s="395" t="n"/>
+      <c r="AR21" s="395" t="n"/>
+      <c r="AS21" s="396" t="n"/>
+      <c r="AT21" s="374" t="n"/>
+      <c r="AU21" s="395" t="n"/>
+      <c r="AV21" s="395" t="n"/>
+      <c r="AW21" s="396" t="n"/>
+      <c r="AX21" s="374" t="n"/>
+      <c r="AY21" s="395" t="n"/>
+      <c r="AZ21" s="395" t="n"/>
+      <c r="BA21" s="395" t="n"/>
+      <c r="BB21" s="395" t="n"/>
+      <c r="BC21" s="395" t="n"/>
+      <c r="BD21" s="396" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="293" t="n"/>
-      <c r="B22" s="322" t="n"/>
-      <c r="C22" s="323" t="n"/>
-      <c r="D22" s="294" t="n"/>
-      <c r="E22" s="324" t="n"/>
-      <c r="F22" s="324" t="n"/>
-      <c r="G22" s="324" t="n"/>
-      <c r="H22" s="325" t="n"/>
-      <c r="I22" s="294" t="n"/>
-      <c r="J22" s="324" t="n"/>
-      <c r="K22" s="324" t="n"/>
-      <c r="L22" s="324" t="n"/>
-      <c r="M22" s="325" t="n"/>
-      <c r="N22" s="294" t="n"/>
-      <c r="O22" s="324" t="n"/>
-      <c r="P22" s="324" t="n"/>
-      <c r="Q22" s="324" t="n"/>
-      <c r="R22" s="324" t="n"/>
-      <c r="S22" s="324" t="n"/>
-      <c r="T22" s="325" t="n"/>
-      <c r="U22" s="294" t="n"/>
-      <c r="V22" s="324" t="n"/>
-      <c r="W22" s="324" t="n"/>
-      <c r="X22" s="324" t="n"/>
-      <c r="Y22" s="324" t="n"/>
-      <c r="Z22" s="325" t="n"/>
-      <c r="AA22" s="294" t="n"/>
-      <c r="AB22" s="324" t="n"/>
-      <c r="AC22" s="324" t="n"/>
-      <c r="AD22" s="324" t="n"/>
-      <c r="AE22" s="324" t="n"/>
-      <c r="AF22" s="324" t="n"/>
-      <c r="AG22" s="325" t="n"/>
-      <c r="AH22" s="294" t="n"/>
-      <c r="AI22" s="324" t="n"/>
-      <c r="AJ22" s="324" t="n"/>
-      <c r="AK22" s="325" t="n"/>
-      <c r="AL22" s="294" t="n"/>
-      <c r="AM22" s="324" t="n"/>
-      <c r="AN22" s="324" t="n"/>
-      <c r="AO22" s="325" t="n"/>
-      <c r="AP22" s="294" t="n"/>
-      <c r="AQ22" s="324" t="n"/>
-      <c r="AR22" s="324" t="n"/>
-      <c r="AS22" s="325" t="n"/>
-      <c r="AT22" s="294" t="n"/>
-      <c r="AU22" s="324" t="n"/>
-      <c r="AV22" s="324" t="n"/>
-      <c r="AW22" s="325" t="n"/>
-      <c r="AX22" s="294" t="n"/>
-      <c r="AY22" s="324" t="n"/>
-      <c r="AZ22" s="324" t="n"/>
-      <c r="BA22" s="324" t="n"/>
-      <c r="BB22" s="324" t="n"/>
-      <c r="BC22" s="324" t="n"/>
-      <c r="BD22" s="325" t="n"/>
+      <c r="A22" s="373" t="n"/>
+      <c r="B22" s="389" t="n"/>
+      <c r="C22" s="390" t="n"/>
+      <c r="D22" s="374" t="n"/>
+      <c r="E22" s="395" t="n"/>
+      <c r="F22" s="395" t="n"/>
+      <c r="G22" s="395" t="n"/>
+      <c r="H22" s="396" t="n"/>
+      <c r="I22" s="374" t="n"/>
+      <c r="J22" s="395" t="n"/>
+      <c r="K22" s="395" t="n"/>
+      <c r="L22" s="395" t="n"/>
+      <c r="M22" s="396" t="n"/>
+      <c r="N22" s="374" t="n"/>
+      <c r="O22" s="395" t="n"/>
+      <c r="P22" s="395" t="n"/>
+      <c r="Q22" s="395" t="n"/>
+      <c r="R22" s="395" t="n"/>
+      <c r="S22" s="395" t="n"/>
+      <c r="T22" s="396" t="n"/>
+      <c r="U22" s="374" t="n"/>
+      <c r="V22" s="395" t="n"/>
+      <c r="W22" s="395" t="n"/>
+      <c r="X22" s="395" t="n"/>
+      <c r="Y22" s="395" t="n"/>
+      <c r="Z22" s="396" t="n"/>
+      <c r="AA22" s="374" t="n"/>
+      <c r="AB22" s="395" t="n"/>
+      <c r="AC22" s="395" t="n"/>
+      <c r="AD22" s="395" t="n"/>
+      <c r="AE22" s="395" t="n"/>
+      <c r="AF22" s="395" t="n"/>
+      <c r="AG22" s="396" t="n"/>
+      <c r="AH22" s="374" t="n"/>
+      <c r="AI22" s="395" t="n"/>
+      <c r="AJ22" s="395" t="n"/>
+      <c r="AK22" s="396" t="n"/>
+      <c r="AL22" s="374" t="n"/>
+      <c r="AM22" s="395" t="n"/>
+      <c r="AN22" s="395" t="n"/>
+      <c r="AO22" s="396" t="n"/>
+      <c r="AP22" s="374" t="n"/>
+      <c r="AQ22" s="395" t="n"/>
+      <c r="AR22" s="395" t="n"/>
+      <c r="AS22" s="396" t="n"/>
+      <c r="AT22" s="374" t="n"/>
+      <c r="AU22" s="395" t="n"/>
+      <c r="AV22" s="395" t="n"/>
+      <c r="AW22" s="396" t="n"/>
+      <c r="AX22" s="374" t="n"/>
+      <c r="AY22" s="395" t="n"/>
+      <c r="AZ22" s="395" t="n"/>
+      <c r="BA22" s="395" t="n"/>
+      <c r="BB22" s="395" t="n"/>
+      <c r="BC22" s="395" t="n"/>
+      <c r="BD22" s="396" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="293" t="n"/>
-      <c r="B23" s="322" t="n"/>
-      <c r="C23" s="323" t="n"/>
-      <c r="D23" s="294" t="n"/>
-      <c r="E23" s="324" t="n"/>
-      <c r="F23" s="324" t="n"/>
-      <c r="G23" s="324" t="n"/>
-      <c r="H23" s="325" t="n"/>
-      <c r="I23" s="294" t="n"/>
-      <c r="J23" s="324" t="n"/>
-      <c r="K23" s="324" t="n"/>
-      <c r="L23" s="324" t="n"/>
-      <c r="M23" s="325" t="n"/>
-      <c r="N23" s="294" t="n"/>
-      <c r="O23" s="324" t="n"/>
-      <c r="P23" s="324" t="n"/>
-      <c r="Q23" s="324" t="n"/>
-      <c r="R23" s="324" t="n"/>
-      <c r="S23" s="324" t="n"/>
-      <c r="T23" s="325" t="n"/>
-      <c r="U23" s="294" t="n"/>
-      <c r="V23" s="324" t="n"/>
-      <c r="W23" s="324" t="n"/>
-      <c r="X23" s="324" t="n"/>
-      <c r="Y23" s="324" t="n"/>
-      <c r="Z23" s="325" t="n"/>
-      <c r="AA23" s="294" t="n"/>
-      <c r="AB23" s="324" t="n"/>
-      <c r="AC23" s="324" t="n"/>
-      <c r="AD23" s="324" t="n"/>
-      <c r="AE23" s="324" t="n"/>
-      <c r="AF23" s="324" t="n"/>
-      <c r="AG23" s="325" t="n"/>
-      <c r="AH23" s="294" t="n"/>
-      <c r="AI23" s="324" t="n"/>
-      <c r="AJ23" s="324" t="n"/>
-      <c r="AK23" s="325" t="n"/>
-      <c r="AL23" s="294" t="n"/>
-      <c r="AM23" s="324" t="n"/>
-      <c r="AN23" s="324" t="n"/>
-      <c r="AO23" s="325" t="n"/>
-      <c r="AP23" s="294" t="n"/>
-      <c r="AQ23" s="324" t="n"/>
-      <c r="AR23" s="324" t="n"/>
-      <c r="AS23" s="325" t="n"/>
-      <c r="AT23" s="294" t="n"/>
-      <c r="AU23" s="324" t="n"/>
-      <c r="AV23" s="324" t="n"/>
-      <c r="AW23" s="325" t="n"/>
-      <c r="AX23" s="294" t="n"/>
-      <c r="AY23" s="324" t="n"/>
-      <c r="AZ23" s="324" t="n"/>
-      <c r="BA23" s="324" t="n"/>
-      <c r="BB23" s="324" t="n"/>
-      <c r="BC23" s="324" t="n"/>
-      <c r="BD23" s="325" t="n"/>
+      <c r="A23" s="373" t="n"/>
+      <c r="B23" s="389" t="n"/>
+      <c r="C23" s="390" t="n"/>
+      <c r="D23" s="374" t="n"/>
+      <c r="E23" s="395" t="n"/>
+      <c r="F23" s="395" t="n"/>
+      <c r="G23" s="395" t="n"/>
+      <c r="H23" s="396" t="n"/>
+      <c r="I23" s="374" t="n"/>
+      <c r="J23" s="395" t="n"/>
+      <c r="K23" s="395" t="n"/>
+      <c r="L23" s="395" t="n"/>
+      <c r="M23" s="396" t="n"/>
+      <c r="N23" s="374" t="n"/>
+      <c r="O23" s="395" t="n"/>
+      <c r="P23" s="395" t="n"/>
+      <c r="Q23" s="395" t="n"/>
+      <c r="R23" s="395" t="n"/>
+      <c r="S23" s="395" t="n"/>
+      <c r="T23" s="396" t="n"/>
+      <c r="U23" s="374" t="n"/>
+      <c r="V23" s="395" t="n"/>
+      <c r="W23" s="395" t="n"/>
+      <c r="X23" s="395" t="n"/>
+      <c r="Y23" s="395" t="n"/>
+      <c r="Z23" s="396" t="n"/>
+      <c r="AA23" s="374" t="n"/>
+      <c r="AB23" s="395" t="n"/>
+      <c r="AC23" s="395" t="n"/>
+      <c r="AD23" s="395" t="n"/>
+      <c r="AE23" s="395" t="n"/>
+      <c r="AF23" s="395" t="n"/>
+      <c r="AG23" s="396" t="n"/>
+      <c r="AH23" s="374" t="n"/>
+      <c r="AI23" s="395" t="n"/>
+      <c r="AJ23" s="395" t="n"/>
+      <c r="AK23" s="396" t="n"/>
+      <c r="AL23" s="374" t="n"/>
+      <c r="AM23" s="395" t="n"/>
+      <c r="AN23" s="395" t="n"/>
+      <c r="AO23" s="396" t="n"/>
+      <c r="AP23" s="374" t="n"/>
+      <c r="AQ23" s="395" t="n"/>
+      <c r="AR23" s="395" t="n"/>
+      <c r="AS23" s="396" t="n"/>
+      <c r="AT23" s="374" t="n"/>
+      <c r="AU23" s="395" t="n"/>
+      <c r="AV23" s="395" t="n"/>
+      <c r="AW23" s="396" t="n"/>
+      <c r="AX23" s="374" t="n"/>
+      <c r="AY23" s="395" t="n"/>
+      <c r="AZ23" s="395" t="n"/>
+      <c r="BA23" s="395" t="n"/>
+      <c r="BB23" s="395" t="n"/>
+      <c r="BC23" s="395" t="n"/>
+      <c r="BD23" s="396" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="293" t="n"/>
-      <c r="B24" s="322" t="n"/>
-      <c r="C24" s="323" t="n"/>
-      <c r="D24" s="294" t="n"/>
-      <c r="E24" s="324" t="n"/>
-      <c r="F24" s="324" t="n"/>
-      <c r="G24" s="324" t="n"/>
-      <c r="H24" s="325" t="n"/>
-      <c r="I24" s="294" t="n"/>
-      <c r="J24" s="324" t="n"/>
-      <c r="K24" s="324" t="n"/>
-      <c r="L24" s="324" t="n"/>
-      <c r="M24" s="325" t="n"/>
-      <c r="N24" s="294" t="n"/>
-      <c r="O24" s="324" t="n"/>
-      <c r="P24" s="324" t="n"/>
-      <c r="Q24" s="324" t="n"/>
-      <c r="R24" s="324" t="n"/>
-      <c r="S24" s="324" t="n"/>
-      <c r="T24" s="325" t="n"/>
-      <c r="U24" s="294" t="n"/>
-      <c r="V24" s="324" t="n"/>
-      <c r="W24" s="324" t="n"/>
-      <c r="X24" s="324" t="n"/>
-      <c r="Y24" s="324" t="n"/>
-      <c r="Z24" s="325" t="n"/>
-      <c r="AA24" s="294" t="n"/>
-      <c r="AB24" s="324" t="n"/>
-      <c r="AC24" s="324" t="n"/>
-      <c r="AD24" s="324" t="n"/>
-      <c r="AE24" s="324" t="n"/>
-      <c r="AF24" s="324" t="n"/>
-      <c r="AG24" s="325" t="n"/>
-      <c r="AH24" s="294" t="n"/>
-      <c r="AI24" s="324" t="n"/>
-      <c r="AJ24" s="324" t="n"/>
-      <c r="AK24" s="325" t="n"/>
-      <c r="AL24" s="294" t="n"/>
-      <c r="AM24" s="324" t="n"/>
-      <c r="AN24" s="324" t="n"/>
-      <c r="AO24" s="325" t="n"/>
-      <c r="AP24" s="294" t="n"/>
-      <c r="AQ24" s="324" t="n"/>
-      <c r="AR24" s="324" t="n"/>
-      <c r="AS24" s="325" t="n"/>
-      <c r="AT24" s="294" t="n"/>
-      <c r="AU24" s="324" t="n"/>
-      <c r="AV24" s="324" t="n"/>
-      <c r="AW24" s="325" t="n"/>
-      <c r="AX24" s="294" t="n"/>
-      <c r="AY24" s="324" t="n"/>
-      <c r="AZ24" s="324" t="n"/>
-      <c r="BA24" s="324" t="n"/>
-      <c r="BB24" s="324" t="n"/>
-      <c r="BC24" s="324" t="n"/>
-      <c r="BD24" s="325" t="n"/>
+      <c r="A24" s="373" t="n"/>
+      <c r="B24" s="389" t="n"/>
+      <c r="C24" s="390" t="n"/>
+      <c r="D24" s="374" t="n"/>
+      <c r="E24" s="395" t="n"/>
+      <c r="F24" s="395" t="n"/>
+      <c r="G24" s="395" t="n"/>
+      <c r="H24" s="396" t="n"/>
+      <c r="I24" s="374" t="n"/>
+      <c r="J24" s="395" t="n"/>
+      <c r="K24" s="395" t="n"/>
+      <c r="L24" s="395" t="n"/>
+      <c r="M24" s="396" t="n"/>
+      <c r="N24" s="374" t="n"/>
+      <c r="O24" s="395" t="n"/>
+      <c r="P24" s="395" t="n"/>
+      <c r="Q24" s="395" t="n"/>
+      <c r="R24" s="395" t="n"/>
+      <c r="S24" s="395" t="n"/>
+      <c r="T24" s="396" t="n"/>
+      <c r="U24" s="374" t="n"/>
+      <c r="V24" s="395" t="n"/>
+      <c r="W24" s="395" t="n"/>
+      <c r="X24" s="395" t="n"/>
+      <c r="Y24" s="395" t="n"/>
+      <c r="Z24" s="396" t="n"/>
+      <c r="AA24" s="374" t="n"/>
+      <c r="AB24" s="395" t="n"/>
+      <c r="AC24" s="395" t="n"/>
+      <c r="AD24" s="395" t="n"/>
+      <c r="AE24" s="395" t="n"/>
+      <c r="AF24" s="395" t="n"/>
+      <c r="AG24" s="396" t="n"/>
+      <c r="AH24" s="374" t="n"/>
+      <c r="AI24" s="395" t="n"/>
+      <c r="AJ24" s="395" t="n"/>
+      <c r="AK24" s="396" t="n"/>
+      <c r="AL24" s="374" t="n"/>
+      <c r="AM24" s="395" t="n"/>
+      <c r="AN24" s="395" t="n"/>
+      <c r="AO24" s="396" t="n"/>
+      <c r="AP24" s="374" t="n"/>
+      <c r="AQ24" s="395" t="n"/>
+      <c r="AR24" s="395" t="n"/>
+      <c r="AS24" s="396" t="n"/>
+      <c r="AT24" s="374" t="n"/>
+      <c r="AU24" s="395" t="n"/>
+      <c r="AV24" s="395" t="n"/>
+      <c r="AW24" s="396" t="n"/>
+      <c r="AX24" s="374" t="n"/>
+      <c r="AY24" s="395" t="n"/>
+      <c r="AZ24" s="395" t="n"/>
+      <c r="BA24" s="395" t="n"/>
+      <c r="BB24" s="395" t="n"/>
+      <c r="BC24" s="395" t="n"/>
+      <c r="BD24" s="396" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="293" t="n"/>
-      <c r="B25" s="322" t="n"/>
-      <c r="C25" s="323" t="n"/>
-      <c r="D25" s="294" t="n"/>
-      <c r="E25" s="324" t="n"/>
-      <c r="F25" s="324" t="n"/>
-      <c r="G25" s="324" t="n"/>
-      <c r="H25" s="325" t="n"/>
-      <c r="I25" s="294" t="n"/>
-      <c r="J25" s="324" t="n"/>
-      <c r="K25" s="324" t="n"/>
-      <c r="L25" s="324" t="n"/>
-      <c r="M25" s="325" t="n"/>
-      <c r="N25" s="294" t="n"/>
-      <c r="O25" s="324" t="n"/>
-      <c r="P25" s="324" t="n"/>
-      <c r="Q25" s="324" t="n"/>
-      <c r="R25" s="324" t="n"/>
-      <c r="S25" s="324" t="n"/>
-      <c r="T25" s="325" t="n"/>
-      <c r="U25" s="294" t="n"/>
-      <c r="V25" s="324" t="n"/>
-      <c r="W25" s="324" t="n"/>
-      <c r="X25" s="324" t="n"/>
-      <c r="Y25" s="324" t="n"/>
-      <c r="Z25" s="325" t="n"/>
-      <c r="AA25" s="294" t="n"/>
-      <c r="AB25" s="324" t="n"/>
-      <c r="AC25" s="324" t="n"/>
-      <c r="AD25" s="324" t="n"/>
-      <c r="AE25" s="324" t="n"/>
-      <c r="AF25" s="324" t="n"/>
-      <c r="AG25" s="325" t="n"/>
-      <c r="AH25" s="294" t="n"/>
-      <c r="AI25" s="324" t="n"/>
-      <c r="AJ25" s="324" t="n"/>
-      <c r="AK25" s="325" t="n"/>
-      <c r="AL25" s="294" t="n"/>
-      <c r="AM25" s="324" t="n"/>
-      <c r="AN25" s="324" t="n"/>
-      <c r="AO25" s="325" t="n"/>
-      <c r="AP25" s="294" t="n"/>
-      <c r="AQ25" s="324" t="n"/>
-      <c r="AR25" s="324" t="n"/>
-      <c r="AS25" s="325" t="n"/>
-      <c r="AT25" s="294" t="n"/>
-      <c r="AU25" s="324" t="n"/>
-      <c r="AV25" s="324" t="n"/>
-      <c r="AW25" s="325" t="n"/>
-      <c r="AX25" s="294" t="n"/>
-      <c r="AY25" s="324" t="n"/>
-      <c r="AZ25" s="324" t="n"/>
-      <c r="BA25" s="324" t="n"/>
-      <c r="BB25" s="324" t="n"/>
-      <c r="BC25" s="324" t="n"/>
-      <c r="BD25" s="325" t="n"/>
+      <c r="A25" s="373" t="n"/>
+      <c r="B25" s="389" t="n"/>
+      <c r="C25" s="390" t="n"/>
+      <c r="D25" s="374" t="n"/>
+      <c r="E25" s="395" t="n"/>
+      <c r="F25" s="395" t="n"/>
+      <c r="G25" s="395" t="n"/>
+      <c r="H25" s="396" t="n"/>
+      <c r="I25" s="374" t="n"/>
+      <c r="J25" s="395" t="n"/>
+      <c r="K25" s="395" t="n"/>
+      <c r="L25" s="395" t="n"/>
+      <c r="M25" s="396" t="n"/>
+      <c r="N25" s="374" t="n"/>
+      <c r="O25" s="395" t="n"/>
+      <c r="P25" s="395" t="n"/>
+      <c r="Q25" s="395" t="n"/>
+      <c r="R25" s="395" t="n"/>
+      <c r="S25" s="395" t="n"/>
+      <c r="T25" s="396" t="n"/>
+      <c r="U25" s="374" t="n"/>
+      <c r="V25" s="395" t="n"/>
+      <c r="W25" s="395" t="n"/>
+      <c r="X25" s="395" t="n"/>
+      <c r="Y25" s="395" t="n"/>
+      <c r="Z25" s="396" t="n"/>
+      <c r="AA25" s="374" t="n"/>
+      <c r="AB25" s="395" t="n"/>
+      <c r="AC25" s="395" t="n"/>
+      <c r="AD25" s="395" t="n"/>
+      <c r="AE25" s="395" t="n"/>
+      <c r="AF25" s="395" t="n"/>
+      <c r="AG25" s="396" t="n"/>
+      <c r="AH25" s="374" t="n"/>
+      <c r="AI25" s="395" t="n"/>
+      <c r="AJ25" s="395" t="n"/>
+      <c r="AK25" s="396" t="n"/>
+      <c r="AL25" s="374" t="n"/>
+      <c r="AM25" s="395" t="n"/>
+      <c r="AN25" s="395" t="n"/>
+      <c r="AO25" s="396" t="n"/>
+      <c r="AP25" s="374" t="n"/>
+      <c r="AQ25" s="395" t="n"/>
+      <c r="AR25" s="395" t="n"/>
+      <c r="AS25" s="396" t="n"/>
+      <c r="AT25" s="374" t="n"/>
+      <c r="AU25" s="395" t="n"/>
+      <c r="AV25" s="395" t="n"/>
+      <c r="AW25" s="396" t="n"/>
+      <c r="AX25" s="374" t="n"/>
+      <c r="AY25" s="395" t="n"/>
+      <c r="AZ25" s="395" t="n"/>
+      <c r="BA25" s="395" t="n"/>
+      <c r="BB25" s="395" t="n"/>
+      <c r="BC25" s="395" t="n"/>
+      <c r="BD25" s="396" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="293" t="n"/>
-      <c r="B26" s="322" t="n"/>
-      <c r="C26" s="323" t="n"/>
-      <c r="D26" s="294" t="n"/>
-      <c r="E26" s="324" t="n"/>
-      <c r="F26" s="324" t="n"/>
-      <c r="G26" s="324" t="n"/>
-      <c r="H26" s="325" t="n"/>
-      <c r="I26" s="294" t="n"/>
-      <c r="J26" s="324" t="n"/>
-      <c r="K26" s="324" t="n"/>
-      <c r="L26" s="324" t="n"/>
-      <c r="M26" s="325" t="n"/>
-      <c r="N26" s="294" t="n"/>
-      <c r="O26" s="324" t="n"/>
-      <c r="P26" s="324" t="n"/>
-      <c r="Q26" s="324" t="n"/>
-      <c r="R26" s="324" t="n"/>
-      <c r="S26" s="324" t="n"/>
-      <c r="T26" s="325" t="n"/>
-      <c r="U26" s="294" t="n"/>
-      <c r="V26" s="324" t="n"/>
-      <c r="W26" s="324" t="n"/>
-      <c r="X26" s="324" t="n"/>
-      <c r="Y26" s="324" t="n"/>
-      <c r="Z26" s="325" t="n"/>
-      <c r="AA26" s="294" t="n"/>
-      <c r="AB26" s="324" t="n"/>
-      <c r="AC26" s="324" t="n"/>
-      <c r="AD26" s="324" t="n"/>
-      <c r="AE26" s="324" t="n"/>
-      <c r="AF26" s="324" t="n"/>
-      <c r="AG26" s="325" t="n"/>
-      <c r="AH26" s="294" t="n"/>
-      <c r="AI26" s="324" t="n"/>
-      <c r="AJ26" s="324" t="n"/>
-      <c r="AK26" s="325" t="n"/>
-      <c r="AL26" s="294" t="n"/>
-      <c r="AM26" s="324" t="n"/>
-      <c r="AN26" s="324" t="n"/>
-      <c r="AO26" s="325" t="n"/>
-      <c r="AP26" s="294" t="n"/>
-      <c r="AQ26" s="324" t="n"/>
-      <c r="AR26" s="324" t="n"/>
-      <c r="AS26" s="325" t="n"/>
-      <c r="AT26" s="294" t="n"/>
-      <c r="AU26" s="324" t="n"/>
-      <c r="AV26" s="324" t="n"/>
-      <c r="AW26" s="325" t="n"/>
-      <c r="AX26" s="294" t="n"/>
-      <c r="AY26" s="324" t="n"/>
-      <c r="AZ26" s="324" t="n"/>
-      <c r="BA26" s="324" t="n"/>
-      <c r="BB26" s="324" t="n"/>
-      <c r="BC26" s="324" t="n"/>
-      <c r="BD26" s="325" t="n"/>
+      <c r="A26" s="373" t="n"/>
+      <c r="B26" s="389" t="n"/>
+      <c r="C26" s="390" t="n"/>
+      <c r="D26" s="374" t="n"/>
+      <c r="E26" s="395" t="n"/>
+      <c r="F26" s="395" t="n"/>
+      <c r="G26" s="395" t="n"/>
+      <c r="H26" s="396" t="n"/>
+      <c r="I26" s="374" t="n"/>
+      <c r="J26" s="395" t="n"/>
+      <c r="K26" s="395" t="n"/>
+      <c r="L26" s="395" t="n"/>
+      <c r="M26" s="396" t="n"/>
+      <c r="N26" s="374" t="n"/>
+      <c r="O26" s="395" t="n"/>
+      <c r="P26" s="395" t="n"/>
+      <c r="Q26" s="395" t="n"/>
+      <c r="R26" s="395" t="n"/>
+      <c r="S26" s="395" t="n"/>
+      <c r="T26" s="396" t="n"/>
+      <c r="U26" s="374" t="n"/>
+      <c r="V26" s="395" t="n"/>
+      <c r="W26" s="395" t="n"/>
+      <c r="X26" s="395" t="n"/>
+      <c r="Y26" s="395" t="n"/>
+      <c r="Z26" s="396" t="n"/>
+      <c r="AA26" s="374" t="n"/>
+      <c r="AB26" s="395" t="n"/>
+      <c r="AC26" s="395" t="n"/>
+      <c r="AD26" s="395" t="n"/>
+      <c r="AE26" s="395" t="n"/>
+      <c r="AF26" s="395" t="n"/>
+      <c r="AG26" s="396" t="n"/>
+      <c r="AH26" s="374" t="n"/>
+      <c r="AI26" s="395" t="n"/>
+      <c r="AJ26" s="395" t="n"/>
+      <c r="AK26" s="396" t="n"/>
+      <c r="AL26" s="374" t="n"/>
+      <c r="AM26" s="395" t="n"/>
+      <c r="AN26" s="395" t="n"/>
+      <c r="AO26" s="396" t="n"/>
+      <c r="AP26" s="374" t="n"/>
+      <c r="AQ26" s="395" t="n"/>
+      <c r="AR26" s="395" t="n"/>
+      <c r="AS26" s="396" t="n"/>
+      <c r="AT26" s="374" t="n"/>
+      <c r="AU26" s="395" t="n"/>
+      <c r="AV26" s="395" t="n"/>
+      <c r="AW26" s="396" t="n"/>
+      <c r="AX26" s="374" t="n"/>
+      <c r="AY26" s="395" t="n"/>
+      <c r="AZ26" s="395" t="n"/>
+      <c r="BA26" s="395" t="n"/>
+      <c r="BB26" s="395" t="n"/>
+      <c r="BC26" s="395" t="n"/>
+      <c r="BD26" s="396" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="293" t="n"/>
-      <c r="B27" s="322" t="n"/>
-      <c r="C27" s="323" t="n"/>
-      <c r="D27" s="294" t="n"/>
-      <c r="E27" s="324" t="n"/>
-      <c r="F27" s="324" t="n"/>
-      <c r="G27" s="324" t="n"/>
-      <c r="H27" s="325" t="n"/>
-      <c r="I27" s="294" t="n"/>
-      <c r="J27" s="324" t="n"/>
-      <c r="K27" s="324" t="n"/>
-      <c r="L27" s="324" t="n"/>
-      <c r="M27" s="325" t="n"/>
-      <c r="N27" s="294" t="n"/>
-      <c r="O27" s="324" t="n"/>
-      <c r="P27" s="324" t="n"/>
-      <c r="Q27" s="324" t="n"/>
-      <c r="R27" s="324" t="n"/>
-      <c r="S27" s="324" t="n"/>
-      <c r="T27" s="325" t="n"/>
-      <c r="U27" s="294" t="n"/>
-      <c r="V27" s="324" t="n"/>
-      <c r="W27" s="324" t="n"/>
-      <c r="X27" s="324" t="n"/>
-      <c r="Y27" s="324" t="n"/>
-      <c r="Z27" s="325" t="n"/>
-      <c r="AA27" s="294" t="n"/>
-      <c r="AB27" s="324" t="n"/>
-      <c r="AC27" s="324" t="n"/>
-      <c r="AD27" s="324" t="n"/>
-      <c r="AE27" s="324" t="n"/>
-      <c r="AF27" s="324" t="n"/>
-      <c r="AG27" s="325" t="n"/>
-      <c r="AH27" s="294" t="n"/>
-      <c r="AI27" s="324" t="n"/>
-      <c r="AJ27" s="324" t="n"/>
-      <c r="AK27" s="325" t="n"/>
-      <c r="AL27" s="294" t="n"/>
-      <c r="AM27" s="324" t="n"/>
-      <c r="AN27" s="324" t="n"/>
-      <c r="AO27" s="325" t="n"/>
-      <c r="AP27" s="294" t="n"/>
-      <c r="AQ27" s="324" t="n"/>
-      <c r="AR27" s="324" t="n"/>
-      <c r="AS27" s="325" t="n"/>
-      <c r="AT27" s="294" t="n"/>
-      <c r="AU27" s="324" t="n"/>
-      <c r="AV27" s="324" t="n"/>
-      <c r="AW27" s="325" t="n"/>
-      <c r="AX27" s="294" t="n"/>
-      <c r="AY27" s="324" t="n"/>
-      <c r="AZ27" s="324" t="n"/>
-      <c r="BA27" s="324" t="n"/>
-      <c r="BB27" s="324" t="n"/>
-      <c r="BC27" s="324" t="n"/>
-      <c r="BD27" s="325" t="n"/>
+      <c r="A27" s="373" t="n"/>
+      <c r="B27" s="389" t="n"/>
+      <c r="C27" s="390" t="n"/>
+      <c r="D27" s="374" t="n"/>
+      <c r="E27" s="395" t="n"/>
+      <c r="F27" s="395" t="n"/>
+      <c r="G27" s="395" t="n"/>
+      <c r="H27" s="396" t="n"/>
+      <c r="I27" s="374" t="n"/>
+      <c r="J27" s="395" t="n"/>
+      <c r="K27" s="395" t="n"/>
+      <c r="L27" s="395" t="n"/>
+      <c r="M27" s="396" t="n"/>
+      <c r="N27" s="374" t="n"/>
+      <c r="O27" s="395" t="n"/>
+      <c r="P27" s="395" t="n"/>
+      <c r="Q27" s="395" t="n"/>
+      <c r="R27" s="395" t="n"/>
+      <c r="S27" s="395" t="n"/>
+      <c r="T27" s="396" t="n"/>
+      <c r="U27" s="374" t="n"/>
+      <c r="V27" s="395" t="n"/>
+      <c r="W27" s="395" t="n"/>
+      <c r="X27" s="395" t="n"/>
+      <c r="Y27" s="395" t="n"/>
+      <c r="Z27" s="396" t="n"/>
+      <c r="AA27" s="374" t="n"/>
+      <c r="AB27" s="395" t="n"/>
+      <c r="AC27" s="395" t="n"/>
+      <c r="AD27" s="395" t="n"/>
+      <c r="AE27" s="395" t="n"/>
+      <c r="AF27" s="395" t="n"/>
+      <c r="AG27" s="396" t="n"/>
+      <c r="AH27" s="374" t="n"/>
+      <c r="AI27" s="395" t="n"/>
+      <c r="AJ27" s="395" t="n"/>
+      <c r="AK27" s="396" t="n"/>
+      <c r="AL27" s="374" t="n"/>
+      <c r="AM27" s="395" t="n"/>
+      <c r="AN27" s="395" t="n"/>
+      <c r="AO27" s="396" t="n"/>
+      <c r="AP27" s="374" t="n"/>
+      <c r="AQ27" s="395" t="n"/>
+      <c r="AR27" s="395" t="n"/>
+      <c r="AS27" s="396" t="n"/>
+      <c r="AT27" s="374" t="n"/>
+      <c r="AU27" s="395" t="n"/>
+      <c r="AV27" s="395" t="n"/>
+      <c r="AW27" s="396" t="n"/>
+      <c r="AX27" s="374" t="n"/>
+      <c r="AY27" s="395" t="n"/>
+      <c r="AZ27" s="395" t="n"/>
+      <c r="BA27" s="395" t="n"/>
+      <c r="BB27" s="395" t="n"/>
+      <c r="BC27" s="395" t="n"/>
+      <c r="BD27" s="396" t="n"/>
     </row>
     <row r="28" ht="4" customHeight="1">
-      <c r="A28" s="304" t="n"/>
-      <c r="D28" s="305" t="n"/>
-      <c r="H28" s="306" t="n"/>
-      <c r="AA28" s="301" t="n"/>
-      <c r="AR28" s="302" t="n"/>
-      <c r="AX28" s="302" t="n"/>
-      <c r="BB28" s="303" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="284" t="inlineStr">
+      <c r="A28" s="375" t="n"/>
+      <c r="B28" s="345" t="n"/>
+      <c r="C28" s="345" t="n"/>
+      <c r="D28" s="376" t="n"/>
+      <c r="E28" s="345" t="n"/>
+      <c r="F28" s="345" t="n"/>
+      <c r="G28" s="345" t="n"/>
+      <c r="H28" s="377" t="n"/>
+      <c r="I28" s="345" t="n"/>
+      <c r="J28" s="345" t="n"/>
+      <c r="K28" s="345" t="n"/>
+      <c r="L28" s="345" t="n"/>
+      <c r="M28" s="345" t="n"/>
+      <c r="N28" s="345" t="n"/>
+      <c r="O28" s="345" t="n"/>
+      <c r="P28" s="345" t="n"/>
+      <c r="Q28" s="345" t="n"/>
+      <c r="R28" s="345" t="n"/>
+      <c r="S28" s="345" t="n"/>
+      <c r="T28" s="345" t="n"/>
+      <c r="U28" s="345" t="n"/>
+      <c r="V28" s="345" t="n"/>
+      <c r="W28" s="345" t="n"/>
+      <c r="X28" s="345" t="n"/>
+      <c r="Y28" s="345" t="n"/>
+      <c r="Z28" s="345" t="n"/>
+      <c r="AA28" s="378" t="n"/>
+      <c r="AB28" s="345" t="n"/>
+      <c r="AC28" s="345" t="n"/>
+      <c r="AD28" s="345" t="n"/>
+      <c r="AE28" s="345" t="n"/>
+      <c r="AF28" s="345" t="n"/>
+      <c r="AG28" s="345" t="n"/>
+      <c r="AH28" s="345" t="n"/>
+      <c r="AI28" s="345" t="n"/>
+      <c r="AJ28" s="345" t="n"/>
+      <c r="AK28" s="345" t="n"/>
+      <c r="AL28" s="345" t="n"/>
+      <c r="AM28" s="345" t="n"/>
+      <c r="AN28" s="345" t="n"/>
+      <c r="AO28" s="345" t="n"/>
+      <c r="AP28" s="345" t="n"/>
+      <c r="AQ28" s="345" t="n"/>
+      <c r="AR28" s="379" t="n"/>
+      <c r="AS28" s="345" t="n"/>
+      <c r="AT28" s="345" t="n"/>
+      <c r="AU28" s="345" t="n"/>
+      <c r="AV28" s="345" t="n"/>
+      <c r="AW28" s="345" t="n"/>
+      <c r="AX28" s="379" t="n"/>
+      <c r="AY28" s="345" t="n"/>
+      <c r="AZ28" s="345" t="n"/>
+      <c r="BA28" s="345" t="n"/>
+      <c r="BB28" s="380" t="n"/>
+      <c r="BC28" s="345" t="n"/>
+      <c r="BD28" s="345" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="366" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. PERIODIC REVIEW / CLOSEOUT</t>
         </is>
       </c>
-      <c r="B29" s="285" t="n"/>
-      <c r="C29" s="285" t="n"/>
-      <c r="D29" s="285" t="n"/>
-      <c r="E29" s="285" t="n"/>
-      <c r="F29" s="285" t="n"/>
-      <c r="G29" s="285" t="n"/>
-      <c r="H29" s="285" t="n"/>
-      <c r="I29" s="285" t="n"/>
-      <c r="J29" s="285" t="n"/>
-      <c r="K29" s="285" t="n"/>
-      <c r="L29" s="285" t="n"/>
-      <c r="M29" s="285" t="n"/>
-      <c r="N29" s="285" t="n"/>
-      <c r="O29" s="285" t="n"/>
-      <c r="P29" s="285" t="n"/>
-      <c r="Q29" s="285" t="n"/>
-      <c r="R29" s="285" t="n"/>
-      <c r="S29" s="285" t="n"/>
-      <c r="T29" s="285" t="n"/>
-      <c r="U29" s="285" t="n"/>
-      <c r="V29" s="285" t="n"/>
-      <c r="W29" s="285" t="n"/>
-      <c r="X29" s="285" t="n"/>
-      <c r="Y29" s="285" t="n"/>
-      <c r="Z29" s="285" t="n"/>
-      <c r="AA29" s="285" t="n"/>
-      <c r="AB29" s="285" t="n"/>
-      <c r="AC29" s="285" t="n"/>
-      <c r="AD29" s="285" t="n"/>
-      <c r="AE29" s="285" t="n"/>
-      <c r="AF29" s="285" t="n"/>
-      <c r="AG29" s="285" t="n"/>
-      <c r="AH29" s="285" t="n"/>
-      <c r="AI29" s="285" t="n"/>
-      <c r="AJ29" s="285" t="n"/>
-      <c r="AK29" s="285" t="n"/>
-      <c r="AL29" s="285" t="n"/>
-      <c r="AM29" s="285" t="n"/>
-      <c r="AN29" s="285" t="n"/>
-      <c r="AO29" s="285" t="n"/>
-      <c r="AP29" s="285" t="n"/>
-      <c r="AQ29" s="285" t="n"/>
-      <c r="AR29" s="285" t="n"/>
-      <c r="AS29" s="285" t="n"/>
-      <c r="AT29" s="285" t="n"/>
-      <c r="AU29" s="285" t="n"/>
-      <c r="AV29" s="285" t="n"/>
-      <c r="AW29" s="285" t="n"/>
-      <c r="AX29" s="285" t="n"/>
-      <c r="AY29" s="285" t="n"/>
-      <c r="AZ29" s="285" t="n"/>
-      <c r="BA29" s="285" t="n"/>
-      <c r="BB29" s="285" t="n"/>
-      <c r="BC29" s="285" t="n"/>
-      <c r="BD29" s="286" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="287" t="inlineStr">
+      <c r="B29" s="389" t="n"/>
+      <c r="C29" s="389" t="n"/>
+      <c r="D29" s="389" t="n"/>
+      <c r="E29" s="389" t="n"/>
+      <c r="F29" s="389" t="n"/>
+      <c r="G29" s="389" t="n"/>
+      <c r="H29" s="389" t="n"/>
+      <c r="I29" s="389" t="n"/>
+      <c r="J29" s="389" t="n"/>
+      <c r="K29" s="389" t="n"/>
+      <c r="L29" s="389" t="n"/>
+      <c r="M29" s="389" t="n"/>
+      <c r="N29" s="389" t="n"/>
+      <c r="O29" s="389" t="n"/>
+      <c r="P29" s="389" t="n"/>
+      <c r="Q29" s="389" t="n"/>
+      <c r="R29" s="389" t="n"/>
+      <c r="S29" s="389" t="n"/>
+      <c r="T29" s="389" t="n"/>
+      <c r="U29" s="389" t="n"/>
+      <c r="V29" s="389" t="n"/>
+      <c r="W29" s="389" t="n"/>
+      <c r="X29" s="389" t="n"/>
+      <c r="Y29" s="389" t="n"/>
+      <c r="Z29" s="389" t="n"/>
+      <c r="AA29" s="389" t="n"/>
+      <c r="AB29" s="389" t="n"/>
+      <c r="AC29" s="389" t="n"/>
+      <c r="AD29" s="389" t="n"/>
+      <c r="AE29" s="389" t="n"/>
+      <c r="AF29" s="389" t="n"/>
+      <c r="AG29" s="389" t="n"/>
+      <c r="AH29" s="389" t="n"/>
+      <c r="AI29" s="389" t="n"/>
+      <c r="AJ29" s="389" t="n"/>
+      <c r="AK29" s="389" t="n"/>
+      <c r="AL29" s="389" t="n"/>
+      <c r="AM29" s="389" t="n"/>
+      <c r="AN29" s="389" t="n"/>
+      <c r="AO29" s="389" t="n"/>
+      <c r="AP29" s="389" t="n"/>
+      <c r="AQ29" s="389" t="n"/>
+      <c r="AR29" s="389" t="n"/>
+      <c r="AS29" s="389" t="n"/>
+      <c r="AT29" s="389" t="n"/>
+      <c r="AU29" s="389" t="n"/>
+      <c r="AV29" s="389" t="n"/>
+      <c r="AW29" s="389" t="n"/>
+      <c r="AX29" s="389" t="n"/>
+      <c r="AY29" s="389" t="n"/>
+      <c r="AZ29" s="389" t="n"/>
+      <c r="BA29" s="389" t="n"/>
+      <c r="BB29" s="389" t="n"/>
+      <c r="BC29" s="389" t="n"/>
+      <c r="BD29" s="390" t="n"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="353" t="inlineStr">
         <is>
           <t>Periodic Review Date</t>
         </is>
       </c>
-      <c r="B30" s="271" t="n"/>
-      <c r="C30" s="271" t="n"/>
-      <c r="D30" s="271" t="n"/>
-      <c r="E30" s="271" t="n"/>
-      <c r="F30" s="271" t="n"/>
-      <c r="G30" s="271" t="n"/>
-      <c r="H30" s="271" t="n"/>
-      <c r="I30" s="271" t="n"/>
-      <c r="J30" s="272" t="n"/>
-      <c r="K30" s="288" t="n"/>
-      <c r="L30" s="319" t="n"/>
-      <c r="M30" s="319" t="n"/>
-      <c r="N30" s="319" t="n"/>
-      <c r="O30" s="319" t="n"/>
-      <c r="P30" s="319" t="n"/>
-      <c r="Q30" s="319" t="n"/>
-      <c r="R30" s="319" t="n"/>
-      <c r="S30" s="319" t="n"/>
-      <c r="T30" s="319" t="n"/>
-      <c r="U30" s="319" t="n"/>
-      <c r="V30" s="319" t="n"/>
-      <c r="W30" s="319" t="n"/>
-      <c r="X30" s="319" t="n"/>
-      <c r="Y30" s="319" t="n"/>
-      <c r="Z30" s="319" t="n"/>
-      <c r="AA30" s="319" t="n"/>
-      <c r="AB30" s="320" t="n"/>
-      <c r="AC30" s="289" t="inlineStr">
+      <c r="B30" s="387" t="n"/>
+      <c r="C30" s="387" t="n"/>
+      <c r="D30" s="387" t="n"/>
+      <c r="E30" s="387" t="n"/>
+      <c r="F30" s="387" t="n"/>
+      <c r="G30" s="387" t="n"/>
+      <c r="H30" s="387" t="n"/>
+      <c r="I30" s="387" t="n"/>
+      <c r="J30" s="388" t="n"/>
+      <c r="K30" s="367" t="n"/>
+      <c r="L30" s="397" t="n"/>
+      <c r="M30" s="397" t="n"/>
+      <c r="N30" s="397" t="n"/>
+      <c r="O30" s="397" t="n"/>
+      <c r="P30" s="397" t="n"/>
+      <c r="Q30" s="397" t="n"/>
+      <c r="R30" s="397" t="n"/>
+      <c r="S30" s="397" t="n"/>
+      <c r="T30" s="397" t="n"/>
+      <c r="U30" s="397" t="n"/>
+      <c r="V30" s="397" t="n"/>
+      <c r="W30" s="397" t="n"/>
+      <c r="X30" s="397" t="n"/>
+      <c r="Y30" s="397" t="n"/>
+      <c r="Z30" s="397" t="n"/>
+      <c r="AA30" s="397" t="n"/>
+      <c r="AB30" s="398" t="n"/>
+      <c r="AC30" s="370" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="AD30" s="271" t="n"/>
-      <c r="AE30" s="271" t="n"/>
-      <c r="AF30" s="271" t="n"/>
-      <c r="AG30" s="271" t="n"/>
-      <c r="AH30" s="271" t="n"/>
-      <c r="AI30" s="271" t="n"/>
-      <c r="AJ30" s="271" t="n"/>
-      <c r="AK30" s="271" t="n"/>
-      <c r="AL30" s="272" t="n"/>
-      <c r="AM30" s="290" t="n"/>
-      <c r="AN30" s="319" t="n"/>
-      <c r="AO30" s="319" t="n"/>
-      <c r="AP30" s="319" t="n"/>
-      <c r="AQ30" s="319" t="n"/>
-      <c r="AR30" s="319" t="n"/>
-      <c r="AS30" s="319" t="n"/>
-      <c r="AT30" s="319" t="n"/>
-      <c r="AU30" s="319" t="n"/>
-      <c r="AV30" s="319" t="n"/>
-      <c r="AW30" s="319" t="n"/>
-      <c r="AX30" s="319" t="n"/>
-      <c r="AY30" s="319" t="n"/>
-      <c r="AZ30" s="319" t="n"/>
-      <c r="BA30" s="319" t="n"/>
-      <c r="BB30" s="319" t="n"/>
-      <c r="BC30" s="319" t="n"/>
-      <c r="BD30" s="321" t="n"/>
+      <c r="AD30" s="387" t="n"/>
+      <c r="AE30" s="387" t="n"/>
+      <c r="AF30" s="387" t="n"/>
+      <c r="AG30" s="387" t="n"/>
+      <c r="AH30" s="387" t="n"/>
+      <c r="AI30" s="387" t="n"/>
+      <c r="AJ30" s="387" t="n"/>
+      <c r="AK30" s="387" t="n"/>
+      <c r="AL30" s="388" t="n"/>
+      <c r="AM30" s="367" t="n"/>
+      <c r="AN30" s="397" t="n"/>
+      <c r="AO30" s="397" t="n"/>
+      <c r="AP30" s="397" t="n"/>
+      <c r="AQ30" s="397" t="n"/>
+      <c r="AR30" s="397" t="n"/>
+      <c r="AS30" s="397" t="n"/>
+      <c r="AT30" s="397" t="n"/>
+      <c r="AU30" s="397" t="n"/>
+      <c r="AV30" s="397" t="n"/>
+      <c r="AW30" s="397" t="n"/>
+      <c r="AX30" s="397" t="n"/>
+      <c r="AY30" s="397" t="n"/>
+      <c r="AZ30" s="397" t="n"/>
+      <c r="BA30" s="397" t="n"/>
+      <c r="BB30" s="397" t="n"/>
+      <c r="BC30" s="397" t="n"/>
+      <c r="BD30" s="398" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="287" t="inlineStr">
+      <c r="A31" s="353" t="inlineStr">
         <is>
           <t>Suspect / Hold Items</t>
         </is>
       </c>
-      <c r="B31" s="271" t="n"/>
-      <c r="C31" s="271" t="n"/>
-      <c r="D31" s="271" t="n"/>
-      <c r="E31" s="271" t="n"/>
-      <c r="F31" s="271" t="n"/>
-      <c r="G31" s="271" t="n"/>
-      <c r="H31" s="271" t="n"/>
-      <c r="I31" s="271" t="n"/>
-      <c r="J31" s="272" t="n"/>
-      <c r="K31" s="288" t="n"/>
-      <c r="L31" s="319" t="n"/>
-      <c r="M31" s="319" t="n"/>
-      <c r="N31" s="319" t="n"/>
-      <c r="O31" s="319" t="n"/>
-      <c r="P31" s="319" t="n"/>
-      <c r="Q31" s="319" t="n"/>
-      <c r="R31" s="319" t="n"/>
-      <c r="S31" s="319" t="n"/>
-      <c r="T31" s="319" t="n"/>
-      <c r="U31" s="319" t="n"/>
-      <c r="V31" s="319" t="n"/>
-      <c r="W31" s="319" t="n"/>
-      <c r="X31" s="319" t="n"/>
-      <c r="Y31" s="319" t="n"/>
-      <c r="Z31" s="319" t="n"/>
-      <c r="AA31" s="319" t="n"/>
-      <c r="AB31" s="320" t="n"/>
-      <c r="AC31" s="289" t="inlineStr">
+      <c r="B31" s="389" t="n"/>
+      <c r="C31" s="389" t="n"/>
+      <c r="D31" s="389" t="n"/>
+      <c r="E31" s="389" t="n"/>
+      <c r="F31" s="389" t="n"/>
+      <c r="G31" s="389" t="n"/>
+      <c r="H31" s="389" t="n"/>
+      <c r="I31" s="389" t="n"/>
+      <c r="J31" s="390" t="n"/>
+      <c r="K31" s="367" t="n"/>
+      <c r="L31" s="395" t="n"/>
+      <c r="M31" s="395" t="n"/>
+      <c r="N31" s="395" t="n"/>
+      <c r="O31" s="395" t="n"/>
+      <c r="P31" s="395" t="n"/>
+      <c r="Q31" s="395" t="n"/>
+      <c r="R31" s="395" t="n"/>
+      <c r="S31" s="395" t="n"/>
+      <c r="T31" s="395" t="n"/>
+      <c r="U31" s="395" t="n"/>
+      <c r="V31" s="395" t="n"/>
+      <c r="W31" s="395" t="n"/>
+      <c r="X31" s="395" t="n"/>
+      <c r="Y31" s="395" t="n"/>
+      <c r="Z31" s="395" t="n"/>
+      <c r="AA31" s="395" t="n"/>
+      <c r="AB31" s="396" t="n"/>
+      <c r="AC31" s="370" t="inlineStr">
         <is>
           <t>Final Status</t>
         </is>
       </c>
-      <c r="AD31" s="271" t="n"/>
-      <c r="AE31" s="271" t="n"/>
-      <c r="AF31" s="271" t="n"/>
-      <c r="AG31" s="271" t="n"/>
-      <c r="AH31" s="271" t="n"/>
-      <c r="AI31" s="271" t="n"/>
-      <c r="AJ31" s="271" t="n"/>
-      <c r="AK31" s="271" t="n"/>
-      <c r="AL31" s="272" t="n"/>
-      <c r="AM31" s="290" t="n"/>
-      <c r="AN31" s="319" t="n"/>
-      <c r="AO31" s="319" t="n"/>
-      <c r="AP31" s="319" t="n"/>
-      <c r="AQ31" s="319" t="n"/>
-      <c r="AR31" s="319" t="n"/>
-      <c r="AS31" s="319" t="n"/>
-      <c r="AT31" s="319" t="n"/>
-      <c r="AU31" s="319" t="n"/>
-      <c r="AV31" s="319" t="n"/>
-      <c r="AW31" s="319" t="n"/>
-      <c r="AX31" s="319" t="n"/>
-      <c r="AY31" s="319" t="n"/>
-      <c r="AZ31" s="319" t="n"/>
-      <c r="BA31" s="319" t="n"/>
-      <c r="BB31" s="319" t="n"/>
-      <c r="BC31" s="319" t="n"/>
-      <c r="BD31" s="321" t="n"/>
+      <c r="AD31" s="389" t="n"/>
+      <c r="AE31" s="389" t="n"/>
+      <c r="AF31" s="389" t="n"/>
+      <c r="AG31" s="389" t="n"/>
+      <c r="AH31" s="389" t="n"/>
+      <c r="AI31" s="389" t="n"/>
+      <c r="AJ31" s="389" t="n"/>
+      <c r="AK31" s="389" t="n"/>
+      <c r="AL31" s="390" t="n"/>
+      <c r="AM31" s="367" t="n"/>
+      <c r="AN31" s="395" t="n"/>
+      <c r="AO31" s="395" t="n"/>
+      <c r="AP31" s="395" t="n"/>
+      <c r="AQ31" s="395" t="n"/>
+      <c r="AR31" s="395" t="n"/>
+      <c r="AS31" s="395" t="n"/>
+      <c r="AT31" s="395" t="n"/>
+      <c r="AU31" s="395" t="n"/>
+      <c r="AV31" s="395" t="n"/>
+      <c r="AW31" s="395" t="n"/>
+      <c r="AX31" s="395" t="n"/>
+      <c r="AY31" s="395" t="n"/>
+      <c r="AZ31" s="395" t="n"/>
+      <c r="BA31" s="395" t="n"/>
+      <c r="BB31" s="395" t="n"/>
+      <c r="BC31" s="395" t="n"/>
+      <c r="BD31" s="396" t="n"/>
     </row>
     <row r="32" ht="4" customHeight="1">
-      <c r="A32" s="25" t="n"/>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="337" t="inlineStr">
+      <c r="A32" s="345" t="n"/>
+      <c r="B32" s="345" t="n"/>
+      <c r="C32" s="345" t="n"/>
+      <c r="D32" s="345" t="n"/>
+      <c r="E32" s="345" t="n"/>
+      <c r="F32" s="345" t="n"/>
+      <c r="G32" s="345" t="n"/>
+      <c r="H32" s="345" t="n"/>
+      <c r="I32" s="345" t="n"/>
+      <c r="J32" s="345" t="n"/>
+      <c r="K32" s="345" t="n"/>
+      <c r="L32" s="345" t="n"/>
+      <c r="M32" s="345" t="n"/>
+      <c r="N32" s="345" t="n"/>
+      <c r="O32" s="345" t="n"/>
+      <c r="P32" s="345" t="n"/>
+      <c r="Q32" s="345" t="n"/>
+      <c r="R32" s="345" t="n"/>
+      <c r="S32" s="345" t="n"/>
+      <c r="T32" s="345" t="n"/>
+      <c r="U32" s="345" t="n"/>
+      <c r="V32" s="345" t="n"/>
+      <c r="W32" s="345" t="n"/>
+      <c r="X32" s="345" t="n"/>
+      <c r="Y32" s="345" t="n"/>
+      <c r="Z32" s="345" t="n"/>
+      <c r="AA32" s="345" t="n"/>
+      <c r="AB32" s="345" t="n"/>
+      <c r="AC32" s="345" t="n"/>
+      <c r="AD32" s="345" t="n"/>
+      <c r="AE32" s="345" t="n"/>
+      <c r="AF32" s="345" t="n"/>
+      <c r="AG32" s="345" t="n"/>
+      <c r="AH32" s="345" t="n"/>
+      <c r="AI32" s="345" t="n"/>
+      <c r="AJ32" s="345" t="n"/>
+      <c r="AK32" s="345" t="n"/>
+      <c r="AL32" s="345" t="n"/>
+      <c r="AM32" s="345" t="n"/>
+      <c r="AN32" s="345" t="n"/>
+      <c r="AO32" s="345" t="n"/>
+      <c r="AP32" s="345" t="n"/>
+      <c r="AQ32" s="345" t="n"/>
+      <c r="AR32" s="345" t="n"/>
+      <c r="AS32" s="345" t="n"/>
+      <c r="AT32" s="345" t="n"/>
+      <c r="AU32" s="345" t="n"/>
+      <c r="AV32" s="345" t="n"/>
+      <c r="AW32" s="345" t="n"/>
+      <c r="AX32" s="345" t="n"/>
+      <c r="AY32" s="345" t="n"/>
+      <c r="AZ32" s="345" t="n"/>
+      <c r="BA32" s="345" t="n"/>
+      <c r="BB32" s="345" t="n"/>
+      <c r="BC32" s="345" t="n"/>
+      <c r="BD32" s="345" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="381" t="inlineStr">
         <is>
           <t>NOTICE: Review face only. Complete row-level entry, filters and frozen-header operations on sheet GAGE_DATA_LOG. Keep English only, preserve history, record owner and evidence reference, and follow controlled dropdowns / gate rules.</t>
         </is>
       </c>
-      <c r="B33" s="281" t="n"/>
-      <c r="C33" s="281" t="n"/>
-      <c r="D33" s="281" t="n"/>
-      <c r="E33" s="281" t="n"/>
-      <c r="F33" s="281" t="n"/>
-      <c r="G33" s="281" t="n"/>
-      <c r="H33" s="281" t="n"/>
-      <c r="I33" s="281" t="n"/>
-      <c r="J33" s="281" t="n"/>
-      <c r="K33" s="281" t="n"/>
-      <c r="L33" s="281" t="n"/>
-      <c r="M33" s="281" t="n"/>
-      <c r="N33" s="281" t="n"/>
-      <c r="O33" s="281" t="n"/>
-      <c r="P33" s="281" t="n"/>
-      <c r="Q33" s="281" t="n"/>
-      <c r="R33" s="281" t="n"/>
-      <c r="S33" s="281" t="n"/>
-      <c r="T33" s="281" t="n"/>
-      <c r="U33" s="281" t="n"/>
-      <c r="V33" s="281" t="n"/>
-      <c r="W33" s="281" t="n"/>
-      <c r="X33" s="281" t="n"/>
-      <c r="Y33" s="281" t="n"/>
-      <c r="Z33" s="281" t="n"/>
-      <c r="AA33" s="281" t="n"/>
-      <c r="AB33" s="281" t="n"/>
-      <c r="AC33" s="281" t="n"/>
-      <c r="AD33" s="281" t="n"/>
-      <c r="AE33" s="281" t="n"/>
-      <c r="AF33" s="281" t="n"/>
-      <c r="AG33" s="281" t="n"/>
-      <c r="AH33" s="281" t="n"/>
-      <c r="AI33" s="281" t="n"/>
-      <c r="AJ33" s="281" t="n"/>
-      <c r="AK33" s="281" t="n"/>
-      <c r="AL33" s="281" t="n"/>
-      <c r="AM33" s="281" t="n"/>
-      <c r="AN33" s="281" t="n"/>
-      <c r="AO33" s="281" t="n"/>
-      <c r="AP33" s="281" t="n"/>
-      <c r="AQ33" s="281" t="n"/>
-      <c r="AR33" s="281" t="n"/>
-      <c r="AS33" s="281" t="n"/>
-      <c r="AT33" s="281" t="n"/>
-      <c r="AU33" s="281" t="n"/>
-      <c r="AV33" s="281" t="n"/>
-      <c r="AW33" s="281" t="n"/>
-      <c r="AX33" s="281" t="n"/>
-      <c r="AY33" s="281" t="n"/>
-      <c r="AZ33" s="281" t="n"/>
-      <c r="BA33" s="281" t="n"/>
-      <c r="BB33" s="281" t="n"/>
-      <c r="BC33" s="281" t="n"/>
-      <c r="BD33" s="283" t="n"/>
+      <c r="B33" s="399" t="n"/>
+      <c r="C33" s="399" t="n"/>
+      <c r="D33" s="399" t="n"/>
+      <c r="E33" s="399" t="n"/>
+      <c r="F33" s="399" t="n"/>
+      <c r="G33" s="399" t="n"/>
+      <c r="H33" s="399" t="n"/>
+      <c r="I33" s="399" t="n"/>
+      <c r="J33" s="399" t="n"/>
+      <c r="K33" s="399" t="n"/>
+      <c r="L33" s="399" t="n"/>
+      <c r="M33" s="399" t="n"/>
+      <c r="N33" s="399" t="n"/>
+      <c r="O33" s="399" t="n"/>
+      <c r="P33" s="399" t="n"/>
+      <c r="Q33" s="399" t="n"/>
+      <c r="R33" s="399" t="n"/>
+      <c r="S33" s="399" t="n"/>
+      <c r="T33" s="399" t="n"/>
+      <c r="U33" s="399" t="n"/>
+      <c r="V33" s="399" t="n"/>
+      <c r="W33" s="399" t="n"/>
+      <c r="X33" s="399" t="n"/>
+      <c r="Y33" s="399" t="n"/>
+      <c r="Z33" s="399" t="n"/>
+      <c r="AA33" s="399" t="n"/>
+      <c r="AB33" s="399" t="n"/>
+      <c r="AC33" s="399" t="n"/>
+      <c r="AD33" s="399" t="n"/>
+      <c r="AE33" s="399" t="n"/>
+      <c r="AF33" s="399" t="n"/>
+      <c r="AG33" s="399" t="n"/>
+      <c r="AH33" s="399" t="n"/>
+      <c r="AI33" s="399" t="n"/>
+      <c r="AJ33" s="399" t="n"/>
+      <c r="AK33" s="399" t="n"/>
+      <c r="AL33" s="399" t="n"/>
+      <c r="AM33" s="399" t="n"/>
+      <c r="AN33" s="399" t="n"/>
+      <c r="AO33" s="399" t="n"/>
+      <c r="AP33" s="399" t="n"/>
+      <c r="AQ33" s="399" t="n"/>
+      <c r="AR33" s="399" t="n"/>
+      <c r="AS33" s="399" t="n"/>
+      <c r="AT33" s="399" t="n"/>
+      <c r="AU33" s="399" t="n"/>
+      <c r="AV33" s="399" t="n"/>
+      <c r="AW33" s="399" t="n"/>
+      <c r="AX33" s="399" t="n"/>
+      <c r="AY33" s="399" t="n"/>
+      <c r="AZ33" s="399" t="n"/>
+      <c r="BA33" s="399" t="n"/>
+      <c r="BB33" s="399" t="n"/>
+      <c r="BC33" s="399" t="n"/>
+      <c r="BD33" s="400" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1"/>
     <row r="35" ht="20" customHeight="1"/>
@@ -7681,7 +9464,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8026,30 +9808,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="317" t="inlineStr">
+      <c r="A1" s="384" t="inlineStr">
         <is>
           <t>Periodic Review Summary</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="402" t="n"/>
+      <c r="C1" s="402" t="n"/>
+      <c r="D1" s="402" t="n"/>
+      <c r="E1" s="402" t="n"/>
+      <c r="F1" s="402" t="n"/>
+      <c r="G1" s="403" t="n"/>
+      <c r="H1" s="342" t="n"/>
+      <c r="I1" s="342" t="n"/>
+      <c r="J1" s="342" t="n"/>
+      <c r="K1" s="342" t="n"/>
+      <c r="L1" s="342" t="n"/>
+      <c r="M1" s="342" t="n"/>
+      <c r="N1" s="342" t="n"/>
+      <c r="O1" s="342" t="n"/>
+      <c r="P1" s="342" t="n"/>
+      <c r="Q1" s="342" t="n"/>
+      <c r="R1" s="342" t="n"/>
+      <c r="S1" s="342" t="n"/>
+      <c r="T1" s="342" t="n"/>
+      <c r="U1" s="342" t="n"/>
+      <c r="V1" s="342" t="n"/>
+      <c r="W1" s="342" t="n"/>
+      <c r="X1" s="342" t="n"/>
+      <c r="Y1" s="342" t="n"/>
+      <c r="Z1" s="342" t="n"/>
+      <c r="AA1" s="342" t="n"/>
+      <c r="AB1" s="342" t="n"/>
+      <c r="AC1" s="342" t="n"/>
+      <c r="AD1" s="342" t="n"/>
+      <c r="AE1" s="342" t="n"/>
+      <c r="AF1" s="342" t="n"/>
+      <c r="AG1" s="342" t="n"/>
+      <c r="AH1" s="342" t="n"/>
+      <c r="AI1" s="342" t="n"/>
+      <c r="AJ1" s="342" t="n"/>
+      <c r="AK1" s="342" t="n"/>
+      <c r="AL1" s="342" t="n"/>
+      <c r="AM1" s="342" t="n"/>
+      <c r="AN1" s="342" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="318" t="inlineStr">
@@ -8057,89 +9905,385 @@
           <t>Pre-use gage-verification gate before FRM-621/631/641 inspection execution and before Pack A first-piece/release decisions. Formal MSA remains in FRM-611/612/613.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="H2" s="342" t="n"/>
+      <c r="I2" s="342" t="n"/>
+      <c r="J2" s="342" t="n"/>
+      <c r="K2" s="342" t="n"/>
+      <c r="L2" s="342" t="n"/>
+      <c r="M2" s="342" t="n"/>
+      <c r="N2" s="342" t="n"/>
+      <c r="O2" s="342" t="n"/>
+      <c r="P2" s="342" t="n"/>
+      <c r="Q2" s="342" t="n"/>
+      <c r="R2" s="342" t="n"/>
+      <c r="S2" s="342" t="n"/>
+      <c r="T2" s="342" t="n"/>
+      <c r="U2" s="342" t="n"/>
+      <c r="V2" s="342" t="n"/>
+      <c r="W2" s="342" t="n"/>
+      <c r="X2" s="342" t="n"/>
+      <c r="Y2" s="342" t="n"/>
+      <c r="Z2" s="342" t="n"/>
+      <c r="AA2" s="342" t="n"/>
+      <c r="AB2" s="342" t="n"/>
+      <c r="AC2" s="342" t="n"/>
+      <c r="AD2" s="342" t="n"/>
+      <c r="AE2" s="342" t="n"/>
+      <c r="AF2" s="342" t="n"/>
+      <c r="AG2" s="342" t="n"/>
+      <c r="AH2" s="342" t="n"/>
+      <c r="AI2" s="342" t="n"/>
+      <c r="AJ2" s="342" t="n"/>
+      <c r="AK2" s="342" t="n"/>
+      <c r="AL2" s="342" t="n"/>
+      <c r="AM2" s="342" t="n"/>
+      <c r="AN2" s="342" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="342" t="n"/>
+      <c r="B3" s="342" t="n"/>
+      <c r="C3" s="342" t="n"/>
+      <c r="D3" s="342" t="n"/>
+      <c r="E3" s="342" t="n"/>
+      <c r="F3" s="342" t="n"/>
+      <c r="G3" s="342" t="n"/>
+      <c r="H3" s="342" t="n"/>
+      <c r="I3" s="342" t="n"/>
+      <c r="J3" s="342" t="n"/>
+      <c r="K3" s="342" t="n"/>
+      <c r="L3" s="342" t="n"/>
+      <c r="M3" s="342" t="n"/>
+      <c r="N3" s="342" t="n"/>
+      <c r="O3" s="342" t="n"/>
+      <c r="P3" s="342" t="n"/>
+      <c r="Q3" s="342" t="n"/>
+      <c r="R3" s="342" t="n"/>
+      <c r="S3" s="342" t="n"/>
+      <c r="T3" s="342" t="n"/>
+      <c r="U3" s="342" t="n"/>
+      <c r="V3" s="342" t="n"/>
+      <c r="W3" s="342" t="n"/>
+      <c r="X3" s="342" t="n"/>
+      <c r="Y3" s="342" t="n"/>
+      <c r="Z3" s="342" t="n"/>
+      <c r="AA3" s="342" t="n"/>
+      <c r="AB3" s="342" t="n"/>
+      <c r="AC3" s="342" t="n"/>
+      <c r="AD3" s="342" t="n"/>
+      <c r="AE3" s="342" t="n"/>
+      <c r="AF3" s="342" t="n"/>
+      <c r="AG3" s="342" t="n"/>
+      <c r="AH3" s="342" t="n"/>
+      <c r="AI3" s="342" t="n"/>
+      <c r="AJ3" s="342" t="n"/>
+      <c r="AK3" s="342" t="n"/>
+      <c r="AL3" s="342" t="n"/>
+      <c r="AM3" s="342" t="n"/>
+      <c r="AN3" s="342" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="291" t="inlineStr">
+      <c r="A4" s="347" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="291" t="inlineStr">
+      <c r="B4" s="347" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="291" t="inlineStr">
+      <c r="C4" s="347" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="342" t="n"/>
+      <c r="E4" s="342" t="n"/>
+      <c r="F4" s="342" t="n"/>
+      <c r="G4" s="342" t="n"/>
+      <c r="H4" s="342" t="n"/>
+      <c r="I4" s="342" t="n"/>
+      <c r="J4" s="342" t="n"/>
+      <c r="K4" s="342" t="n"/>
+      <c r="L4" s="342" t="n"/>
+      <c r="M4" s="342" t="n"/>
+      <c r="N4" s="342" t="n"/>
+      <c r="O4" s="342" t="n"/>
+      <c r="P4" s="342" t="n"/>
+      <c r="Q4" s="342" t="n"/>
+      <c r="R4" s="342" t="n"/>
+      <c r="S4" s="342" t="n"/>
+      <c r="T4" s="342" t="n"/>
+      <c r="U4" s="342" t="n"/>
+      <c r="V4" s="342" t="n"/>
+      <c r="W4" s="342" t="n"/>
+      <c r="X4" s="342" t="n"/>
+      <c r="Y4" s="342" t="n"/>
+      <c r="Z4" s="342" t="n"/>
+      <c r="AA4" s="342" t="n"/>
+      <c r="AB4" s="342" t="n"/>
+      <c r="AC4" s="342" t="n"/>
+      <c r="AD4" s="342" t="n"/>
+      <c r="AE4" s="342" t="n"/>
+      <c r="AF4" s="342" t="n"/>
+      <c r="AG4" s="342" t="n"/>
+      <c r="AH4" s="342" t="n"/>
+      <c r="AI4" s="342" t="n"/>
+      <c r="AJ4" s="342" t="n"/>
+      <c r="AK4" s="342" t="n"/>
+      <c r="AL4" s="342" t="n"/>
+      <c r="AM4" s="342" t="n"/>
+      <c r="AN4" s="342" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="293" t="inlineStr">
+      <c r="A5" s="385" t="inlineStr">
         <is>
           <t>Review Period</t>
         </is>
       </c>
-      <c r="B5" s="294" t="inlineStr"/>
-      <c r="C5" s="294" t="inlineStr">
+      <c r="B5" s="386" t="inlineStr"/>
+      <c r="C5" s="386" t="inlineStr">
         <is>
           <t>Define the review cycle for this log.</t>
         </is>
       </c>
+      <c r="D5" s="342" t="n"/>
+      <c r="E5" s="342" t="n"/>
+      <c r="F5" s="342" t="n"/>
+      <c r="G5" s="342" t="n"/>
+      <c r="H5" s="342" t="n"/>
+      <c r="I5" s="342" t="n"/>
+      <c r="J5" s="342" t="n"/>
+      <c r="K5" s="342" t="n"/>
+      <c r="L5" s="342" t="n"/>
+      <c r="M5" s="342" t="n"/>
+      <c r="N5" s="342" t="n"/>
+      <c r="O5" s="342" t="n"/>
+      <c r="P5" s="342" t="n"/>
+      <c r="Q5" s="342" t="n"/>
+      <c r="R5" s="342" t="n"/>
+      <c r="S5" s="342" t="n"/>
+      <c r="T5" s="342" t="n"/>
+      <c r="U5" s="342" t="n"/>
+      <c r="V5" s="342" t="n"/>
+      <c r="W5" s="342" t="n"/>
+      <c r="X5" s="342" t="n"/>
+      <c r="Y5" s="342" t="n"/>
+      <c r="Z5" s="342" t="n"/>
+      <c r="AA5" s="342" t="n"/>
+      <c r="AB5" s="342" t="n"/>
+      <c r="AC5" s="342" t="n"/>
+      <c r="AD5" s="342" t="n"/>
+      <c r="AE5" s="342" t="n"/>
+      <c r="AF5" s="342" t="n"/>
+      <c r="AG5" s="342" t="n"/>
+      <c r="AH5" s="342" t="n"/>
+      <c r="AI5" s="342" t="n"/>
+      <c r="AJ5" s="342" t="n"/>
+      <c r="AK5" s="342" t="n"/>
+      <c r="AL5" s="342" t="n"/>
+      <c r="AM5" s="342" t="n"/>
+      <c r="AN5" s="342" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="293" t="inlineStr">
+      <c r="A6" s="385" t="inlineStr">
         <is>
           <t>Responsible Owner</t>
         </is>
       </c>
-      <c r="B6" s="294" t="inlineStr"/>
-      <c r="C6" s="294" t="inlineStr">
+      <c r="B6" s="386" t="inlineStr"/>
+      <c r="C6" s="386" t="inlineStr">
         <is>
           <t>No per-row release signature is required unless a row contains an explicit disposition or escalation. A named owner shall review the register or log at the defined cadence, and any formal period-end review shall be signed or e-signed by the responsible owner.</t>
         </is>
       </c>
+      <c r="D6" s="342" t="n"/>
+      <c r="E6" s="342" t="n"/>
+      <c r="F6" s="342" t="n"/>
+      <c r="G6" s="342" t="n"/>
+      <c r="H6" s="342" t="n"/>
+      <c r="I6" s="342" t="n"/>
+      <c r="J6" s="342" t="n"/>
+      <c r="K6" s="342" t="n"/>
+      <c r="L6" s="342" t="n"/>
+      <c r="M6" s="342" t="n"/>
+      <c r="N6" s="342" t="n"/>
+      <c r="O6" s="342" t="n"/>
+      <c r="P6" s="342" t="n"/>
+      <c r="Q6" s="342" t="n"/>
+      <c r="R6" s="342" t="n"/>
+      <c r="S6" s="342" t="n"/>
+      <c r="T6" s="342" t="n"/>
+      <c r="U6" s="342" t="n"/>
+      <c r="V6" s="342" t="n"/>
+      <c r="W6" s="342" t="n"/>
+      <c r="X6" s="342" t="n"/>
+      <c r="Y6" s="342" t="n"/>
+      <c r="Z6" s="342" t="n"/>
+      <c r="AA6" s="342" t="n"/>
+      <c r="AB6" s="342" t="n"/>
+      <c r="AC6" s="342" t="n"/>
+      <c r="AD6" s="342" t="n"/>
+      <c r="AE6" s="342" t="n"/>
+      <c r="AF6" s="342" t="n"/>
+      <c r="AG6" s="342" t="n"/>
+      <c r="AH6" s="342" t="n"/>
+      <c r="AI6" s="342" t="n"/>
+      <c r="AJ6" s="342" t="n"/>
+      <c r="AK6" s="342" t="n"/>
+      <c r="AL6" s="342" t="n"/>
+      <c r="AM6" s="342" t="n"/>
+      <c r="AN6" s="342" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="293" t="inlineStr">
+      <c r="A7" s="385" t="inlineStr">
         <is>
           <t>Open Items</t>
         </is>
       </c>
-      <c r="B7" s="294" t="inlineStr"/>
-      <c r="C7" s="294" t="inlineStr">
+      <c r="B7" s="386" t="inlineStr"/>
+      <c r="C7" s="386" t="inlineStr">
         <is>
           <t>Count from main log where status remains open or in progress.</t>
         </is>
       </c>
+      <c r="D7" s="342" t="n"/>
+      <c r="E7" s="342" t="n"/>
+      <c r="F7" s="342" t="n"/>
+      <c r="G7" s="342" t="n"/>
+      <c r="H7" s="342" t="n"/>
+      <c r="I7" s="342" t="n"/>
+      <c r="J7" s="342" t="n"/>
+      <c r="K7" s="342" t="n"/>
+      <c r="L7" s="342" t="n"/>
+      <c r="M7" s="342" t="n"/>
+      <c r="N7" s="342" t="n"/>
+      <c r="O7" s="342" t="n"/>
+      <c r="P7" s="342" t="n"/>
+      <c r="Q7" s="342" t="n"/>
+      <c r="R7" s="342" t="n"/>
+      <c r="S7" s="342" t="n"/>
+      <c r="T7" s="342" t="n"/>
+      <c r="U7" s="342" t="n"/>
+      <c r="V7" s="342" t="n"/>
+      <c r="W7" s="342" t="n"/>
+      <c r="X7" s="342" t="n"/>
+      <c r="Y7" s="342" t="n"/>
+      <c r="Z7" s="342" t="n"/>
+      <c r="AA7" s="342" t="n"/>
+      <c r="AB7" s="342" t="n"/>
+      <c r="AC7" s="342" t="n"/>
+      <c r="AD7" s="342" t="n"/>
+      <c r="AE7" s="342" t="n"/>
+      <c r="AF7" s="342" t="n"/>
+      <c r="AG7" s="342" t="n"/>
+      <c r="AH7" s="342" t="n"/>
+      <c r="AI7" s="342" t="n"/>
+      <c r="AJ7" s="342" t="n"/>
+      <c r="AK7" s="342" t="n"/>
+      <c r="AL7" s="342" t="n"/>
+      <c r="AM7" s="342" t="n"/>
+      <c r="AN7" s="342" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="293" t="inlineStr">
+      <c r="A8" s="373" t="inlineStr">
         <is>
           <t>Escalated / Blocked Items</t>
         </is>
       </c>
-      <c r="B8" s="294" t="inlineStr"/>
-      <c r="C8" s="294" t="inlineStr">
+      <c r="B8" s="374" t="inlineStr"/>
+      <c r="C8" s="374" t="inlineStr">
         <is>
           <t>Reference abnormal findings that require management attention.</t>
         </is>
       </c>
+      <c r="D8" s="350" t="n"/>
+      <c r="E8" s="350" t="n"/>
+      <c r="F8" s="350" t="n"/>
+      <c r="G8" s="350" t="n"/>
+      <c r="H8" s="350" t="n"/>
+      <c r="I8" s="350" t="n"/>
+      <c r="J8" s="350" t="n"/>
+      <c r="K8" s="350" t="n"/>
+      <c r="L8" s="350" t="n"/>
+      <c r="M8" s="350" t="n"/>
+      <c r="N8" s="350" t="n"/>
+      <c r="O8" s="350" t="n"/>
+      <c r="P8" s="350" t="n"/>
+      <c r="Q8" s="350" t="n"/>
+      <c r="R8" s="350" t="n"/>
+      <c r="S8" s="350" t="n"/>
+      <c r="T8" s="350" t="n"/>
+      <c r="U8" s="350" t="n"/>
+      <c r="V8" s="350" t="n"/>
+      <c r="W8" s="350" t="n"/>
+      <c r="X8" s="350" t="n"/>
+      <c r="Y8" s="350" t="n"/>
+      <c r="Z8" s="350" t="n"/>
+      <c r="AA8" s="350" t="n"/>
+      <c r="AB8" s="350" t="n"/>
+      <c r="AC8" s="350" t="n"/>
+      <c r="AD8" s="350" t="n"/>
+      <c r="AE8" s="350" t="n"/>
+      <c r="AF8" s="350" t="n"/>
+      <c r="AG8" s="350" t="n"/>
+      <c r="AH8" s="350" t="n"/>
+      <c r="AI8" s="350" t="n"/>
+      <c r="AJ8" s="350" t="n"/>
+      <c r="AK8" s="350" t="n"/>
+      <c r="AL8" s="350" t="n"/>
+      <c r="AM8" s="350" t="n"/>
+      <c r="AN8" s="350" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="293" t="inlineStr">
+      <c r="A9" s="373" t="inlineStr">
         <is>
           <t>Review Conclusion</t>
         </is>
       </c>
-      <c r="B9" s="294" t="inlineStr"/>
-      <c r="C9" s="294" t="inlineStr">
+      <c r="B9" s="374" t="inlineStr"/>
+      <c r="C9" s="374" t="inlineStr">
         <is>
           <t>Use final status field on the main sheet for period closeout.</t>
         </is>
       </c>
+      <c r="D9" s="350" t="n"/>
+      <c r="E9" s="350" t="n"/>
+      <c r="F9" s="350" t="n"/>
+      <c r="G9" s="350" t="n"/>
+      <c r="H9" s="350" t="n"/>
+      <c r="I9" s="350" t="n"/>
+      <c r="J9" s="350" t="n"/>
+      <c r="K9" s="350" t="n"/>
+      <c r="L9" s="350" t="n"/>
+      <c r="M9" s="350" t="n"/>
+      <c r="N9" s="350" t="n"/>
+      <c r="O9" s="350" t="n"/>
+      <c r="P9" s="350" t="n"/>
+      <c r="Q9" s="350" t="n"/>
+      <c r="R9" s="350" t="n"/>
+      <c r="S9" s="350" t="n"/>
+      <c r="T9" s="350" t="n"/>
+      <c r="U9" s="350" t="n"/>
+      <c r="V9" s="350" t="n"/>
+      <c r="W9" s="350" t="n"/>
+      <c r="X9" s="350" t="n"/>
+      <c r="Y9" s="350" t="n"/>
+      <c r="Z9" s="350" t="n"/>
+      <c r="AA9" s="350" t="n"/>
+      <c r="AB9" s="350" t="n"/>
+      <c r="AC9" s="350" t="n"/>
+      <c r="AD9" s="350" t="n"/>
+      <c r="AE9" s="350" t="n"/>
+      <c r="AF9" s="350" t="n"/>
+      <c r="AG9" s="350" t="n"/>
+      <c r="AH9" s="350" t="n"/>
+      <c r="AI9" s="350" t="n"/>
+      <c r="AJ9" s="350" t="n"/>
+      <c r="AK9" s="350" t="n"/>
+      <c r="AL9" s="350" t="n"/>
+      <c r="AM9" s="350" t="n"/>
+      <c r="AN9" s="350" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -8148,7 +10292,8 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -8158,30 +10303,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="317" t="inlineStr">
+      <c r="A1" s="384" t="inlineStr">
         <is>
           <t>Import / Reference Guidance</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="402" t="n"/>
+      <c r="C1" s="402" t="n"/>
+      <c r="D1" s="402" t="n"/>
+      <c r="E1" s="402" t="n"/>
+      <c r="F1" s="402" t="n"/>
+      <c r="G1" s="403" t="n"/>
+      <c r="H1" s="342" t="n"/>
+      <c r="I1" s="342" t="n"/>
+      <c r="J1" s="342" t="n"/>
+      <c r="K1" s="342" t="n"/>
+      <c r="L1" s="342" t="n"/>
+      <c r="M1" s="342" t="n"/>
+      <c r="N1" s="342" t="n"/>
+      <c r="O1" s="342" t="n"/>
+      <c r="P1" s="342" t="n"/>
+      <c r="Q1" s="342" t="n"/>
+      <c r="R1" s="342" t="n"/>
+      <c r="S1" s="342" t="n"/>
+      <c r="T1" s="342" t="n"/>
+      <c r="U1" s="342" t="n"/>
+      <c r="V1" s="342" t="n"/>
+      <c r="W1" s="342" t="n"/>
+      <c r="X1" s="342" t="n"/>
+      <c r="Y1" s="342" t="n"/>
+      <c r="Z1" s="342" t="n"/>
+      <c r="AA1" s="342" t="n"/>
+      <c r="AB1" s="342" t="n"/>
+      <c r="AC1" s="342" t="n"/>
+      <c r="AD1" s="342" t="n"/>
+      <c r="AE1" s="342" t="n"/>
+      <c r="AF1" s="342" t="n"/>
+      <c r="AG1" s="342" t="n"/>
+      <c r="AH1" s="342" t="n"/>
+      <c r="AI1" s="342" t="n"/>
+      <c r="AJ1" s="342" t="n"/>
+      <c r="AK1" s="342" t="n"/>
+      <c r="AL1" s="342" t="n"/>
+      <c r="AM1" s="342" t="n"/>
+      <c r="AN1" s="342" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="318" t="inlineStr">
@@ -8189,54 +10400,202 @@
           <t>Import or reference keys from Epicor / M365 / calibration master rather than re-keying duplicates.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="H2" s="342" t="n"/>
+      <c r="I2" s="342" t="n"/>
+      <c r="J2" s="342" t="n"/>
+      <c r="K2" s="342" t="n"/>
+      <c r="L2" s="342" t="n"/>
+      <c r="M2" s="342" t="n"/>
+      <c r="N2" s="342" t="n"/>
+      <c r="O2" s="342" t="n"/>
+      <c r="P2" s="342" t="n"/>
+      <c r="Q2" s="342" t="n"/>
+      <c r="R2" s="342" t="n"/>
+      <c r="S2" s="342" t="n"/>
+      <c r="T2" s="342" t="n"/>
+      <c r="U2" s="342" t="n"/>
+      <c r="V2" s="342" t="n"/>
+      <c r="W2" s="342" t="n"/>
+      <c r="X2" s="342" t="n"/>
+      <c r="Y2" s="342" t="n"/>
+      <c r="Z2" s="342" t="n"/>
+      <c r="AA2" s="342" t="n"/>
+      <c r="AB2" s="342" t="n"/>
+      <c r="AC2" s="342" t="n"/>
+      <c r="AD2" s="342" t="n"/>
+      <c r="AE2" s="342" t="n"/>
+      <c r="AF2" s="342" t="n"/>
+      <c r="AG2" s="342" t="n"/>
+      <c r="AH2" s="342" t="n"/>
+      <c r="AI2" s="342" t="n"/>
+      <c r="AJ2" s="342" t="n"/>
+      <c r="AK2" s="342" t="n"/>
+      <c r="AL2" s="342" t="n"/>
+      <c r="AM2" s="342" t="n"/>
+      <c r="AN2" s="342" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="342" t="n"/>
+      <c r="B3" s="342" t="n"/>
+      <c r="C3" s="342" t="n"/>
+      <c r="D3" s="342" t="n"/>
+      <c r="E3" s="342" t="n"/>
+      <c r="F3" s="342" t="n"/>
+      <c r="G3" s="342" t="n"/>
+      <c r="H3" s="342" t="n"/>
+      <c r="I3" s="342" t="n"/>
+      <c r="J3" s="342" t="n"/>
+      <c r="K3" s="342" t="n"/>
+      <c r="L3" s="342" t="n"/>
+      <c r="M3" s="342" t="n"/>
+      <c r="N3" s="342" t="n"/>
+      <c r="O3" s="342" t="n"/>
+      <c r="P3" s="342" t="n"/>
+      <c r="Q3" s="342" t="n"/>
+      <c r="R3" s="342" t="n"/>
+      <c r="S3" s="342" t="n"/>
+      <c r="T3" s="342" t="n"/>
+      <c r="U3" s="342" t="n"/>
+      <c r="V3" s="342" t="n"/>
+      <c r="W3" s="342" t="n"/>
+      <c r="X3" s="342" t="n"/>
+      <c r="Y3" s="342" t="n"/>
+      <c r="Z3" s="342" t="n"/>
+      <c r="AA3" s="342" t="n"/>
+      <c r="AB3" s="342" t="n"/>
+      <c r="AC3" s="342" t="n"/>
+      <c r="AD3" s="342" t="n"/>
+      <c r="AE3" s="342" t="n"/>
+      <c r="AF3" s="342" t="n"/>
+      <c r="AG3" s="342" t="n"/>
+      <c r="AH3" s="342" t="n"/>
+      <c r="AI3" s="342" t="n"/>
+      <c r="AJ3" s="342" t="n"/>
+      <c r="AK3" s="342" t="n"/>
+      <c r="AL3" s="342" t="n"/>
+      <c r="AM3" s="342" t="n"/>
+      <c r="AN3" s="342" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="291" t="inlineStr">
+      <c r="A4" s="347" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="291" t="inlineStr">
+      <c r="B4" s="347" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="291" t="inlineStr">
+      <c r="C4" s="347" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="342" t="n"/>
+      <c r="E4" s="342" t="n"/>
+      <c r="F4" s="342" t="n"/>
+      <c r="G4" s="342" t="n"/>
+      <c r="H4" s="342" t="n"/>
+      <c r="I4" s="342" t="n"/>
+      <c r="J4" s="342" t="n"/>
+      <c r="K4" s="342" t="n"/>
+      <c r="L4" s="342" t="n"/>
+      <c r="M4" s="342" t="n"/>
+      <c r="N4" s="342" t="n"/>
+      <c r="O4" s="342" t="n"/>
+      <c r="P4" s="342" t="n"/>
+      <c r="Q4" s="342" t="n"/>
+      <c r="R4" s="342" t="n"/>
+      <c r="S4" s="342" t="n"/>
+      <c r="T4" s="342" t="n"/>
+      <c r="U4" s="342" t="n"/>
+      <c r="V4" s="342" t="n"/>
+      <c r="W4" s="342" t="n"/>
+      <c r="X4" s="342" t="n"/>
+      <c r="Y4" s="342" t="n"/>
+      <c r="Z4" s="342" t="n"/>
+      <c r="AA4" s="342" t="n"/>
+      <c r="AB4" s="342" t="n"/>
+      <c r="AC4" s="342" t="n"/>
+      <c r="AD4" s="342" t="n"/>
+      <c r="AE4" s="342" t="n"/>
+      <c r="AF4" s="342" t="n"/>
+      <c r="AG4" s="342" t="n"/>
+      <c r="AH4" s="342" t="n"/>
+      <c r="AI4" s="342" t="n"/>
+      <c r="AJ4" s="342" t="n"/>
+      <c r="AK4" s="342" t="n"/>
+      <c r="AL4" s="342" t="n"/>
+      <c r="AM4" s="342" t="n"/>
+      <c r="AN4" s="342" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="293" t="inlineStr">
+      <c r="A5" s="385" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="294" t="inlineStr">
+      <c r="B5" s="386" t="inlineStr">
         <is>
           <t>Calibration / QA file + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="294" t="inlineStr">
+      <c r="C5" s="386" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
+      <c r="D5" s="342" t="n"/>
+      <c r="E5" s="342" t="n"/>
+      <c r="F5" s="342" t="n"/>
+      <c r="G5" s="342" t="n"/>
+      <c r="H5" s="342" t="n"/>
+      <c r="I5" s="342" t="n"/>
+      <c r="J5" s="342" t="n"/>
+      <c r="K5" s="342" t="n"/>
+      <c r="L5" s="342" t="n"/>
+      <c r="M5" s="342" t="n"/>
+      <c r="N5" s="342" t="n"/>
+      <c r="O5" s="342" t="n"/>
+      <c r="P5" s="342" t="n"/>
+      <c r="Q5" s="342" t="n"/>
+      <c r="R5" s="342" t="n"/>
+      <c r="S5" s="342" t="n"/>
+      <c r="T5" s="342" t="n"/>
+      <c r="U5" s="342" t="n"/>
+      <c r="V5" s="342" t="n"/>
+      <c r="W5" s="342" t="n"/>
+      <c r="X5" s="342" t="n"/>
+      <c r="Y5" s="342" t="n"/>
+      <c r="Z5" s="342" t="n"/>
+      <c r="AA5" s="342" t="n"/>
+      <c r="AB5" s="342" t="n"/>
+      <c r="AC5" s="342" t="n"/>
+      <c r="AD5" s="342" t="n"/>
+      <c r="AE5" s="342" t="n"/>
+      <c r="AF5" s="342" t="n"/>
+      <c r="AG5" s="342" t="n"/>
+      <c r="AH5" s="342" t="n"/>
+      <c r="AI5" s="342" t="n"/>
+      <c r="AJ5" s="342" t="n"/>
+      <c r="AK5" s="342" t="n"/>
+      <c r="AL5" s="342" t="n"/>
+      <c r="AM5" s="342" t="n"/>
+      <c r="AN5" s="342" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="293" t="inlineStr">
+      <c r="A6" s="385" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="294" t="inlineStr">
+      <c r="B6" s="386" t="inlineStr">
         <is>
           <t>Pre-use gage-verification gate before FRM-621/631/641 inspection execution and before Pack A first-piece/release decisions. Formal MSA remains in FRM-611/612/613.</t>
         </is>
       </c>
-      <c r="C6" s="294" t="inlineStr">
+      <c r="C6" s="386" t="inlineStr">
         <is>
           <t>This form does not replace SOP-601; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-602; this form captures results, checks, decisions or exceptions only.
@@ -8244,159 +10603,529 @@
 System-of-record / source-of-truth boundary: Calibration / QA file + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
+      <c r="D6" s="342" t="n"/>
+      <c r="E6" s="342" t="n"/>
+      <c r="F6" s="342" t="n"/>
+      <c r="G6" s="342" t="n"/>
+      <c r="H6" s="342" t="n"/>
+      <c r="I6" s="342" t="n"/>
+      <c r="J6" s="342" t="n"/>
+      <c r="K6" s="342" t="n"/>
+      <c r="L6" s="342" t="n"/>
+      <c r="M6" s="342" t="n"/>
+      <c r="N6" s="342" t="n"/>
+      <c r="O6" s="342" t="n"/>
+      <c r="P6" s="342" t="n"/>
+      <c r="Q6" s="342" t="n"/>
+      <c r="R6" s="342" t="n"/>
+      <c r="S6" s="342" t="n"/>
+      <c r="T6" s="342" t="n"/>
+      <c r="U6" s="342" t="n"/>
+      <c r="V6" s="342" t="n"/>
+      <c r="W6" s="342" t="n"/>
+      <c r="X6" s="342" t="n"/>
+      <c r="Y6" s="342" t="n"/>
+      <c r="Z6" s="342" t="n"/>
+      <c r="AA6" s="342" t="n"/>
+      <c r="AB6" s="342" t="n"/>
+      <c r="AC6" s="342" t="n"/>
+      <c r="AD6" s="342" t="n"/>
+      <c r="AE6" s="342" t="n"/>
+      <c r="AF6" s="342" t="n"/>
+      <c r="AG6" s="342" t="n"/>
+      <c r="AH6" s="342" t="n"/>
+      <c r="AI6" s="342" t="n"/>
+      <c r="AJ6" s="342" t="n"/>
+      <c r="AK6" s="342" t="n"/>
+      <c r="AL6" s="342" t="n"/>
+      <c r="AM6" s="342" t="n"/>
+      <c r="AN6" s="342" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="293" t="inlineStr">
+      <c r="A7" s="385" t="inlineStr">
         <is>
           <t>SOP SOP-601</t>
         </is>
       </c>
-      <c r="B7" s="294" t="inlineStr">
+      <c r="B7" s="386" t="inlineStr">
         <is>
           <t>SOP-601 — Hiệu chuẩn và kiểm soát dụng cụ đo | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="294" t="inlineStr">
+      <c r="C7" s="386" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-601-calibration-and-gage-control.html</t>
         </is>
       </c>
+      <c r="D7" s="342" t="n"/>
+      <c r="E7" s="342" t="n"/>
+      <c r="F7" s="342" t="n"/>
+      <c r="G7" s="342" t="n"/>
+      <c r="H7" s="342" t="n"/>
+      <c r="I7" s="342" t="n"/>
+      <c r="J7" s="342" t="n"/>
+      <c r="K7" s="342" t="n"/>
+      <c r="L7" s="342" t="n"/>
+      <c r="M7" s="342" t="n"/>
+      <c r="N7" s="342" t="n"/>
+      <c r="O7" s="342" t="n"/>
+      <c r="P7" s="342" t="n"/>
+      <c r="Q7" s="342" t="n"/>
+      <c r="R7" s="342" t="n"/>
+      <c r="S7" s="342" t="n"/>
+      <c r="T7" s="342" t="n"/>
+      <c r="U7" s="342" t="n"/>
+      <c r="V7" s="342" t="n"/>
+      <c r="W7" s="342" t="n"/>
+      <c r="X7" s="342" t="n"/>
+      <c r="Y7" s="342" t="n"/>
+      <c r="Z7" s="342" t="n"/>
+      <c r="AA7" s="342" t="n"/>
+      <c r="AB7" s="342" t="n"/>
+      <c r="AC7" s="342" t="n"/>
+      <c r="AD7" s="342" t="n"/>
+      <c r="AE7" s="342" t="n"/>
+      <c r="AF7" s="342" t="n"/>
+      <c r="AG7" s="342" t="n"/>
+      <c r="AH7" s="342" t="n"/>
+      <c r="AI7" s="342" t="n"/>
+      <c r="AJ7" s="342" t="n"/>
+      <c r="AK7" s="342" t="n"/>
+      <c r="AL7" s="342" t="n"/>
+      <c r="AM7" s="342" t="n"/>
+      <c r="AN7" s="342" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="293" t="inlineStr">
+      <c r="A8" s="373" t="inlineStr">
         <is>
           <t>WI WI-602</t>
         </is>
       </c>
-      <c r="B8" s="294" t="inlineStr">
+      <c r="B8" s="374" t="inlineStr">
         <is>
           <t>WI-602 — Kiểm trước khi dùng dụng cụ đo, trạng thái CAL và xử lý nghi ngờ</t>
         </is>
       </c>
-      <c r="C8" s="294" t="inlineStr">
+      <c r="C8" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-602-gage-pre-use-verification-and-status-control.html</t>
         </is>
       </c>
+      <c r="D8" s="350" t="n"/>
+      <c r="E8" s="350" t="n"/>
+      <c r="F8" s="350" t="n"/>
+      <c r="G8" s="350" t="n"/>
+      <c r="H8" s="350" t="n"/>
+      <c r="I8" s="350" t="n"/>
+      <c r="J8" s="350" t="n"/>
+      <c r="K8" s="350" t="n"/>
+      <c r="L8" s="350" t="n"/>
+      <c r="M8" s="350" t="n"/>
+      <c r="N8" s="350" t="n"/>
+      <c r="O8" s="350" t="n"/>
+      <c r="P8" s="350" t="n"/>
+      <c r="Q8" s="350" t="n"/>
+      <c r="R8" s="350" t="n"/>
+      <c r="S8" s="350" t="n"/>
+      <c r="T8" s="350" t="n"/>
+      <c r="U8" s="350" t="n"/>
+      <c r="V8" s="350" t="n"/>
+      <c r="W8" s="350" t="n"/>
+      <c r="X8" s="350" t="n"/>
+      <c r="Y8" s="350" t="n"/>
+      <c r="Z8" s="350" t="n"/>
+      <c r="AA8" s="350" t="n"/>
+      <c r="AB8" s="350" t="n"/>
+      <c r="AC8" s="350" t="n"/>
+      <c r="AD8" s="350" t="n"/>
+      <c r="AE8" s="350" t="n"/>
+      <c r="AF8" s="350" t="n"/>
+      <c r="AG8" s="350" t="n"/>
+      <c r="AH8" s="350" t="n"/>
+      <c r="AI8" s="350" t="n"/>
+      <c r="AJ8" s="350" t="n"/>
+      <c r="AK8" s="350" t="n"/>
+      <c r="AL8" s="350" t="n"/>
+      <c r="AM8" s="350" t="n"/>
+      <c r="AN8" s="350" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="293" t="inlineStr">
+      <c r="A9" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-001</t>
         </is>
       </c>
-      <c r="B9" s="294" t="inlineStr">
+      <c r="B9" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
         </is>
       </c>
-      <c r="C9" s="294" t="inlineStr">
+      <c r="C9" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
         </is>
       </c>
+      <c r="D9" s="350" t="n"/>
+      <c r="E9" s="350" t="n"/>
+      <c r="F9" s="350" t="n"/>
+      <c r="G9" s="350" t="n"/>
+      <c r="H9" s="350" t="n"/>
+      <c r="I9" s="350" t="n"/>
+      <c r="J9" s="350" t="n"/>
+      <c r="K9" s="350" t="n"/>
+      <c r="L9" s="350" t="n"/>
+      <c r="M9" s="350" t="n"/>
+      <c r="N9" s="350" t="n"/>
+      <c r="O9" s="350" t="n"/>
+      <c r="P9" s="350" t="n"/>
+      <c r="Q9" s="350" t="n"/>
+      <c r="R9" s="350" t="n"/>
+      <c r="S9" s="350" t="n"/>
+      <c r="T9" s="350" t="n"/>
+      <c r="U9" s="350" t="n"/>
+      <c r="V9" s="350" t="n"/>
+      <c r="W9" s="350" t="n"/>
+      <c r="X9" s="350" t="n"/>
+      <c r="Y9" s="350" t="n"/>
+      <c r="Z9" s="350" t="n"/>
+      <c r="AA9" s="350" t="n"/>
+      <c r="AB9" s="350" t="n"/>
+      <c r="AC9" s="350" t="n"/>
+      <c r="AD9" s="350" t="n"/>
+      <c r="AE9" s="350" t="n"/>
+      <c r="AF9" s="350" t="n"/>
+      <c r="AG9" s="350" t="n"/>
+      <c r="AH9" s="350" t="n"/>
+      <c r="AI9" s="350" t="n"/>
+      <c r="AJ9" s="350" t="n"/>
+      <c r="AK9" s="350" t="n"/>
+      <c r="AL9" s="350" t="n"/>
+      <c r="AM9" s="350" t="n"/>
+      <c r="AN9" s="350" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="293" t="inlineStr">
+      <c r="A10" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-002</t>
         </is>
       </c>
-      <c r="B10" s="294" t="inlineStr">
+      <c r="B10" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
         </is>
       </c>
-      <c r="C10" s="294" t="inlineStr">
+      <c r="C10" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
         </is>
       </c>
+      <c r="D10" s="350" t="n"/>
+      <c r="E10" s="350" t="n"/>
+      <c r="F10" s="350" t="n"/>
+      <c r="G10" s="350" t="n"/>
+      <c r="H10" s="350" t="n"/>
+      <c r="I10" s="350" t="n"/>
+      <c r="J10" s="350" t="n"/>
+      <c r="K10" s="350" t="n"/>
+      <c r="L10" s="350" t="n"/>
+      <c r="M10" s="350" t="n"/>
+      <c r="N10" s="350" t="n"/>
+      <c r="O10" s="350" t="n"/>
+      <c r="P10" s="350" t="n"/>
+      <c r="Q10" s="350" t="n"/>
+      <c r="R10" s="350" t="n"/>
+      <c r="S10" s="350" t="n"/>
+      <c r="T10" s="350" t="n"/>
+      <c r="U10" s="350" t="n"/>
+      <c r="V10" s="350" t="n"/>
+      <c r="W10" s="350" t="n"/>
+      <c r="X10" s="350" t="n"/>
+      <c r="Y10" s="350" t="n"/>
+      <c r="Z10" s="350" t="n"/>
+      <c r="AA10" s="350" t="n"/>
+      <c r="AB10" s="350" t="n"/>
+      <c r="AC10" s="350" t="n"/>
+      <c r="AD10" s="350" t="n"/>
+      <c r="AE10" s="350" t="n"/>
+      <c r="AF10" s="350" t="n"/>
+      <c r="AG10" s="350" t="n"/>
+      <c r="AH10" s="350" t="n"/>
+      <c r="AI10" s="350" t="n"/>
+      <c r="AJ10" s="350" t="n"/>
+      <c r="AK10" s="350" t="n"/>
+      <c r="AL10" s="350" t="n"/>
+      <c r="AM10" s="350" t="n"/>
+      <c r="AN10" s="350" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="293" t="inlineStr">
+      <c r="A11" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-003</t>
         </is>
       </c>
-      <c r="B11" s="294" t="inlineStr">
+      <c r="B11" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
         </is>
       </c>
-      <c r="C11" s="294" t="inlineStr">
+      <c r="C11" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
         </is>
       </c>
+      <c r="D11" s="350" t="n"/>
+      <c r="E11" s="350" t="n"/>
+      <c r="F11" s="350" t="n"/>
+      <c r="G11" s="350" t="n"/>
+      <c r="H11" s="350" t="n"/>
+      <c r="I11" s="350" t="n"/>
+      <c r="J11" s="350" t="n"/>
+      <c r="K11" s="350" t="n"/>
+      <c r="L11" s="350" t="n"/>
+      <c r="M11" s="350" t="n"/>
+      <c r="N11" s="350" t="n"/>
+      <c r="O11" s="350" t="n"/>
+      <c r="P11" s="350" t="n"/>
+      <c r="Q11" s="350" t="n"/>
+      <c r="R11" s="350" t="n"/>
+      <c r="S11" s="350" t="n"/>
+      <c r="T11" s="350" t="n"/>
+      <c r="U11" s="350" t="n"/>
+      <c r="V11" s="350" t="n"/>
+      <c r="W11" s="350" t="n"/>
+      <c r="X11" s="350" t="n"/>
+      <c r="Y11" s="350" t="n"/>
+      <c r="Z11" s="350" t="n"/>
+      <c r="AA11" s="350" t="n"/>
+      <c r="AB11" s="350" t="n"/>
+      <c r="AC11" s="350" t="n"/>
+      <c r="AD11" s="350" t="n"/>
+      <c r="AE11" s="350" t="n"/>
+      <c r="AF11" s="350" t="n"/>
+      <c r="AG11" s="350" t="n"/>
+      <c r="AH11" s="350" t="n"/>
+      <c r="AI11" s="350" t="n"/>
+      <c r="AJ11" s="350" t="n"/>
+      <c r="AK11" s="350" t="n"/>
+      <c r="AL11" s="350" t="n"/>
+      <c r="AM11" s="350" t="n"/>
+      <c r="AN11" s="350" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="293" t="inlineStr">
+      <c r="A12" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-004</t>
         </is>
       </c>
-      <c r="B12" s="294" t="inlineStr">
+      <c r="B12" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
         </is>
       </c>
-      <c r="C12" s="294" t="inlineStr">
+      <c r="C12" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
         </is>
       </c>
+      <c r="D12" s="350" t="n"/>
+      <c r="E12" s="350" t="n"/>
+      <c r="F12" s="350" t="n"/>
+      <c r="G12" s="350" t="n"/>
+      <c r="H12" s="350" t="n"/>
+      <c r="I12" s="350" t="n"/>
+      <c r="J12" s="350" t="n"/>
+      <c r="K12" s="350" t="n"/>
+      <c r="L12" s="350" t="n"/>
+      <c r="M12" s="350" t="n"/>
+      <c r="N12" s="350" t="n"/>
+      <c r="O12" s="350" t="n"/>
+      <c r="P12" s="350" t="n"/>
+      <c r="Q12" s="350" t="n"/>
+      <c r="R12" s="350" t="n"/>
+      <c r="S12" s="350" t="n"/>
+      <c r="T12" s="350" t="n"/>
+      <c r="U12" s="350" t="n"/>
+      <c r="V12" s="350" t="n"/>
+      <c r="W12" s="350" t="n"/>
+      <c r="X12" s="350" t="n"/>
+      <c r="Y12" s="350" t="n"/>
+      <c r="Z12" s="350" t="n"/>
+      <c r="AA12" s="350" t="n"/>
+      <c r="AB12" s="350" t="n"/>
+      <c r="AC12" s="350" t="n"/>
+      <c r="AD12" s="350" t="n"/>
+      <c r="AE12" s="350" t="n"/>
+      <c r="AF12" s="350" t="n"/>
+      <c r="AG12" s="350" t="n"/>
+      <c r="AH12" s="350" t="n"/>
+      <c r="AI12" s="350" t="n"/>
+      <c r="AJ12" s="350" t="n"/>
+      <c r="AK12" s="350" t="n"/>
+      <c r="AL12" s="350" t="n"/>
+      <c r="AM12" s="350" t="n"/>
+      <c r="AN12" s="350" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="293" t="inlineStr">
+      <c r="A13" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-006</t>
         </is>
       </c>
-      <c r="B13" s="294" t="inlineStr">
+      <c r="B13" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
         </is>
       </c>
-      <c r="C13" s="294" t="inlineStr">
+      <c r="C13" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
         </is>
       </c>
+      <c r="D13" s="350" t="n"/>
+      <c r="E13" s="350" t="n"/>
+      <c r="F13" s="350" t="n"/>
+      <c r="G13" s="350" t="n"/>
+      <c r="H13" s="350" t="n"/>
+      <c r="I13" s="350" t="n"/>
+      <c r="J13" s="350" t="n"/>
+      <c r="K13" s="350" t="n"/>
+      <c r="L13" s="350" t="n"/>
+      <c r="M13" s="350" t="n"/>
+      <c r="N13" s="350" t="n"/>
+      <c r="O13" s="350" t="n"/>
+      <c r="P13" s="350" t="n"/>
+      <c r="Q13" s="350" t="n"/>
+      <c r="R13" s="350" t="n"/>
+      <c r="S13" s="350" t="n"/>
+      <c r="T13" s="350" t="n"/>
+      <c r="U13" s="350" t="n"/>
+      <c r="V13" s="350" t="n"/>
+      <c r="W13" s="350" t="n"/>
+      <c r="X13" s="350" t="n"/>
+      <c r="Y13" s="350" t="n"/>
+      <c r="Z13" s="350" t="n"/>
+      <c r="AA13" s="350" t="n"/>
+      <c r="AB13" s="350" t="n"/>
+      <c r="AC13" s="350" t="n"/>
+      <c r="AD13" s="350" t="n"/>
+      <c r="AE13" s="350" t="n"/>
+      <c r="AF13" s="350" t="n"/>
+      <c r="AG13" s="350" t="n"/>
+      <c r="AH13" s="350" t="n"/>
+      <c r="AI13" s="350" t="n"/>
+      <c r="AJ13" s="350" t="n"/>
+      <c r="AK13" s="350" t="n"/>
+      <c r="AL13" s="350" t="n"/>
+      <c r="AM13" s="350" t="n"/>
+      <c r="AN13" s="350" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="293" t="inlineStr">
+      <c r="A14" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-007</t>
         </is>
       </c>
-      <c r="B14" s="294" t="inlineStr">
+      <c r="B14" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
         </is>
       </c>
-      <c r="C14" s="294" t="inlineStr">
+      <c r="C14" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
         </is>
       </c>
+      <c r="D14" s="350" t="n"/>
+      <c r="E14" s="350" t="n"/>
+      <c r="F14" s="350" t="n"/>
+      <c r="G14" s="350" t="n"/>
+      <c r="H14" s="350" t="n"/>
+      <c r="I14" s="350" t="n"/>
+      <c r="J14" s="350" t="n"/>
+      <c r="K14" s="350" t="n"/>
+      <c r="L14" s="350" t="n"/>
+      <c r="M14" s="350" t="n"/>
+      <c r="N14" s="350" t="n"/>
+      <c r="O14" s="350" t="n"/>
+      <c r="P14" s="350" t="n"/>
+      <c r="Q14" s="350" t="n"/>
+      <c r="R14" s="350" t="n"/>
+      <c r="S14" s="350" t="n"/>
+      <c r="T14" s="350" t="n"/>
+      <c r="U14" s="350" t="n"/>
+      <c r="V14" s="350" t="n"/>
+      <c r="W14" s="350" t="n"/>
+      <c r="X14" s="350" t="n"/>
+      <c r="Y14" s="350" t="n"/>
+      <c r="Z14" s="350" t="n"/>
+      <c r="AA14" s="350" t="n"/>
+      <c r="AB14" s="350" t="n"/>
+      <c r="AC14" s="350" t="n"/>
+      <c r="AD14" s="350" t="n"/>
+      <c r="AE14" s="350" t="n"/>
+      <c r="AF14" s="350" t="n"/>
+      <c r="AG14" s="350" t="n"/>
+      <c r="AH14" s="350" t="n"/>
+      <c r="AI14" s="350" t="n"/>
+      <c r="AJ14" s="350" t="n"/>
+      <c r="AK14" s="350" t="n"/>
+      <c r="AL14" s="350" t="n"/>
+      <c r="AM14" s="350" t="n"/>
+      <c r="AN14" s="350" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="293" t="inlineStr">
+      <c r="A15" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QMS-020</t>
         </is>
       </c>
-      <c r="B15" s="294" t="inlineStr">
+      <c r="B15" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
         </is>
       </c>
-      <c r="C15" s="294" t="inlineStr">
+      <c r="C15" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
         </is>
       </c>
+      <c r="D15" s="350" t="n"/>
+      <c r="E15" s="350" t="n"/>
+      <c r="F15" s="350" t="n"/>
+      <c r="G15" s="350" t="n"/>
+      <c r="H15" s="350" t="n"/>
+      <c r="I15" s="350" t="n"/>
+      <c r="J15" s="350" t="n"/>
+      <c r="K15" s="350" t="n"/>
+      <c r="L15" s="350" t="n"/>
+      <c r="M15" s="350" t="n"/>
+      <c r="N15" s="350" t="n"/>
+      <c r="O15" s="350" t="n"/>
+      <c r="P15" s="350" t="n"/>
+      <c r="Q15" s="350" t="n"/>
+      <c r="R15" s="350" t="n"/>
+      <c r="S15" s="350" t="n"/>
+      <c r="T15" s="350" t="n"/>
+      <c r="U15" s="350" t="n"/>
+      <c r="V15" s="350" t="n"/>
+      <c r="W15" s="350" t="n"/>
+      <c r="X15" s="350" t="n"/>
+      <c r="Y15" s="350" t="n"/>
+      <c r="Z15" s="350" t="n"/>
+      <c r="AA15" s="350" t="n"/>
+      <c r="AB15" s="350" t="n"/>
+      <c r="AC15" s="350" t="n"/>
+      <c r="AD15" s="350" t="n"/>
+      <c r="AE15" s="350" t="n"/>
+      <c r="AF15" s="350" t="n"/>
+      <c r="AG15" s="350" t="n"/>
+      <c r="AH15" s="350" t="n"/>
+      <c r="AI15" s="350" t="n"/>
+      <c r="AJ15" s="350" t="n"/>
+      <c r="AK15" s="350" t="n"/>
+      <c r="AL15" s="350" t="n"/>
+      <c r="AM15" s="350" t="n"/>
+      <c r="AN15" s="350" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -8405,7 +11134,8 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -8415,30 +11145,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="317" t="inlineStr">
+      <c r="A1" s="384" t="inlineStr">
         <is>
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="402" t="n"/>
+      <c r="C1" s="402" t="n"/>
+      <c r="D1" s="402" t="n"/>
+      <c r="E1" s="402" t="n"/>
+      <c r="F1" s="402" t="n"/>
+      <c r="G1" s="403" t="n"/>
+      <c r="H1" s="342" t="n"/>
+      <c r="I1" s="342" t="n"/>
+      <c r="J1" s="342" t="n"/>
+      <c r="K1" s="342" t="n"/>
+      <c r="L1" s="342" t="n"/>
+      <c r="M1" s="342" t="n"/>
+      <c r="N1" s="342" t="n"/>
+      <c r="O1" s="342" t="n"/>
+      <c r="P1" s="342" t="n"/>
+      <c r="Q1" s="342" t="n"/>
+      <c r="R1" s="342" t="n"/>
+      <c r="S1" s="342" t="n"/>
+      <c r="T1" s="342" t="n"/>
+      <c r="U1" s="342" t="n"/>
+      <c r="V1" s="342" t="n"/>
+      <c r="W1" s="342" t="n"/>
+      <c r="X1" s="342" t="n"/>
+      <c r="Y1" s="342" t="n"/>
+      <c r="Z1" s="342" t="n"/>
+      <c r="AA1" s="342" t="n"/>
+      <c r="AB1" s="342" t="n"/>
+      <c r="AC1" s="342" t="n"/>
+      <c r="AD1" s="342" t="n"/>
+      <c r="AE1" s="342" t="n"/>
+      <c r="AF1" s="342" t="n"/>
+      <c r="AG1" s="342" t="n"/>
+      <c r="AH1" s="342" t="n"/>
+      <c r="AI1" s="342" t="n"/>
+      <c r="AJ1" s="342" t="n"/>
+      <c r="AK1" s="342" t="n"/>
+      <c r="AL1" s="342" t="n"/>
+      <c r="AM1" s="342" t="n"/>
+      <c r="AN1" s="342" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="318" t="inlineStr">
@@ -8446,54 +11242,202 @@
           <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="H2" s="342" t="n"/>
+      <c r="I2" s="342" t="n"/>
+      <c r="J2" s="342" t="n"/>
+      <c r="K2" s="342" t="n"/>
+      <c r="L2" s="342" t="n"/>
+      <c r="M2" s="342" t="n"/>
+      <c r="N2" s="342" t="n"/>
+      <c r="O2" s="342" t="n"/>
+      <c r="P2" s="342" t="n"/>
+      <c r="Q2" s="342" t="n"/>
+      <c r="R2" s="342" t="n"/>
+      <c r="S2" s="342" t="n"/>
+      <c r="T2" s="342" t="n"/>
+      <c r="U2" s="342" t="n"/>
+      <c r="V2" s="342" t="n"/>
+      <c r="W2" s="342" t="n"/>
+      <c r="X2" s="342" t="n"/>
+      <c r="Y2" s="342" t="n"/>
+      <c r="Z2" s="342" t="n"/>
+      <c r="AA2" s="342" t="n"/>
+      <c r="AB2" s="342" t="n"/>
+      <c r="AC2" s="342" t="n"/>
+      <c r="AD2" s="342" t="n"/>
+      <c r="AE2" s="342" t="n"/>
+      <c r="AF2" s="342" t="n"/>
+      <c r="AG2" s="342" t="n"/>
+      <c r="AH2" s="342" t="n"/>
+      <c r="AI2" s="342" t="n"/>
+      <c r="AJ2" s="342" t="n"/>
+      <c r="AK2" s="342" t="n"/>
+      <c r="AL2" s="342" t="n"/>
+      <c r="AM2" s="342" t="n"/>
+      <c r="AN2" s="342" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="342" t="n"/>
+      <c r="B3" s="342" t="n"/>
+      <c r="C3" s="342" t="n"/>
+      <c r="D3" s="342" t="n"/>
+      <c r="E3" s="342" t="n"/>
+      <c r="F3" s="342" t="n"/>
+      <c r="G3" s="342" t="n"/>
+      <c r="H3" s="342" t="n"/>
+      <c r="I3" s="342" t="n"/>
+      <c r="J3" s="342" t="n"/>
+      <c r="K3" s="342" t="n"/>
+      <c r="L3" s="342" t="n"/>
+      <c r="M3" s="342" t="n"/>
+      <c r="N3" s="342" t="n"/>
+      <c r="O3" s="342" t="n"/>
+      <c r="P3" s="342" t="n"/>
+      <c r="Q3" s="342" t="n"/>
+      <c r="R3" s="342" t="n"/>
+      <c r="S3" s="342" t="n"/>
+      <c r="T3" s="342" t="n"/>
+      <c r="U3" s="342" t="n"/>
+      <c r="V3" s="342" t="n"/>
+      <c r="W3" s="342" t="n"/>
+      <c r="X3" s="342" t="n"/>
+      <c r="Y3" s="342" t="n"/>
+      <c r="Z3" s="342" t="n"/>
+      <c r="AA3" s="342" t="n"/>
+      <c r="AB3" s="342" t="n"/>
+      <c r="AC3" s="342" t="n"/>
+      <c r="AD3" s="342" t="n"/>
+      <c r="AE3" s="342" t="n"/>
+      <c r="AF3" s="342" t="n"/>
+      <c r="AG3" s="342" t="n"/>
+      <c r="AH3" s="342" t="n"/>
+      <c r="AI3" s="342" t="n"/>
+      <c r="AJ3" s="342" t="n"/>
+      <c r="AK3" s="342" t="n"/>
+      <c r="AL3" s="342" t="n"/>
+      <c r="AM3" s="342" t="n"/>
+      <c r="AN3" s="342" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="291" t="inlineStr">
+      <c r="A4" s="347" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="291" t="inlineStr">
+      <c r="B4" s="347" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="291" t="inlineStr">
+      <c r="C4" s="347" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="342" t="n"/>
+      <c r="E4" s="342" t="n"/>
+      <c r="F4" s="342" t="n"/>
+      <c r="G4" s="342" t="n"/>
+      <c r="H4" s="342" t="n"/>
+      <c r="I4" s="342" t="n"/>
+      <c r="J4" s="342" t="n"/>
+      <c r="K4" s="342" t="n"/>
+      <c r="L4" s="342" t="n"/>
+      <c r="M4" s="342" t="n"/>
+      <c r="N4" s="342" t="n"/>
+      <c r="O4" s="342" t="n"/>
+      <c r="P4" s="342" t="n"/>
+      <c r="Q4" s="342" t="n"/>
+      <c r="R4" s="342" t="n"/>
+      <c r="S4" s="342" t="n"/>
+      <c r="T4" s="342" t="n"/>
+      <c r="U4" s="342" t="n"/>
+      <c r="V4" s="342" t="n"/>
+      <c r="W4" s="342" t="n"/>
+      <c r="X4" s="342" t="n"/>
+      <c r="Y4" s="342" t="n"/>
+      <c r="Z4" s="342" t="n"/>
+      <c r="AA4" s="342" t="n"/>
+      <c r="AB4" s="342" t="n"/>
+      <c r="AC4" s="342" t="n"/>
+      <c r="AD4" s="342" t="n"/>
+      <c r="AE4" s="342" t="n"/>
+      <c r="AF4" s="342" t="n"/>
+      <c r="AG4" s="342" t="n"/>
+      <c r="AH4" s="342" t="n"/>
+      <c r="AI4" s="342" t="n"/>
+      <c r="AJ4" s="342" t="n"/>
+      <c r="AK4" s="342" t="n"/>
+      <c r="AL4" s="342" t="n"/>
+      <c r="AM4" s="342" t="n"/>
+      <c r="AN4" s="342" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="293" t="inlineStr">
+      <c r="A5" s="385" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="294" t="inlineStr">
+      <c r="B5" s="386" t="inlineStr">
         <is>
           <t>Calibration / QA file + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="294" t="inlineStr">
+      <c r="C5" s="386" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
+      <c r="D5" s="342" t="n"/>
+      <c r="E5" s="342" t="n"/>
+      <c r="F5" s="342" t="n"/>
+      <c r="G5" s="342" t="n"/>
+      <c r="H5" s="342" t="n"/>
+      <c r="I5" s="342" t="n"/>
+      <c r="J5" s="342" t="n"/>
+      <c r="K5" s="342" t="n"/>
+      <c r="L5" s="342" t="n"/>
+      <c r="M5" s="342" t="n"/>
+      <c r="N5" s="342" t="n"/>
+      <c r="O5" s="342" t="n"/>
+      <c r="P5" s="342" t="n"/>
+      <c r="Q5" s="342" t="n"/>
+      <c r="R5" s="342" t="n"/>
+      <c r="S5" s="342" t="n"/>
+      <c r="T5" s="342" t="n"/>
+      <c r="U5" s="342" t="n"/>
+      <c r="V5" s="342" t="n"/>
+      <c r="W5" s="342" t="n"/>
+      <c r="X5" s="342" t="n"/>
+      <c r="Y5" s="342" t="n"/>
+      <c r="Z5" s="342" t="n"/>
+      <c r="AA5" s="342" t="n"/>
+      <c r="AB5" s="342" t="n"/>
+      <c r="AC5" s="342" t="n"/>
+      <c r="AD5" s="342" t="n"/>
+      <c r="AE5" s="342" t="n"/>
+      <c r="AF5" s="342" t="n"/>
+      <c r="AG5" s="342" t="n"/>
+      <c r="AH5" s="342" t="n"/>
+      <c r="AI5" s="342" t="n"/>
+      <c r="AJ5" s="342" t="n"/>
+      <c r="AK5" s="342" t="n"/>
+      <c r="AL5" s="342" t="n"/>
+      <c r="AM5" s="342" t="n"/>
+      <c r="AN5" s="342" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="293" t="inlineStr">
+      <c r="A6" s="385" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="294" t="inlineStr">
+      <c r="B6" s="386" t="inlineStr">
         <is>
           <t>Pre-use gage-verification gate before FRM-621/631/641 inspection execution and before Pack A first-piece/release decisions. Formal MSA remains in FRM-611/612/613.</t>
         </is>
       </c>
-      <c r="C6" s="294" t="inlineStr">
+      <c r="C6" s="386" t="inlineStr">
         <is>
           <t>This form does not replace SOP-601; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-602; this form captures results, checks, decisions or exceptions only.
@@ -8501,165 +11445,536 @@
 System-of-record / source-of-truth boundary: Calibration / QA file + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
+      <c r="D6" s="342" t="n"/>
+      <c r="E6" s="342" t="n"/>
+      <c r="F6" s="342" t="n"/>
+      <c r="G6" s="342" t="n"/>
+      <c r="H6" s="342" t="n"/>
+      <c r="I6" s="342" t="n"/>
+      <c r="J6" s="342" t="n"/>
+      <c r="K6" s="342" t="n"/>
+      <c r="L6" s="342" t="n"/>
+      <c r="M6" s="342" t="n"/>
+      <c r="N6" s="342" t="n"/>
+      <c r="O6" s="342" t="n"/>
+      <c r="P6" s="342" t="n"/>
+      <c r="Q6" s="342" t="n"/>
+      <c r="R6" s="342" t="n"/>
+      <c r="S6" s="342" t="n"/>
+      <c r="T6" s="342" t="n"/>
+      <c r="U6" s="342" t="n"/>
+      <c r="V6" s="342" t="n"/>
+      <c r="W6" s="342" t="n"/>
+      <c r="X6" s="342" t="n"/>
+      <c r="Y6" s="342" t="n"/>
+      <c r="Z6" s="342" t="n"/>
+      <c r="AA6" s="342" t="n"/>
+      <c r="AB6" s="342" t="n"/>
+      <c r="AC6" s="342" t="n"/>
+      <c r="AD6" s="342" t="n"/>
+      <c r="AE6" s="342" t="n"/>
+      <c r="AF6" s="342" t="n"/>
+      <c r="AG6" s="342" t="n"/>
+      <c r="AH6" s="342" t="n"/>
+      <c r="AI6" s="342" t="n"/>
+      <c r="AJ6" s="342" t="n"/>
+      <c r="AK6" s="342" t="n"/>
+      <c r="AL6" s="342" t="n"/>
+      <c r="AM6" s="342" t="n"/>
+      <c r="AN6" s="342" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="293" t="inlineStr">
+      <c r="A7" s="385" t="inlineStr">
         <is>
           <t>SOP SOP-601</t>
         </is>
       </c>
-      <c r="B7" s="294" t="inlineStr">
+      <c r="B7" s="386" t="inlineStr">
         <is>
           <t>SOP-601 — Hiệu chuẩn và kiểm soát dụng cụ đo | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="294" t="inlineStr">
+      <c r="C7" s="386" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-601-calibration-and-gage-control.html</t>
         </is>
       </c>
+      <c r="D7" s="342" t="n"/>
+      <c r="E7" s="342" t="n"/>
+      <c r="F7" s="342" t="n"/>
+      <c r="G7" s="342" t="n"/>
+      <c r="H7" s="342" t="n"/>
+      <c r="I7" s="342" t="n"/>
+      <c r="J7" s="342" t="n"/>
+      <c r="K7" s="342" t="n"/>
+      <c r="L7" s="342" t="n"/>
+      <c r="M7" s="342" t="n"/>
+      <c r="N7" s="342" t="n"/>
+      <c r="O7" s="342" t="n"/>
+      <c r="P7" s="342" t="n"/>
+      <c r="Q7" s="342" t="n"/>
+      <c r="R7" s="342" t="n"/>
+      <c r="S7" s="342" t="n"/>
+      <c r="T7" s="342" t="n"/>
+      <c r="U7" s="342" t="n"/>
+      <c r="V7" s="342" t="n"/>
+      <c r="W7" s="342" t="n"/>
+      <c r="X7" s="342" t="n"/>
+      <c r="Y7" s="342" t="n"/>
+      <c r="Z7" s="342" t="n"/>
+      <c r="AA7" s="342" t="n"/>
+      <c r="AB7" s="342" t="n"/>
+      <c r="AC7" s="342" t="n"/>
+      <c r="AD7" s="342" t="n"/>
+      <c r="AE7" s="342" t="n"/>
+      <c r="AF7" s="342" t="n"/>
+      <c r="AG7" s="342" t="n"/>
+      <c r="AH7" s="342" t="n"/>
+      <c r="AI7" s="342" t="n"/>
+      <c r="AJ7" s="342" t="n"/>
+      <c r="AK7" s="342" t="n"/>
+      <c r="AL7" s="342" t="n"/>
+      <c r="AM7" s="342" t="n"/>
+      <c r="AN7" s="342" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="293" t="inlineStr">
+      <c r="A8" s="373" t="inlineStr">
         <is>
           <t>WI WI-602</t>
         </is>
       </c>
-      <c r="B8" s="294" t="inlineStr">
+      <c r="B8" s="374" t="inlineStr">
         <is>
           <t>WI-602 — Kiểm trước khi dùng dụng cụ đo, trạng thái CAL và xử lý nghi ngờ</t>
         </is>
       </c>
-      <c r="C8" s="294" t="inlineStr">
+      <c r="C8" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-602-gage-pre-use-verification-and-status-control.html</t>
         </is>
       </c>
+      <c r="D8" s="350" t="n"/>
+      <c r="E8" s="350" t="n"/>
+      <c r="F8" s="350" t="n"/>
+      <c r="G8" s="350" t="n"/>
+      <c r="H8" s="350" t="n"/>
+      <c r="I8" s="350" t="n"/>
+      <c r="J8" s="350" t="n"/>
+      <c r="K8" s="350" t="n"/>
+      <c r="L8" s="350" t="n"/>
+      <c r="M8" s="350" t="n"/>
+      <c r="N8" s="350" t="n"/>
+      <c r="O8" s="350" t="n"/>
+      <c r="P8" s="350" t="n"/>
+      <c r="Q8" s="350" t="n"/>
+      <c r="R8" s="350" t="n"/>
+      <c r="S8" s="350" t="n"/>
+      <c r="T8" s="350" t="n"/>
+      <c r="U8" s="350" t="n"/>
+      <c r="V8" s="350" t="n"/>
+      <c r="W8" s="350" t="n"/>
+      <c r="X8" s="350" t="n"/>
+      <c r="Y8" s="350" t="n"/>
+      <c r="Z8" s="350" t="n"/>
+      <c r="AA8" s="350" t="n"/>
+      <c r="AB8" s="350" t="n"/>
+      <c r="AC8" s="350" t="n"/>
+      <c r="AD8" s="350" t="n"/>
+      <c r="AE8" s="350" t="n"/>
+      <c r="AF8" s="350" t="n"/>
+      <c r="AG8" s="350" t="n"/>
+      <c r="AH8" s="350" t="n"/>
+      <c r="AI8" s="350" t="n"/>
+      <c r="AJ8" s="350" t="n"/>
+      <c r="AK8" s="350" t="n"/>
+      <c r="AL8" s="350" t="n"/>
+      <c r="AM8" s="350" t="n"/>
+      <c r="AN8" s="350" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="293" t="inlineStr">
+      <c r="A9" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-001</t>
         </is>
       </c>
-      <c r="B9" s="294" t="inlineStr">
+      <c r="B9" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
         </is>
       </c>
-      <c r="C9" s="294" t="inlineStr">
+      <c r="C9" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
         </is>
       </c>
+      <c r="D9" s="350" t="n"/>
+      <c r="E9" s="350" t="n"/>
+      <c r="F9" s="350" t="n"/>
+      <c r="G9" s="350" t="n"/>
+      <c r="H9" s="350" t="n"/>
+      <c r="I9" s="350" t="n"/>
+      <c r="J9" s="350" t="n"/>
+      <c r="K9" s="350" t="n"/>
+      <c r="L9" s="350" t="n"/>
+      <c r="M9" s="350" t="n"/>
+      <c r="N9" s="350" t="n"/>
+      <c r="O9" s="350" t="n"/>
+      <c r="P9" s="350" t="n"/>
+      <c r="Q9" s="350" t="n"/>
+      <c r="R9" s="350" t="n"/>
+      <c r="S9" s="350" t="n"/>
+      <c r="T9" s="350" t="n"/>
+      <c r="U9" s="350" t="n"/>
+      <c r="V9" s="350" t="n"/>
+      <c r="W9" s="350" t="n"/>
+      <c r="X9" s="350" t="n"/>
+      <c r="Y9" s="350" t="n"/>
+      <c r="Z9" s="350" t="n"/>
+      <c r="AA9" s="350" t="n"/>
+      <c r="AB9" s="350" t="n"/>
+      <c r="AC9" s="350" t="n"/>
+      <c r="AD9" s="350" t="n"/>
+      <c r="AE9" s="350" t="n"/>
+      <c r="AF9" s="350" t="n"/>
+      <c r="AG9" s="350" t="n"/>
+      <c r="AH9" s="350" t="n"/>
+      <c r="AI9" s="350" t="n"/>
+      <c r="AJ9" s="350" t="n"/>
+      <c r="AK9" s="350" t="n"/>
+      <c r="AL9" s="350" t="n"/>
+      <c r="AM9" s="350" t="n"/>
+      <c r="AN9" s="350" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="293" t="inlineStr">
+      <c r="A10" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-002</t>
         </is>
       </c>
-      <c r="B10" s="294" t="inlineStr">
+      <c r="B10" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
         </is>
       </c>
-      <c r="C10" s="294" t="inlineStr">
+      <c r="C10" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
         </is>
       </c>
+      <c r="D10" s="350" t="n"/>
+      <c r="E10" s="350" t="n"/>
+      <c r="F10" s="350" t="n"/>
+      <c r="G10" s="350" t="n"/>
+      <c r="H10" s="350" t="n"/>
+      <c r="I10" s="350" t="n"/>
+      <c r="J10" s="350" t="n"/>
+      <c r="K10" s="350" t="n"/>
+      <c r="L10" s="350" t="n"/>
+      <c r="M10" s="350" t="n"/>
+      <c r="N10" s="350" t="n"/>
+      <c r="O10" s="350" t="n"/>
+      <c r="P10" s="350" t="n"/>
+      <c r="Q10" s="350" t="n"/>
+      <c r="R10" s="350" t="n"/>
+      <c r="S10" s="350" t="n"/>
+      <c r="T10" s="350" t="n"/>
+      <c r="U10" s="350" t="n"/>
+      <c r="V10" s="350" t="n"/>
+      <c r="W10" s="350" t="n"/>
+      <c r="X10" s="350" t="n"/>
+      <c r="Y10" s="350" t="n"/>
+      <c r="Z10" s="350" t="n"/>
+      <c r="AA10" s="350" t="n"/>
+      <c r="AB10" s="350" t="n"/>
+      <c r="AC10" s="350" t="n"/>
+      <c r="AD10" s="350" t="n"/>
+      <c r="AE10" s="350" t="n"/>
+      <c r="AF10" s="350" t="n"/>
+      <c r="AG10" s="350" t="n"/>
+      <c r="AH10" s="350" t="n"/>
+      <c r="AI10" s="350" t="n"/>
+      <c r="AJ10" s="350" t="n"/>
+      <c r="AK10" s="350" t="n"/>
+      <c r="AL10" s="350" t="n"/>
+      <c r="AM10" s="350" t="n"/>
+      <c r="AN10" s="350" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="293" t="inlineStr">
+      <c r="A11" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-003</t>
         </is>
       </c>
-      <c r="B11" s="294" t="inlineStr">
+      <c r="B11" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
         </is>
       </c>
-      <c r="C11" s="294" t="inlineStr">
+      <c r="C11" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
         </is>
       </c>
+      <c r="D11" s="350" t="n"/>
+      <c r="E11" s="350" t="n"/>
+      <c r="F11" s="350" t="n"/>
+      <c r="G11" s="350" t="n"/>
+      <c r="H11" s="350" t="n"/>
+      <c r="I11" s="350" t="n"/>
+      <c r="J11" s="350" t="n"/>
+      <c r="K11" s="350" t="n"/>
+      <c r="L11" s="350" t="n"/>
+      <c r="M11" s="350" t="n"/>
+      <c r="N11" s="350" t="n"/>
+      <c r="O11" s="350" t="n"/>
+      <c r="P11" s="350" t="n"/>
+      <c r="Q11" s="350" t="n"/>
+      <c r="R11" s="350" t="n"/>
+      <c r="S11" s="350" t="n"/>
+      <c r="T11" s="350" t="n"/>
+      <c r="U11" s="350" t="n"/>
+      <c r="V11" s="350" t="n"/>
+      <c r="W11" s="350" t="n"/>
+      <c r="X11" s="350" t="n"/>
+      <c r="Y11" s="350" t="n"/>
+      <c r="Z11" s="350" t="n"/>
+      <c r="AA11" s="350" t="n"/>
+      <c r="AB11" s="350" t="n"/>
+      <c r="AC11" s="350" t="n"/>
+      <c r="AD11" s="350" t="n"/>
+      <c r="AE11" s="350" t="n"/>
+      <c r="AF11" s="350" t="n"/>
+      <c r="AG11" s="350" t="n"/>
+      <c r="AH11" s="350" t="n"/>
+      <c r="AI11" s="350" t="n"/>
+      <c r="AJ11" s="350" t="n"/>
+      <c r="AK11" s="350" t="n"/>
+      <c r="AL11" s="350" t="n"/>
+      <c r="AM11" s="350" t="n"/>
+      <c r="AN11" s="350" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="293" t="inlineStr">
+      <c r="A12" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-004</t>
         </is>
       </c>
-      <c r="B12" s="294" t="inlineStr">
+      <c r="B12" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
         </is>
       </c>
-      <c r="C12" s="294" t="inlineStr">
+      <c r="C12" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
         </is>
       </c>
+      <c r="D12" s="350" t="n"/>
+      <c r="E12" s="350" t="n"/>
+      <c r="F12" s="350" t="n"/>
+      <c r="G12" s="350" t="n"/>
+      <c r="H12" s="350" t="n"/>
+      <c r="I12" s="350" t="n"/>
+      <c r="J12" s="350" t="n"/>
+      <c r="K12" s="350" t="n"/>
+      <c r="L12" s="350" t="n"/>
+      <c r="M12" s="350" t="n"/>
+      <c r="N12" s="350" t="n"/>
+      <c r="O12" s="350" t="n"/>
+      <c r="P12" s="350" t="n"/>
+      <c r="Q12" s="350" t="n"/>
+      <c r="R12" s="350" t="n"/>
+      <c r="S12" s="350" t="n"/>
+      <c r="T12" s="350" t="n"/>
+      <c r="U12" s="350" t="n"/>
+      <c r="V12" s="350" t="n"/>
+      <c r="W12" s="350" t="n"/>
+      <c r="X12" s="350" t="n"/>
+      <c r="Y12" s="350" t="n"/>
+      <c r="Z12" s="350" t="n"/>
+      <c r="AA12" s="350" t="n"/>
+      <c r="AB12" s="350" t="n"/>
+      <c r="AC12" s="350" t="n"/>
+      <c r="AD12" s="350" t="n"/>
+      <c r="AE12" s="350" t="n"/>
+      <c r="AF12" s="350" t="n"/>
+      <c r="AG12" s="350" t="n"/>
+      <c r="AH12" s="350" t="n"/>
+      <c r="AI12" s="350" t="n"/>
+      <c r="AJ12" s="350" t="n"/>
+      <c r="AK12" s="350" t="n"/>
+      <c r="AL12" s="350" t="n"/>
+      <c r="AM12" s="350" t="n"/>
+      <c r="AN12" s="350" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="293" t="inlineStr">
+      <c r="A13" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-006</t>
         </is>
       </c>
-      <c r="B13" s="294" t="inlineStr">
+      <c r="B13" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
         </is>
       </c>
-      <c r="C13" s="294" t="inlineStr">
+      <c r="C13" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
         </is>
       </c>
+      <c r="D13" s="350" t="n"/>
+      <c r="E13" s="350" t="n"/>
+      <c r="F13" s="350" t="n"/>
+      <c r="G13" s="350" t="n"/>
+      <c r="H13" s="350" t="n"/>
+      <c r="I13" s="350" t="n"/>
+      <c r="J13" s="350" t="n"/>
+      <c r="K13" s="350" t="n"/>
+      <c r="L13" s="350" t="n"/>
+      <c r="M13" s="350" t="n"/>
+      <c r="N13" s="350" t="n"/>
+      <c r="O13" s="350" t="n"/>
+      <c r="P13" s="350" t="n"/>
+      <c r="Q13" s="350" t="n"/>
+      <c r="R13" s="350" t="n"/>
+      <c r="S13" s="350" t="n"/>
+      <c r="T13" s="350" t="n"/>
+      <c r="U13" s="350" t="n"/>
+      <c r="V13" s="350" t="n"/>
+      <c r="W13" s="350" t="n"/>
+      <c r="X13" s="350" t="n"/>
+      <c r="Y13" s="350" t="n"/>
+      <c r="Z13" s="350" t="n"/>
+      <c r="AA13" s="350" t="n"/>
+      <c r="AB13" s="350" t="n"/>
+      <c r="AC13" s="350" t="n"/>
+      <c r="AD13" s="350" t="n"/>
+      <c r="AE13" s="350" t="n"/>
+      <c r="AF13" s="350" t="n"/>
+      <c r="AG13" s="350" t="n"/>
+      <c r="AH13" s="350" t="n"/>
+      <c r="AI13" s="350" t="n"/>
+      <c r="AJ13" s="350" t="n"/>
+      <c r="AK13" s="350" t="n"/>
+      <c r="AL13" s="350" t="n"/>
+      <c r="AM13" s="350" t="n"/>
+      <c r="AN13" s="350" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="293" t="inlineStr">
+      <c r="A14" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-007</t>
         </is>
       </c>
-      <c r="B14" s="294" t="inlineStr">
+      <c r="B14" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
         </is>
       </c>
-      <c r="C14" s="294" t="inlineStr">
+      <c r="C14" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
         </is>
       </c>
+      <c r="D14" s="350" t="n"/>
+      <c r="E14" s="350" t="n"/>
+      <c r="F14" s="350" t="n"/>
+      <c r="G14" s="350" t="n"/>
+      <c r="H14" s="350" t="n"/>
+      <c r="I14" s="350" t="n"/>
+      <c r="J14" s="350" t="n"/>
+      <c r="K14" s="350" t="n"/>
+      <c r="L14" s="350" t="n"/>
+      <c r="M14" s="350" t="n"/>
+      <c r="N14" s="350" t="n"/>
+      <c r="O14" s="350" t="n"/>
+      <c r="P14" s="350" t="n"/>
+      <c r="Q14" s="350" t="n"/>
+      <c r="R14" s="350" t="n"/>
+      <c r="S14" s="350" t="n"/>
+      <c r="T14" s="350" t="n"/>
+      <c r="U14" s="350" t="n"/>
+      <c r="V14" s="350" t="n"/>
+      <c r="W14" s="350" t="n"/>
+      <c r="X14" s="350" t="n"/>
+      <c r="Y14" s="350" t="n"/>
+      <c r="Z14" s="350" t="n"/>
+      <c r="AA14" s="350" t="n"/>
+      <c r="AB14" s="350" t="n"/>
+      <c r="AC14" s="350" t="n"/>
+      <c r="AD14" s="350" t="n"/>
+      <c r="AE14" s="350" t="n"/>
+      <c r="AF14" s="350" t="n"/>
+      <c r="AG14" s="350" t="n"/>
+      <c r="AH14" s="350" t="n"/>
+      <c r="AI14" s="350" t="n"/>
+      <c r="AJ14" s="350" t="n"/>
+      <c r="AK14" s="350" t="n"/>
+      <c r="AL14" s="350" t="n"/>
+      <c r="AM14" s="350" t="n"/>
+      <c r="AN14" s="350" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="293" t="inlineStr">
+      <c r="A15" s="373" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QMS-020</t>
         </is>
       </c>
-      <c r="B15" s="294" t="inlineStr">
+      <c r="B15" s="374" t="inlineStr">
         <is>
           <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
         </is>
       </c>
-      <c r="C15" s="294" t="inlineStr">
+      <c r="C15" s="374" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
         </is>
       </c>
+      <c r="D15" s="350" t="n"/>
+      <c r="E15" s="350" t="n"/>
+      <c r="F15" s="350" t="n"/>
+      <c r="G15" s="350" t="n"/>
+      <c r="H15" s="350" t="n"/>
+      <c r="I15" s="350" t="n"/>
+      <c r="J15" s="350" t="n"/>
+      <c r="K15" s="350" t="n"/>
+      <c r="L15" s="350" t="n"/>
+      <c r="M15" s="350" t="n"/>
+      <c r="N15" s="350" t="n"/>
+      <c r="O15" s="350" t="n"/>
+      <c r="P15" s="350" t="n"/>
+      <c r="Q15" s="350" t="n"/>
+      <c r="R15" s="350" t="n"/>
+      <c r="S15" s="350" t="n"/>
+      <c r="T15" s="350" t="n"/>
+      <c r="U15" s="350" t="n"/>
+      <c r="V15" s="350" t="n"/>
+      <c r="W15" s="350" t="n"/>
+      <c r="X15" s="350" t="n"/>
+      <c r="Y15" s="350" t="n"/>
+      <c r="Z15" s="350" t="n"/>
+      <c r="AA15" s="350" t="n"/>
+      <c r="AB15" s="350" t="n"/>
+      <c r="AC15" s="350" t="n"/>
+      <c r="AD15" s="350" t="n"/>
+      <c r="AE15" s="350" t="n"/>
+      <c r="AF15" s="350" t="n"/>
+      <c r="AG15" s="350" t="n"/>
+      <c r="AH15" s="350" t="n"/>
+      <c r="AI15" s="350" t="n"/>
+      <c r="AJ15" s="350" t="n"/>
+      <c r="AK15" s="350" t="n"/>
+      <c r="AL15" s="350" t="n"/>
+      <c r="AM15" s="350" t="n"/>
+      <c r="AN15" s="350" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="84">
+  <fonts count="86">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -503,6 +503,17 @@
       <color rgb="000C2D48"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001B3A6B"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001B3A6B"/>
+      <sz val="7"/>
+    </font>
   </fonts>
   <fills count="52">
     <fill>
@@ -762,7 +773,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="321">
+  <borders count="360">
     <border>
       <left/>
       <right/>
@@ -4188,13 +4199,462 @@
       </top>
       <bottom style="medium">
         <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="520">
+  <cellXfs count="573">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5441,6 +5901,145 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="307" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="321" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="323" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="322" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="351" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="353" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="355" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5541,6 +6140,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5553,11 +6155,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
+      <colOff>298782</colOff>
+      <row>0</row>
+      <rowOff>275446</rowOff>
     </from>
-    <ext cx="1792692" cy="517122"/>
+    <ext cx="1394316" cy="402206"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -5601,6 +6203,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5631,6 +6236,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5661,6 +6269,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5977,7 +6588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN42"/>
+  <dimension ref="A1:CU42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -6028,16 +6639,16 @@
           <t>Gage Verification Log</t>
         </is>
       </c>
-      <c r="B1" s="409" t="n"/>
-      <c r="C1" s="409" t="n"/>
-      <c r="D1" s="409" t="n"/>
-      <c r="E1" s="409" t="n"/>
-      <c r="F1" s="409" t="n"/>
-      <c r="G1" s="409" t="n"/>
-      <c r="H1" s="410" t="n"/>
-      <c r="I1" s="411" t="n"/>
-      <c r="J1" s="412" t="n"/>
-      <c r="K1" s="412" t="n"/>
+      <c r="B1" s="520" t="n"/>
+      <c r="C1" s="520" t="n"/>
+      <c r="D1" s="520" t="n"/>
+      <c r="E1" s="520" t="n"/>
+      <c r="F1" s="520" t="n"/>
+      <c r="G1" s="520" t="n"/>
+      <c r="H1" s="520" t="n"/>
+      <c r="I1" s="520" t="n"/>
+      <c r="J1" s="520" t="n"/>
+      <c r="K1" s="520" t="n"/>
       <c r="L1" s="412" t="n"/>
       <c r="M1" s="412" t="n"/>
       <c r="N1" s="412" t="n"/>
@@ -6074,16 +6685,6 @@
           <t>Operational Data Sheet · FRM-602 · Owner: QA</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
-      <c r="H2" s="421" t="n"/>
-      <c r="I2" s="422" t="n"/>
-      <c r="J2" s="423" t="n"/>
-      <c r="K2" s="423" t="n"/>
       <c r="L2" s="423" t="n"/>
       <c r="M2" s="423" t="n"/>
       <c r="N2" s="423" t="n"/>
@@ -6120,16 +6721,6 @@
           <t>Controlled row-level entry. Use approved dropdowns only. Do not delete history. Refer to the FACE sheet for review context and sign-off.</t>
         </is>
       </c>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="421" t="n"/>
-      <c r="I3" s="422" t="n"/>
-      <c r="J3" s="423" t="n"/>
-      <c r="K3" s="423" t="n"/>
       <c r="L3" s="423" t="n"/>
       <c r="M3" s="423" t="n"/>
       <c r="N3" s="423" t="n"/>
@@ -6208,16 +6799,16 @@
           <t xml:space="preserve">  1. ACTIVE LOG TABLE</t>
         </is>
       </c>
-      <c r="B5" s="439" t="n"/>
-      <c r="C5" s="439" t="n"/>
-      <c r="D5" s="439" t="n"/>
-      <c r="E5" s="439" t="n"/>
-      <c r="F5" s="439" t="n"/>
-      <c r="G5" s="439" t="n"/>
-      <c r="H5" s="440" t="n"/>
-      <c r="I5" s="441" t="n"/>
-      <c r="J5" s="442" t="n"/>
-      <c r="K5" s="442" t="n"/>
+      <c r="B5" s="521" t="n"/>
+      <c r="C5" s="521" t="n"/>
+      <c r="D5" s="521" t="n"/>
+      <c r="E5" s="521" t="n"/>
+      <c r="F5" s="521" t="n"/>
+      <c r="G5" s="521" t="n"/>
+      <c r="H5" s="521" t="n"/>
+      <c r="I5" s="521" t="n"/>
+      <c r="J5" s="521" t="n"/>
+      <c r="K5" s="521" t="n"/>
       <c r="L5" s="442" t="n"/>
       <c r="M5" s="442" t="n"/>
       <c r="N5" s="442" t="n"/>
@@ -7732,16 +8323,16 @@
           <t xml:space="preserve">  2. PERIODIC REVIEW / CLOSEOUT</t>
         </is>
       </c>
-      <c r="B38" s="467" t="n"/>
-      <c r="C38" s="467" t="n"/>
-      <c r="D38" s="467" t="n"/>
-      <c r="E38" s="467" t="n"/>
-      <c r="F38" s="467" t="n"/>
-      <c r="G38" s="467" t="n"/>
-      <c r="H38" s="467" t="n"/>
-      <c r="I38" s="467" t="n"/>
-      <c r="J38" s="467" t="n"/>
-      <c r="K38" s="467" t="n"/>
+      <c r="B38" s="522" t="n"/>
+      <c r="C38" s="522" t="n"/>
+      <c r="D38" s="522" t="n"/>
+      <c r="E38" s="522" t="n"/>
+      <c r="F38" s="522" t="n"/>
+      <c r="G38" s="522" t="n"/>
+      <c r="H38" s="522" t="n"/>
+      <c r="I38" s="522" t="n"/>
+      <c r="J38" s="522" t="n"/>
+      <c r="K38" s="522" t="n"/>
       <c r="L38" s="467" t="n"/>
       <c r="M38" s="467" t="n"/>
       <c r="N38" s="467" t="n"/>
@@ -7778,20 +8369,20 @@
           <t>Review Date</t>
         </is>
       </c>
-      <c r="B39" s="456" t="n"/>
+      <c r="B39" s="523" t="n"/>
       <c r="C39" s="470" t="inlineStr"/>
-      <c r="D39" s="456" t="n"/>
-      <c r="E39" s="456" t="n"/>
+      <c r="D39" s="523" t="n"/>
+      <c r="E39" s="523" t="n"/>
       <c r="F39" s="471" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="G39" s="456" t="n"/>
+      <c r="G39" s="523" t="n"/>
       <c r="H39" s="470" t="inlineStr"/>
-      <c r="I39" s="456" t="n"/>
-      <c r="J39" s="456" t="n"/>
-      <c r="K39" s="456" t="n"/>
+      <c r="I39" s="523" t="n"/>
+      <c r="J39" s="523" t="n"/>
+      <c r="K39" s="523" t="n"/>
       <c r="L39" s="472" t="n"/>
       <c r="M39" s="456" t="n"/>
       <c r="N39" s="456" t="n"/>
@@ -7828,20 +8419,20 @@
           <t>Open Items / Exceptions</t>
         </is>
       </c>
-      <c r="B40" s="340" t="n"/>
+      <c r="B40" s="402" t="n"/>
       <c r="C40" s="474" t="inlineStr"/>
-      <c r="D40" s="340" t="n"/>
-      <c r="E40" s="340" t="n"/>
+      <c r="D40" s="402" t="n"/>
+      <c r="E40" s="402" t="n"/>
       <c r="F40" s="475" t="inlineStr">
         <is>
           <t>Final Status</t>
         </is>
       </c>
-      <c r="G40" s="340" t="n"/>
+      <c r="G40" s="402" t="n"/>
       <c r="H40" s="474" t="inlineStr"/>
-      <c r="I40" s="340" t="n"/>
-      <c r="J40" s="340" t="n"/>
-      <c r="K40" s="340" t="n"/>
+      <c r="I40" s="402" t="n"/>
+      <c r="J40" s="402" t="n"/>
+      <c r="K40" s="402" t="n"/>
       <c r="L40" s="476" t="n"/>
       <c r="M40" s="351" t="n"/>
       <c r="N40" s="351" t="n"/>
@@ -7920,16 +8511,16 @@
           <t>NOTICE: Complete in English. Do not back-date, delete history, or overwrite a closed row without a controlled supplemental entry. Review / sign-off context remains on sheet GAGE_VERIFY_LOG.</t>
         </is>
       </c>
-      <c r="B42" s="467" t="n"/>
-      <c r="C42" s="467" t="n"/>
-      <c r="D42" s="467" t="n"/>
-      <c r="E42" s="467" t="n"/>
-      <c r="F42" s="467" t="n"/>
-      <c r="G42" s="467" t="n"/>
-      <c r="H42" s="467" t="n"/>
-      <c r="I42" s="467" t="n"/>
-      <c r="J42" s="467" t="n"/>
-      <c r="K42" s="467" t="n"/>
+      <c r="B42" s="522" t="n"/>
+      <c r="C42" s="522" t="n"/>
+      <c r="D42" s="522" t="n"/>
+      <c r="E42" s="522" t="n"/>
+      <c r="F42" s="522" t="n"/>
+      <c r="G42" s="522" t="n"/>
+      <c r="H42" s="522" t="n"/>
+      <c r="I42" s="522" t="n"/>
+      <c r="J42" s="522" t="n"/>
+      <c r="K42" s="522" t="n"/>
       <c r="L42" s="467" t="n"/>
       <c r="M42" s="467" t="n"/>
       <c r="N42" s="467" t="n"/>
@@ -8069,2086 +8660,2086 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="477" t="inlineStr"/>
-      <c r="B1" s="409" t="n"/>
-      <c r="C1" s="409" t="n"/>
-      <c r="D1" s="409" t="n"/>
-      <c r="E1" s="409" t="n"/>
-      <c r="F1" s="409" t="n"/>
-      <c r="G1" s="409" t="n"/>
-      <c r="H1" s="409" t="n"/>
-      <c r="I1" s="409" t="n"/>
-      <c r="J1" s="409" t="n"/>
-      <c r="K1" s="410" t="n"/>
-      <c r="L1" s="411" t="inlineStr">
+      <c r="A1" s="524" t="inlineStr"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="53" t="n"/>
+      <c r="L1" s="525" t="inlineStr">
         <is>
           <t>Gage Verification Log</t>
         </is>
       </c>
-      <c r="M1" s="412" t="n"/>
-      <c r="N1" s="412" t="n"/>
-      <c r="O1" s="412" t="n"/>
-      <c r="P1" s="412" t="n"/>
-      <c r="Q1" s="412" t="n"/>
-      <c r="R1" s="412" t="n"/>
-      <c r="S1" s="412" t="n"/>
-      <c r="T1" s="412" t="n"/>
-      <c r="U1" s="412" t="n"/>
-      <c r="V1" s="412" t="n"/>
-      <c r="W1" s="412" t="n"/>
-      <c r="X1" s="412" t="n"/>
-      <c r="Y1" s="412" t="n"/>
-      <c r="Z1" s="412" t="n"/>
-      <c r="AA1" s="412" t="n"/>
-      <c r="AB1" s="412" t="n"/>
-      <c r="AC1" s="412" t="n"/>
-      <c r="AD1" s="412" t="n"/>
-      <c r="AE1" s="412" t="n"/>
-      <c r="AF1" s="412" t="n"/>
-      <c r="AG1" s="412" t="n"/>
-      <c r="AH1" s="412" t="n"/>
-      <c r="AI1" s="412" t="n"/>
-      <c r="AJ1" s="412" t="n"/>
-      <c r="AK1" s="412" t="n"/>
-      <c r="AL1" s="412" t="n"/>
-      <c r="AM1" s="412" t="n"/>
-      <c r="AN1" s="412" t="n"/>
-      <c r="AO1" s="412" t="n"/>
-      <c r="AP1" s="413" t="n"/>
-      <c r="AQ1" s="414" t="inlineStr">
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="2" t="n"/>
+      <c r="AI1" s="2" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="2" t="n"/>
+      <c r="AO1" s="2" t="n"/>
+      <c r="AP1" s="2" t="n"/>
+      <c r="AQ1" s="526" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="415" t="n"/>
-      <c r="AS1" s="415" t="n"/>
-      <c r="AT1" s="415" t="n"/>
-      <c r="AU1" s="415" t="n"/>
-      <c r="AV1" s="416" t="n"/>
-      <c r="AW1" s="417" t="inlineStr">
+      <c r="AR1" s="2" t="n"/>
+      <c r="AS1" s="2" t="n"/>
+      <c r="AT1" s="2" t="n"/>
+      <c r="AU1" s="2" t="n"/>
+      <c r="AV1" s="527" t="n"/>
+      <c r="AW1" s="528" t="inlineStr">
         <is>
           <t>FRM-602</t>
         </is>
       </c>
-      <c r="AX1" s="418" t="n"/>
-      <c r="AY1" s="418" t="n"/>
-      <c r="AZ1" s="418" t="n"/>
-      <c r="BA1" s="418" t="n"/>
-      <c r="BB1" s="418" t="n"/>
-      <c r="BC1" s="418" t="n"/>
-      <c r="BD1" s="419" t="n"/>
+      <c r="AX1" s="2" t="n"/>
+      <c r="AY1" s="2" t="n"/>
+      <c r="AZ1" s="2" t="n"/>
+      <c r="BA1" s="2" t="n"/>
+      <c r="BB1" s="2" t="n"/>
+      <c r="BC1" s="2" t="n"/>
+      <c r="BD1" s="53" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="478" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
-      <c r="H2" s="25" t="n"/>
-      <c r="I2" s="25" t="n"/>
-      <c r="J2" s="25" t="n"/>
-      <c r="K2" s="421" t="n"/>
-      <c r="L2" s="422" t="n"/>
-      <c r="M2" s="423" t="n"/>
-      <c r="N2" s="423" t="n"/>
-      <c r="O2" s="423" t="n"/>
-      <c r="P2" s="423" t="n"/>
-      <c r="Q2" s="423" t="n"/>
-      <c r="R2" s="423" t="n"/>
-      <c r="S2" s="423" t="n"/>
-      <c r="T2" s="423" t="n"/>
-      <c r="U2" s="423" t="n"/>
-      <c r="V2" s="423" t="n"/>
-      <c r="W2" s="423" t="n"/>
-      <c r="X2" s="423" t="n"/>
-      <c r="Y2" s="423" t="n"/>
-      <c r="Z2" s="423" t="n"/>
-      <c r="AA2" s="423" t="n"/>
-      <c r="AB2" s="423" t="n"/>
-      <c r="AC2" s="423" t="n"/>
-      <c r="AD2" s="423" t="n"/>
-      <c r="AE2" s="423" t="n"/>
-      <c r="AF2" s="423" t="n"/>
-      <c r="AG2" s="423" t="n"/>
-      <c r="AH2" s="423" t="n"/>
-      <c r="AI2" s="423" t="n"/>
-      <c r="AJ2" s="423" t="n"/>
-      <c r="AK2" s="423" t="n"/>
-      <c r="AL2" s="423" t="n"/>
-      <c r="AM2" s="423" t="n"/>
-      <c r="AN2" s="423" t="n"/>
-      <c r="AO2" s="423" t="n"/>
-      <c r="AP2" s="424" t="n"/>
-      <c r="AQ2" s="425" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="54" t="n"/>
+      <c r="L2" s="9" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="10" t="n"/>
+      <c r="AE2" s="10" t="n"/>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="10" t="n"/>
+      <c r="AI2" s="10" t="n"/>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="10" t="n"/>
+      <c r="AO2" s="10" t="n"/>
+      <c r="AP2" s="10" t="n"/>
+      <c r="AQ2" s="529" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="426" t="n"/>
-      <c r="AS2" s="426" t="n"/>
-      <c r="AT2" s="426" t="n"/>
-      <c r="AU2" s="426" t="n"/>
-      <c r="AV2" s="427" t="n"/>
-      <c r="AW2" s="428" t="inlineStr">
+      <c r="AR2" s="530" t="n"/>
+      <c r="AS2" s="530" t="n"/>
+      <c r="AT2" s="530" t="n"/>
+      <c r="AU2" s="530" t="n"/>
+      <c r="AV2" s="531" t="n"/>
+      <c r="AW2" s="532" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="429" t="n"/>
-      <c r="AY2" s="429" t="n"/>
-      <c r="AZ2" s="429" t="n"/>
-      <c r="BA2" s="429" t="n"/>
-      <c r="BB2" s="429" t="n"/>
-      <c r="BC2" s="429" t="n"/>
-      <c r="BD2" s="430" t="n"/>
+      <c r="AX2" s="530" t="n"/>
+      <c r="AY2" s="530" t="n"/>
+      <c r="AZ2" s="530" t="n"/>
+      <c r="BA2" s="530" t="n"/>
+      <c r="BB2" s="530" t="n"/>
+      <c r="BC2" s="530" t="n"/>
+      <c r="BD2" s="533" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="478" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="25" t="n"/>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="421" t="n"/>
-      <c r="L3" s="422" t="n"/>
-      <c r="M3" s="423" t="n"/>
-      <c r="N3" s="423" t="n"/>
-      <c r="O3" s="423" t="n"/>
-      <c r="P3" s="423" t="n"/>
-      <c r="Q3" s="423" t="n"/>
-      <c r="R3" s="423" t="n"/>
-      <c r="S3" s="423" t="n"/>
-      <c r="T3" s="423" t="n"/>
-      <c r="U3" s="423" t="n"/>
-      <c r="V3" s="423" t="n"/>
-      <c r="W3" s="423" t="n"/>
-      <c r="X3" s="423" t="n"/>
-      <c r="Y3" s="423" t="n"/>
-      <c r="Z3" s="423" t="n"/>
-      <c r="AA3" s="423" t="n"/>
-      <c r="AB3" s="423" t="n"/>
-      <c r="AC3" s="423" t="n"/>
-      <c r="AD3" s="423" t="n"/>
-      <c r="AE3" s="423" t="n"/>
-      <c r="AF3" s="423" t="n"/>
-      <c r="AG3" s="423" t="n"/>
-      <c r="AH3" s="423" t="n"/>
-      <c r="AI3" s="423" t="n"/>
-      <c r="AJ3" s="423" t="n"/>
-      <c r="AK3" s="423" t="n"/>
-      <c r="AL3" s="423" t="n"/>
-      <c r="AM3" s="423" t="n"/>
-      <c r="AN3" s="423" t="n"/>
-      <c r="AO3" s="423" t="n"/>
-      <c r="AP3" s="424" t="n"/>
-      <c r="AQ3" s="425" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="9" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="10" t="n"/>
+      <c r="AI3" s="10" t="n"/>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="10" t="n"/>
+      <c r="AO3" s="10" t="n"/>
+      <c r="AP3" s="10" t="n"/>
+      <c r="AQ3" s="529" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="426" t="n"/>
-      <c r="AS3" s="426" t="n"/>
-      <c r="AT3" s="426" t="n"/>
-      <c r="AU3" s="426" t="n"/>
-      <c r="AV3" s="427" t="n"/>
-      <c r="AW3" s="428" t="inlineStr">
+      <c r="AR3" s="530" t="n"/>
+      <c r="AS3" s="530" t="n"/>
+      <c r="AT3" s="530" t="n"/>
+      <c r="AU3" s="530" t="n"/>
+      <c r="AV3" s="531" t="n"/>
+      <c r="AW3" s="532" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="429" t="n"/>
-      <c r="AY3" s="429" t="n"/>
-      <c r="AZ3" s="429" t="n"/>
-      <c r="BA3" s="429" t="n"/>
-      <c r="BB3" s="429" t="n"/>
-      <c r="BC3" s="429" t="n"/>
-      <c r="BD3" s="430" t="n"/>
+      <c r="AX3" s="530" t="n"/>
+      <c r="AY3" s="530" t="n"/>
+      <c r="AZ3" s="530" t="n"/>
+      <c r="BA3" s="530" t="n"/>
+      <c r="BB3" s="530" t="n"/>
+      <c r="BC3" s="530" t="n"/>
+      <c r="BD3" s="533" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="478" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="421" t="n"/>
-      <c r="L4" s="435" t="inlineStr">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="54" t="n"/>
+      <c r="L4" s="534" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="436" t="n"/>
-      <c r="N4" s="436" t="n"/>
-      <c r="O4" s="436" t="n"/>
-      <c r="P4" s="436" t="n"/>
-      <c r="Q4" s="436" t="n"/>
-      <c r="R4" s="436" t="n"/>
-      <c r="S4" s="436" t="n"/>
-      <c r="T4" s="436" t="n"/>
-      <c r="U4" s="436" t="n"/>
-      <c r="V4" s="436" t="n"/>
-      <c r="W4" s="436" t="n"/>
-      <c r="X4" s="436" t="n"/>
-      <c r="Y4" s="436" t="n"/>
-      <c r="Z4" s="436" t="n"/>
-      <c r="AA4" s="436" t="n"/>
-      <c r="AB4" s="436" t="n"/>
-      <c r="AC4" s="436" t="n"/>
-      <c r="AD4" s="436" t="n"/>
-      <c r="AE4" s="436" t="n"/>
-      <c r="AF4" s="436" t="n"/>
-      <c r="AG4" s="436" t="n"/>
-      <c r="AH4" s="436" t="n"/>
-      <c r="AI4" s="436" t="n"/>
-      <c r="AJ4" s="436" t="n"/>
-      <c r="AK4" s="436" t="n"/>
-      <c r="AL4" s="436" t="n"/>
-      <c r="AM4" s="436" t="n"/>
-      <c r="AN4" s="436" t="n"/>
-      <c r="AO4" s="436" t="n"/>
-      <c r="AP4" s="437" t="n"/>
-      <c r="AQ4" s="425" t="inlineStr">
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="10" t="n"/>
+      <c r="AI4" s="10" t="n"/>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="10" t="n"/>
+      <c r="AO4" s="10" t="n"/>
+      <c r="AP4" s="10" t="n"/>
+      <c r="AQ4" s="529" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="426" t="n"/>
-      <c r="AS4" s="426" t="n"/>
-      <c r="AT4" s="426" t="n"/>
-      <c r="AU4" s="426" t="n"/>
-      <c r="AV4" s="427" t="n"/>
-      <c r="AW4" s="428" t="inlineStr">
+      <c r="AR4" s="530" t="n"/>
+      <c r="AS4" s="530" t="n"/>
+      <c r="AT4" s="530" t="n"/>
+      <c r="AU4" s="530" t="n"/>
+      <c r="AV4" s="531" t="n"/>
+      <c r="AW4" s="532" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="429" t="n"/>
-      <c r="AY4" s="429" t="n"/>
-      <c r="AZ4" s="429" t="n"/>
-      <c r="BA4" s="429" t="n"/>
-      <c r="BB4" s="429" t="n"/>
-      <c r="BC4" s="429" t="n"/>
-      <c r="BD4" s="430" t="n"/>
+      <c r="AX4" s="530" t="n"/>
+      <c r="AY4" s="530" t="n"/>
+      <c r="AZ4" s="530" t="n"/>
+      <c r="BA4" s="530" t="n"/>
+      <c r="BB4" s="530" t="n"/>
+      <c r="BC4" s="530" t="n"/>
+      <c r="BD4" s="533" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="479" t="n"/>
-      <c r="B5" s="439" t="n"/>
-      <c r="C5" s="439" t="n"/>
-      <c r="D5" s="439" t="n"/>
-      <c r="E5" s="439" t="n"/>
-      <c r="F5" s="439" t="n"/>
-      <c r="G5" s="439" t="n"/>
-      <c r="H5" s="439" t="n"/>
-      <c r="I5" s="439" t="n"/>
-      <c r="J5" s="439" t="n"/>
-      <c r="K5" s="440" t="n"/>
-      <c r="L5" s="441" t="inlineStr">
+      <c r="A5" s="18" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="19" t="n"/>
+      <c r="J5" s="19" t="n"/>
+      <c r="K5" s="24" t="n"/>
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="442" t="n"/>
-      <c r="N5" s="442" t="n"/>
-      <c r="O5" s="442" t="n"/>
-      <c r="P5" s="442" t="n"/>
-      <c r="Q5" s="442" t="n"/>
-      <c r="R5" s="442" t="n"/>
-      <c r="S5" s="442" t="n"/>
-      <c r="T5" s="442" t="n"/>
-      <c r="U5" s="442" t="n"/>
-      <c r="V5" s="442" t="n"/>
-      <c r="W5" s="442" t="n"/>
-      <c r="X5" s="442" t="n"/>
-      <c r="Y5" s="442" t="n"/>
-      <c r="Z5" s="442" t="n"/>
-      <c r="AA5" s="442" t="n"/>
-      <c r="AB5" s="442" t="n"/>
-      <c r="AC5" s="442" t="n"/>
-      <c r="AD5" s="442" t="n"/>
-      <c r="AE5" s="442" t="n"/>
-      <c r="AF5" s="442" t="n"/>
-      <c r="AG5" s="442" t="n"/>
-      <c r="AH5" s="442" t="n"/>
-      <c r="AI5" s="442" t="n"/>
-      <c r="AJ5" s="442" t="n"/>
-      <c r="AK5" s="442" t="n"/>
-      <c r="AL5" s="442" t="n"/>
-      <c r="AM5" s="442" t="n"/>
-      <c r="AN5" s="442" t="n"/>
-      <c r="AO5" s="442" t="n"/>
-      <c r="AP5" s="443" t="n"/>
-      <c r="AQ5" s="444" t="inlineStr">
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="19" t="n"/>
+      <c r="Q5" s="19" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="S5" s="19" t="n"/>
+      <c r="T5" s="19" t="n"/>
+      <c r="U5" s="19" t="n"/>
+      <c r="V5" s="19" t="n"/>
+      <c r="W5" s="19" t="n"/>
+      <c r="X5" s="19" t="n"/>
+      <c r="Y5" s="19" t="n"/>
+      <c r="Z5" s="19" t="n"/>
+      <c r="AA5" s="19" t="n"/>
+      <c r="AB5" s="19" t="n"/>
+      <c r="AC5" s="19" t="n"/>
+      <c r="AD5" s="19" t="n"/>
+      <c r="AE5" s="19" t="n"/>
+      <c r="AF5" s="19" t="n"/>
+      <c r="AG5" s="19" t="n"/>
+      <c r="AH5" s="19" t="n"/>
+      <c r="AI5" s="19" t="n"/>
+      <c r="AJ5" s="19" t="n"/>
+      <c r="AK5" s="19" t="n"/>
+      <c r="AL5" s="19" t="n"/>
+      <c r="AM5" s="19" t="n"/>
+      <c r="AN5" s="19" t="n"/>
+      <c r="AO5" s="19" t="n"/>
+      <c r="AP5" s="19" t="n"/>
+      <c r="AQ5" s="535" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="445" t="n"/>
-      <c r="AS5" s="445" t="n"/>
-      <c r="AT5" s="445" t="n"/>
-      <c r="AU5" s="445" t="n"/>
-      <c r="AV5" s="446" t="n"/>
-      <c r="AW5" s="447" t="inlineStr">
+      <c r="AR5" s="536" t="n"/>
+      <c r="AS5" s="536" t="n"/>
+      <c r="AT5" s="536" t="n"/>
+      <c r="AU5" s="536" t="n"/>
+      <c r="AV5" s="537" t="n"/>
+      <c r="AW5" s="538" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="448" t="n"/>
-      <c r="AY5" s="448" t="n"/>
-      <c r="AZ5" s="448" t="n"/>
-      <c r="BA5" s="448" t="n"/>
-      <c r="BB5" s="448" t="n"/>
-      <c r="BC5" s="448" t="n"/>
-      <c r="BD5" s="449" t="n"/>
+      <c r="AX5" s="536" t="n"/>
+      <c r="AY5" s="536" t="n"/>
+      <c r="AZ5" s="536" t="n"/>
+      <c r="BA5" s="536" t="n"/>
+      <c r="BB5" s="536" t="n"/>
+      <c r="BC5" s="536" t="n"/>
+      <c r="BD5" s="539" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="480" t="n"/>
-      <c r="B6" s="480" t="n"/>
-      <c r="C6" s="480" t="n"/>
-      <c r="D6" s="480" t="n"/>
-      <c r="E6" s="480" t="n"/>
-      <c r="F6" s="480" t="n"/>
-      <c r="G6" s="480" t="n"/>
-      <c r="H6" s="480" t="n"/>
-      <c r="I6" s="480" t="n"/>
-      <c r="J6" s="480" t="n"/>
-      <c r="K6" s="480" t="n"/>
-      <c r="L6" s="480" t="n"/>
-      <c r="M6" s="480" t="n"/>
-      <c r="N6" s="480" t="n"/>
-      <c r="O6" s="480" t="n"/>
-      <c r="P6" s="480" t="n"/>
-      <c r="Q6" s="480" t="n"/>
-      <c r="R6" s="480" t="n"/>
-      <c r="S6" s="480" t="n"/>
-      <c r="T6" s="480" t="n"/>
-      <c r="U6" s="480" t="n"/>
-      <c r="V6" s="480" t="n"/>
-      <c r="W6" s="480" t="n"/>
-      <c r="X6" s="480" t="n"/>
-      <c r="Y6" s="480" t="n"/>
-      <c r="Z6" s="480" t="n"/>
-      <c r="AA6" s="480" t="n"/>
-      <c r="AB6" s="480" t="n"/>
-      <c r="AC6" s="480" t="n"/>
-      <c r="AD6" s="480" t="n"/>
-      <c r="AE6" s="480" t="n"/>
-      <c r="AF6" s="480" t="n"/>
-      <c r="AG6" s="480" t="n"/>
-      <c r="AH6" s="480" t="n"/>
-      <c r="AI6" s="480" t="n"/>
-      <c r="AJ6" s="480" t="n"/>
-      <c r="AK6" s="480" t="n"/>
-      <c r="AL6" s="480" t="n"/>
-      <c r="AM6" s="480" t="n"/>
-      <c r="AN6" s="480" t="n"/>
-      <c r="AO6" s="480" t="n"/>
-      <c r="AP6" s="480" t="n"/>
-      <c r="AQ6" s="480" t="n"/>
-      <c r="AR6" s="480" t="n"/>
-      <c r="AS6" s="480" t="n"/>
-      <c r="AT6" s="480" t="n"/>
-      <c r="AU6" s="480" t="n"/>
-      <c r="AV6" s="480" t="n"/>
-      <c r="AW6" s="480" t="n"/>
-      <c r="AX6" s="480" t="n"/>
-      <c r="AY6" s="480" t="n"/>
-      <c r="AZ6" s="480" t="n"/>
-      <c r="BA6" s="480" t="n"/>
-      <c r="BB6" s="480" t="n"/>
-      <c r="BC6" s="480" t="n"/>
-      <c r="BD6" s="480" t="n"/>
+      <c r="A6" s="433" t="n"/>
+      <c r="B6" s="433" t="n"/>
+      <c r="C6" s="433" t="n"/>
+      <c r="D6" s="433" t="n"/>
+      <c r="E6" s="433" t="n"/>
+      <c r="F6" s="433" t="n"/>
+      <c r="G6" s="433" t="n"/>
+      <c r="H6" s="433" t="n"/>
+      <c r="I6" s="433" t="n"/>
+      <c r="J6" s="433" t="n"/>
+      <c r="K6" s="433" t="n"/>
+      <c r="L6" s="433" t="n"/>
+      <c r="M6" s="433" t="n"/>
+      <c r="N6" s="433" t="n"/>
+      <c r="O6" s="433" t="n"/>
+      <c r="P6" s="433" t="n"/>
+      <c r="Q6" s="433" t="n"/>
+      <c r="R6" s="433" t="n"/>
+      <c r="S6" s="433" t="n"/>
+      <c r="T6" s="433" t="n"/>
+      <c r="U6" s="433" t="n"/>
+      <c r="V6" s="433" t="n"/>
+      <c r="W6" s="433" t="n"/>
+      <c r="X6" s="433" t="n"/>
+      <c r="Y6" s="433" t="n"/>
+      <c r="Z6" s="433" t="n"/>
+      <c r="AA6" s="433" t="n"/>
+      <c r="AB6" s="433" t="n"/>
+      <c r="AC6" s="433" t="n"/>
+      <c r="AD6" s="433" t="n"/>
+      <c r="AE6" s="433" t="n"/>
+      <c r="AF6" s="433" t="n"/>
+      <c r="AG6" s="433" t="n"/>
+      <c r="AH6" s="433" t="n"/>
+      <c r="AI6" s="433" t="n"/>
+      <c r="AJ6" s="433" t="n"/>
+      <c r="AK6" s="433" t="n"/>
+      <c r="AL6" s="433" t="n"/>
+      <c r="AM6" s="433" t="n"/>
+      <c r="AN6" s="433" t="n"/>
+      <c r="AO6" s="433" t="n"/>
+      <c r="AP6" s="433" t="n"/>
+      <c r="AQ6" s="433" t="n"/>
+      <c r="AR6" s="433" t="n"/>
+      <c r="AS6" s="433" t="n"/>
+      <c r="AT6" s="433" t="n"/>
+      <c r="AU6" s="433" t="n"/>
+      <c r="AV6" s="433" t="n"/>
+      <c r="AW6" s="433" t="n"/>
+      <c r="AX6" s="433" t="n"/>
+      <c r="AY6" s="433" t="n"/>
+      <c r="AZ6" s="433" t="n"/>
+      <c r="BA6" s="433" t="n"/>
+      <c r="BB6" s="433" t="n"/>
+      <c r="BC6" s="433" t="n"/>
+      <c r="BD6" s="433" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="466" t="inlineStr">
+      <c r="A7" s="540" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. SCOPE / REVIEW CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="467" t="n"/>
-      <c r="C7" s="467" t="n"/>
-      <c r="D7" s="467" t="n"/>
-      <c r="E7" s="467" t="n"/>
-      <c r="F7" s="467" t="n"/>
-      <c r="G7" s="467" t="n"/>
-      <c r="H7" s="467" t="n"/>
-      <c r="I7" s="467" t="n"/>
-      <c r="J7" s="467" t="n"/>
-      <c r="K7" s="467" t="n"/>
-      <c r="L7" s="467" t="n"/>
-      <c r="M7" s="467" t="n"/>
-      <c r="N7" s="467" t="n"/>
-      <c r="O7" s="467" t="n"/>
-      <c r="P7" s="467" t="n"/>
-      <c r="Q7" s="467" t="n"/>
-      <c r="R7" s="467" t="n"/>
-      <c r="S7" s="467" t="n"/>
-      <c r="T7" s="467" t="n"/>
-      <c r="U7" s="467" t="n"/>
-      <c r="V7" s="467" t="n"/>
-      <c r="W7" s="467" t="n"/>
-      <c r="X7" s="467" t="n"/>
-      <c r="Y7" s="467" t="n"/>
-      <c r="Z7" s="467" t="n"/>
-      <c r="AA7" s="467" t="n"/>
-      <c r="AB7" s="467" t="n"/>
-      <c r="AC7" s="467" t="n"/>
-      <c r="AD7" s="467" t="n"/>
-      <c r="AE7" s="467" t="n"/>
-      <c r="AF7" s="467" t="n"/>
-      <c r="AG7" s="467" t="n"/>
-      <c r="AH7" s="467" t="n"/>
-      <c r="AI7" s="467" t="n"/>
-      <c r="AJ7" s="467" t="n"/>
-      <c r="AK7" s="467" t="n"/>
-      <c r="AL7" s="467" t="n"/>
-      <c r="AM7" s="467" t="n"/>
-      <c r="AN7" s="467" t="n"/>
-      <c r="AO7" s="467" t="n"/>
-      <c r="AP7" s="467" t="n"/>
-      <c r="AQ7" s="467" t="n"/>
-      <c r="AR7" s="467" t="n"/>
-      <c r="AS7" s="467" t="n"/>
-      <c r="AT7" s="467" t="n"/>
-      <c r="AU7" s="467" t="n"/>
-      <c r="AV7" s="467" t="n"/>
-      <c r="AW7" s="467" t="n"/>
-      <c r="AX7" s="467" t="n"/>
-      <c r="AY7" s="467" t="n"/>
-      <c r="AZ7" s="467" t="n"/>
-      <c r="BA7" s="467" t="n"/>
-      <c r="BB7" s="467" t="n"/>
-      <c r="BC7" s="467" t="n"/>
-      <c r="BD7" s="468" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="27" t="n"/>
+      <c r="J7" s="27" t="n"/>
+      <c r="K7" s="27" t="n"/>
+      <c r="L7" s="27" t="n"/>
+      <c r="M7" s="27" t="n"/>
+      <c r="N7" s="27" t="n"/>
+      <c r="O7" s="27" t="n"/>
+      <c r="P7" s="27" t="n"/>
+      <c r="Q7" s="27" t="n"/>
+      <c r="R7" s="27" t="n"/>
+      <c r="S7" s="27" t="n"/>
+      <c r="T7" s="27" t="n"/>
+      <c r="U7" s="27" t="n"/>
+      <c r="V7" s="27" t="n"/>
+      <c r="W7" s="27" t="n"/>
+      <c r="X7" s="27" t="n"/>
+      <c r="Y7" s="27" t="n"/>
+      <c r="Z7" s="27" t="n"/>
+      <c r="AA7" s="27" t="n"/>
+      <c r="AB7" s="27" t="n"/>
+      <c r="AC7" s="27" t="n"/>
+      <c r="AD7" s="27" t="n"/>
+      <c r="AE7" s="27" t="n"/>
+      <c r="AF7" s="27" t="n"/>
+      <c r="AG7" s="27" t="n"/>
+      <c r="AH7" s="27" t="n"/>
+      <c r="AI7" s="27" t="n"/>
+      <c r="AJ7" s="27" t="n"/>
+      <c r="AK7" s="27" t="n"/>
+      <c r="AL7" s="27" t="n"/>
+      <c r="AM7" s="27" t="n"/>
+      <c r="AN7" s="27" t="n"/>
+      <c r="AO7" s="27" t="n"/>
+      <c r="AP7" s="27" t="n"/>
+      <c r="AQ7" s="27" t="n"/>
+      <c r="AR7" s="27" t="n"/>
+      <c r="AS7" s="27" t="n"/>
+      <c r="AT7" s="27" t="n"/>
+      <c r="AU7" s="27" t="n"/>
+      <c r="AV7" s="27" t="n"/>
+      <c r="AW7" s="27" t="n"/>
+      <c r="AX7" s="27" t="n"/>
+      <c r="AY7" s="27" t="n"/>
+      <c r="AZ7" s="27" t="n"/>
+      <c r="BA7" s="27" t="n"/>
+      <c r="BB7" s="27" t="n"/>
+      <c r="BC7" s="27" t="n"/>
+      <c r="BD7" s="28" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="469" t="inlineStr">
+      <c r="A8" s="541" t="inlineStr">
         <is>
           <t>Verification ID</t>
         </is>
       </c>
-      <c r="B8" s="456" t="n"/>
-      <c r="C8" s="456" t="n"/>
-      <c r="D8" s="456" t="n"/>
-      <c r="E8" s="456" t="n"/>
-      <c r="F8" s="456" t="n"/>
-      <c r="G8" s="456" t="n"/>
-      <c r="H8" s="456" t="n"/>
-      <c r="I8" s="456" t="n"/>
-      <c r="J8" s="456" t="n"/>
-      <c r="K8" s="481" t="n"/>
-      <c r="L8" s="482" t="n"/>
-      <c r="M8" s="482" t="n"/>
-      <c r="N8" s="482" t="n"/>
-      <c r="O8" s="482" t="n"/>
-      <c r="P8" s="482" t="n"/>
-      <c r="Q8" s="482" t="n"/>
-      <c r="R8" s="482" t="n"/>
-      <c r="S8" s="482" t="n"/>
-      <c r="T8" s="482" t="n"/>
-      <c r="U8" s="482" t="n"/>
-      <c r="V8" s="482" t="n"/>
-      <c r="W8" s="482" t="n"/>
-      <c r="X8" s="482" t="n"/>
-      <c r="Y8" s="482" t="n"/>
-      <c r="Z8" s="482" t="n"/>
-      <c r="AA8" s="482" t="n"/>
-      <c r="AB8" s="482" t="n"/>
-      <c r="AC8" s="471" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="542" t="n"/>
+      <c r="L8" s="543" t="n"/>
+      <c r="M8" s="543" t="n"/>
+      <c r="N8" s="543" t="n"/>
+      <c r="O8" s="543" t="n"/>
+      <c r="P8" s="543" t="n"/>
+      <c r="Q8" s="543" t="n"/>
+      <c r="R8" s="543" t="n"/>
+      <c r="S8" s="543" t="n"/>
+      <c r="T8" s="543" t="n"/>
+      <c r="U8" s="543" t="n"/>
+      <c r="V8" s="543" t="n"/>
+      <c r="W8" s="543" t="n"/>
+      <c r="X8" s="543" t="n"/>
+      <c r="Y8" s="543" t="n"/>
+      <c r="Z8" s="543" t="n"/>
+      <c r="AA8" s="543" t="n"/>
+      <c r="AB8" s="544" t="n"/>
+      <c r="AC8" s="545" t="inlineStr">
         <is>
           <t>Verification Result</t>
         </is>
       </c>
-      <c r="AD8" s="456" t="n"/>
-      <c r="AE8" s="456" t="n"/>
-      <c r="AF8" s="456" t="n"/>
-      <c r="AG8" s="456" t="n"/>
-      <c r="AH8" s="456" t="n"/>
-      <c r="AI8" s="456" t="n"/>
-      <c r="AJ8" s="456" t="n"/>
-      <c r="AK8" s="456" t="n"/>
-      <c r="AL8" s="456" t="n"/>
-      <c r="AM8" s="481" t="n"/>
-      <c r="AN8" s="482" t="n"/>
-      <c r="AO8" s="482" t="n"/>
-      <c r="AP8" s="482" t="n"/>
-      <c r="AQ8" s="482" t="n"/>
-      <c r="AR8" s="482" t="n"/>
-      <c r="AS8" s="482" t="n"/>
-      <c r="AT8" s="482" t="n"/>
-      <c r="AU8" s="482" t="n"/>
-      <c r="AV8" s="482" t="n"/>
-      <c r="AW8" s="482" t="n"/>
-      <c r="AX8" s="482" t="n"/>
-      <c r="AY8" s="482" t="n"/>
-      <c r="AZ8" s="482" t="n"/>
-      <c r="BA8" s="482" t="n"/>
-      <c r="BB8" s="482" t="n"/>
-      <c r="BC8" s="482" t="n"/>
-      <c r="BD8" s="483" t="n"/>
+      <c r="AD8" s="5" t="n"/>
+      <c r="AE8" s="5" t="n"/>
+      <c r="AF8" s="5" t="n"/>
+      <c r="AG8" s="5" t="n"/>
+      <c r="AH8" s="5" t="n"/>
+      <c r="AI8" s="5" t="n"/>
+      <c r="AJ8" s="5" t="n"/>
+      <c r="AK8" s="5" t="n"/>
+      <c r="AL8" s="6" t="n"/>
+      <c r="AM8" s="542" t="n"/>
+      <c r="AN8" s="543" t="n"/>
+      <c r="AO8" s="543" t="n"/>
+      <c r="AP8" s="543" t="n"/>
+      <c r="AQ8" s="543" t="n"/>
+      <c r="AR8" s="543" t="n"/>
+      <c r="AS8" s="543" t="n"/>
+      <c r="AT8" s="543" t="n"/>
+      <c r="AU8" s="543" t="n"/>
+      <c r="AV8" s="543" t="n"/>
+      <c r="AW8" s="543" t="n"/>
+      <c r="AX8" s="543" t="n"/>
+      <c r="AY8" s="543" t="n"/>
+      <c r="AZ8" s="543" t="n"/>
+      <c r="BA8" s="543" t="n"/>
+      <c r="BB8" s="543" t="n"/>
+      <c r="BC8" s="543" t="n"/>
+      <c r="BD8" s="546" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="473" t="inlineStr">
+      <c r="A9" s="547" t="inlineStr">
         <is>
           <t>Equipment ID / Description</t>
         </is>
       </c>
-      <c r="B9" s="340" t="n"/>
-      <c r="C9" s="340" t="n"/>
-      <c r="D9" s="340" t="n"/>
-      <c r="E9" s="340" t="n"/>
-      <c r="F9" s="340" t="n"/>
-      <c r="G9" s="340" t="n"/>
-      <c r="H9" s="340" t="n"/>
-      <c r="I9" s="340" t="n"/>
-      <c r="J9" s="340" t="n"/>
-      <c r="K9" s="484" t="n"/>
-      <c r="L9" s="371" t="n"/>
-      <c r="M9" s="371" t="n"/>
-      <c r="N9" s="371" t="n"/>
-      <c r="O9" s="371" t="n"/>
-      <c r="P9" s="371" t="n"/>
-      <c r="Q9" s="371" t="n"/>
-      <c r="R9" s="371" t="n"/>
-      <c r="S9" s="371" t="n"/>
-      <c r="T9" s="371" t="n"/>
-      <c r="U9" s="371" t="n"/>
-      <c r="V9" s="371" t="n"/>
-      <c r="W9" s="371" t="n"/>
-      <c r="X9" s="371" t="n"/>
-      <c r="Y9" s="371" t="n"/>
-      <c r="Z9" s="371" t="n"/>
-      <c r="AA9" s="371" t="n"/>
-      <c r="AB9" s="371" t="n"/>
-      <c r="AC9" s="475" t="inlineStr">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="548" t="n"/>
+      <c r="L9" s="549" t="n"/>
+      <c r="M9" s="549" t="n"/>
+      <c r="N9" s="549" t="n"/>
+      <c r="O9" s="549" t="n"/>
+      <c r="P9" s="549" t="n"/>
+      <c r="Q9" s="549" t="n"/>
+      <c r="R9" s="549" t="n"/>
+      <c r="S9" s="549" t="n"/>
+      <c r="T9" s="549" t="n"/>
+      <c r="U9" s="549" t="n"/>
+      <c r="V9" s="549" t="n"/>
+      <c r="W9" s="549" t="n"/>
+      <c r="X9" s="549" t="n"/>
+      <c r="Y9" s="549" t="n"/>
+      <c r="Z9" s="549" t="n"/>
+      <c r="AA9" s="549" t="n"/>
+      <c r="AB9" s="550" t="n"/>
+      <c r="AC9" s="551" t="inlineStr">
         <is>
           <t>User / Area</t>
         </is>
       </c>
-      <c r="AD9" s="340" t="n"/>
-      <c r="AE9" s="340" t="n"/>
-      <c r="AF9" s="340" t="n"/>
-      <c r="AG9" s="340" t="n"/>
-      <c r="AH9" s="340" t="n"/>
-      <c r="AI9" s="340" t="n"/>
-      <c r="AJ9" s="340" t="n"/>
-      <c r="AK9" s="340" t="n"/>
-      <c r="AL9" s="340" t="n"/>
-      <c r="AM9" s="484" t="n"/>
-      <c r="AN9" s="371" t="n"/>
-      <c r="AO9" s="371" t="n"/>
-      <c r="AP9" s="371" t="n"/>
-      <c r="AQ9" s="371" t="n"/>
-      <c r="AR9" s="371" t="n"/>
-      <c r="AS9" s="371" t="n"/>
-      <c r="AT9" s="371" t="n"/>
-      <c r="AU9" s="371" t="n"/>
-      <c r="AV9" s="371" t="n"/>
-      <c r="AW9" s="371" t="n"/>
-      <c r="AX9" s="371" t="n"/>
-      <c r="AY9" s="371" t="n"/>
-      <c r="AZ9" s="371" t="n"/>
-      <c r="BA9" s="371" t="n"/>
-      <c r="BB9" s="371" t="n"/>
-      <c r="BC9" s="371" t="n"/>
-      <c r="BD9" s="485" t="n"/>
+      <c r="AD9" s="12" t="n"/>
+      <c r="AE9" s="12" t="n"/>
+      <c r="AF9" s="12" t="n"/>
+      <c r="AG9" s="12" t="n"/>
+      <c r="AH9" s="12" t="n"/>
+      <c r="AI9" s="12" t="n"/>
+      <c r="AJ9" s="12" t="n"/>
+      <c r="AK9" s="12" t="n"/>
+      <c r="AL9" s="13" t="n"/>
+      <c r="AM9" s="548" t="n"/>
+      <c r="AN9" s="549" t="n"/>
+      <c r="AO9" s="549" t="n"/>
+      <c r="AP9" s="549" t="n"/>
+      <c r="AQ9" s="549" t="n"/>
+      <c r="AR9" s="549" t="n"/>
+      <c r="AS9" s="549" t="n"/>
+      <c r="AT9" s="549" t="n"/>
+      <c r="AU9" s="549" t="n"/>
+      <c r="AV9" s="549" t="n"/>
+      <c r="AW9" s="549" t="n"/>
+      <c r="AX9" s="549" t="n"/>
+      <c r="AY9" s="549" t="n"/>
+      <c r="AZ9" s="549" t="n"/>
+      <c r="BA9" s="549" t="n"/>
+      <c r="BB9" s="549" t="n"/>
+      <c r="BC9" s="549" t="n"/>
+      <c r="BD9" s="552" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="473" t="inlineStr">
+      <c r="A10" s="547" t="inlineStr">
         <is>
           <t>Verification Type</t>
         </is>
       </c>
-      <c r="B10" s="340" t="n"/>
-      <c r="C10" s="340" t="n"/>
-      <c r="D10" s="340" t="n"/>
-      <c r="E10" s="340" t="n"/>
-      <c r="F10" s="340" t="n"/>
-      <c r="G10" s="340" t="n"/>
-      <c r="H10" s="340" t="n"/>
-      <c r="I10" s="340" t="n"/>
-      <c r="J10" s="340" t="n"/>
-      <c r="K10" s="484" t="n"/>
-      <c r="L10" s="371" t="n"/>
-      <c r="M10" s="371" t="n"/>
-      <c r="N10" s="371" t="n"/>
-      <c r="O10" s="371" t="n"/>
-      <c r="P10" s="371" t="n"/>
-      <c r="Q10" s="371" t="n"/>
-      <c r="R10" s="371" t="n"/>
-      <c r="S10" s="371" t="n"/>
-      <c r="T10" s="371" t="n"/>
-      <c r="U10" s="371" t="n"/>
-      <c r="V10" s="371" t="n"/>
-      <c r="W10" s="371" t="n"/>
-      <c r="X10" s="371" t="n"/>
-      <c r="Y10" s="371" t="n"/>
-      <c r="Z10" s="371" t="n"/>
-      <c r="AA10" s="371" t="n"/>
-      <c r="AB10" s="371" t="n"/>
-      <c r="AC10" s="475" t="inlineStr">
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="548" t="n"/>
+      <c r="L10" s="549" t="n"/>
+      <c r="M10" s="549" t="n"/>
+      <c r="N10" s="549" t="n"/>
+      <c r="O10" s="549" t="n"/>
+      <c r="P10" s="549" t="n"/>
+      <c r="Q10" s="549" t="n"/>
+      <c r="R10" s="549" t="n"/>
+      <c r="S10" s="549" t="n"/>
+      <c r="T10" s="549" t="n"/>
+      <c r="U10" s="549" t="n"/>
+      <c r="V10" s="549" t="n"/>
+      <c r="W10" s="549" t="n"/>
+      <c r="X10" s="549" t="n"/>
+      <c r="Y10" s="549" t="n"/>
+      <c r="Z10" s="549" t="n"/>
+      <c r="AA10" s="549" t="n"/>
+      <c r="AB10" s="550" t="n"/>
+      <c r="AC10" s="551" t="inlineStr">
         <is>
           <t>CAL Status</t>
         </is>
       </c>
-      <c r="AD10" s="340" t="n"/>
-      <c r="AE10" s="340" t="n"/>
-      <c r="AF10" s="340" t="n"/>
-      <c r="AG10" s="340" t="n"/>
-      <c r="AH10" s="340" t="n"/>
-      <c r="AI10" s="340" t="n"/>
-      <c r="AJ10" s="340" t="n"/>
-      <c r="AK10" s="340" t="n"/>
-      <c r="AL10" s="340" t="n"/>
-      <c r="AM10" s="484" t="n"/>
-      <c r="AN10" s="371" t="n"/>
-      <c r="AO10" s="371" t="n"/>
-      <c r="AP10" s="371" t="n"/>
-      <c r="AQ10" s="371" t="n"/>
-      <c r="AR10" s="371" t="n"/>
-      <c r="AS10" s="371" t="n"/>
-      <c r="AT10" s="371" t="n"/>
-      <c r="AU10" s="371" t="n"/>
-      <c r="AV10" s="371" t="n"/>
-      <c r="AW10" s="371" t="n"/>
-      <c r="AX10" s="371" t="n"/>
-      <c r="AY10" s="371" t="n"/>
-      <c r="AZ10" s="371" t="n"/>
-      <c r="BA10" s="371" t="n"/>
-      <c r="BB10" s="371" t="n"/>
-      <c r="BC10" s="371" t="n"/>
-      <c r="BD10" s="485" t="n"/>
+      <c r="AD10" s="12" t="n"/>
+      <c r="AE10" s="12" t="n"/>
+      <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="12" t="n"/>
+      <c r="AH10" s="12" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="12" t="n"/>
+      <c r="AK10" s="12" t="n"/>
+      <c r="AL10" s="13" t="n"/>
+      <c r="AM10" s="548" t="n"/>
+      <c r="AN10" s="549" t="n"/>
+      <c r="AO10" s="549" t="n"/>
+      <c r="AP10" s="549" t="n"/>
+      <c r="AQ10" s="549" t="n"/>
+      <c r="AR10" s="549" t="n"/>
+      <c r="AS10" s="549" t="n"/>
+      <c r="AT10" s="549" t="n"/>
+      <c r="AU10" s="549" t="n"/>
+      <c r="AV10" s="549" t="n"/>
+      <c r="AW10" s="549" t="n"/>
+      <c r="AX10" s="549" t="n"/>
+      <c r="AY10" s="549" t="n"/>
+      <c r="AZ10" s="549" t="n"/>
+      <c r="BA10" s="549" t="n"/>
+      <c r="BB10" s="549" t="n"/>
+      <c r="BC10" s="549" t="n"/>
+      <c r="BD10" s="552" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="473" t="inlineStr">
+      <c r="A11" s="547" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="340" t="n"/>
-      <c r="C11" s="340" t="n"/>
-      <c r="D11" s="340" t="n"/>
-      <c r="E11" s="340" t="n"/>
-      <c r="F11" s="340" t="n"/>
-      <c r="G11" s="340" t="n"/>
-      <c r="H11" s="340" t="n"/>
-      <c r="I11" s="340" t="n"/>
-      <c r="J11" s="340" t="n"/>
-      <c r="K11" s="484" t="n"/>
-      <c r="L11" s="371" t="n"/>
-      <c r="M11" s="371" t="n"/>
-      <c r="N11" s="371" t="n"/>
-      <c r="O11" s="371" t="n"/>
-      <c r="P11" s="371" t="n"/>
-      <c r="Q11" s="371" t="n"/>
-      <c r="R11" s="371" t="n"/>
-      <c r="S11" s="371" t="n"/>
-      <c r="T11" s="371" t="n"/>
-      <c r="U11" s="371" t="n"/>
-      <c r="V11" s="371" t="n"/>
-      <c r="W11" s="371" t="n"/>
-      <c r="X11" s="371" t="n"/>
-      <c r="Y11" s="371" t="n"/>
-      <c r="Z11" s="371" t="n"/>
-      <c r="AA11" s="371" t="n"/>
-      <c r="AB11" s="371" t="n"/>
-      <c r="AC11" s="475" t="inlineStr">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="548" t="n"/>
+      <c r="L11" s="549" t="n"/>
+      <c r="M11" s="549" t="n"/>
+      <c r="N11" s="549" t="n"/>
+      <c r="O11" s="549" t="n"/>
+      <c r="P11" s="549" t="n"/>
+      <c r="Q11" s="549" t="n"/>
+      <c r="R11" s="549" t="n"/>
+      <c r="S11" s="549" t="n"/>
+      <c r="T11" s="549" t="n"/>
+      <c r="U11" s="549" t="n"/>
+      <c r="V11" s="549" t="n"/>
+      <c r="W11" s="549" t="n"/>
+      <c r="X11" s="549" t="n"/>
+      <c r="Y11" s="549" t="n"/>
+      <c r="Z11" s="549" t="n"/>
+      <c r="AA11" s="549" t="n"/>
+      <c r="AB11" s="550" t="n"/>
+      <c r="AC11" s="551" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="AD11" s="340" t="n"/>
-      <c r="AE11" s="340" t="n"/>
-      <c r="AF11" s="340" t="n"/>
-      <c r="AG11" s="340" t="n"/>
-      <c r="AH11" s="340" t="n"/>
-      <c r="AI11" s="340" t="n"/>
-      <c r="AJ11" s="340" t="n"/>
-      <c r="AK11" s="340" t="n"/>
-      <c r="AL11" s="340" t="n"/>
-      <c r="AM11" s="484" t="n"/>
-      <c r="AN11" s="371" t="n"/>
-      <c r="AO11" s="371" t="n"/>
-      <c r="AP11" s="371" t="n"/>
-      <c r="AQ11" s="371" t="n"/>
-      <c r="AR11" s="371" t="n"/>
-      <c r="AS11" s="371" t="n"/>
-      <c r="AT11" s="371" t="n"/>
-      <c r="AU11" s="371" t="n"/>
-      <c r="AV11" s="371" t="n"/>
-      <c r="AW11" s="371" t="n"/>
-      <c r="AX11" s="371" t="n"/>
-      <c r="AY11" s="371" t="n"/>
-      <c r="AZ11" s="371" t="n"/>
-      <c r="BA11" s="371" t="n"/>
-      <c r="BB11" s="371" t="n"/>
-      <c r="BC11" s="371" t="n"/>
-      <c r="BD11" s="485" t="n"/>
+      <c r="AD11" s="12" t="n"/>
+      <c r="AE11" s="12" t="n"/>
+      <c r="AF11" s="12" t="n"/>
+      <c r="AG11" s="12" t="n"/>
+      <c r="AH11" s="12" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="12" t="n"/>
+      <c r="AK11" s="12" t="n"/>
+      <c r="AL11" s="13" t="n"/>
+      <c r="AM11" s="548" t="n"/>
+      <c r="AN11" s="549" t="n"/>
+      <c r="AO11" s="549" t="n"/>
+      <c r="AP11" s="549" t="n"/>
+      <c r="AQ11" s="549" t="n"/>
+      <c r="AR11" s="549" t="n"/>
+      <c r="AS11" s="549" t="n"/>
+      <c r="AT11" s="549" t="n"/>
+      <c r="AU11" s="549" t="n"/>
+      <c r="AV11" s="549" t="n"/>
+      <c r="AW11" s="549" t="n"/>
+      <c r="AX11" s="549" t="n"/>
+      <c r="AY11" s="549" t="n"/>
+      <c r="AZ11" s="549" t="n"/>
+      <c r="BA11" s="549" t="n"/>
+      <c r="BB11" s="549" t="n"/>
+      <c r="BC11" s="549" t="n"/>
+      <c r="BD11" s="552" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="486" t="inlineStr">
+      <c r="A12" s="553" t="inlineStr">
         <is>
           <t>Method / Acceptance Ref</t>
         </is>
       </c>
-      <c r="B12" s="487" t="n"/>
-      <c r="C12" s="487" t="n"/>
-      <c r="D12" s="487" t="n"/>
-      <c r="E12" s="487" t="n"/>
-      <c r="F12" s="487" t="n"/>
-      <c r="G12" s="487" t="n"/>
-      <c r="H12" s="487" t="n"/>
-      <c r="I12" s="487" t="n"/>
-      <c r="J12" s="487" t="n"/>
-      <c r="K12" s="488" t="n"/>
-      <c r="L12" s="489" t="n"/>
-      <c r="M12" s="489" t="n"/>
-      <c r="N12" s="489" t="n"/>
-      <c r="O12" s="489" t="n"/>
-      <c r="P12" s="489" t="n"/>
-      <c r="Q12" s="489" t="n"/>
-      <c r="R12" s="489" t="n"/>
-      <c r="S12" s="489" t="n"/>
-      <c r="T12" s="489" t="n"/>
-      <c r="U12" s="489" t="n"/>
-      <c r="V12" s="489" t="n"/>
-      <c r="W12" s="489" t="n"/>
-      <c r="X12" s="489" t="n"/>
-      <c r="Y12" s="489" t="n"/>
-      <c r="Z12" s="489" t="n"/>
-      <c r="AA12" s="489" t="n"/>
-      <c r="AB12" s="489" t="n"/>
-      <c r="AC12" s="490" t="inlineStr">
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="554" t="n"/>
+      <c r="L12" s="555" t="n"/>
+      <c r="M12" s="555" t="n"/>
+      <c r="N12" s="555" t="n"/>
+      <c r="O12" s="555" t="n"/>
+      <c r="P12" s="555" t="n"/>
+      <c r="Q12" s="555" t="n"/>
+      <c r="R12" s="555" t="n"/>
+      <c r="S12" s="555" t="n"/>
+      <c r="T12" s="555" t="n"/>
+      <c r="U12" s="555" t="n"/>
+      <c r="V12" s="555" t="n"/>
+      <c r="W12" s="555" t="n"/>
+      <c r="X12" s="555" t="n"/>
+      <c r="Y12" s="555" t="n"/>
+      <c r="Z12" s="555" t="n"/>
+      <c r="AA12" s="555" t="n"/>
+      <c r="AB12" s="556" t="n"/>
+      <c r="AC12" s="557" t="inlineStr">
         <is>
           <t>Affected Job Ref</t>
         </is>
       </c>
-      <c r="AD12" s="487" t="n"/>
-      <c r="AE12" s="487" t="n"/>
-      <c r="AF12" s="487" t="n"/>
-      <c r="AG12" s="487" t="n"/>
-      <c r="AH12" s="487" t="n"/>
-      <c r="AI12" s="487" t="n"/>
-      <c r="AJ12" s="487" t="n"/>
-      <c r="AK12" s="487" t="n"/>
-      <c r="AL12" s="487" t="n"/>
-      <c r="AM12" s="488" t="n"/>
-      <c r="AN12" s="489" t="n"/>
-      <c r="AO12" s="489" t="n"/>
-      <c r="AP12" s="489" t="n"/>
-      <c r="AQ12" s="489" t="n"/>
-      <c r="AR12" s="489" t="n"/>
-      <c r="AS12" s="489" t="n"/>
-      <c r="AT12" s="489" t="n"/>
-      <c r="AU12" s="489" t="n"/>
-      <c r="AV12" s="489" t="n"/>
-      <c r="AW12" s="489" t="n"/>
-      <c r="AX12" s="489" t="n"/>
-      <c r="AY12" s="489" t="n"/>
-      <c r="AZ12" s="489" t="n"/>
-      <c r="BA12" s="489" t="n"/>
-      <c r="BB12" s="489" t="n"/>
-      <c r="BC12" s="489" t="n"/>
-      <c r="BD12" s="491" t="n"/>
+      <c r="AD12" s="19" t="n"/>
+      <c r="AE12" s="19" t="n"/>
+      <c r="AF12" s="19" t="n"/>
+      <c r="AG12" s="19" t="n"/>
+      <c r="AH12" s="19" t="n"/>
+      <c r="AI12" s="19" t="n"/>
+      <c r="AJ12" s="19" t="n"/>
+      <c r="AK12" s="19" t="n"/>
+      <c r="AL12" s="22" t="n"/>
+      <c r="AM12" s="554" t="n"/>
+      <c r="AN12" s="555" t="n"/>
+      <c r="AO12" s="555" t="n"/>
+      <c r="AP12" s="555" t="n"/>
+      <c r="AQ12" s="555" t="n"/>
+      <c r="AR12" s="555" t="n"/>
+      <c r="AS12" s="555" t="n"/>
+      <c r="AT12" s="555" t="n"/>
+      <c r="AU12" s="555" t="n"/>
+      <c r="AV12" s="555" t="n"/>
+      <c r="AW12" s="555" t="n"/>
+      <c r="AX12" s="555" t="n"/>
+      <c r="AY12" s="555" t="n"/>
+      <c r="AZ12" s="555" t="n"/>
+      <c r="BA12" s="555" t="n"/>
+      <c r="BB12" s="555" t="n"/>
+      <c r="BC12" s="555" t="n"/>
+      <c r="BD12" s="558" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
-      <c r="A13" s="345" t="n"/>
-      <c r="B13" s="345" t="n"/>
-      <c r="C13" s="345" t="n"/>
-      <c r="D13" s="345" t="n"/>
-      <c r="E13" s="345" t="n"/>
-      <c r="F13" s="345" t="n"/>
-      <c r="G13" s="345" t="n"/>
-      <c r="H13" s="345" t="n"/>
-      <c r="I13" s="345" t="n"/>
-      <c r="J13" s="345" t="n"/>
-      <c r="K13" s="345" t="n"/>
-      <c r="L13" s="345" t="n"/>
-      <c r="M13" s="345" t="n"/>
-      <c r="N13" s="345" t="n"/>
-      <c r="O13" s="345" t="n"/>
-      <c r="P13" s="345" t="n"/>
-      <c r="Q13" s="345" t="n"/>
-      <c r="R13" s="345" t="n"/>
-      <c r="S13" s="345" t="n"/>
-      <c r="T13" s="345" t="n"/>
-      <c r="U13" s="345" t="n"/>
-      <c r="V13" s="345" t="n"/>
-      <c r="W13" s="345" t="n"/>
-      <c r="X13" s="345" t="n"/>
-      <c r="Y13" s="345" t="n"/>
-      <c r="Z13" s="345" t="n"/>
-      <c r="AA13" s="345" t="n"/>
-      <c r="AB13" s="345" t="n"/>
-      <c r="AC13" s="345" t="n"/>
-      <c r="AD13" s="345" t="n"/>
-      <c r="AE13" s="345" t="n"/>
-      <c r="AF13" s="345" t="n"/>
-      <c r="AG13" s="345" t="n"/>
-      <c r="AH13" s="345" t="n"/>
-      <c r="AI13" s="345" t="n"/>
-      <c r="AJ13" s="345" t="n"/>
-      <c r="AK13" s="345" t="n"/>
-      <c r="AL13" s="345" t="n"/>
-      <c r="AM13" s="345" t="n"/>
-      <c r="AN13" s="345" t="n"/>
-      <c r="AO13" s="345" t="n"/>
-      <c r="AP13" s="345" t="n"/>
-      <c r="AQ13" s="345" t="n"/>
-      <c r="AR13" s="345" t="n"/>
-      <c r="AS13" s="345" t="n"/>
-      <c r="AT13" s="345" t="n"/>
-      <c r="AU13" s="345" t="n"/>
-      <c r="AV13" s="345" t="n"/>
-      <c r="AW13" s="345" t="n"/>
-      <c r="AX13" s="345" t="n"/>
-      <c r="AY13" s="345" t="n"/>
-      <c r="AZ13" s="345" t="n"/>
-      <c r="BA13" s="345" t="n"/>
-      <c r="BB13" s="345" t="n"/>
-      <c r="BC13" s="345" t="n"/>
-      <c r="BD13" s="345" t="n"/>
+      <c r="A13" s="559" t="n"/>
+      <c r="B13" s="559" t="n"/>
+      <c r="C13" s="559" t="n"/>
+      <c r="D13" s="559" t="n"/>
+      <c r="E13" s="559" t="n"/>
+      <c r="F13" s="559" t="n"/>
+      <c r="G13" s="559" t="n"/>
+      <c r="H13" s="559" t="n"/>
+      <c r="I13" s="559" t="n"/>
+      <c r="J13" s="559" t="n"/>
+      <c r="K13" s="559" t="n"/>
+      <c r="L13" s="559" t="n"/>
+      <c r="M13" s="559" t="n"/>
+      <c r="N13" s="559" t="n"/>
+      <c r="O13" s="559" t="n"/>
+      <c r="P13" s="559" t="n"/>
+      <c r="Q13" s="559" t="n"/>
+      <c r="R13" s="559" t="n"/>
+      <c r="S13" s="559" t="n"/>
+      <c r="T13" s="559" t="n"/>
+      <c r="U13" s="559" t="n"/>
+      <c r="V13" s="559" t="n"/>
+      <c r="W13" s="559" t="n"/>
+      <c r="X13" s="559" t="n"/>
+      <c r="Y13" s="559" t="n"/>
+      <c r="Z13" s="559" t="n"/>
+      <c r="AA13" s="559" t="n"/>
+      <c r="AB13" s="559" t="n"/>
+      <c r="AC13" s="559" t="n"/>
+      <c r="AD13" s="559" t="n"/>
+      <c r="AE13" s="559" t="n"/>
+      <c r="AF13" s="559" t="n"/>
+      <c r="AG13" s="559" t="n"/>
+      <c r="AH13" s="559" t="n"/>
+      <c r="AI13" s="559" t="n"/>
+      <c r="AJ13" s="559" t="n"/>
+      <c r="AK13" s="559" t="n"/>
+      <c r="AL13" s="559" t="n"/>
+      <c r="AM13" s="559" t="n"/>
+      <c r="AN13" s="559" t="n"/>
+      <c r="AO13" s="559" t="n"/>
+      <c r="AP13" s="559" t="n"/>
+      <c r="AQ13" s="559" t="n"/>
+      <c r="AR13" s="559" t="n"/>
+      <c r="AS13" s="559" t="n"/>
+      <c r="AT13" s="559" t="n"/>
+      <c r="AU13" s="559" t="n"/>
+      <c r="AV13" s="559" t="n"/>
+      <c r="AW13" s="559" t="n"/>
+      <c r="AX13" s="559" t="n"/>
+      <c r="AY13" s="559" t="n"/>
+      <c r="AZ13" s="559" t="n"/>
+      <c r="BA13" s="559" t="n"/>
+      <c r="BB13" s="559" t="n"/>
+      <c r="BC13" s="559" t="n"/>
+      <c r="BD13" s="559" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="466" t="inlineStr">
+      <c r="A14" s="540" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. REVIEW SNAPSHOT / LIVE ENTRY ON GAGE_DATA_LOG</t>
         </is>
       </c>
-      <c r="B14" s="467" t="n"/>
-      <c r="C14" s="467" t="n"/>
-      <c r="D14" s="467" t="n"/>
-      <c r="E14" s="467" t="n"/>
-      <c r="F14" s="467" t="n"/>
-      <c r="G14" s="467" t="n"/>
-      <c r="H14" s="467" t="n"/>
-      <c r="I14" s="467" t="n"/>
-      <c r="J14" s="467" t="n"/>
-      <c r="K14" s="467" t="n"/>
-      <c r="L14" s="467" t="n"/>
-      <c r="M14" s="467" t="n"/>
-      <c r="N14" s="467" t="n"/>
-      <c r="O14" s="467" t="n"/>
-      <c r="P14" s="467" t="n"/>
-      <c r="Q14" s="467" t="n"/>
-      <c r="R14" s="467" t="n"/>
-      <c r="S14" s="467" t="n"/>
-      <c r="T14" s="467" t="n"/>
-      <c r="U14" s="467" t="n"/>
-      <c r="V14" s="467" t="n"/>
-      <c r="W14" s="467" t="n"/>
-      <c r="X14" s="467" t="n"/>
-      <c r="Y14" s="467" t="n"/>
-      <c r="Z14" s="467" t="n"/>
-      <c r="AA14" s="467" t="n"/>
-      <c r="AB14" s="467" t="n"/>
-      <c r="AC14" s="467" t="n"/>
-      <c r="AD14" s="467" t="n"/>
-      <c r="AE14" s="467" t="n"/>
-      <c r="AF14" s="467" t="n"/>
-      <c r="AG14" s="467" t="n"/>
-      <c r="AH14" s="467" t="n"/>
-      <c r="AI14" s="467" t="n"/>
-      <c r="AJ14" s="467" t="n"/>
-      <c r="AK14" s="467" t="n"/>
-      <c r="AL14" s="467" t="n"/>
-      <c r="AM14" s="467" t="n"/>
-      <c r="AN14" s="467" t="n"/>
-      <c r="AO14" s="467" t="n"/>
-      <c r="AP14" s="467" t="n"/>
-      <c r="AQ14" s="467" t="n"/>
-      <c r="AR14" s="467" t="n"/>
-      <c r="AS14" s="467" t="n"/>
-      <c r="AT14" s="467" t="n"/>
-      <c r="AU14" s="467" t="n"/>
-      <c r="AV14" s="467" t="n"/>
-      <c r="AW14" s="467" t="n"/>
-      <c r="AX14" s="467" t="n"/>
-      <c r="AY14" s="467" t="n"/>
-      <c r="AZ14" s="467" t="n"/>
-      <c r="BA14" s="467" t="n"/>
-      <c r="BB14" s="467" t="n"/>
-      <c r="BC14" s="467" t="n"/>
-      <c r="BD14" s="468" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="27" t="n"/>
+      <c r="J14" s="27" t="n"/>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="27" t="n"/>
+      <c r="M14" s="27" t="n"/>
+      <c r="N14" s="27" t="n"/>
+      <c r="O14" s="27" t="n"/>
+      <c r="P14" s="27" t="n"/>
+      <c r="Q14" s="27" t="n"/>
+      <c r="R14" s="27" t="n"/>
+      <c r="S14" s="27" t="n"/>
+      <c r="T14" s="27" t="n"/>
+      <c r="U14" s="27" t="n"/>
+      <c r="V14" s="27" t="n"/>
+      <c r="W14" s="27" t="n"/>
+      <c r="X14" s="27" t="n"/>
+      <c r="Y14" s="27" t="n"/>
+      <c r="Z14" s="27" t="n"/>
+      <c r="AA14" s="27" t="n"/>
+      <c r="AB14" s="27" t="n"/>
+      <c r="AC14" s="27" t="n"/>
+      <c r="AD14" s="27" t="n"/>
+      <c r="AE14" s="27" t="n"/>
+      <c r="AF14" s="27" t="n"/>
+      <c r="AG14" s="27" t="n"/>
+      <c r="AH14" s="27" t="n"/>
+      <c r="AI14" s="27" t="n"/>
+      <c r="AJ14" s="27" t="n"/>
+      <c r="AK14" s="27" t="n"/>
+      <c r="AL14" s="27" t="n"/>
+      <c r="AM14" s="27" t="n"/>
+      <c r="AN14" s="27" t="n"/>
+      <c r="AO14" s="27" t="n"/>
+      <c r="AP14" s="27" t="n"/>
+      <c r="AQ14" s="27" t="n"/>
+      <c r="AR14" s="27" t="n"/>
+      <c r="AS14" s="27" t="n"/>
+      <c r="AT14" s="27" t="n"/>
+      <c r="AU14" s="27" t="n"/>
+      <c r="AV14" s="27" t="n"/>
+      <c r="AW14" s="27" t="n"/>
+      <c r="AX14" s="27" t="n"/>
+      <c r="AY14" s="27" t="n"/>
+      <c r="AZ14" s="27" t="n"/>
+      <c r="BA14" s="27" t="n"/>
+      <c r="BB14" s="27" t="n"/>
+      <c r="BC14" s="27" t="n"/>
+      <c r="BD14" s="28" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="450" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="451" t="n"/>
-      <c r="C15" s="451" t="n"/>
-      <c r="D15" s="492" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E15" s="451" t="n"/>
-      <c r="F15" s="451" t="n"/>
-      <c r="G15" s="451" t="n"/>
-      <c r="H15" s="451" t="n"/>
-      <c r="I15" s="492" t="inlineStr">
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="37" t="inlineStr">
         <is>
           <t>Gage ID</t>
         </is>
       </c>
-      <c r="J15" s="451" t="n"/>
-      <c r="K15" s="451" t="n"/>
-      <c r="L15" s="451" t="n"/>
-      <c r="M15" s="451" t="n"/>
-      <c r="N15" s="492" t="inlineStr">
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="37" t="inlineStr">
         <is>
           <t>Verification Type</t>
         </is>
       </c>
-      <c r="O15" s="451" t="n"/>
-      <c r="P15" s="451" t="n"/>
-      <c r="Q15" s="451" t="n"/>
-      <c r="R15" s="451" t="n"/>
-      <c r="S15" s="451" t="n"/>
-      <c r="T15" s="451" t="n"/>
-      <c r="U15" s="492" t="inlineStr">
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="6" t="n"/>
+      <c r="U15" s="37" t="inlineStr">
         <is>
           <t>Check Artifact / Master</t>
         </is>
       </c>
-      <c r="V15" s="451" t="n"/>
-      <c r="W15" s="451" t="n"/>
-      <c r="X15" s="451" t="n"/>
-      <c r="Y15" s="451" t="n"/>
-      <c r="Z15" s="451" t="n"/>
-      <c r="AA15" s="492" t="inlineStr">
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+      <c r="Y15" s="5" t="n"/>
+      <c r="Z15" s="6" t="n"/>
+      <c r="AA15" s="37" t="inlineStr">
         <is>
           <t>Criteria</t>
         </is>
       </c>
-      <c r="AB15" s="451" t="n"/>
-      <c r="AC15" s="451" t="n"/>
-      <c r="AD15" s="451" t="n"/>
-      <c r="AE15" s="451" t="n"/>
-      <c r="AF15" s="451" t="n"/>
-      <c r="AG15" s="451" t="n"/>
-      <c r="AH15" s="492" t="inlineStr">
+      <c r="AB15" s="5" t="n"/>
+      <c r="AC15" s="5" t="n"/>
+      <c r="AD15" s="5" t="n"/>
+      <c r="AE15" s="5" t="n"/>
+      <c r="AF15" s="5" t="n"/>
+      <c r="AG15" s="6" t="n"/>
+      <c r="AH15" s="37" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AI15" s="451" t="n"/>
-      <c r="AJ15" s="451" t="n"/>
-      <c r="AK15" s="451" t="n"/>
-      <c r="AL15" s="492" t="inlineStr">
+      <c r="AI15" s="5" t="n"/>
+      <c r="AJ15" s="5" t="n"/>
+      <c r="AK15" s="6" t="n"/>
+      <c r="AL15" s="37" t="inlineStr">
         <is>
           <t>CAL Status</t>
         </is>
       </c>
-      <c r="AM15" s="451" t="n"/>
-      <c r="AN15" s="451" t="n"/>
-      <c r="AO15" s="451" t="n"/>
-      <c r="AP15" s="492" t="inlineStr">
+      <c r="AM15" s="5" t="n"/>
+      <c r="AN15" s="5" t="n"/>
+      <c r="AO15" s="6" t="n"/>
+      <c r="AP15" s="37" t="inlineStr">
         <is>
           <t>Use Stop (Y/N)</t>
         </is>
       </c>
-      <c r="AQ15" s="451" t="n"/>
-      <c r="AR15" s="451" t="n"/>
-      <c r="AS15" s="451" t="n"/>
-      <c r="AT15" s="492" t="inlineStr">
+      <c r="AQ15" s="5" t="n"/>
+      <c r="AR15" s="5" t="n"/>
+      <c r="AS15" s="6" t="n"/>
+      <c r="AT15" s="37" t="inlineStr">
         <is>
           <t>Owner Dept</t>
         </is>
       </c>
-      <c r="AU15" s="451" t="n"/>
-      <c r="AV15" s="451" t="n"/>
-      <c r="AW15" s="451" t="n"/>
-      <c r="AX15" s="492" t="inlineStr">
+      <c r="AU15" s="5" t="n"/>
+      <c r="AV15" s="5" t="n"/>
+      <c r="AW15" s="6" t="n"/>
+      <c r="AX15" s="37" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AY15" s="451" t="n"/>
-      <c r="AZ15" s="451" t="n"/>
-      <c r="BA15" s="451" t="n"/>
-      <c r="BB15" s="451" t="n"/>
-      <c r="BC15" s="451" t="n"/>
-      <c r="BD15" s="452" t="n"/>
+      <c r="AY15" s="5" t="n"/>
+      <c r="AZ15" s="5" t="n"/>
+      <c r="BA15" s="5" t="n"/>
+      <c r="BB15" s="5" t="n"/>
+      <c r="BC15" s="5" t="n"/>
+      <c r="BD15" s="8" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="493" t="n"/>
-      <c r="B16" s="456" t="n"/>
-      <c r="C16" s="456" t="n"/>
-      <c r="D16" s="494" t="n"/>
-      <c r="E16" s="482" t="n"/>
-      <c r="F16" s="482" t="n"/>
-      <c r="G16" s="482" t="n"/>
-      <c r="H16" s="482" t="n"/>
-      <c r="I16" s="494" t="n"/>
-      <c r="J16" s="482" t="n"/>
-      <c r="K16" s="482" t="n"/>
-      <c r="L16" s="482" t="n"/>
-      <c r="M16" s="482" t="n"/>
-      <c r="N16" s="494" t="n"/>
-      <c r="O16" s="482" t="n"/>
-      <c r="P16" s="482" t="n"/>
-      <c r="Q16" s="482" t="n"/>
-      <c r="R16" s="482" t="n"/>
-      <c r="S16" s="482" t="n"/>
-      <c r="T16" s="482" t="n"/>
-      <c r="U16" s="494" t="n"/>
-      <c r="V16" s="482" t="n"/>
-      <c r="W16" s="482" t="n"/>
-      <c r="X16" s="482" t="n"/>
-      <c r="Y16" s="482" t="n"/>
-      <c r="Z16" s="482" t="n"/>
-      <c r="AA16" s="494" t="n"/>
-      <c r="AB16" s="482" t="n"/>
-      <c r="AC16" s="482" t="n"/>
-      <c r="AD16" s="482" t="n"/>
-      <c r="AE16" s="482" t="n"/>
-      <c r="AF16" s="482" t="n"/>
-      <c r="AG16" s="482" t="n"/>
-      <c r="AH16" s="494" t="n"/>
-      <c r="AI16" s="482" t="n"/>
-      <c r="AJ16" s="482" t="n"/>
-      <c r="AK16" s="482" t="n"/>
-      <c r="AL16" s="494" t="n"/>
-      <c r="AM16" s="482" t="n"/>
-      <c r="AN16" s="482" t="n"/>
-      <c r="AO16" s="482" t="n"/>
-      <c r="AP16" s="494" t="n"/>
-      <c r="AQ16" s="482" t="n"/>
-      <c r="AR16" s="482" t="n"/>
-      <c r="AS16" s="482" t="n"/>
-      <c r="AT16" s="494" t="n"/>
-      <c r="AU16" s="482" t="n"/>
-      <c r="AV16" s="482" t="n"/>
-      <c r="AW16" s="482" t="n"/>
-      <c r="AX16" s="494" t="n"/>
-      <c r="AY16" s="482" t="n"/>
-      <c r="AZ16" s="482" t="n"/>
-      <c r="BA16" s="482" t="n"/>
-      <c r="BB16" s="482" t="n"/>
-      <c r="BC16" s="482" t="n"/>
-      <c r="BD16" s="483" t="n"/>
+      <c r="A16" s="560" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="561" t="n"/>
+      <c r="E16" s="543" t="n"/>
+      <c r="F16" s="543" t="n"/>
+      <c r="G16" s="543" t="n"/>
+      <c r="H16" s="544" t="n"/>
+      <c r="I16" s="561" t="n"/>
+      <c r="J16" s="543" t="n"/>
+      <c r="K16" s="543" t="n"/>
+      <c r="L16" s="543" t="n"/>
+      <c r="M16" s="544" t="n"/>
+      <c r="N16" s="561" t="n"/>
+      <c r="O16" s="543" t="n"/>
+      <c r="P16" s="543" t="n"/>
+      <c r="Q16" s="543" t="n"/>
+      <c r="R16" s="543" t="n"/>
+      <c r="S16" s="543" t="n"/>
+      <c r="T16" s="544" t="n"/>
+      <c r="U16" s="561" t="n"/>
+      <c r="V16" s="543" t="n"/>
+      <c r="W16" s="543" t="n"/>
+      <c r="X16" s="543" t="n"/>
+      <c r="Y16" s="543" t="n"/>
+      <c r="Z16" s="544" t="n"/>
+      <c r="AA16" s="561" t="n"/>
+      <c r="AB16" s="543" t="n"/>
+      <c r="AC16" s="543" t="n"/>
+      <c r="AD16" s="543" t="n"/>
+      <c r="AE16" s="543" t="n"/>
+      <c r="AF16" s="543" t="n"/>
+      <c r="AG16" s="544" t="n"/>
+      <c r="AH16" s="561" t="n"/>
+      <c r="AI16" s="543" t="n"/>
+      <c r="AJ16" s="543" t="n"/>
+      <c r="AK16" s="544" t="n"/>
+      <c r="AL16" s="561" t="n"/>
+      <c r="AM16" s="543" t="n"/>
+      <c r="AN16" s="543" t="n"/>
+      <c r="AO16" s="544" t="n"/>
+      <c r="AP16" s="561" t="n"/>
+      <c r="AQ16" s="543" t="n"/>
+      <c r="AR16" s="543" t="n"/>
+      <c r="AS16" s="544" t="n"/>
+      <c r="AT16" s="561" t="n"/>
+      <c r="AU16" s="543" t="n"/>
+      <c r="AV16" s="543" t="n"/>
+      <c r="AW16" s="544" t="n"/>
+      <c r="AX16" s="561" t="n"/>
+      <c r="AY16" s="543" t="n"/>
+      <c r="AZ16" s="543" t="n"/>
+      <c r="BA16" s="543" t="n"/>
+      <c r="BB16" s="543" t="n"/>
+      <c r="BC16" s="543" t="n"/>
+      <c r="BD16" s="546" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="495" t="n"/>
-      <c r="B17" s="340" t="n"/>
-      <c r="C17" s="340" t="n"/>
-      <c r="D17" s="496" t="n"/>
-      <c r="E17" s="371" t="n"/>
-      <c r="F17" s="371" t="n"/>
-      <c r="G17" s="371" t="n"/>
-      <c r="H17" s="371" t="n"/>
-      <c r="I17" s="496" t="n"/>
-      <c r="J17" s="371" t="n"/>
-      <c r="K17" s="371" t="n"/>
-      <c r="L17" s="371" t="n"/>
-      <c r="M17" s="371" t="n"/>
-      <c r="N17" s="496" t="n"/>
-      <c r="O17" s="371" t="n"/>
-      <c r="P17" s="371" t="n"/>
-      <c r="Q17" s="371" t="n"/>
-      <c r="R17" s="371" t="n"/>
-      <c r="S17" s="371" t="n"/>
-      <c r="T17" s="371" t="n"/>
-      <c r="U17" s="496" t="n"/>
-      <c r="V17" s="371" t="n"/>
-      <c r="W17" s="371" t="n"/>
-      <c r="X17" s="371" t="n"/>
-      <c r="Y17" s="371" t="n"/>
-      <c r="Z17" s="371" t="n"/>
-      <c r="AA17" s="496" t="n"/>
-      <c r="AB17" s="371" t="n"/>
-      <c r="AC17" s="371" t="n"/>
-      <c r="AD17" s="371" t="n"/>
-      <c r="AE17" s="371" t="n"/>
-      <c r="AF17" s="371" t="n"/>
-      <c r="AG17" s="371" t="n"/>
-      <c r="AH17" s="496" t="n"/>
-      <c r="AI17" s="371" t="n"/>
-      <c r="AJ17" s="371" t="n"/>
-      <c r="AK17" s="371" t="n"/>
-      <c r="AL17" s="496" t="n"/>
-      <c r="AM17" s="371" t="n"/>
-      <c r="AN17" s="371" t="n"/>
-      <c r="AO17" s="371" t="n"/>
-      <c r="AP17" s="496" t="n"/>
-      <c r="AQ17" s="371" t="n"/>
-      <c r="AR17" s="371" t="n"/>
-      <c r="AS17" s="371" t="n"/>
-      <c r="AT17" s="496" t="n"/>
-      <c r="AU17" s="371" t="n"/>
-      <c r="AV17" s="371" t="n"/>
-      <c r="AW17" s="371" t="n"/>
-      <c r="AX17" s="496" t="n"/>
-      <c r="AY17" s="371" t="n"/>
-      <c r="AZ17" s="371" t="n"/>
-      <c r="BA17" s="371" t="n"/>
-      <c r="BB17" s="371" t="n"/>
-      <c r="BC17" s="371" t="n"/>
-      <c r="BD17" s="485" t="n"/>
+      <c r="A17" s="562" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="563" t="n"/>
+      <c r="E17" s="549" t="n"/>
+      <c r="F17" s="549" t="n"/>
+      <c r="G17" s="549" t="n"/>
+      <c r="H17" s="550" t="n"/>
+      <c r="I17" s="563" t="n"/>
+      <c r="J17" s="549" t="n"/>
+      <c r="K17" s="549" t="n"/>
+      <c r="L17" s="549" t="n"/>
+      <c r="M17" s="550" t="n"/>
+      <c r="N17" s="563" t="n"/>
+      <c r="O17" s="549" t="n"/>
+      <c r="P17" s="549" t="n"/>
+      <c r="Q17" s="549" t="n"/>
+      <c r="R17" s="549" t="n"/>
+      <c r="S17" s="549" t="n"/>
+      <c r="T17" s="550" t="n"/>
+      <c r="U17" s="563" t="n"/>
+      <c r="V17" s="549" t="n"/>
+      <c r="W17" s="549" t="n"/>
+      <c r="X17" s="549" t="n"/>
+      <c r="Y17" s="549" t="n"/>
+      <c r="Z17" s="550" t="n"/>
+      <c r="AA17" s="563" t="n"/>
+      <c r="AB17" s="549" t="n"/>
+      <c r="AC17" s="549" t="n"/>
+      <c r="AD17" s="549" t="n"/>
+      <c r="AE17" s="549" t="n"/>
+      <c r="AF17" s="549" t="n"/>
+      <c r="AG17" s="550" t="n"/>
+      <c r="AH17" s="563" t="n"/>
+      <c r="AI17" s="549" t="n"/>
+      <c r="AJ17" s="549" t="n"/>
+      <c r="AK17" s="550" t="n"/>
+      <c r="AL17" s="563" t="n"/>
+      <c r="AM17" s="549" t="n"/>
+      <c r="AN17" s="549" t="n"/>
+      <c r="AO17" s="550" t="n"/>
+      <c r="AP17" s="563" t="n"/>
+      <c r="AQ17" s="549" t="n"/>
+      <c r="AR17" s="549" t="n"/>
+      <c r="AS17" s="550" t="n"/>
+      <c r="AT17" s="563" t="n"/>
+      <c r="AU17" s="549" t="n"/>
+      <c r="AV17" s="549" t="n"/>
+      <c r="AW17" s="550" t="n"/>
+      <c r="AX17" s="563" t="n"/>
+      <c r="AY17" s="549" t="n"/>
+      <c r="AZ17" s="549" t="n"/>
+      <c r="BA17" s="549" t="n"/>
+      <c r="BB17" s="549" t="n"/>
+      <c r="BC17" s="549" t="n"/>
+      <c r="BD17" s="552" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="495" t="n"/>
-      <c r="B18" s="340" t="n"/>
-      <c r="C18" s="340" t="n"/>
-      <c r="D18" s="496" t="n"/>
-      <c r="E18" s="371" t="n"/>
-      <c r="F18" s="371" t="n"/>
-      <c r="G18" s="371" t="n"/>
-      <c r="H18" s="371" t="n"/>
-      <c r="I18" s="496" t="n"/>
-      <c r="J18" s="371" t="n"/>
-      <c r="K18" s="371" t="n"/>
-      <c r="L18" s="371" t="n"/>
-      <c r="M18" s="371" t="n"/>
-      <c r="N18" s="496" t="n"/>
-      <c r="O18" s="371" t="n"/>
-      <c r="P18" s="371" t="n"/>
-      <c r="Q18" s="371" t="n"/>
-      <c r="R18" s="371" t="n"/>
-      <c r="S18" s="371" t="n"/>
-      <c r="T18" s="371" t="n"/>
-      <c r="U18" s="496" t="n"/>
-      <c r="V18" s="371" t="n"/>
-      <c r="W18" s="371" t="n"/>
-      <c r="X18" s="371" t="n"/>
-      <c r="Y18" s="371" t="n"/>
-      <c r="Z18" s="371" t="n"/>
-      <c r="AA18" s="496" t="n"/>
-      <c r="AB18" s="371" t="n"/>
-      <c r="AC18" s="371" t="n"/>
-      <c r="AD18" s="371" t="n"/>
-      <c r="AE18" s="371" t="n"/>
-      <c r="AF18" s="371" t="n"/>
-      <c r="AG18" s="371" t="n"/>
-      <c r="AH18" s="496" t="n"/>
-      <c r="AI18" s="371" t="n"/>
-      <c r="AJ18" s="371" t="n"/>
-      <c r="AK18" s="371" t="n"/>
-      <c r="AL18" s="496" t="n"/>
-      <c r="AM18" s="371" t="n"/>
-      <c r="AN18" s="371" t="n"/>
-      <c r="AO18" s="371" t="n"/>
-      <c r="AP18" s="496" t="n"/>
-      <c r="AQ18" s="371" t="n"/>
-      <c r="AR18" s="371" t="n"/>
-      <c r="AS18" s="371" t="n"/>
-      <c r="AT18" s="496" t="n"/>
-      <c r="AU18" s="371" t="n"/>
-      <c r="AV18" s="371" t="n"/>
-      <c r="AW18" s="371" t="n"/>
-      <c r="AX18" s="496" t="n"/>
-      <c r="AY18" s="371" t="n"/>
-      <c r="AZ18" s="371" t="n"/>
-      <c r="BA18" s="371" t="n"/>
-      <c r="BB18" s="371" t="n"/>
-      <c r="BC18" s="371" t="n"/>
-      <c r="BD18" s="485" t="n"/>
+      <c r="A18" s="562" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="563" t="n"/>
+      <c r="E18" s="549" t="n"/>
+      <c r="F18" s="549" t="n"/>
+      <c r="G18" s="549" t="n"/>
+      <c r="H18" s="550" t="n"/>
+      <c r="I18" s="563" t="n"/>
+      <c r="J18" s="549" t="n"/>
+      <c r="K18" s="549" t="n"/>
+      <c r="L18" s="549" t="n"/>
+      <c r="M18" s="550" t="n"/>
+      <c r="N18" s="563" t="n"/>
+      <c r="O18" s="549" t="n"/>
+      <c r="P18" s="549" t="n"/>
+      <c r="Q18" s="549" t="n"/>
+      <c r="R18" s="549" t="n"/>
+      <c r="S18" s="549" t="n"/>
+      <c r="T18" s="550" t="n"/>
+      <c r="U18" s="563" t="n"/>
+      <c r="V18" s="549" t="n"/>
+      <c r="W18" s="549" t="n"/>
+      <c r="X18" s="549" t="n"/>
+      <c r="Y18" s="549" t="n"/>
+      <c r="Z18" s="550" t="n"/>
+      <c r="AA18" s="563" t="n"/>
+      <c r="AB18" s="549" t="n"/>
+      <c r="AC18" s="549" t="n"/>
+      <c r="AD18" s="549" t="n"/>
+      <c r="AE18" s="549" t="n"/>
+      <c r="AF18" s="549" t="n"/>
+      <c r="AG18" s="550" t="n"/>
+      <c r="AH18" s="563" t="n"/>
+      <c r="AI18" s="549" t="n"/>
+      <c r="AJ18" s="549" t="n"/>
+      <c r="AK18" s="550" t="n"/>
+      <c r="AL18" s="563" t="n"/>
+      <c r="AM18" s="549" t="n"/>
+      <c r="AN18" s="549" t="n"/>
+      <c r="AO18" s="550" t="n"/>
+      <c r="AP18" s="563" t="n"/>
+      <c r="AQ18" s="549" t="n"/>
+      <c r="AR18" s="549" t="n"/>
+      <c r="AS18" s="550" t="n"/>
+      <c r="AT18" s="563" t="n"/>
+      <c r="AU18" s="549" t="n"/>
+      <c r="AV18" s="549" t="n"/>
+      <c r="AW18" s="550" t="n"/>
+      <c r="AX18" s="563" t="n"/>
+      <c r="AY18" s="549" t="n"/>
+      <c r="AZ18" s="549" t="n"/>
+      <c r="BA18" s="549" t="n"/>
+      <c r="BB18" s="549" t="n"/>
+      <c r="BC18" s="549" t="n"/>
+      <c r="BD18" s="552" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="495" t="n"/>
-      <c r="B19" s="340" t="n"/>
-      <c r="C19" s="340" t="n"/>
-      <c r="D19" s="496" t="n"/>
-      <c r="E19" s="371" t="n"/>
-      <c r="F19" s="371" t="n"/>
-      <c r="G19" s="371" t="n"/>
-      <c r="H19" s="371" t="n"/>
-      <c r="I19" s="496" t="n"/>
-      <c r="J19" s="371" t="n"/>
-      <c r="K19" s="371" t="n"/>
-      <c r="L19" s="371" t="n"/>
-      <c r="M19" s="371" t="n"/>
-      <c r="N19" s="496" t="n"/>
-      <c r="O19" s="371" t="n"/>
-      <c r="P19" s="371" t="n"/>
-      <c r="Q19" s="371" t="n"/>
-      <c r="R19" s="371" t="n"/>
-      <c r="S19" s="371" t="n"/>
-      <c r="T19" s="371" t="n"/>
-      <c r="U19" s="496" t="n"/>
-      <c r="V19" s="371" t="n"/>
-      <c r="W19" s="371" t="n"/>
-      <c r="X19" s="371" t="n"/>
-      <c r="Y19" s="371" t="n"/>
-      <c r="Z19" s="371" t="n"/>
-      <c r="AA19" s="496" t="n"/>
-      <c r="AB19" s="371" t="n"/>
-      <c r="AC19" s="371" t="n"/>
-      <c r="AD19" s="371" t="n"/>
-      <c r="AE19" s="371" t="n"/>
-      <c r="AF19" s="371" t="n"/>
-      <c r="AG19" s="371" t="n"/>
-      <c r="AH19" s="496" t="n"/>
-      <c r="AI19" s="371" t="n"/>
-      <c r="AJ19" s="371" t="n"/>
-      <c r="AK19" s="371" t="n"/>
-      <c r="AL19" s="496" t="n"/>
-      <c r="AM19" s="371" t="n"/>
-      <c r="AN19" s="371" t="n"/>
-      <c r="AO19" s="371" t="n"/>
-      <c r="AP19" s="496" t="n"/>
-      <c r="AQ19" s="371" t="n"/>
-      <c r="AR19" s="371" t="n"/>
-      <c r="AS19" s="371" t="n"/>
-      <c r="AT19" s="496" t="n"/>
-      <c r="AU19" s="371" t="n"/>
-      <c r="AV19" s="371" t="n"/>
-      <c r="AW19" s="371" t="n"/>
-      <c r="AX19" s="496" t="n"/>
-      <c r="AY19" s="371" t="n"/>
-      <c r="AZ19" s="371" t="n"/>
-      <c r="BA19" s="371" t="n"/>
-      <c r="BB19" s="371" t="n"/>
-      <c r="BC19" s="371" t="n"/>
-      <c r="BD19" s="485" t="n"/>
+      <c r="A19" s="562" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="563" t="n"/>
+      <c r="E19" s="549" t="n"/>
+      <c r="F19" s="549" t="n"/>
+      <c r="G19" s="549" t="n"/>
+      <c r="H19" s="550" t="n"/>
+      <c r="I19" s="563" t="n"/>
+      <c r="J19" s="549" t="n"/>
+      <c r="K19" s="549" t="n"/>
+      <c r="L19" s="549" t="n"/>
+      <c r="M19" s="550" t="n"/>
+      <c r="N19" s="563" t="n"/>
+      <c r="O19" s="549" t="n"/>
+      <c r="P19" s="549" t="n"/>
+      <c r="Q19" s="549" t="n"/>
+      <c r="R19" s="549" t="n"/>
+      <c r="S19" s="549" t="n"/>
+      <c r="T19" s="550" t="n"/>
+      <c r="U19" s="563" t="n"/>
+      <c r="V19" s="549" t="n"/>
+      <c r="W19" s="549" t="n"/>
+      <c r="X19" s="549" t="n"/>
+      <c r="Y19" s="549" t="n"/>
+      <c r="Z19" s="550" t="n"/>
+      <c r="AA19" s="563" t="n"/>
+      <c r="AB19" s="549" t="n"/>
+      <c r="AC19" s="549" t="n"/>
+      <c r="AD19" s="549" t="n"/>
+      <c r="AE19" s="549" t="n"/>
+      <c r="AF19" s="549" t="n"/>
+      <c r="AG19" s="550" t="n"/>
+      <c r="AH19" s="563" t="n"/>
+      <c r="AI19" s="549" t="n"/>
+      <c r="AJ19" s="549" t="n"/>
+      <c r="AK19" s="550" t="n"/>
+      <c r="AL19" s="563" t="n"/>
+      <c r="AM19" s="549" t="n"/>
+      <c r="AN19" s="549" t="n"/>
+      <c r="AO19" s="550" t="n"/>
+      <c r="AP19" s="563" t="n"/>
+      <c r="AQ19" s="549" t="n"/>
+      <c r="AR19" s="549" t="n"/>
+      <c r="AS19" s="550" t="n"/>
+      <c r="AT19" s="563" t="n"/>
+      <c r="AU19" s="549" t="n"/>
+      <c r="AV19" s="549" t="n"/>
+      <c r="AW19" s="550" t="n"/>
+      <c r="AX19" s="563" t="n"/>
+      <c r="AY19" s="549" t="n"/>
+      <c r="AZ19" s="549" t="n"/>
+      <c r="BA19" s="549" t="n"/>
+      <c r="BB19" s="549" t="n"/>
+      <c r="BC19" s="549" t="n"/>
+      <c r="BD19" s="552" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="495" t="n"/>
-      <c r="B20" s="340" t="n"/>
-      <c r="C20" s="340" t="n"/>
-      <c r="D20" s="496" t="n"/>
-      <c r="E20" s="371" t="n"/>
-      <c r="F20" s="371" t="n"/>
-      <c r="G20" s="371" t="n"/>
-      <c r="H20" s="371" t="n"/>
-      <c r="I20" s="496" t="n"/>
-      <c r="J20" s="371" t="n"/>
-      <c r="K20" s="371" t="n"/>
-      <c r="L20" s="371" t="n"/>
-      <c r="M20" s="371" t="n"/>
-      <c r="N20" s="496" t="n"/>
-      <c r="O20" s="371" t="n"/>
-      <c r="P20" s="371" t="n"/>
-      <c r="Q20" s="371" t="n"/>
-      <c r="R20" s="371" t="n"/>
-      <c r="S20" s="371" t="n"/>
-      <c r="T20" s="371" t="n"/>
-      <c r="U20" s="496" t="n"/>
-      <c r="V20" s="371" t="n"/>
-      <c r="W20" s="371" t="n"/>
-      <c r="X20" s="371" t="n"/>
-      <c r="Y20" s="371" t="n"/>
-      <c r="Z20" s="371" t="n"/>
-      <c r="AA20" s="496" t="n"/>
-      <c r="AB20" s="371" t="n"/>
-      <c r="AC20" s="371" t="n"/>
-      <c r="AD20" s="371" t="n"/>
-      <c r="AE20" s="371" t="n"/>
-      <c r="AF20" s="371" t="n"/>
-      <c r="AG20" s="371" t="n"/>
-      <c r="AH20" s="496" t="n"/>
-      <c r="AI20" s="371" t="n"/>
-      <c r="AJ20" s="371" t="n"/>
-      <c r="AK20" s="371" t="n"/>
-      <c r="AL20" s="496" t="n"/>
-      <c r="AM20" s="371" t="n"/>
-      <c r="AN20" s="371" t="n"/>
-      <c r="AO20" s="371" t="n"/>
-      <c r="AP20" s="496" t="n"/>
-      <c r="AQ20" s="371" t="n"/>
-      <c r="AR20" s="371" t="n"/>
-      <c r="AS20" s="371" t="n"/>
-      <c r="AT20" s="496" t="n"/>
-      <c r="AU20" s="371" t="n"/>
-      <c r="AV20" s="371" t="n"/>
-      <c r="AW20" s="371" t="n"/>
-      <c r="AX20" s="496" t="n"/>
-      <c r="AY20" s="371" t="n"/>
-      <c r="AZ20" s="371" t="n"/>
-      <c r="BA20" s="371" t="n"/>
-      <c r="BB20" s="371" t="n"/>
-      <c r="BC20" s="371" t="n"/>
-      <c r="BD20" s="485" t="n"/>
+      <c r="A20" s="562" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="563" t="n"/>
+      <c r="E20" s="549" t="n"/>
+      <c r="F20" s="549" t="n"/>
+      <c r="G20" s="549" t="n"/>
+      <c r="H20" s="550" t="n"/>
+      <c r="I20" s="563" t="n"/>
+      <c r="J20" s="549" t="n"/>
+      <c r="K20" s="549" t="n"/>
+      <c r="L20" s="549" t="n"/>
+      <c r="M20" s="550" t="n"/>
+      <c r="N20" s="563" t="n"/>
+      <c r="O20" s="549" t="n"/>
+      <c r="P20" s="549" t="n"/>
+      <c r="Q20" s="549" t="n"/>
+      <c r="R20" s="549" t="n"/>
+      <c r="S20" s="549" t="n"/>
+      <c r="T20" s="550" t="n"/>
+      <c r="U20" s="563" t="n"/>
+      <c r="V20" s="549" t="n"/>
+      <c r="W20" s="549" t="n"/>
+      <c r="X20" s="549" t="n"/>
+      <c r="Y20" s="549" t="n"/>
+      <c r="Z20" s="550" t="n"/>
+      <c r="AA20" s="563" t="n"/>
+      <c r="AB20" s="549" t="n"/>
+      <c r="AC20" s="549" t="n"/>
+      <c r="AD20" s="549" t="n"/>
+      <c r="AE20" s="549" t="n"/>
+      <c r="AF20" s="549" t="n"/>
+      <c r="AG20" s="550" t="n"/>
+      <c r="AH20" s="563" t="n"/>
+      <c r="AI20" s="549" t="n"/>
+      <c r="AJ20" s="549" t="n"/>
+      <c r="AK20" s="550" t="n"/>
+      <c r="AL20" s="563" t="n"/>
+      <c r="AM20" s="549" t="n"/>
+      <c r="AN20" s="549" t="n"/>
+      <c r="AO20" s="550" t="n"/>
+      <c r="AP20" s="563" t="n"/>
+      <c r="AQ20" s="549" t="n"/>
+      <c r="AR20" s="549" t="n"/>
+      <c r="AS20" s="550" t="n"/>
+      <c r="AT20" s="563" t="n"/>
+      <c r="AU20" s="549" t="n"/>
+      <c r="AV20" s="549" t="n"/>
+      <c r="AW20" s="550" t="n"/>
+      <c r="AX20" s="563" t="n"/>
+      <c r="AY20" s="549" t="n"/>
+      <c r="AZ20" s="549" t="n"/>
+      <c r="BA20" s="549" t="n"/>
+      <c r="BB20" s="549" t="n"/>
+      <c r="BC20" s="549" t="n"/>
+      <c r="BD20" s="552" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="495" t="n"/>
-      <c r="B21" s="340" t="n"/>
-      <c r="C21" s="340" t="n"/>
-      <c r="D21" s="496" t="n"/>
-      <c r="E21" s="371" t="n"/>
-      <c r="F21" s="371" t="n"/>
-      <c r="G21" s="371" t="n"/>
-      <c r="H21" s="371" t="n"/>
-      <c r="I21" s="496" t="n"/>
-      <c r="J21" s="371" t="n"/>
-      <c r="K21" s="371" t="n"/>
-      <c r="L21" s="371" t="n"/>
-      <c r="M21" s="371" t="n"/>
-      <c r="N21" s="496" t="n"/>
-      <c r="O21" s="371" t="n"/>
-      <c r="P21" s="371" t="n"/>
-      <c r="Q21" s="371" t="n"/>
-      <c r="R21" s="371" t="n"/>
-      <c r="S21" s="371" t="n"/>
-      <c r="T21" s="371" t="n"/>
-      <c r="U21" s="496" t="n"/>
-      <c r="V21" s="371" t="n"/>
-      <c r="W21" s="371" t="n"/>
-      <c r="X21" s="371" t="n"/>
-      <c r="Y21" s="371" t="n"/>
-      <c r="Z21" s="371" t="n"/>
-      <c r="AA21" s="496" t="n"/>
-      <c r="AB21" s="371" t="n"/>
-      <c r="AC21" s="371" t="n"/>
-      <c r="AD21" s="371" t="n"/>
-      <c r="AE21" s="371" t="n"/>
-      <c r="AF21" s="371" t="n"/>
-      <c r="AG21" s="371" t="n"/>
-      <c r="AH21" s="496" t="n"/>
-      <c r="AI21" s="371" t="n"/>
-      <c r="AJ21" s="371" t="n"/>
-      <c r="AK21" s="371" t="n"/>
-      <c r="AL21" s="496" t="n"/>
-      <c r="AM21" s="371" t="n"/>
-      <c r="AN21" s="371" t="n"/>
-      <c r="AO21" s="371" t="n"/>
-      <c r="AP21" s="496" t="n"/>
-      <c r="AQ21" s="371" t="n"/>
-      <c r="AR21" s="371" t="n"/>
-      <c r="AS21" s="371" t="n"/>
-      <c r="AT21" s="496" t="n"/>
-      <c r="AU21" s="371" t="n"/>
-      <c r="AV21" s="371" t="n"/>
-      <c r="AW21" s="371" t="n"/>
-      <c r="AX21" s="496" t="n"/>
-      <c r="AY21" s="371" t="n"/>
-      <c r="AZ21" s="371" t="n"/>
-      <c r="BA21" s="371" t="n"/>
-      <c r="BB21" s="371" t="n"/>
-      <c r="BC21" s="371" t="n"/>
-      <c r="BD21" s="485" t="n"/>
+      <c r="A21" s="562" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="563" t="n"/>
+      <c r="E21" s="549" t="n"/>
+      <c r="F21" s="549" t="n"/>
+      <c r="G21" s="549" t="n"/>
+      <c r="H21" s="550" t="n"/>
+      <c r="I21" s="563" t="n"/>
+      <c r="J21" s="549" t="n"/>
+      <c r="K21" s="549" t="n"/>
+      <c r="L21" s="549" t="n"/>
+      <c r="M21" s="550" t="n"/>
+      <c r="N21" s="563" t="n"/>
+      <c r="O21" s="549" t="n"/>
+      <c r="P21" s="549" t="n"/>
+      <c r="Q21" s="549" t="n"/>
+      <c r="R21" s="549" t="n"/>
+      <c r="S21" s="549" t="n"/>
+      <c r="T21" s="550" t="n"/>
+      <c r="U21" s="563" t="n"/>
+      <c r="V21" s="549" t="n"/>
+      <c r="W21" s="549" t="n"/>
+      <c r="X21" s="549" t="n"/>
+      <c r="Y21" s="549" t="n"/>
+      <c r="Z21" s="550" t="n"/>
+      <c r="AA21" s="563" t="n"/>
+      <c r="AB21" s="549" t="n"/>
+      <c r="AC21" s="549" t="n"/>
+      <c r="AD21" s="549" t="n"/>
+      <c r="AE21" s="549" t="n"/>
+      <c r="AF21" s="549" t="n"/>
+      <c r="AG21" s="550" t="n"/>
+      <c r="AH21" s="563" t="n"/>
+      <c r="AI21" s="549" t="n"/>
+      <c r="AJ21" s="549" t="n"/>
+      <c r="AK21" s="550" t="n"/>
+      <c r="AL21" s="563" t="n"/>
+      <c r="AM21" s="549" t="n"/>
+      <c r="AN21" s="549" t="n"/>
+      <c r="AO21" s="550" t="n"/>
+      <c r="AP21" s="563" t="n"/>
+      <c r="AQ21" s="549" t="n"/>
+      <c r="AR21" s="549" t="n"/>
+      <c r="AS21" s="550" t="n"/>
+      <c r="AT21" s="563" t="n"/>
+      <c r="AU21" s="549" t="n"/>
+      <c r="AV21" s="549" t="n"/>
+      <c r="AW21" s="550" t="n"/>
+      <c r="AX21" s="563" t="n"/>
+      <c r="AY21" s="549" t="n"/>
+      <c r="AZ21" s="549" t="n"/>
+      <c r="BA21" s="549" t="n"/>
+      <c r="BB21" s="549" t="n"/>
+      <c r="BC21" s="549" t="n"/>
+      <c r="BD21" s="552" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="495" t="n"/>
-      <c r="B22" s="340" t="n"/>
-      <c r="C22" s="340" t="n"/>
-      <c r="D22" s="496" t="n"/>
-      <c r="E22" s="371" t="n"/>
-      <c r="F22" s="371" t="n"/>
-      <c r="G22" s="371" t="n"/>
-      <c r="H22" s="371" t="n"/>
-      <c r="I22" s="496" t="n"/>
-      <c r="J22" s="371" t="n"/>
-      <c r="K22" s="371" t="n"/>
-      <c r="L22" s="371" t="n"/>
-      <c r="M22" s="371" t="n"/>
-      <c r="N22" s="496" t="n"/>
-      <c r="O22" s="371" t="n"/>
-      <c r="P22" s="371" t="n"/>
-      <c r="Q22" s="371" t="n"/>
-      <c r="R22" s="371" t="n"/>
-      <c r="S22" s="371" t="n"/>
-      <c r="T22" s="371" t="n"/>
-      <c r="U22" s="496" t="n"/>
-      <c r="V22" s="371" t="n"/>
-      <c r="W22" s="371" t="n"/>
-      <c r="X22" s="371" t="n"/>
-      <c r="Y22" s="371" t="n"/>
-      <c r="Z22" s="371" t="n"/>
-      <c r="AA22" s="496" t="n"/>
-      <c r="AB22" s="371" t="n"/>
-      <c r="AC22" s="371" t="n"/>
-      <c r="AD22" s="371" t="n"/>
-      <c r="AE22" s="371" t="n"/>
-      <c r="AF22" s="371" t="n"/>
-      <c r="AG22" s="371" t="n"/>
-      <c r="AH22" s="496" t="n"/>
-      <c r="AI22" s="371" t="n"/>
-      <c r="AJ22" s="371" t="n"/>
-      <c r="AK22" s="371" t="n"/>
-      <c r="AL22" s="496" t="n"/>
-      <c r="AM22" s="371" t="n"/>
-      <c r="AN22" s="371" t="n"/>
-      <c r="AO22" s="371" t="n"/>
-      <c r="AP22" s="496" t="n"/>
-      <c r="AQ22" s="371" t="n"/>
-      <c r="AR22" s="371" t="n"/>
-      <c r="AS22" s="371" t="n"/>
-      <c r="AT22" s="496" t="n"/>
-      <c r="AU22" s="371" t="n"/>
-      <c r="AV22" s="371" t="n"/>
-      <c r="AW22" s="371" t="n"/>
-      <c r="AX22" s="496" t="n"/>
-      <c r="AY22" s="371" t="n"/>
-      <c r="AZ22" s="371" t="n"/>
-      <c r="BA22" s="371" t="n"/>
-      <c r="BB22" s="371" t="n"/>
-      <c r="BC22" s="371" t="n"/>
-      <c r="BD22" s="485" t="n"/>
+      <c r="A22" s="562" t="n"/>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="563" t="n"/>
+      <c r="E22" s="549" t="n"/>
+      <c r="F22" s="549" t="n"/>
+      <c r="G22" s="549" t="n"/>
+      <c r="H22" s="550" t="n"/>
+      <c r="I22" s="563" t="n"/>
+      <c r="J22" s="549" t="n"/>
+      <c r="K22" s="549" t="n"/>
+      <c r="L22" s="549" t="n"/>
+      <c r="M22" s="550" t="n"/>
+      <c r="N22" s="563" t="n"/>
+      <c r="O22" s="549" t="n"/>
+      <c r="P22" s="549" t="n"/>
+      <c r="Q22" s="549" t="n"/>
+      <c r="R22" s="549" t="n"/>
+      <c r="S22" s="549" t="n"/>
+      <c r="T22" s="550" t="n"/>
+      <c r="U22" s="563" t="n"/>
+      <c r="V22" s="549" t="n"/>
+      <c r="W22" s="549" t="n"/>
+      <c r="X22" s="549" t="n"/>
+      <c r="Y22" s="549" t="n"/>
+      <c r="Z22" s="550" t="n"/>
+      <c r="AA22" s="563" t="n"/>
+      <c r="AB22" s="549" t="n"/>
+      <c r="AC22" s="549" t="n"/>
+      <c r="AD22" s="549" t="n"/>
+      <c r="AE22" s="549" t="n"/>
+      <c r="AF22" s="549" t="n"/>
+      <c r="AG22" s="550" t="n"/>
+      <c r="AH22" s="563" t="n"/>
+      <c r="AI22" s="549" t="n"/>
+      <c r="AJ22" s="549" t="n"/>
+      <c r="AK22" s="550" t="n"/>
+      <c r="AL22" s="563" t="n"/>
+      <c r="AM22" s="549" t="n"/>
+      <c r="AN22" s="549" t="n"/>
+      <c r="AO22" s="550" t="n"/>
+      <c r="AP22" s="563" t="n"/>
+      <c r="AQ22" s="549" t="n"/>
+      <c r="AR22" s="549" t="n"/>
+      <c r="AS22" s="550" t="n"/>
+      <c r="AT22" s="563" t="n"/>
+      <c r="AU22" s="549" t="n"/>
+      <c r="AV22" s="549" t="n"/>
+      <c r="AW22" s="550" t="n"/>
+      <c r="AX22" s="563" t="n"/>
+      <c r="AY22" s="549" t="n"/>
+      <c r="AZ22" s="549" t="n"/>
+      <c r="BA22" s="549" t="n"/>
+      <c r="BB22" s="549" t="n"/>
+      <c r="BC22" s="549" t="n"/>
+      <c r="BD22" s="552" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="495" t="n"/>
-      <c r="B23" s="340" t="n"/>
-      <c r="C23" s="340" t="n"/>
-      <c r="D23" s="496" t="n"/>
-      <c r="E23" s="371" t="n"/>
-      <c r="F23" s="371" t="n"/>
-      <c r="G23" s="371" t="n"/>
-      <c r="H23" s="371" t="n"/>
-      <c r="I23" s="496" t="n"/>
-      <c r="J23" s="371" t="n"/>
-      <c r="K23" s="371" t="n"/>
-      <c r="L23" s="371" t="n"/>
-      <c r="M23" s="371" t="n"/>
-      <c r="N23" s="496" t="n"/>
-      <c r="O23" s="371" t="n"/>
-      <c r="P23" s="371" t="n"/>
-      <c r="Q23" s="371" t="n"/>
-      <c r="R23" s="371" t="n"/>
-      <c r="S23" s="371" t="n"/>
-      <c r="T23" s="371" t="n"/>
-      <c r="U23" s="496" t="n"/>
-      <c r="V23" s="371" t="n"/>
-      <c r="W23" s="371" t="n"/>
-      <c r="X23" s="371" t="n"/>
-      <c r="Y23" s="371" t="n"/>
-      <c r="Z23" s="371" t="n"/>
-      <c r="AA23" s="496" t="n"/>
-      <c r="AB23" s="371" t="n"/>
-      <c r="AC23" s="371" t="n"/>
-      <c r="AD23" s="371" t="n"/>
-      <c r="AE23" s="371" t="n"/>
-      <c r="AF23" s="371" t="n"/>
-      <c r="AG23" s="371" t="n"/>
-      <c r="AH23" s="496" t="n"/>
-      <c r="AI23" s="371" t="n"/>
-      <c r="AJ23" s="371" t="n"/>
-      <c r="AK23" s="371" t="n"/>
-      <c r="AL23" s="496" t="n"/>
-      <c r="AM23" s="371" t="n"/>
-      <c r="AN23" s="371" t="n"/>
-      <c r="AO23" s="371" t="n"/>
-      <c r="AP23" s="496" t="n"/>
-      <c r="AQ23" s="371" t="n"/>
-      <c r="AR23" s="371" t="n"/>
-      <c r="AS23" s="371" t="n"/>
-      <c r="AT23" s="496" t="n"/>
-      <c r="AU23" s="371" t="n"/>
-      <c r="AV23" s="371" t="n"/>
-      <c r="AW23" s="371" t="n"/>
-      <c r="AX23" s="496" t="n"/>
-      <c r="AY23" s="371" t="n"/>
-      <c r="AZ23" s="371" t="n"/>
-      <c r="BA23" s="371" t="n"/>
-      <c r="BB23" s="371" t="n"/>
-      <c r="BC23" s="371" t="n"/>
-      <c r="BD23" s="485" t="n"/>
+      <c r="A23" s="562" t="n"/>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="563" t="n"/>
+      <c r="E23" s="549" t="n"/>
+      <c r="F23" s="549" t="n"/>
+      <c r="G23" s="549" t="n"/>
+      <c r="H23" s="550" t="n"/>
+      <c r="I23" s="563" t="n"/>
+      <c r="J23" s="549" t="n"/>
+      <c r="K23" s="549" t="n"/>
+      <c r="L23" s="549" t="n"/>
+      <c r="M23" s="550" t="n"/>
+      <c r="N23" s="563" t="n"/>
+      <c r="O23" s="549" t="n"/>
+      <c r="P23" s="549" t="n"/>
+      <c r="Q23" s="549" t="n"/>
+      <c r="R23" s="549" t="n"/>
+      <c r="S23" s="549" t="n"/>
+      <c r="T23" s="550" t="n"/>
+      <c r="U23" s="563" t="n"/>
+      <c r="V23" s="549" t="n"/>
+      <c r="W23" s="549" t="n"/>
+      <c r="X23" s="549" t="n"/>
+      <c r="Y23" s="549" t="n"/>
+      <c r="Z23" s="550" t="n"/>
+      <c r="AA23" s="563" t="n"/>
+      <c r="AB23" s="549" t="n"/>
+      <c r="AC23" s="549" t="n"/>
+      <c r="AD23" s="549" t="n"/>
+      <c r="AE23" s="549" t="n"/>
+      <c r="AF23" s="549" t="n"/>
+      <c r="AG23" s="550" t="n"/>
+      <c r="AH23" s="563" t="n"/>
+      <c r="AI23" s="549" t="n"/>
+      <c r="AJ23" s="549" t="n"/>
+      <c r="AK23" s="550" t="n"/>
+      <c r="AL23" s="563" t="n"/>
+      <c r="AM23" s="549" t="n"/>
+      <c r="AN23" s="549" t="n"/>
+      <c r="AO23" s="550" t="n"/>
+      <c r="AP23" s="563" t="n"/>
+      <c r="AQ23" s="549" t="n"/>
+      <c r="AR23" s="549" t="n"/>
+      <c r="AS23" s="550" t="n"/>
+      <c r="AT23" s="563" t="n"/>
+      <c r="AU23" s="549" t="n"/>
+      <c r="AV23" s="549" t="n"/>
+      <c r="AW23" s="550" t="n"/>
+      <c r="AX23" s="563" t="n"/>
+      <c r="AY23" s="549" t="n"/>
+      <c r="AZ23" s="549" t="n"/>
+      <c r="BA23" s="549" t="n"/>
+      <c r="BB23" s="549" t="n"/>
+      <c r="BC23" s="549" t="n"/>
+      <c r="BD23" s="552" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="495" t="n"/>
-      <c r="B24" s="340" t="n"/>
-      <c r="C24" s="340" t="n"/>
-      <c r="D24" s="496" t="n"/>
-      <c r="E24" s="371" t="n"/>
-      <c r="F24" s="371" t="n"/>
-      <c r="G24" s="371" t="n"/>
-      <c r="H24" s="371" t="n"/>
-      <c r="I24" s="496" t="n"/>
-      <c r="J24" s="371" t="n"/>
-      <c r="K24" s="371" t="n"/>
-      <c r="L24" s="371" t="n"/>
-      <c r="M24" s="371" t="n"/>
-      <c r="N24" s="496" t="n"/>
-      <c r="O24" s="371" t="n"/>
-      <c r="P24" s="371" t="n"/>
-      <c r="Q24" s="371" t="n"/>
-      <c r="R24" s="371" t="n"/>
-      <c r="S24" s="371" t="n"/>
-      <c r="T24" s="371" t="n"/>
-      <c r="U24" s="496" t="n"/>
-      <c r="V24" s="371" t="n"/>
-      <c r="W24" s="371" t="n"/>
-      <c r="X24" s="371" t="n"/>
-      <c r="Y24" s="371" t="n"/>
-      <c r="Z24" s="371" t="n"/>
-      <c r="AA24" s="496" t="n"/>
-      <c r="AB24" s="371" t="n"/>
-      <c r="AC24" s="371" t="n"/>
-      <c r="AD24" s="371" t="n"/>
-      <c r="AE24" s="371" t="n"/>
-      <c r="AF24" s="371" t="n"/>
-      <c r="AG24" s="371" t="n"/>
-      <c r="AH24" s="496" t="n"/>
-      <c r="AI24" s="371" t="n"/>
-      <c r="AJ24" s="371" t="n"/>
-      <c r="AK24" s="371" t="n"/>
-      <c r="AL24" s="496" t="n"/>
-      <c r="AM24" s="371" t="n"/>
-      <c r="AN24" s="371" t="n"/>
-      <c r="AO24" s="371" t="n"/>
-      <c r="AP24" s="496" t="n"/>
-      <c r="AQ24" s="371" t="n"/>
-      <c r="AR24" s="371" t="n"/>
-      <c r="AS24" s="371" t="n"/>
-      <c r="AT24" s="496" t="n"/>
-      <c r="AU24" s="371" t="n"/>
-      <c r="AV24" s="371" t="n"/>
-      <c r="AW24" s="371" t="n"/>
-      <c r="AX24" s="496" t="n"/>
-      <c r="AY24" s="371" t="n"/>
-      <c r="AZ24" s="371" t="n"/>
-      <c r="BA24" s="371" t="n"/>
-      <c r="BB24" s="371" t="n"/>
-      <c r="BC24" s="371" t="n"/>
-      <c r="BD24" s="485" t="n"/>
+      <c r="A24" s="562" t="n"/>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="563" t="n"/>
+      <c r="E24" s="549" t="n"/>
+      <c r="F24" s="549" t="n"/>
+      <c r="G24" s="549" t="n"/>
+      <c r="H24" s="550" t="n"/>
+      <c r="I24" s="563" t="n"/>
+      <c r="J24" s="549" t="n"/>
+      <c r="K24" s="549" t="n"/>
+      <c r="L24" s="549" t="n"/>
+      <c r="M24" s="550" t="n"/>
+      <c r="N24" s="563" t="n"/>
+      <c r="O24" s="549" t="n"/>
+      <c r="P24" s="549" t="n"/>
+      <c r="Q24" s="549" t="n"/>
+      <c r="R24" s="549" t="n"/>
+      <c r="S24" s="549" t="n"/>
+      <c r="T24" s="550" t="n"/>
+      <c r="U24" s="563" t="n"/>
+      <c r="V24" s="549" t="n"/>
+      <c r="W24" s="549" t="n"/>
+      <c r="X24" s="549" t="n"/>
+      <c r="Y24" s="549" t="n"/>
+      <c r="Z24" s="550" t="n"/>
+      <c r="AA24" s="563" t="n"/>
+      <c r="AB24" s="549" t="n"/>
+      <c r="AC24" s="549" t="n"/>
+      <c r="AD24" s="549" t="n"/>
+      <c r="AE24" s="549" t="n"/>
+      <c r="AF24" s="549" t="n"/>
+      <c r="AG24" s="550" t="n"/>
+      <c r="AH24" s="563" t="n"/>
+      <c r="AI24" s="549" t="n"/>
+      <c r="AJ24" s="549" t="n"/>
+      <c r="AK24" s="550" t="n"/>
+      <c r="AL24" s="563" t="n"/>
+      <c r="AM24" s="549" t="n"/>
+      <c r="AN24" s="549" t="n"/>
+      <c r="AO24" s="550" t="n"/>
+      <c r="AP24" s="563" t="n"/>
+      <c r="AQ24" s="549" t="n"/>
+      <c r="AR24" s="549" t="n"/>
+      <c r="AS24" s="550" t="n"/>
+      <c r="AT24" s="563" t="n"/>
+      <c r="AU24" s="549" t="n"/>
+      <c r="AV24" s="549" t="n"/>
+      <c r="AW24" s="550" t="n"/>
+      <c r="AX24" s="563" t="n"/>
+      <c r="AY24" s="549" t="n"/>
+      <c r="AZ24" s="549" t="n"/>
+      <c r="BA24" s="549" t="n"/>
+      <c r="BB24" s="549" t="n"/>
+      <c r="BC24" s="549" t="n"/>
+      <c r="BD24" s="552" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="495" t="n"/>
-      <c r="B25" s="340" t="n"/>
-      <c r="C25" s="340" t="n"/>
-      <c r="D25" s="496" t="n"/>
-      <c r="E25" s="371" t="n"/>
-      <c r="F25" s="371" t="n"/>
-      <c r="G25" s="371" t="n"/>
-      <c r="H25" s="371" t="n"/>
-      <c r="I25" s="496" t="n"/>
-      <c r="J25" s="371" t="n"/>
-      <c r="K25" s="371" t="n"/>
-      <c r="L25" s="371" t="n"/>
-      <c r="M25" s="371" t="n"/>
-      <c r="N25" s="496" t="n"/>
-      <c r="O25" s="371" t="n"/>
-      <c r="P25" s="371" t="n"/>
-      <c r="Q25" s="371" t="n"/>
-      <c r="R25" s="371" t="n"/>
-      <c r="S25" s="371" t="n"/>
-      <c r="T25" s="371" t="n"/>
-      <c r="U25" s="496" t="n"/>
-      <c r="V25" s="371" t="n"/>
-      <c r="W25" s="371" t="n"/>
-      <c r="X25" s="371" t="n"/>
-      <c r="Y25" s="371" t="n"/>
-      <c r="Z25" s="371" t="n"/>
-      <c r="AA25" s="496" t="n"/>
-      <c r="AB25" s="371" t="n"/>
-      <c r="AC25" s="371" t="n"/>
-      <c r="AD25" s="371" t="n"/>
-      <c r="AE25" s="371" t="n"/>
-      <c r="AF25" s="371" t="n"/>
-      <c r="AG25" s="371" t="n"/>
-      <c r="AH25" s="496" t="n"/>
-      <c r="AI25" s="371" t="n"/>
-      <c r="AJ25" s="371" t="n"/>
-      <c r="AK25" s="371" t="n"/>
-      <c r="AL25" s="496" t="n"/>
-      <c r="AM25" s="371" t="n"/>
-      <c r="AN25" s="371" t="n"/>
-      <c r="AO25" s="371" t="n"/>
-      <c r="AP25" s="496" t="n"/>
-      <c r="AQ25" s="371" t="n"/>
-      <c r="AR25" s="371" t="n"/>
-      <c r="AS25" s="371" t="n"/>
-      <c r="AT25" s="496" t="n"/>
-      <c r="AU25" s="371" t="n"/>
-      <c r="AV25" s="371" t="n"/>
-      <c r="AW25" s="371" t="n"/>
-      <c r="AX25" s="496" t="n"/>
-      <c r="AY25" s="371" t="n"/>
-      <c r="AZ25" s="371" t="n"/>
-      <c r="BA25" s="371" t="n"/>
-      <c r="BB25" s="371" t="n"/>
-      <c r="BC25" s="371" t="n"/>
-      <c r="BD25" s="485" t="n"/>
+      <c r="A25" s="562" t="n"/>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="563" t="n"/>
+      <c r="E25" s="549" t="n"/>
+      <c r="F25" s="549" t="n"/>
+      <c r="G25" s="549" t="n"/>
+      <c r="H25" s="550" t="n"/>
+      <c r="I25" s="563" t="n"/>
+      <c r="J25" s="549" t="n"/>
+      <c r="K25" s="549" t="n"/>
+      <c r="L25" s="549" t="n"/>
+      <c r="M25" s="550" t="n"/>
+      <c r="N25" s="563" t="n"/>
+      <c r="O25" s="549" t="n"/>
+      <c r="P25" s="549" t="n"/>
+      <c r="Q25" s="549" t="n"/>
+      <c r="R25" s="549" t="n"/>
+      <c r="S25" s="549" t="n"/>
+      <c r="T25" s="550" t="n"/>
+      <c r="U25" s="563" t="n"/>
+      <c r="V25" s="549" t="n"/>
+      <c r="W25" s="549" t="n"/>
+      <c r="X25" s="549" t="n"/>
+      <c r="Y25" s="549" t="n"/>
+      <c r="Z25" s="550" t="n"/>
+      <c r="AA25" s="563" t="n"/>
+      <c r="AB25" s="549" t="n"/>
+      <c r="AC25" s="549" t="n"/>
+      <c r="AD25" s="549" t="n"/>
+      <c r="AE25" s="549" t="n"/>
+      <c r="AF25" s="549" t="n"/>
+      <c r="AG25" s="550" t="n"/>
+      <c r="AH25" s="563" t="n"/>
+      <c r="AI25" s="549" t="n"/>
+      <c r="AJ25" s="549" t="n"/>
+      <c r="AK25" s="550" t="n"/>
+      <c r="AL25" s="563" t="n"/>
+      <c r="AM25" s="549" t="n"/>
+      <c r="AN25" s="549" t="n"/>
+      <c r="AO25" s="550" t="n"/>
+      <c r="AP25" s="563" t="n"/>
+      <c r="AQ25" s="549" t="n"/>
+      <c r="AR25" s="549" t="n"/>
+      <c r="AS25" s="550" t="n"/>
+      <c r="AT25" s="563" t="n"/>
+      <c r="AU25" s="549" t="n"/>
+      <c r="AV25" s="549" t="n"/>
+      <c r="AW25" s="550" t="n"/>
+      <c r="AX25" s="563" t="n"/>
+      <c r="AY25" s="549" t="n"/>
+      <c r="AZ25" s="549" t="n"/>
+      <c r="BA25" s="549" t="n"/>
+      <c r="BB25" s="549" t="n"/>
+      <c r="BC25" s="549" t="n"/>
+      <c r="BD25" s="552" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="495" t="n"/>
-      <c r="B26" s="340" t="n"/>
-      <c r="C26" s="340" t="n"/>
-      <c r="D26" s="496" t="n"/>
-      <c r="E26" s="371" t="n"/>
-      <c r="F26" s="371" t="n"/>
-      <c r="G26" s="371" t="n"/>
-      <c r="H26" s="371" t="n"/>
-      <c r="I26" s="496" t="n"/>
-      <c r="J26" s="371" t="n"/>
-      <c r="K26" s="371" t="n"/>
-      <c r="L26" s="371" t="n"/>
-      <c r="M26" s="371" t="n"/>
-      <c r="N26" s="496" t="n"/>
-      <c r="O26" s="371" t="n"/>
-      <c r="P26" s="371" t="n"/>
-      <c r="Q26" s="371" t="n"/>
-      <c r="R26" s="371" t="n"/>
-      <c r="S26" s="371" t="n"/>
-      <c r="T26" s="371" t="n"/>
-      <c r="U26" s="496" t="n"/>
-      <c r="V26" s="371" t="n"/>
-      <c r="W26" s="371" t="n"/>
-      <c r="X26" s="371" t="n"/>
-      <c r="Y26" s="371" t="n"/>
-      <c r="Z26" s="371" t="n"/>
-      <c r="AA26" s="496" t="n"/>
-      <c r="AB26" s="371" t="n"/>
-      <c r="AC26" s="371" t="n"/>
-      <c r="AD26" s="371" t="n"/>
-      <c r="AE26" s="371" t="n"/>
-      <c r="AF26" s="371" t="n"/>
-      <c r="AG26" s="371" t="n"/>
-      <c r="AH26" s="496" t="n"/>
-      <c r="AI26" s="371" t="n"/>
-      <c r="AJ26" s="371" t="n"/>
-      <c r="AK26" s="371" t="n"/>
-      <c r="AL26" s="496" t="n"/>
-      <c r="AM26" s="371" t="n"/>
-      <c r="AN26" s="371" t="n"/>
-      <c r="AO26" s="371" t="n"/>
-      <c r="AP26" s="496" t="n"/>
-      <c r="AQ26" s="371" t="n"/>
-      <c r="AR26" s="371" t="n"/>
-      <c r="AS26" s="371" t="n"/>
-      <c r="AT26" s="496" t="n"/>
-      <c r="AU26" s="371" t="n"/>
-      <c r="AV26" s="371" t="n"/>
-      <c r="AW26" s="371" t="n"/>
-      <c r="AX26" s="496" t="n"/>
-      <c r="AY26" s="371" t="n"/>
-      <c r="AZ26" s="371" t="n"/>
-      <c r="BA26" s="371" t="n"/>
-      <c r="BB26" s="371" t="n"/>
-      <c r="BC26" s="371" t="n"/>
-      <c r="BD26" s="485" t="n"/>
+      <c r="A26" s="562" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="563" t="n"/>
+      <c r="E26" s="549" t="n"/>
+      <c r="F26" s="549" t="n"/>
+      <c r="G26" s="549" t="n"/>
+      <c r="H26" s="550" t="n"/>
+      <c r="I26" s="563" t="n"/>
+      <c r="J26" s="549" t="n"/>
+      <c r="K26" s="549" t="n"/>
+      <c r="L26" s="549" t="n"/>
+      <c r="M26" s="550" t="n"/>
+      <c r="N26" s="563" t="n"/>
+      <c r="O26" s="549" t="n"/>
+      <c r="P26" s="549" t="n"/>
+      <c r="Q26" s="549" t="n"/>
+      <c r="R26" s="549" t="n"/>
+      <c r="S26" s="549" t="n"/>
+      <c r="T26" s="550" t="n"/>
+      <c r="U26" s="563" t="n"/>
+      <c r="V26" s="549" t="n"/>
+      <c r="W26" s="549" t="n"/>
+      <c r="X26" s="549" t="n"/>
+      <c r="Y26" s="549" t="n"/>
+      <c r="Z26" s="550" t="n"/>
+      <c r="AA26" s="563" t="n"/>
+      <c r="AB26" s="549" t="n"/>
+      <c r="AC26" s="549" t="n"/>
+      <c r="AD26" s="549" t="n"/>
+      <c r="AE26" s="549" t="n"/>
+      <c r="AF26" s="549" t="n"/>
+      <c r="AG26" s="550" t="n"/>
+      <c r="AH26" s="563" t="n"/>
+      <c r="AI26" s="549" t="n"/>
+      <c r="AJ26" s="549" t="n"/>
+      <c r="AK26" s="550" t="n"/>
+      <c r="AL26" s="563" t="n"/>
+      <c r="AM26" s="549" t="n"/>
+      <c r="AN26" s="549" t="n"/>
+      <c r="AO26" s="550" t="n"/>
+      <c r="AP26" s="563" t="n"/>
+      <c r="AQ26" s="549" t="n"/>
+      <c r="AR26" s="549" t="n"/>
+      <c r="AS26" s="550" t="n"/>
+      <c r="AT26" s="563" t="n"/>
+      <c r="AU26" s="549" t="n"/>
+      <c r="AV26" s="549" t="n"/>
+      <c r="AW26" s="550" t="n"/>
+      <c r="AX26" s="563" t="n"/>
+      <c r="AY26" s="549" t="n"/>
+      <c r="AZ26" s="549" t="n"/>
+      <c r="BA26" s="549" t="n"/>
+      <c r="BB26" s="549" t="n"/>
+      <c r="BC26" s="549" t="n"/>
+      <c r="BD26" s="552" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="497" t="n"/>
-      <c r="B27" s="487" t="n"/>
-      <c r="C27" s="487" t="n"/>
-      <c r="D27" s="498" t="n"/>
-      <c r="E27" s="489" t="n"/>
-      <c r="F27" s="489" t="n"/>
-      <c r="G27" s="489" t="n"/>
-      <c r="H27" s="489" t="n"/>
-      <c r="I27" s="498" t="n"/>
-      <c r="J27" s="489" t="n"/>
-      <c r="K27" s="489" t="n"/>
-      <c r="L27" s="489" t="n"/>
-      <c r="M27" s="489" t="n"/>
-      <c r="N27" s="498" t="n"/>
-      <c r="O27" s="489" t="n"/>
-      <c r="P27" s="489" t="n"/>
-      <c r="Q27" s="489" t="n"/>
-      <c r="R27" s="489" t="n"/>
-      <c r="S27" s="489" t="n"/>
-      <c r="T27" s="489" t="n"/>
-      <c r="U27" s="498" t="n"/>
-      <c r="V27" s="489" t="n"/>
-      <c r="W27" s="489" t="n"/>
-      <c r="X27" s="489" t="n"/>
-      <c r="Y27" s="489" t="n"/>
-      <c r="Z27" s="489" t="n"/>
-      <c r="AA27" s="498" t="n"/>
-      <c r="AB27" s="489" t="n"/>
-      <c r="AC27" s="489" t="n"/>
-      <c r="AD27" s="489" t="n"/>
-      <c r="AE27" s="489" t="n"/>
-      <c r="AF27" s="489" t="n"/>
-      <c r="AG27" s="489" t="n"/>
-      <c r="AH27" s="498" t="n"/>
-      <c r="AI27" s="489" t="n"/>
-      <c r="AJ27" s="489" t="n"/>
-      <c r="AK27" s="489" t="n"/>
-      <c r="AL27" s="498" t="n"/>
-      <c r="AM27" s="489" t="n"/>
-      <c r="AN27" s="489" t="n"/>
-      <c r="AO27" s="489" t="n"/>
-      <c r="AP27" s="498" t="n"/>
-      <c r="AQ27" s="489" t="n"/>
-      <c r="AR27" s="489" t="n"/>
-      <c r="AS27" s="489" t="n"/>
-      <c r="AT27" s="498" t="n"/>
-      <c r="AU27" s="489" t="n"/>
-      <c r="AV27" s="489" t="n"/>
-      <c r="AW27" s="489" t="n"/>
-      <c r="AX27" s="498" t="n"/>
-      <c r="AY27" s="489" t="n"/>
-      <c r="AZ27" s="489" t="n"/>
-      <c r="BA27" s="489" t="n"/>
-      <c r="BB27" s="489" t="n"/>
-      <c r="BC27" s="489" t="n"/>
-      <c r="BD27" s="491" t="n"/>
+      <c r="A27" s="564" t="n"/>
+      <c r="B27" s="19" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="565" t="n"/>
+      <c r="E27" s="555" t="n"/>
+      <c r="F27" s="555" t="n"/>
+      <c r="G27" s="555" t="n"/>
+      <c r="H27" s="556" t="n"/>
+      <c r="I27" s="565" t="n"/>
+      <c r="J27" s="555" t="n"/>
+      <c r="K27" s="555" t="n"/>
+      <c r="L27" s="555" t="n"/>
+      <c r="M27" s="556" t="n"/>
+      <c r="N27" s="565" t="n"/>
+      <c r="O27" s="555" t="n"/>
+      <c r="P27" s="555" t="n"/>
+      <c r="Q27" s="555" t="n"/>
+      <c r="R27" s="555" t="n"/>
+      <c r="S27" s="555" t="n"/>
+      <c r="T27" s="556" t="n"/>
+      <c r="U27" s="565" t="n"/>
+      <c r="V27" s="555" t="n"/>
+      <c r="W27" s="555" t="n"/>
+      <c r="X27" s="555" t="n"/>
+      <c r="Y27" s="555" t="n"/>
+      <c r="Z27" s="556" t="n"/>
+      <c r="AA27" s="565" t="n"/>
+      <c r="AB27" s="555" t="n"/>
+      <c r="AC27" s="555" t="n"/>
+      <c r="AD27" s="555" t="n"/>
+      <c r="AE27" s="555" t="n"/>
+      <c r="AF27" s="555" t="n"/>
+      <c r="AG27" s="556" t="n"/>
+      <c r="AH27" s="565" t="n"/>
+      <c r="AI27" s="555" t="n"/>
+      <c r="AJ27" s="555" t="n"/>
+      <c r="AK27" s="556" t="n"/>
+      <c r="AL27" s="565" t="n"/>
+      <c r="AM27" s="555" t="n"/>
+      <c r="AN27" s="555" t="n"/>
+      <c r="AO27" s="556" t="n"/>
+      <c r="AP27" s="565" t="n"/>
+      <c r="AQ27" s="555" t="n"/>
+      <c r="AR27" s="555" t="n"/>
+      <c r="AS27" s="556" t="n"/>
+      <c r="AT27" s="565" t="n"/>
+      <c r="AU27" s="555" t="n"/>
+      <c r="AV27" s="555" t="n"/>
+      <c r="AW27" s="556" t="n"/>
+      <c r="AX27" s="565" t="n"/>
+      <c r="AY27" s="555" t="n"/>
+      <c r="AZ27" s="555" t="n"/>
+      <c r="BA27" s="555" t="n"/>
+      <c r="BB27" s="555" t="n"/>
+      <c r="BC27" s="555" t="n"/>
+      <c r="BD27" s="558" t="n"/>
     </row>
     <row r="28" ht="3" customHeight="1">
-      <c r="A28" s="375" t="n"/>
-      <c r="B28" s="345" t="n"/>
-      <c r="C28" s="345" t="n"/>
-      <c r="D28" s="376" t="n"/>
-      <c r="E28" s="345" t="n"/>
-      <c r="F28" s="345" t="n"/>
-      <c r="G28" s="345" t="n"/>
-      <c r="H28" s="377" t="n"/>
-      <c r="I28" s="345" t="n"/>
-      <c r="J28" s="345" t="n"/>
-      <c r="K28" s="345" t="n"/>
-      <c r="L28" s="345" t="n"/>
-      <c r="M28" s="345" t="n"/>
-      <c r="N28" s="345" t="n"/>
-      <c r="O28" s="345" t="n"/>
-      <c r="P28" s="345" t="n"/>
-      <c r="Q28" s="345" t="n"/>
-      <c r="R28" s="345" t="n"/>
-      <c r="S28" s="345" t="n"/>
-      <c r="T28" s="345" t="n"/>
-      <c r="U28" s="345" t="n"/>
-      <c r="V28" s="345" t="n"/>
-      <c r="W28" s="345" t="n"/>
-      <c r="X28" s="345" t="n"/>
-      <c r="Y28" s="345" t="n"/>
-      <c r="Z28" s="345" t="n"/>
-      <c r="AA28" s="378" t="n"/>
-      <c r="AB28" s="345" t="n"/>
-      <c r="AC28" s="345" t="n"/>
-      <c r="AD28" s="345" t="n"/>
-      <c r="AE28" s="345" t="n"/>
-      <c r="AF28" s="345" t="n"/>
-      <c r="AG28" s="345" t="n"/>
-      <c r="AH28" s="345" t="n"/>
-      <c r="AI28" s="345" t="n"/>
-      <c r="AJ28" s="345" t="n"/>
-      <c r="AK28" s="345" t="n"/>
-      <c r="AL28" s="345" t="n"/>
-      <c r="AM28" s="345" t="n"/>
-      <c r="AN28" s="345" t="n"/>
-      <c r="AO28" s="345" t="n"/>
-      <c r="AP28" s="345" t="n"/>
-      <c r="AQ28" s="345" t="n"/>
-      <c r="AR28" s="379" t="n"/>
-      <c r="AS28" s="345" t="n"/>
-      <c r="AT28" s="345" t="n"/>
-      <c r="AU28" s="345" t="n"/>
-      <c r="AV28" s="345" t="n"/>
-      <c r="AW28" s="345" t="n"/>
-      <c r="AX28" s="379" t="n"/>
-      <c r="AY28" s="345" t="n"/>
-      <c r="AZ28" s="345" t="n"/>
-      <c r="BA28" s="345" t="n"/>
-      <c r="BB28" s="380" t="n"/>
-      <c r="BC28" s="345" t="n"/>
-      <c r="BD28" s="345" t="n"/>
+      <c r="A28" s="566" t="n"/>
+      <c r="B28" s="559" t="n"/>
+      <c r="C28" s="559" t="n"/>
+      <c r="D28" s="567" t="n"/>
+      <c r="E28" s="559" t="n"/>
+      <c r="F28" s="559" t="n"/>
+      <c r="G28" s="559" t="n"/>
+      <c r="H28" s="568" t="n"/>
+      <c r="I28" s="559" t="n"/>
+      <c r="J28" s="559" t="n"/>
+      <c r="K28" s="559" t="n"/>
+      <c r="L28" s="559" t="n"/>
+      <c r="M28" s="559" t="n"/>
+      <c r="N28" s="559" t="n"/>
+      <c r="O28" s="559" t="n"/>
+      <c r="P28" s="559" t="n"/>
+      <c r="Q28" s="559" t="n"/>
+      <c r="R28" s="559" t="n"/>
+      <c r="S28" s="559" t="n"/>
+      <c r="T28" s="559" t="n"/>
+      <c r="U28" s="559" t="n"/>
+      <c r="V28" s="559" t="n"/>
+      <c r="W28" s="559" t="n"/>
+      <c r="X28" s="559" t="n"/>
+      <c r="Y28" s="559" t="n"/>
+      <c r="Z28" s="559" t="n"/>
+      <c r="AA28" s="569" t="n"/>
+      <c r="AB28" s="559" t="n"/>
+      <c r="AC28" s="559" t="n"/>
+      <c r="AD28" s="559" t="n"/>
+      <c r="AE28" s="559" t="n"/>
+      <c r="AF28" s="559" t="n"/>
+      <c r="AG28" s="559" t="n"/>
+      <c r="AH28" s="559" t="n"/>
+      <c r="AI28" s="559" t="n"/>
+      <c r="AJ28" s="559" t="n"/>
+      <c r="AK28" s="559" t="n"/>
+      <c r="AL28" s="559" t="n"/>
+      <c r="AM28" s="559" t="n"/>
+      <c r="AN28" s="559" t="n"/>
+      <c r="AO28" s="559" t="n"/>
+      <c r="AP28" s="559" t="n"/>
+      <c r="AQ28" s="559" t="n"/>
+      <c r="AR28" s="570" t="n"/>
+      <c r="AS28" s="559" t="n"/>
+      <c r="AT28" s="559" t="n"/>
+      <c r="AU28" s="559" t="n"/>
+      <c r="AV28" s="559" t="n"/>
+      <c r="AW28" s="559" t="n"/>
+      <c r="AX28" s="570" t="n"/>
+      <c r="AY28" s="559" t="n"/>
+      <c r="AZ28" s="559" t="n"/>
+      <c r="BA28" s="559" t="n"/>
+      <c r="BB28" s="571" t="n"/>
+      <c r="BC28" s="559" t="n"/>
+      <c r="BD28" s="559" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="466" t="inlineStr">
+      <c r="A29" s="540" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. PERIODIC REVIEW / CLOSEOUT</t>
         </is>
       </c>
-      <c r="B29" s="467" t="n"/>
-      <c r="C29" s="467" t="n"/>
-      <c r="D29" s="467" t="n"/>
-      <c r="E29" s="467" t="n"/>
-      <c r="F29" s="467" t="n"/>
-      <c r="G29" s="467" t="n"/>
-      <c r="H29" s="467" t="n"/>
-      <c r="I29" s="467" t="n"/>
-      <c r="J29" s="467" t="n"/>
-      <c r="K29" s="467" t="n"/>
-      <c r="L29" s="467" t="n"/>
-      <c r="M29" s="467" t="n"/>
-      <c r="N29" s="467" t="n"/>
-      <c r="O29" s="467" t="n"/>
-      <c r="P29" s="467" t="n"/>
-      <c r="Q29" s="467" t="n"/>
-      <c r="R29" s="467" t="n"/>
-      <c r="S29" s="467" t="n"/>
-      <c r="T29" s="467" t="n"/>
-      <c r="U29" s="467" t="n"/>
-      <c r="V29" s="467" t="n"/>
-      <c r="W29" s="467" t="n"/>
-      <c r="X29" s="467" t="n"/>
-      <c r="Y29" s="467" t="n"/>
-      <c r="Z29" s="467" t="n"/>
-      <c r="AA29" s="467" t="n"/>
-      <c r="AB29" s="467" t="n"/>
-      <c r="AC29" s="467" t="n"/>
-      <c r="AD29" s="467" t="n"/>
-      <c r="AE29" s="467" t="n"/>
-      <c r="AF29" s="467" t="n"/>
-      <c r="AG29" s="467" t="n"/>
-      <c r="AH29" s="467" t="n"/>
-      <c r="AI29" s="467" t="n"/>
-      <c r="AJ29" s="467" t="n"/>
-      <c r="AK29" s="467" t="n"/>
-      <c r="AL29" s="467" t="n"/>
-      <c r="AM29" s="467" t="n"/>
-      <c r="AN29" s="467" t="n"/>
-      <c r="AO29" s="467" t="n"/>
-      <c r="AP29" s="467" t="n"/>
-      <c r="AQ29" s="467" t="n"/>
-      <c r="AR29" s="467" t="n"/>
-      <c r="AS29" s="467" t="n"/>
-      <c r="AT29" s="467" t="n"/>
-      <c r="AU29" s="467" t="n"/>
-      <c r="AV29" s="467" t="n"/>
-      <c r="AW29" s="467" t="n"/>
-      <c r="AX29" s="467" t="n"/>
-      <c r="AY29" s="467" t="n"/>
-      <c r="AZ29" s="467" t="n"/>
-      <c r="BA29" s="467" t="n"/>
-      <c r="BB29" s="467" t="n"/>
-      <c r="BC29" s="467" t="n"/>
-      <c r="BD29" s="468" t="n"/>
+      <c r="B29" s="27" t="n"/>
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="27" t="n"/>
+      <c r="H29" s="27" t="n"/>
+      <c r="I29" s="27" t="n"/>
+      <c r="J29" s="27" t="n"/>
+      <c r="K29" s="27" t="n"/>
+      <c r="L29" s="27" t="n"/>
+      <c r="M29" s="27" t="n"/>
+      <c r="N29" s="27" t="n"/>
+      <c r="O29" s="27" t="n"/>
+      <c r="P29" s="27" t="n"/>
+      <c r="Q29" s="27" t="n"/>
+      <c r="R29" s="27" t="n"/>
+      <c r="S29" s="27" t="n"/>
+      <c r="T29" s="27" t="n"/>
+      <c r="U29" s="27" t="n"/>
+      <c r="V29" s="27" t="n"/>
+      <c r="W29" s="27" t="n"/>
+      <c r="X29" s="27" t="n"/>
+      <c r="Y29" s="27" t="n"/>
+      <c r="Z29" s="27" t="n"/>
+      <c r="AA29" s="27" t="n"/>
+      <c r="AB29" s="27" t="n"/>
+      <c r="AC29" s="27" t="n"/>
+      <c r="AD29" s="27" t="n"/>
+      <c r="AE29" s="27" t="n"/>
+      <c r="AF29" s="27" t="n"/>
+      <c r="AG29" s="27" t="n"/>
+      <c r="AH29" s="27" t="n"/>
+      <c r="AI29" s="27" t="n"/>
+      <c r="AJ29" s="27" t="n"/>
+      <c r="AK29" s="27" t="n"/>
+      <c r="AL29" s="27" t="n"/>
+      <c r="AM29" s="27" t="n"/>
+      <c r="AN29" s="27" t="n"/>
+      <c r="AO29" s="27" t="n"/>
+      <c r="AP29" s="27" t="n"/>
+      <c r="AQ29" s="27" t="n"/>
+      <c r="AR29" s="27" t="n"/>
+      <c r="AS29" s="27" t="n"/>
+      <c r="AT29" s="27" t="n"/>
+      <c r="AU29" s="27" t="n"/>
+      <c r="AV29" s="27" t="n"/>
+      <c r="AW29" s="27" t="n"/>
+      <c r="AX29" s="27" t="n"/>
+      <c r="AY29" s="27" t="n"/>
+      <c r="AZ29" s="27" t="n"/>
+      <c r="BA29" s="27" t="n"/>
+      <c r="BB29" s="27" t="n"/>
+      <c r="BC29" s="27" t="n"/>
+      <c r="BD29" s="28" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="469" t="inlineStr">
+      <c r="A30" s="541" t="inlineStr">
         <is>
           <t>Periodic Review Date</t>
         </is>
       </c>
-      <c r="B30" s="456" t="n"/>
-      <c r="C30" s="456" t="n"/>
-      <c r="D30" s="456" t="n"/>
-      <c r="E30" s="456" t="n"/>
-      <c r="F30" s="456" t="n"/>
-      <c r="G30" s="456" t="n"/>
-      <c r="H30" s="456" t="n"/>
-      <c r="I30" s="456" t="n"/>
-      <c r="J30" s="456" t="n"/>
-      <c r="K30" s="481" t="n"/>
-      <c r="L30" s="482" t="n"/>
-      <c r="M30" s="482" t="n"/>
-      <c r="N30" s="482" t="n"/>
-      <c r="O30" s="482" t="n"/>
-      <c r="P30" s="482" t="n"/>
-      <c r="Q30" s="482" t="n"/>
-      <c r="R30" s="482" t="n"/>
-      <c r="S30" s="482" t="n"/>
-      <c r="T30" s="482" t="n"/>
-      <c r="U30" s="482" t="n"/>
-      <c r="V30" s="482" t="n"/>
-      <c r="W30" s="482" t="n"/>
-      <c r="X30" s="482" t="n"/>
-      <c r="Y30" s="482" t="n"/>
-      <c r="Z30" s="482" t="n"/>
-      <c r="AA30" s="482" t="n"/>
-      <c r="AB30" s="482" t="n"/>
-      <c r="AC30" s="471" t="inlineStr">
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="542" t="n"/>
+      <c r="L30" s="543" t="n"/>
+      <c r="M30" s="543" t="n"/>
+      <c r="N30" s="543" t="n"/>
+      <c r="O30" s="543" t="n"/>
+      <c r="P30" s="543" t="n"/>
+      <c r="Q30" s="543" t="n"/>
+      <c r="R30" s="543" t="n"/>
+      <c r="S30" s="543" t="n"/>
+      <c r="T30" s="543" t="n"/>
+      <c r="U30" s="543" t="n"/>
+      <c r="V30" s="543" t="n"/>
+      <c r="W30" s="543" t="n"/>
+      <c r="X30" s="543" t="n"/>
+      <c r="Y30" s="543" t="n"/>
+      <c r="Z30" s="543" t="n"/>
+      <c r="AA30" s="543" t="n"/>
+      <c r="AB30" s="544" t="n"/>
+      <c r="AC30" s="545" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="AD30" s="456" t="n"/>
-      <c r="AE30" s="456" t="n"/>
-      <c r="AF30" s="456" t="n"/>
-      <c r="AG30" s="456" t="n"/>
-      <c r="AH30" s="456" t="n"/>
-      <c r="AI30" s="456" t="n"/>
-      <c r="AJ30" s="456" t="n"/>
-      <c r="AK30" s="456" t="n"/>
-      <c r="AL30" s="456" t="n"/>
-      <c r="AM30" s="481" t="n"/>
-      <c r="AN30" s="482" t="n"/>
-      <c r="AO30" s="482" t="n"/>
-      <c r="AP30" s="482" t="n"/>
-      <c r="AQ30" s="482" t="n"/>
-      <c r="AR30" s="482" t="n"/>
-      <c r="AS30" s="482" t="n"/>
-      <c r="AT30" s="482" t="n"/>
-      <c r="AU30" s="482" t="n"/>
-      <c r="AV30" s="482" t="n"/>
-      <c r="AW30" s="482" t="n"/>
-      <c r="AX30" s="482" t="n"/>
-      <c r="AY30" s="482" t="n"/>
-      <c r="AZ30" s="482" t="n"/>
-      <c r="BA30" s="482" t="n"/>
-      <c r="BB30" s="482" t="n"/>
-      <c r="BC30" s="482" t="n"/>
-      <c r="BD30" s="483" t="n"/>
+      <c r="AD30" s="5" t="n"/>
+      <c r="AE30" s="5" t="n"/>
+      <c r="AF30" s="5" t="n"/>
+      <c r="AG30" s="5" t="n"/>
+      <c r="AH30" s="5" t="n"/>
+      <c r="AI30" s="5" t="n"/>
+      <c r="AJ30" s="5" t="n"/>
+      <c r="AK30" s="5" t="n"/>
+      <c r="AL30" s="6" t="n"/>
+      <c r="AM30" s="542" t="n"/>
+      <c r="AN30" s="543" t="n"/>
+      <c r="AO30" s="543" t="n"/>
+      <c r="AP30" s="543" t="n"/>
+      <c r="AQ30" s="543" t="n"/>
+      <c r="AR30" s="543" t="n"/>
+      <c r="AS30" s="543" t="n"/>
+      <c r="AT30" s="543" t="n"/>
+      <c r="AU30" s="543" t="n"/>
+      <c r="AV30" s="543" t="n"/>
+      <c r="AW30" s="543" t="n"/>
+      <c r="AX30" s="543" t="n"/>
+      <c r="AY30" s="543" t="n"/>
+      <c r="AZ30" s="543" t="n"/>
+      <c r="BA30" s="543" t="n"/>
+      <c r="BB30" s="543" t="n"/>
+      <c r="BC30" s="543" t="n"/>
+      <c r="BD30" s="546" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="486" t="inlineStr">
+      <c r="A31" s="553" t="inlineStr">
         <is>
           <t>Suspect / Hold Items</t>
         </is>
       </c>
-      <c r="B31" s="487" t="n"/>
-      <c r="C31" s="487" t="n"/>
-      <c r="D31" s="487" t="n"/>
-      <c r="E31" s="487" t="n"/>
-      <c r="F31" s="487" t="n"/>
-      <c r="G31" s="487" t="n"/>
-      <c r="H31" s="487" t="n"/>
-      <c r="I31" s="487" t="n"/>
-      <c r="J31" s="487" t="n"/>
-      <c r="K31" s="488" t="n"/>
-      <c r="L31" s="489" t="n"/>
-      <c r="M31" s="489" t="n"/>
-      <c r="N31" s="489" t="n"/>
-      <c r="O31" s="489" t="n"/>
-      <c r="P31" s="489" t="n"/>
-      <c r="Q31" s="489" t="n"/>
-      <c r="R31" s="489" t="n"/>
-      <c r="S31" s="489" t="n"/>
-      <c r="T31" s="489" t="n"/>
-      <c r="U31" s="489" t="n"/>
-      <c r="V31" s="489" t="n"/>
-      <c r="W31" s="489" t="n"/>
-      <c r="X31" s="489" t="n"/>
-      <c r="Y31" s="489" t="n"/>
-      <c r="Z31" s="489" t="n"/>
-      <c r="AA31" s="489" t="n"/>
-      <c r="AB31" s="489" t="n"/>
-      <c r="AC31" s="490" t="inlineStr">
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="n"/>
+      <c r="I31" s="19" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="554" t="n"/>
+      <c r="L31" s="555" t="n"/>
+      <c r="M31" s="555" t="n"/>
+      <c r="N31" s="555" t="n"/>
+      <c r="O31" s="555" t="n"/>
+      <c r="P31" s="555" t="n"/>
+      <c r="Q31" s="555" t="n"/>
+      <c r="R31" s="555" t="n"/>
+      <c r="S31" s="555" t="n"/>
+      <c r="T31" s="555" t="n"/>
+      <c r="U31" s="555" t="n"/>
+      <c r="V31" s="555" t="n"/>
+      <c r="W31" s="555" t="n"/>
+      <c r="X31" s="555" t="n"/>
+      <c r="Y31" s="555" t="n"/>
+      <c r="Z31" s="555" t="n"/>
+      <c r="AA31" s="555" t="n"/>
+      <c r="AB31" s="556" t="n"/>
+      <c r="AC31" s="557" t="inlineStr">
         <is>
           <t>Final Status</t>
         </is>
       </c>
-      <c r="AD31" s="487" t="n"/>
-      <c r="AE31" s="487" t="n"/>
-      <c r="AF31" s="487" t="n"/>
-      <c r="AG31" s="487" t="n"/>
-      <c r="AH31" s="487" t="n"/>
-      <c r="AI31" s="487" t="n"/>
-      <c r="AJ31" s="487" t="n"/>
-      <c r="AK31" s="487" t="n"/>
-      <c r="AL31" s="487" t="n"/>
-      <c r="AM31" s="488" t="n"/>
-      <c r="AN31" s="489" t="n"/>
-      <c r="AO31" s="489" t="n"/>
-      <c r="AP31" s="489" t="n"/>
-      <c r="AQ31" s="489" t="n"/>
-      <c r="AR31" s="489" t="n"/>
-      <c r="AS31" s="489" t="n"/>
-      <c r="AT31" s="489" t="n"/>
-      <c r="AU31" s="489" t="n"/>
-      <c r="AV31" s="489" t="n"/>
-      <c r="AW31" s="489" t="n"/>
-      <c r="AX31" s="489" t="n"/>
-      <c r="AY31" s="489" t="n"/>
-      <c r="AZ31" s="489" t="n"/>
-      <c r="BA31" s="489" t="n"/>
-      <c r="BB31" s="489" t="n"/>
-      <c r="BC31" s="489" t="n"/>
-      <c r="BD31" s="491" t="n"/>
+      <c r="AD31" s="19" t="n"/>
+      <c r="AE31" s="19" t="n"/>
+      <c r="AF31" s="19" t="n"/>
+      <c r="AG31" s="19" t="n"/>
+      <c r="AH31" s="19" t="n"/>
+      <c r="AI31" s="19" t="n"/>
+      <c r="AJ31" s="19" t="n"/>
+      <c r="AK31" s="19" t="n"/>
+      <c r="AL31" s="22" t="n"/>
+      <c r="AM31" s="554" t="n"/>
+      <c r="AN31" s="555" t="n"/>
+      <c r="AO31" s="555" t="n"/>
+      <c r="AP31" s="555" t="n"/>
+      <c r="AQ31" s="555" t="n"/>
+      <c r="AR31" s="555" t="n"/>
+      <c r="AS31" s="555" t="n"/>
+      <c r="AT31" s="555" t="n"/>
+      <c r="AU31" s="555" t="n"/>
+      <c r="AV31" s="555" t="n"/>
+      <c r="AW31" s="555" t="n"/>
+      <c r="AX31" s="555" t="n"/>
+      <c r="AY31" s="555" t="n"/>
+      <c r="AZ31" s="555" t="n"/>
+      <c r="BA31" s="555" t="n"/>
+      <c r="BB31" s="555" t="n"/>
+      <c r="BC31" s="555" t="n"/>
+      <c r="BD31" s="558" t="n"/>
     </row>
     <row r="32" ht="3" customHeight="1">
-      <c r="A32" s="345" t="n"/>
-      <c r="B32" s="345" t="n"/>
-      <c r="C32" s="345" t="n"/>
-      <c r="D32" s="345" t="n"/>
-      <c r="E32" s="345" t="n"/>
-      <c r="F32" s="345" t="n"/>
-      <c r="G32" s="345" t="n"/>
-      <c r="H32" s="345" t="n"/>
-      <c r="I32" s="345" t="n"/>
-      <c r="J32" s="345" t="n"/>
-      <c r="K32" s="345" t="n"/>
-      <c r="L32" s="345" t="n"/>
-      <c r="M32" s="345" t="n"/>
-      <c r="N32" s="345" t="n"/>
-      <c r="O32" s="345" t="n"/>
-      <c r="P32" s="345" t="n"/>
-      <c r="Q32" s="345" t="n"/>
-      <c r="R32" s="345" t="n"/>
-      <c r="S32" s="345" t="n"/>
-      <c r="T32" s="345" t="n"/>
-      <c r="U32" s="345" t="n"/>
-      <c r="V32" s="345" t="n"/>
-      <c r="W32" s="345" t="n"/>
-      <c r="X32" s="345" t="n"/>
-      <c r="Y32" s="345" t="n"/>
-      <c r="Z32" s="345" t="n"/>
-      <c r="AA32" s="345" t="n"/>
-      <c r="AB32" s="345" t="n"/>
-      <c r="AC32" s="345" t="n"/>
-      <c r="AD32" s="345" t="n"/>
-      <c r="AE32" s="345" t="n"/>
-      <c r="AF32" s="345" t="n"/>
-      <c r="AG32" s="345" t="n"/>
-      <c r="AH32" s="345" t="n"/>
-      <c r="AI32" s="345" t="n"/>
-      <c r="AJ32" s="345" t="n"/>
-      <c r="AK32" s="345" t="n"/>
-      <c r="AL32" s="345" t="n"/>
-      <c r="AM32" s="345" t="n"/>
-      <c r="AN32" s="345" t="n"/>
-      <c r="AO32" s="345" t="n"/>
-      <c r="AP32" s="345" t="n"/>
-      <c r="AQ32" s="345" t="n"/>
-      <c r="AR32" s="345" t="n"/>
-      <c r="AS32" s="345" t="n"/>
-      <c r="AT32" s="345" t="n"/>
-      <c r="AU32" s="345" t="n"/>
-      <c r="AV32" s="345" t="n"/>
-      <c r="AW32" s="345" t="n"/>
-      <c r="AX32" s="345" t="n"/>
-      <c r="AY32" s="345" t="n"/>
-      <c r="AZ32" s="345" t="n"/>
-      <c r="BA32" s="345" t="n"/>
-      <c r="BB32" s="345" t="n"/>
-      <c r="BC32" s="345" t="n"/>
-      <c r="BD32" s="345" t="n"/>
+      <c r="A32" s="559" t="n"/>
+      <c r="B32" s="559" t="n"/>
+      <c r="C32" s="559" t="n"/>
+      <c r="D32" s="559" t="n"/>
+      <c r="E32" s="559" t="n"/>
+      <c r="F32" s="559" t="n"/>
+      <c r="G32" s="559" t="n"/>
+      <c r="H32" s="559" t="n"/>
+      <c r="I32" s="559" t="n"/>
+      <c r="J32" s="559" t="n"/>
+      <c r="K32" s="559" t="n"/>
+      <c r="L32" s="559" t="n"/>
+      <c r="M32" s="559" t="n"/>
+      <c r="N32" s="559" t="n"/>
+      <c r="O32" s="559" t="n"/>
+      <c r="P32" s="559" t="n"/>
+      <c r="Q32" s="559" t="n"/>
+      <c r="R32" s="559" t="n"/>
+      <c r="S32" s="559" t="n"/>
+      <c r="T32" s="559" t="n"/>
+      <c r="U32" s="559" t="n"/>
+      <c r="V32" s="559" t="n"/>
+      <c r="W32" s="559" t="n"/>
+      <c r="X32" s="559" t="n"/>
+      <c r="Y32" s="559" t="n"/>
+      <c r="Z32" s="559" t="n"/>
+      <c r="AA32" s="559" t="n"/>
+      <c r="AB32" s="559" t="n"/>
+      <c r="AC32" s="559" t="n"/>
+      <c r="AD32" s="559" t="n"/>
+      <c r="AE32" s="559" t="n"/>
+      <c r="AF32" s="559" t="n"/>
+      <c r="AG32" s="559" t="n"/>
+      <c r="AH32" s="559" t="n"/>
+      <c r="AI32" s="559" t="n"/>
+      <c r="AJ32" s="559" t="n"/>
+      <c r="AK32" s="559" t="n"/>
+      <c r="AL32" s="559" t="n"/>
+      <c r="AM32" s="559" t="n"/>
+      <c r="AN32" s="559" t="n"/>
+      <c r="AO32" s="559" t="n"/>
+      <c r="AP32" s="559" t="n"/>
+      <c r="AQ32" s="559" t="n"/>
+      <c r="AR32" s="559" t="n"/>
+      <c r="AS32" s="559" t="n"/>
+      <c r="AT32" s="559" t="n"/>
+      <c r="AU32" s="559" t="n"/>
+      <c r="AV32" s="559" t="n"/>
+      <c r="AW32" s="559" t="n"/>
+      <c r="AX32" s="559" t="n"/>
+      <c r="AY32" s="559" t="n"/>
+      <c r="AZ32" s="559" t="n"/>
+      <c r="BA32" s="559" t="n"/>
+      <c r="BB32" s="559" t="n"/>
+      <c r="BC32" s="559" t="n"/>
+      <c r="BD32" s="559" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="499" t="inlineStr">
+      <c r="A33" s="572" t="inlineStr">
         <is>
           <t>NOTICE: Review face only. Complete row-level entry, filters and frozen-header operations on sheet GAGE_DATA_LOG. Keep English only, preserve history, record owner and evidence reference, and follow controlled dropdowns / gate rules.</t>
         </is>
       </c>
-      <c r="B33" s="500" t="n"/>
-      <c r="C33" s="500" t="n"/>
-      <c r="D33" s="500" t="n"/>
-      <c r="E33" s="500" t="n"/>
-      <c r="F33" s="500" t="n"/>
-      <c r="G33" s="500" t="n"/>
-      <c r="H33" s="500" t="n"/>
-      <c r="I33" s="500" t="n"/>
-      <c r="J33" s="500" t="n"/>
-      <c r="K33" s="500" t="n"/>
-      <c r="L33" s="500" t="n"/>
-      <c r="M33" s="500" t="n"/>
-      <c r="N33" s="500" t="n"/>
-      <c r="O33" s="500" t="n"/>
-      <c r="P33" s="500" t="n"/>
-      <c r="Q33" s="500" t="n"/>
-      <c r="R33" s="500" t="n"/>
-      <c r="S33" s="500" t="n"/>
-      <c r="T33" s="500" t="n"/>
-      <c r="U33" s="500" t="n"/>
-      <c r="V33" s="500" t="n"/>
-      <c r="W33" s="500" t="n"/>
-      <c r="X33" s="500" t="n"/>
-      <c r="Y33" s="500" t="n"/>
-      <c r="Z33" s="500" t="n"/>
-      <c r="AA33" s="500" t="n"/>
-      <c r="AB33" s="500" t="n"/>
-      <c r="AC33" s="500" t="n"/>
-      <c r="AD33" s="500" t="n"/>
-      <c r="AE33" s="500" t="n"/>
-      <c r="AF33" s="500" t="n"/>
-      <c r="AG33" s="500" t="n"/>
-      <c r="AH33" s="500" t="n"/>
-      <c r="AI33" s="500" t="n"/>
-      <c r="AJ33" s="500" t="n"/>
-      <c r="AK33" s="500" t="n"/>
-      <c r="AL33" s="500" t="n"/>
-      <c r="AM33" s="500" t="n"/>
-      <c r="AN33" s="500" t="n"/>
-      <c r="AO33" s="500" t="n"/>
-      <c r="AP33" s="500" t="n"/>
-      <c r="AQ33" s="500" t="n"/>
-      <c r="AR33" s="500" t="n"/>
-      <c r="AS33" s="500" t="n"/>
-      <c r="AT33" s="500" t="n"/>
-      <c r="AU33" s="500" t="n"/>
-      <c r="AV33" s="500" t="n"/>
-      <c r="AW33" s="500" t="n"/>
-      <c r="AX33" s="500" t="n"/>
-      <c r="AY33" s="500" t="n"/>
-      <c r="AZ33" s="500" t="n"/>
-      <c r="BA33" s="500" t="n"/>
-      <c r="BB33" s="500" t="n"/>
-      <c r="BC33" s="500" t="n"/>
-      <c r="BD33" s="501" t="n"/>
+      <c r="B33" s="27" t="n"/>
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="27" t="n"/>
+      <c r="E33" s="27" t="n"/>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="27" t="n"/>
+      <c r="H33" s="27" t="n"/>
+      <c r="I33" s="27" t="n"/>
+      <c r="J33" s="27" t="n"/>
+      <c r="K33" s="27" t="n"/>
+      <c r="L33" s="27" t="n"/>
+      <c r="M33" s="27" t="n"/>
+      <c r="N33" s="27" t="n"/>
+      <c r="O33" s="27" t="n"/>
+      <c r="P33" s="27" t="n"/>
+      <c r="Q33" s="27" t="n"/>
+      <c r="R33" s="27" t="n"/>
+      <c r="S33" s="27" t="n"/>
+      <c r="T33" s="27" t="n"/>
+      <c r="U33" s="27" t="n"/>
+      <c r="V33" s="27" t="n"/>
+      <c r="W33" s="27" t="n"/>
+      <c r="X33" s="27" t="n"/>
+      <c r="Y33" s="27" t="n"/>
+      <c r="Z33" s="27" t="n"/>
+      <c r="AA33" s="27" t="n"/>
+      <c r="AB33" s="27" t="n"/>
+      <c r="AC33" s="27" t="n"/>
+      <c r="AD33" s="27" t="n"/>
+      <c r="AE33" s="27" t="n"/>
+      <c r="AF33" s="27" t="n"/>
+      <c r="AG33" s="27" t="n"/>
+      <c r="AH33" s="27" t="n"/>
+      <c r="AI33" s="27" t="n"/>
+      <c r="AJ33" s="27" t="n"/>
+      <c r="AK33" s="27" t="n"/>
+      <c r="AL33" s="27" t="n"/>
+      <c r="AM33" s="27" t="n"/>
+      <c r="AN33" s="27" t="n"/>
+      <c r="AO33" s="27" t="n"/>
+      <c r="AP33" s="27" t="n"/>
+      <c r="AQ33" s="27" t="n"/>
+      <c r="AR33" s="27" t="n"/>
+      <c r="AS33" s="27" t="n"/>
+      <c r="AT33" s="27" t="n"/>
+      <c r="AU33" s="27" t="n"/>
+      <c r="AV33" s="27" t="n"/>
+      <c r="AW33" s="27" t="n"/>
+      <c r="AX33" s="27" t="n"/>
+      <c r="AY33" s="27" t="n"/>
+      <c r="AZ33" s="27" t="n"/>
+      <c r="BA33" s="27" t="n"/>
+      <c r="BB33" s="27" t="n"/>
+      <c r="BC33" s="27" t="n"/>
+      <c r="BD33" s="28" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1"/>
     <row r="35" ht="20" customHeight="1"/>
@@ -10169,9 +10760,9 @@
   <mergeCells count="189">
     <mergeCell ref="AP27:AS27"/>
     <mergeCell ref="AH26:AK26"/>
+    <mergeCell ref="AA18:AG18"/>
+    <mergeCell ref="AL17:AO17"/>
     <mergeCell ref="AW2:BD2"/>
-    <mergeCell ref="AL17:AO17"/>
-    <mergeCell ref="AA18:AG18"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="AP17:AS17"/>
     <mergeCell ref="A21:C21"/>
@@ -10361,7 +10952,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"-,Regular"&amp;7 FRM-602  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
+    <oddFooter>&amp;C&amp;"Segoe UI"&amp;7 FRM-602  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -10377,7 +10968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:CU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10712,7 +11303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:CU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10763,12 +11354,12 @@
           <t>Periodic Review Summary</t>
         </is>
       </c>
-      <c r="B1" s="409" t="n"/>
-      <c r="C1" s="409" t="n"/>
-      <c r="D1" s="409" t="n"/>
-      <c r="E1" s="409" t="n"/>
-      <c r="F1" s="409" t="n"/>
-      <c r="G1" s="409" t="n"/>
+      <c r="B1" s="520" t="n"/>
+      <c r="C1" s="520" t="n"/>
+      <c r="D1" s="520" t="n"/>
+      <c r="E1" s="520" t="n"/>
+      <c r="F1" s="520" t="n"/>
+      <c r="G1" s="520" t="n"/>
       <c r="H1" s="503" t="n"/>
       <c r="I1" s="411" t="n"/>
       <c r="J1" s="412" t="n"/>
@@ -10809,12 +11400,6 @@
           <t>Pre-use gage-verification gate before FRM-621/631/641 inspection execution and before Pack A first-piece/release decisions. Formal MSA remains in FRM-611/612/613.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="434" t="n"/>
       <c r="I2" s="422" t="n"/>
       <c r="J2" s="423" t="n"/>
@@ -11214,7 +11799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:CU15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -11265,12 +11850,12 @@
           <t>Import / Reference Guidance</t>
         </is>
       </c>
-      <c r="B1" s="409" t="n"/>
-      <c r="C1" s="409" t="n"/>
-      <c r="D1" s="409" t="n"/>
-      <c r="E1" s="409" t="n"/>
-      <c r="F1" s="409" t="n"/>
-      <c r="G1" s="409" t="n"/>
+      <c r="B1" s="520" t="n"/>
+      <c r="C1" s="520" t="n"/>
+      <c r="D1" s="520" t="n"/>
+      <c r="E1" s="520" t="n"/>
+      <c r="F1" s="520" t="n"/>
+      <c r="G1" s="520" t="n"/>
       <c r="H1" s="503" t="n"/>
       <c r="I1" s="411" t="n"/>
       <c r="J1" s="412" t="n"/>
@@ -11311,12 +11896,6 @@
           <t>Import or reference keys from Epicor / M365 / calibration master rather than re-keying duplicates.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="434" t="n"/>
       <c r="I2" s="422" t="n"/>
       <c r="J2" s="423" t="n"/>
@@ -12063,7 +12642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:CU15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -12114,12 +12693,12 @@
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="409" t="n"/>
-      <c r="C1" s="409" t="n"/>
-      <c r="D1" s="409" t="n"/>
-      <c r="E1" s="409" t="n"/>
-      <c r="F1" s="409" t="n"/>
-      <c r="G1" s="409" t="n"/>
+      <c r="B1" s="520" t="n"/>
+      <c r="C1" s="520" t="n"/>
+      <c r="D1" s="520" t="n"/>
+      <c r="E1" s="520" t="n"/>
+      <c r="F1" s="520" t="n"/>
+      <c r="G1" s="520" t="n"/>
       <c r="H1" s="503" t="n"/>
       <c r="I1" s="411" t="n"/>
       <c r="J1" s="412" t="n"/>
@@ -12160,12 +12739,6 @@
           <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="434" t="n"/>
       <c r="I2" s="422" t="n"/>
       <c r="J2" s="423" t="n"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAGE_DATA_LOG" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAGE_VERIFY_LOG" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW_SUMMARY" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_REF" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="3" state="veryHidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW_SUMMARY" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="6" state="veryHidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'GAGE_DATA_LOG'!$A$1:$K$42</definedName>
@@ -773,7 +773,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="360">
+  <borders count="367">
     <border>
       <left/>
       <right/>
@@ -4650,11 +4650,97 @@
         <color rgb="000078D4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="573">
+  <cellXfs count="616">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6039,6 +6125,125 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="85" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="270" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="361" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="359" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="365" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="136" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -6173,6 +6378,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6588,7 +6796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CU42"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -8660,346 +8868,229 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="524" t="inlineStr"/>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="53" t="n"/>
+      <c r="A1" s="573" t="inlineStr"/>
+      <c r="B1" s="268" t="n"/>
+      <c r="C1" s="268" t="n"/>
+      <c r="D1" s="268" t="n"/>
+      <c r="E1" s="268" t="n"/>
+      <c r="F1" s="268" t="n"/>
+      <c r="G1" s="268" t="n"/>
+      <c r="H1" s="268" t="n"/>
+      <c r="I1" s="268" t="n"/>
+      <c r="J1" s="268" t="n"/>
+      <c r="K1" s="574" t="n"/>
       <c r="L1" s="525" t="inlineStr">
         <is>
           <t>Gage Verification Log</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-      <c r="W1" s="2" t="n"/>
-      <c r="X1" s="2" t="n"/>
-      <c r="Y1" s="2" t="n"/>
-      <c r="Z1" s="2" t="n"/>
-      <c r="AA1" s="2" t="n"/>
-      <c r="AB1" s="2" t="n"/>
-      <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="2" t="n"/>
-      <c r="AE1" s="2" t="n"/>
-      <c r="AF1" s="2" t="n"/>
-      <c r="AG1" s="2" t="n"/>
-      <c r="AH1" s="2" t="n"/>
-      <c r="AI1" s="2" t="n"/>
-      <c r="AJ1" s="2" t="n"/>
-      <c r="AK1" s="2" t="n"/>
-      <c r="AL1" s="2" t="n"/>
-      <c r="AM1" s="2" t="n"/>
-      <c r="AN1" s="2" t="n"/>
-      <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
-      <c r="AQ1" s="526" t="inlineStr">
+      <c r="M1" s="268" t="n"/>
+      <c r="N1" s="268" t="n"/>
+      <c r="O1" s="268" t="n"/>
+      <c r="P1" s="268" t="n"/>
+      <c r="Q1" s="268" t="n"/>
+      <c r="R1" s="268" t="n"/>
+      <c r="S1" s="268" t="n"/>
+      <c r="T1" s="268" t="n"/>
+      <c r="U1" s="268" t="n"/>
+      <c r="V1" s="268" t="n"/>
+      <c r="W1" s="268" t="n"/>
+      <c r="X1" s="268" t="n"/>
+      <c r="Y1" s="268" t="n"/>
+      <c r="Z1" s="268" t="n"/>
+      <c r="AA1" s="268" t="n"/>
+      <c r="AB1" s="268" t="n"/>
+      <c r="AC1" s="268" t="n"/>
+      <c r="AD1" s="268" t="n"/>
+      <c r="AE1" s="268" t="n"/>
+      <c r="AF1" s="268" t="n"/>
+      <c r="AG1" s="268" t="n"/>
+      <c r="AH1" s="268" t="n"/>
+      <c r="AI1" s="268" t="n"/>
+      <c r="AJ1" s="268" t="n"/>
+      <c r="AK1" s="268" t="n"/>
+      <c r="AL1" s="268" t="n"/>
+      <c r="AM1" s="268" t="n"/>
+      <c r="AN1" s="268" t="n"/>
+      <c r="AO1" s="268" t="n"/>
+      <c r="AP1" s="268" t="n"/>
+      <c r="AQ1" s="575" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="2" t="n"/>
-      <c r="AS1" s="2" t="n"/>
-      <c r="AT1" s="2" t="n"/>
-      <c r="AU1" s="2" t="n"/>
-      <c r="AV1" s="527" t="n"/>
-      <c r="AW1" s="528" t="inlineStr">
+      <c r="AR1" s="268" t="n"/>
+      <c r="AS1" s="268" t="n"/>
+      <c r="AT1" s="268" t="n"/>
+      <c r="AU1" s="268" t="n"/>
+      <c r="AV1" s="576" t="n"/>
+      <c r="AW1" s="577" t="inlineStr">
         <is>
           <t>FRM-602</t>
         </is>
       </c>
-      <c r="AX1" s="2" t="n"/>
-      <c r="AY1" s="2" t="n"/>
-      <c r="AZ1" s="2" t="n"/>
-      <c r="BA1" s="2" t="n"/>
-      <c r="BB1" s="2" t="n"/>
-      <c r="BC1" s="2" t="n"/>
-      <c r="BD1" s="53" t="n"/>
+      <c r="AX1" s="268" t="n"/>
+      <c r="AY1" s="268" t="n"/>
+      <c r="AZ1" s="268" t="n"/>
+      <c r="BA1" s="268" t="n"/>
+      <c r="BB1" s="268" t="n"/>
+      <c r="BC1" s="268" t="n"/>
+      <c r="BD1" s="574" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="54" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="10" t="n"/>
-      <c r="AE2" s="10" t="n"/>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="10" t="n"/>
-      <c r="AI2" s="10" t="n"/>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="10" t="n"/>
-      <c r="AO2" s="10" t="n"/>
-      <c r="AP2" s="10" t="n"/>
-      <c r="AQ2" s="529" t="inlineStr">
+      <c r="A2" s="275" t="n"/>
+      <c r="K2" s="578" t="n"/>
+      <c r="L2" s="275" t="n"/>
+      <c r="AQ2" s="579" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="530" t="n"/>
-      <c r="AS2" s="530" t="n"/>
-      <c r="AT2" s="530" t="n"/>
-      <c r="AU2" s="530" t="n"/>
-      <c r="AV2" s="531" t="n"/>
-      <c r="AW2" s="532" t="inlineStr">
+      <c r="AR2" s="580" t="n"/>
+      <c r="AS2" s="580" t="n"/>
+      <c r="AT2" s="580" t="n"/>
+      <c r="AU2" s="580" t="n"/>
+      <c r="AV2" s="581" t="n"/>
+      <c r="AW2" s="582" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="530" t="n"/>
-      <c r="AY2" s="530" t="n"/>
-      <c r="AZ2" s="530" t="n"/>
-      <c r="BA2" s="530" t="n"/>
-      <c r="BB2" s="530" t="n"/>
-      <c r="BC2" s="530" t="n"/>
-      <c r="BD2" s="533" t="n"/>
+      <c r="AX2" s="580" t="n"/>
+      <c r="AY2" s="580" t="n"/>
+      <c r="AZ2" s="580" t="n"/>
+      <c r="BA2" s="580" t="n"/>
+      <c r="BB2" s="580" t="n"/>
+      <c r="BC2" s="580" t="n"/>
+      <c r="BD2" s="583" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="54" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="10" t="n"/>
-      <c r="AE3" s="10" t="n"/>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="10" t="n"/>
-      <c r="AI3" s="10" t="n"/>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="10" t="n"/>
-      <c r="AO3" s="10" t="n"/>
-      <c r="AP3" s="10" t="n"/>
-      <c r="AQ3" s="529" t="inlineStr">
+      <c r="A3" s="275" t="n"/>
+      <c r="K3" s="578" t="n"/>
+      <c r="L3" s="275" t="n"/>
+      <c r="AQ3" s="579" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="530" t="n"/>
-      <c r="AS3" s="530" t="n"/>
-      <c r="AT3" s="530" t="n"/>
-      <c r="AU3" s="530" t="n"/>
-      <c r="AV3" s="531" t="n"/>
-      <c r="AW3" s="532" t="inlineStr">
+      <c r="AR3" s="580" t="n"/>
+      <c r="AS3" s="580" t="n"/>
+      <c r="AT3" s="580" t="n"/>
+      <c r="AU3" s="580" t="n"/>
+      <c r="AV3" s="581" t="n"/>
+      <c r="AW3" s="582" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="530" t="n"/>
-      <c r="AY3" s="530" t="n"/>
-      <c r="AZ3" s="530" t="n"/>
-      <c r="BA3" s="530" t="n"/>
-      <c r="BB3" s="530" t="n"/>
-      <c r="BC3" s="530" t="n"/>
-      <c r="BD3" s="533" t="n"/>
+      <c r="AX3" s="580" t="n"/>
+      <c r="AY3" s="580" t="n"/>
+      <c r="AZ3" s="580" t="n"/>
+      <c r="BA3" s="580" t="n"/>
+      <c r="BB3" s="580" t="n"/>
+      <c r="BC3" s="580" t="n"/>
+      <c r="BD3" s="583" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n"/>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="54" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="K4" s="578" t="n"/>
       <c r="L4" s="534" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="10" t="n"/>
-      <c r="AE4" s="10" t="n"/>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="10" t="n"/>
-      <c r="AI4" s="10" t="n"/>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="10" t="n"/>
-      <c r="AO4" s="10" t="n"/>
-      <c r="AP4" s="10" t="n"/>
-      <c r="AQ4" s="529" t="inlineStr">
+      <c r="AQ4" s="579" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="530" t="n"/>
-      <c r="AS4" s="530" t="n"/>
-      <c r="AT4" s="530" t="n"/>
-      <c r="AU4" s="530" t="n"/>
-      <c r="AV4" s="531" t="n"/>
-      <c r="AW4" s="532" t="inlineStr">
+      <c r="AR4" s="580" t="n"/>
+      <c r="AS4" s="580" t="n"/>
+      <c r="AT4" s="580" t="n"/>
+      <c r="AU4" s="580" t="n"/>
+      <c r="AV4" s="581" t="n"/>
+      <c r="AW4" s="582" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="530" t="n"/>
-      <c r="AY4" s="530" t="n"/>
-      <c r="AZ4" s="530" t="n"/>
-      <c r="BA4" s="530" t="n"/>
-      <c r="BB4" s="530" t="n"/>
-      <c r="BC4" s="530" t="n"/>
-      <c r="BD4" s="533" t="n"/>
+      <c r="AX4" s="580" t="n"/>
+      <c r="AY4" s="580" t="n"/>
+      <c r="AZ4" s="580" t="n"/>
+      <c r="BA4" s="580" t="n"/>
+      <c r="BB4" s="580" t="n"/>
+      <c r="BC4" s="580" t="n"/>
+      <c r="BD4" s="583" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="19" t="n"/>
-      <c r="I5" s="19" t="n"/>
-      <c r="J5" s="19" t="n"/>
-      <c r="K5" s="24" t="n"/>
+      <c r="A5" s="280" t="n"/>
+      <c r="B5" s="281" t="n"/>
+      <c r="C5" s="281" t="n"/>
+      <c r="D5" s="281" t="n"/>
+      <c r="E5" s="281" t="n"/>
+      <c r="F5" s="281" t="n"/>
+      <c r="G5" s="281" t="n"/>
+      <c r="H5" s="281" t="n"/>
+      <c r="I5" s="281" t="n"/>
+      <c r="J5" s="281" t="n"/>
+      <c r="K5" s="283" t="n"/>
       <c r="L5" s="20" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="19" t="n"/>
-      <c r="N5" s="19" t="n"/>
-      <c r="O5" s="19" t="n"/>
-      <c r="P5" s="19" t="n"/>
-      <c r="Q5" s="19" t="n"/>
-      <c r="R5" s="19" t="n"/>
-      <c r="S5" s="19" t="n"/>
-      <c r="T5" s="19" t="n"/>
-      <c r="U5" s="19" t="n"/>
-      <c r="V5" s="19" t="n"/>
-      <c r="W5" s="19" t="n"/>
-      <c r="X5" s="19" t="n"/>
-      <c r="Y5" s="19" t="n"/>
-      <c r="Z5" s="19" t="n"/>
-      <c r="AA5" s="19" t="n"/>
-      <c r="AB5" s="19" t="n"/>
-      <c r="AC5" s="19" t="n"/>
-      <c r="AD5" s="19" t="n"/>
-      <c r="AE5" s="19" t="n"/>
-      <c r="AF5" s="19" t="n"/>
-      <c r="AG5" s="19" t="n"/>
-      <c r="AH5" s="19" t="n"/>
-      <c r="AI5" s="19" t="n"/>
-      <c r="AJ5" s="19" t="n"/>
-      <c r="AK5" s="19" t="n"/>
-      <c r="AL5" s="19" t="n"/>
-      <c r="AM5" s="19" t="n"/>
-      <c r="AN5" s="19" t="n"/>
-      <c r="AO5" s="19" t="n"/>
-      <c r="AP5" s="19" t="n"/>
-      <c r="AQ5" s="535" t="inlineStr">
+      <c r="M5" s="281" t="n"/>
+      <c r="N5" s="281" t="n"/>
+      <c r="O5" s="281" t="n"/>
+      <c r="P5" s="281" t="n"/>
+      <c r="Q5" s="281" t="n"/>
+      <c r="R5" s="281" t="n"/>
+      <c r="S5" s="281" t="n"/>
+      <c r="T5" s="281" t="n"/>
+      <c r="U5" s="281" t="n"/>
+      <c r="V5" s="281" t="n"/>
+      <c r="W5" s="281" t="n"/>
+      <c r="X5" s="281" t="n"/>
+      <c r="Y5" s="281" t="n"/>
+      <c r="Z5" s="281" t="n"/>
+      <c r="AA5" s="281" t="n"/>
+      <c r="AB5" s="281" t="n"/>
+      <c r="AC5" s="281" t="n"/>
+      <c r="AD5" s="281" t="n"/>
+      <c r="AE5" s="281" t="n"/>
+      <c r="AF5" s="281" t="n"/>
+      <c r="AG5" s="281" t="n"/>
+      <c r="AH5" s="281" t="n"/>
+      <c r="AI5" s="281" t="n"/>
+      <c r="AJ5" s="281" t="n"/>
+      <c r="AK5" s="281" t="n"/>
+      <c r="AL5" s="281" t="n"/>
+      <c r="AM5" s="281" t="n"/>
+      <c r="AN5" s="281" t="n"/>
+      <c r="AO5" s="281" t="n"/>
+      <c r="AP5" s="281" t="n"/>
+      <c r="AQ5" s="584" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="536" t="n"/>
-      <c r="AS5" s="536" t="n"/>
-      <c r="AT5" s="536" t="n"/>
-      <c r="AU5" s="536" t="n"/>
-      <c r="AV5" s="537" t="n"/>
-      <c r="AW5" s="538" t="inlineStr">
+      <c r="AR5" s="585" t="n"/>
+      <c r="AS5" s="585" t="n"/>
+      <c r="AT5" s="585" t="n"/>
+      <c r="AU5" s="585" t="n"/>
+      <c r="AV5" s="586" t="n"/>
+      <c r="AW5" s="587" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="536" t="n"/>
-      <c r="AY5" s="536" t="n"/>
-      <c r="AZ5" s="536" t="n"/>
-      <c r="BA5" s="536" t="n"/>
-      <c r="BB5" s="536" t="n"/>
-      <c r="BC5" s="536" t="n"/>
-      <c r="BD5" s="539" t="n"/>
+      <c r="AX5" s="585" t="n"/>
+      <c r="AY5" s="585" t="n"/>
+      <c r="AZ5" s="585" t="n"/>
+      <c r="BA5" s="585" t="n"/>
+      <c r="BB5" s="585" t="n"/>
+      <c r="BC5" s="585" t="n"/>
+      <c r="BD5" s="588" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="433" t="n"/>
@@ -9060,396 +9151,396 @@
       <c r="BD6" s="433" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="540" t="inlineStr">
+      <c r="A7" s="589" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. SCOPE / REVIEW CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
-      <c r="Q7" s="27" t="n"/>
-      <c r="R7" s="27" t="n"/>
-      <c r="S7" s="27" t="n"/>
-      <c r="T7" s="27" t="n"/>
-      <c r="U7" s="27" t="n"/>
-      <c r="V7" s="27" t="n"/>
-      <c r="W7" s="27" t="n"/>
-      <c r="X7" s="27" t="n"/>
-      <c r="Y7" s="27" t="n"/>
-      <c r="Z7" s="27" t="n"/>
-      <c r="AA7" s="27" t="n"/>
-      <c r="AB7" s="27" t="n"/>
-      <c r="AC7" s="27" t="n"/>
-      <c r="AD7" s="27" t="n"/>
-      <c r="AE7" s="27" t="n"/>
-      <c r="AF7" s="27" t="n"/>
-      <c r="AG7" s="27" t="n"/>
-      <c r="AH7" s="27" t="n"/>
-      <c r="AI7" s="27" t="n"/>
-      <c r="AJ7" s="27" t="n"/>
-      <c r="AK7" s="27" t="n"/>
-      <c r="AL7" s="27" t="n"/>
-      <c r="AM7" s="27" t="n"/>
-      <c r="AN7" s="27" t="n"/>
-      <c r="AO7" s="27" t="n"/>
-      <c r="AP7" s="27" t="n"/>
-      <c r="AQ7" s="27" t="n"/>
-      <c r="AR7" s="27" t="n"/>
-      <c r="AS7" s="27" t="n"/>
-      <c r="AT7" s="27" t="n"/>
-      <c r="AU7" s="27" t="n"/>
-      <c r="AV7" s="27" t="n"/>
-      <c r="AW7" s="27" t="n"/>
-      <c r="AX7" s="27" t="n"/>
-      <c r="AY7" s="27" t="n"/>
-      <c r="AZ7" s="27" t="n"/>
-      <c r="BA7" s="27" t="n"/>
-      <c r="BB7" s="27" t="n"/>
-      <c r="BC7" s="27" t="n"/>
-      <c r="BD7" s="28" t="n"/>
+      <c r="B7" s="285" t="n"/>
+      <c r="C7" s="285" t="n"/>
+      <c r="D7" s="285" t="n"/>
+      <c r="E7" s="285" t="n"/>
+      <c r="F7" s="285" t="n"/>
+      <c r="G7" s="285" t="n"/>
+      <c r="H7" s="285" t="n"/>
+      <c r="I7" s="285" t="n"/>
+      <c r="J7" s="285" t="n"/>
+      <c r="K7" s="285" t="n"/>
+      <c r="L7" s="285" t="n"/>
+      <c r="M7" s="285" t="n"/>
+      <c r="N7" s="285" t="n"/>
+      <c r="O7" s="285" t="n"/>
+      <c r="P7" s="285" t="n"/>
+      <c r="Q7" s="285" t="n"/>
+      <c r="R7" s="285" t="n"/>
+      <c r="S7" s="285" t="n"/>
+      <c r="T7" s="285" t="n"/>
+      <c r="U7" s="285" t="n"/>
+      <c r="V7" s="285" t="n"/>
+      <c r="W7" s="285" t="n"/>
+      <c r="X7" s="285" t="n"/>
+      <c r="Y7" s="285" t="n"/>
+      <c r="Z7" s="285" t="n"/>
+      <c r="AA7" s="285" t="n"/>
+      <c r="AB7" s="285" t="n"/>
+      <c r="AC7" s="285" t="n"/>
+      <c r="AD7" s="285" t="n"/>
+      <c r="AE7" s="285" t="n"/>
+      <c r="AF7" s="285" t="n"/>
+      <c r="AG7" s="285" t="n"/>
+      <c r="AH7" s="285" t="n"/>
+      <c r="AI7" s="285" t="n"/>
+      <c r="AJ7" s="285" t="n"/>
+      <c r="AK7" s="285" t="n"/>
+      <c r="AL7" s="285" t="n"/>
+      <c r="AM7" s="285" t="n"/>
+      <c r="AN7" s="285" t="n"/>
+      <c r="AO7" s="285" t="n"/>
+      <c r="AP7" s="285" t="n"/>
+      <c r="AQ7" s="285" t="n"/>
+      <c r="AR7" s="285" t="n"/>
+      <c r="AS7" s="285" t="n"/>
+      <c r="AT7" s="285" t="n"/>
+      <c r="AU7" s="285" t="n"/>
+      <c r="AV7" s="285" t="n"/>
+      <c r="AW7" s="285" t="n"/>
+      <c r="AX7" s="285" t="n"/>
+      <c r="AY7" s="285" t="n"/>
+      <c r="AZ7" s="285" t="n"/>
+      <c r="BA7" s="285" t="n"/>
+      <c r="BB7" s="285" t="n"/>
+      <c r="BC7" s="285" t="n"/>
+      <c r="BD7" s="286" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="541" t="inlineStr">
+      <c r="A8" s="590" t="inlineStr">
         <is>
           <t>Verification ID</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="542" t="n"/>
-      <c r="L8" s="543" t="n"/>
-      <c r="M8" s="543" t="n"/>
-      <c r="N8" s="543" t="n"/>
-      <c r="O8" s="543" t="n"/>
-      <c r="P8" s="543" t="n"/>
-      <c r="Q8" s="543" t="n"/>
-      <c r="R8" s="543" t="n"/>
-      <c r="S8" s="543" t="n"/>
-      <c r="T8" s="543" t="n"/>
-      <c r="U8" s="543" t="n"/>
-      <c r="V8" s="543" t="n"/>
-      <c r="W8" s="543" t="n"/>
-      <c r="X8" s="543" t="n"/>
-      <c r="Y8" s="543" t="n"/>
-      <c r="Z8" s="543" t="n"/>
-      <c r="AA8" s="543" t="n"/>
-      <c r="AB8" s="544" t="n"/>
-      <c r="AC8" s="545" t="inlineStr">
+      <c r="B8" s="271" t="n"/>
+      <c r="C8" s="271" t="n"/>
+      <c r="D8" s="271" t="n"/>
+      <c r="E8" s="271" t="n"/>
+      <c r="F8" s="271" t="n"/>
+      <c r="G8" s="271" t="n"/>
+      <c r="H8" s="271" t="n"/>
+      <c r="I8" s="271" t="n"/>
+      <c r="J8" s="272" t="n"/>
+      <c r="K8" s="288" t="n"/>
+      <c r="L8" s="319" t="n"/>
+      <c r="M8" s="319" t="n"/>
+      <c r="N8" s="319" t="n"/>
+      <c r="O8" s="319" t="n"/>
+      <c r="P8" s="319" t="n"/>
+      <c r="Q8" s="319" t="n"/>
+      <c r="R8" s="319" t="n"/>
+      <c r="S8" s="319" t="n"/>
+      <c r="T8" s="319" t="n"/>
+      <c r="U8" s="319" t="n"/>
+      <c r="V8" s="319" t="n"/>
+      <c r="W8" s="319" t="n"/>
+      <c r="X8" s="319" t="n"/>
+      <c r="Y8" s="319" t="n"/>
+      <c r="Z8" s="319" t="n"/>
+      <c r="AA8" s="319" t="n"/>
+      <c r="AB8" s="320" t="n"/>
+      <c r="AC8" s="591" t="inlineStr">
         <is>
           <t>Verification Result</t>
         </is>
       </c>
-      <c r="AD8" s="5" t="n"/>
-      <c r="AE8" s="5" t="n"/>
-      <c r="AF8" s="5" t="n"/>
-      <c r="AG8" s="5" t="n"/>
-      <c r="AH8" s="5" t="n"/>
-      <c r="AI8" s="5" t="n"/>
-      <c r="AJ8" s="5" t="n"/>
-      <c r="AK8" s="5" t="n"/>
-      <c r="AL8" s="6" t="n"/>
-      <c r="AM8" s="542" t="n"/>
-      <c r="AN8" s="543" t="n"/>
-      <c r="AO8" s="543" t="n"/>
-      <c r="AP8" s="543" t="n"/>
-      <c r="AQ8" s="543" t="n"/>
-      <c r="AR8" s="543" t="n"/>
-      <c r="AS8" s="543" t="n"/>
-      <c r="AT8" s="543" t="n"/>
-      <c r="AU8" s="543" t="n"/>
-      <c r="AV8" s="543" t="n"/>
-      <c r="AW8" s="543" t="n"/>
-      <c r="AX8" s="543" t="n"/>
-      <c r="AY8" s="543" t="n"/>
-      <c r="AZ8" s="543" t="n"/>
-      <c r="BA8" s="543" t="n"/>
-      <c r="BB8" s="543" t="n"/>
-      <c r="BC8" s="543" t="n"/>
-      <c r="BD8" s="546" t="n"/>
+      <c r="AD8" s="271" t="n"/>
+      <c r="AE8" s="271" t="n"/>
+      <c r="AF8" s="271" t="n"/>
+      <c r="AG8" s="271" t="n"/>
+      <c r="AH8" s="271" t="n"/>
+      <c r="AI8" s="271" t="n"/>
+      <c r="AJ8" s="271" t="n"/>
+      <c r="AK8" s="271" t="n"/>
+      <c r="AL8" s="272" t="n"/>
+      <c r="AM8" s="290" t="n"/>
+      <c r="AN8" s="319" t="n"/>
+      <c r="AO8" s="319" t="n"/>
+      <c r="AP8" s="319" t="n"/>
+      <c r="AQ8" s="319" t="n"/>
+      <c r="AR8" s="319" t="n"/>
+      <c r="AS8" s="319" t="n"/>
+      <c r="AT8" s="319" t="n"/>
+      <c r="AU8" s="319" t="n"/>
+      <c r="AV8" s="319" t="n"/>
+      <c r="AW8" s="319" t="n"/>
+      <c r="AX8" s="319" t="n"/>
+      <c r="AY8" s="319" t="n"/>
+      <c r="AZ8" s="319" t="n"/>
+      <c r="BA8" s="319" t="n"/>
+      <c r="BB8" s="319" t="n"/>
+      <c r="BC8" s="319" t="n"/>
+      <c r="BD8" s="321" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="547" t="inlineStr">
+      <c r="A9" s="592" t="inlineStr">
         <is>
           <t>Equipment ID / Description</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="548" t="n"/>
-      <c r="L9" s="549" t="n"/>
-      <c r="M9" s="549" t="n"/>
-      <c r="N9" s="549" t="n"/>
-      <c r="O9" s="549" t="n"/>
-      <c r="P9" s="549" t="n"/>
-      <c r="Q9" s="549" t="n"/>
-      <c r="R9" s="549" t="n"/>
-      <c r="S9" s="549" t="n"/>
-      <c r="T9" s="549" t="n"/>
-      <c r="U9" s="549" t="n"/>
-      <c r="V9" s="549" t="n"/>
-      <c r="W9" s="549" t="n"/>
-      <c r="X9" s="549" t="n"/>
-      <c r="Y9" s="549" t="n"/>
-      <c r="Z9" s="549" t="n"/>
-      <c r="AA9" s="549" t="n"/>
-      <c r="AB9" s="550" t="n"/>
-      <c r="AC9" s="551" t="inlineStr">
+      <c r="B9" s="276" t="n"/>
+      <c r="C9" s="276" t="n"/>
+      <c r="D9" s="276" t="n"/>
+      <c r="E9" s="276" t="n"/>
+      <c r="F9" s="276" t="n"/>
+      <c r="G9" s="276" t="n"/>
+      <c r="H9" s="276" t="n"/>
+      <c r="I9" s="276" t="n"/>
+      <c r="J9" s="277" t="n"/>
+      <c r="K9" s="593" t="n"/>
+      <c r="L9" s="594" t="n"/>
+      <c r="M9" s="594" t="n"/>
+      <c r="N9" s="594" t="n"/>
+      <c r="O9" s="594" t="n"/>
+      <c r="P9" s="594" t="n"/>
+      <c r="Q9" s="594" t="n"/>
+      <c r="R9" s="594" t="n"/>
+      <c r="S9" s="594" t="n"/>
+      <c r="T9" s="594" t="n"/>
+      <c r="U9" s="594" t="n"/>
+      <c r="V9" s="594" t="n"/>
+      <c r="W9" s="594" t="n"/>
+      <c r="X9" s="594" t="n"/>
+      <c r="Y9" s="594" t="n"/>
+      <c r="Z9" s="594" t="n"/>
+      <c r="AA9" s="594" t="n"/>
+      <c r="AB9" s="595" t="n"/>
+      <c r="AC9" s="596" t="inlineStr">
         <is>
           <t>User / Area</t>
         </is>
       </c>
-      <c r="AD9" s="12" t="n"/>
-      <c r="AE9" s="12" t="n"/>
-      <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="12" t="n"/>
-      <c r="AH9" s="12" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="12" t="n"/>
-      <c r="AK9" s="12" t="n"/>
-      <c r="AL9" s="13" t="n"/>
-      <c r="AM9" s="548" t="n"/>
-      <c r="AN9" s="549" t="n"/>
-      <c r="AO9" s="549" t="n"/>
-      <c r="AP9" s="549" t="n"/>
-      <c r="AQ9" s="549" t="n"/>
-      <c r="AR9" s="549" t="n"/>
-      <c r="AS9" s="549" t="n"/>
-      <c r="AT9" s="549" t="n"/>
-      <c r="AU9" s="549" t="n"/>
-      <c r="AV9" s="549" t="n"/>
-      <c r="AW9" s="549" t="n"/>
-      <c r="AX9" s="549" t="n"/>
-      <c r="AY9" s="549" t="n"/>
-      <c r="AZ9" s="549" t="n"/>
-      <c r="BA9" s="549" t="n"/>
-      <c r="BB9" s="549" t="n"/>
-      <c r="BC9" s="549" t="n"/>
-      <c r="BD9" s="552" t="n"/>
+      <c r="AD9" s="276" t="n"/>
+      <c r="AE9" s="276" t="n"/>
+      <c r="AF9" s="276" t="n"/>
+      <c r="AG9" s="276" t="n"/>
+      <c r="AH9" s="276" t="n"/>
+      <c r="AI9" s="276" t="n"/>
+      <c r="AJ9" s="276" t="n"/>
+      <c r="AK9" s="276" t="n"/>
+      <c r="AL9" s="277" t="n"/>
+      <c r="AM9" s="597" t="n"/>
+      <c r="AN9" s="594" t="n"/>
+      <c r="AO9" s="594" t="n"/>
+      <c r="AP9" s="594" t="n"/>
+      <c r="AQ9" s="594" t="n"/>
+      <c r="AR9" s="594" t="n"/>
+      <c r="AS9" s="594" t="n"/>
+      <c r="AT9" s="594" t="n"/>
+      <c r="AU9" s="594" t="n"/>
+      <c r="AV9" s="594" t="n"/>
+      <c r="AW9" s="594" t="n"/>
+      <c r="AX9" s="594" t="n"/>
+      <c r="AY9" s="594" t="n"/>
+      <c r="AZ9" s="594" t="n"/>
+      <c r="BA9" s="594" t="n"/>
+      <c r="BB9" s="594" t="n"/>
+      <c r="BC9" s="594" t="n"/>
+      <c r="BD9" s="598" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="547" t="inlineStr">
+      <c r="A10" s="592" t="inlineStr">
         <is>
           <t>Verification Type</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="548" t="n"/>
-      <c r="L10" s="549" t="n"/>
-      <c r="M10" s="549" t="n"/>
-      <c r="N10" s="549" t="n"/>
-      <c r="O10" s="549" t="n"/>
-      <c r="P10" s="549" t="n"/>
-      <c r="Q10" s="549" t="n"/>
-      <c r="R10" s="549" t="n"/>
-      <c r="S10" s="549" t="n"/>
-      <c r="T10" s="549" t="n"/>
-      <c r="U10" s="549" t="n"/>
-      <c r="V10" s="549" t="n"/>
-      <c r="W10" s="549" t="n"/>
-      <c r="X10" s="549" t="n"/>
-      <c r="Y10" s="549" t="n"/>
-      <c r="Z10" s="549" t="n"/>
-      <c r="AA10" s="549" t="n"/>
-      <c r="AB10" s="550" t="n"/>
-      <c r="AC10" s="551" t="inlineStr">
+      <c r="B10" s="276" t="n"/>
+      <c r="C10" s="276" t="n"/>
+      <c r="D10" s="276" t="n"/>
+      <c r="E10" s="276" t="n"/>
+      <c r="F10" s="276" t="n"/>
+      <c r="G10" s="276" t="n"/>
+      <c r="H10" s="276" t="n"/>
+      <c r="I10" s="276" t="n"/>
+      <c r="J10" s="277" t="n"/>
+      <c r="K10" s="593" t="n"/>
+      <c r="L10" s="594" t="n"/>
+      <c r="M10" s="594" t="n"/>
+      <c r="N10" s="594" t="n"/>
+      <c r="O10" s="594" t="n"/>
+      <c r="P10" s="594" t="n"/>
+      <c r="Q10" s="594" t="n"/>
+      <c r="R10" s="594" t="n"/>
+      <c r="S10" s="594" t="n"/>
+      <c r="T10" s="594" t="n"/>
+      <c r="U10" s="594" t="n"/>
+      <c r="V10" s="594" t="n"/>
+      <c r="W10" s="594" t="n"/>
+      <c r="X10" s="594" t="n"/>
+      <c r="Y10" s="594" t="n"/>
+      <c r="Z10" s="594" t="n"/>
+      <c r="AA10" s="594" t="n"/>
+      <c r="AB10" s="595" t="n"/>
+      <c r="AC10" s="596" t="inlineStr">
         <is>
           <t>CAL Status</t>
         </is>
       </c>
-      <c r="AD10" s="12" t="n"/>
-      <c r="AE10" s="12" t="n"/>
-      <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="12" t="n"/>
-      <c r="AH10" s="12" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="12" t="n"/>
-      <c r="AK10" s="12" t="n"/>
-      <c r="AL10" s="13" t="n"/>
-      <c r="AM10" s="548" t="n"/>
-      <c r="AN10" s="549" t="n"/>
-      <c r="AO10" s="549" t="n"/>
-      <c r="AP10" s="549" t="n"/>
-      <c r="AQ10" s="549" t="n"/>
-      <c r="AR10" s="549" t="n"/>
-      <c r="AS10" s="549" t="n"/>
-      <c r="AT10" s="549" t="n"/>
-      <c r="AU10" s="549" t="n"/>
-      <c r="AV10" s="549" t="n"/>
-      <c r="AW10" s="549" t="n"/>
-      <c r="AX10" s="549" t="n"/>
-      <c r="AY10" s="549" t="n"/>
-      <c r="AZ10" s="549" t="n"/>
-      <c r="BA10" s="549" t="n"/>
-      <c r="BB10" s="549" t="n"/>
-      <c r="BC10" s="549" t="n"/>
-      <c r="BD10" s="552" t="n"/>
+      <c r="AD10" s="276" t="n"/>
+      <c r="AE10" s="276" t="n"/>
+      <c r="AF10" s="276" t="n"/>
+      <c r="AG10" s="276" t="n"/>
+      <c r="AH10" s="276" t="n"/>
+      <c r="AI10" s="276" t="n"/>
+      <c r="AJ10" s="276" t="n"/>
+      <c r="AK10" s="276" t="n"/>
+      <c r="AL10" s="277" t="n"/>
+      <c r="AM10" s="597" t="n"/>
+      <c r="AN10" s="594" t="n"/>
+      <c r="AO10" s="594" t="n"/>
+      <c r="AP10" s="594" t="n"/>
+      <c r="AQ10" s="594" t="n"/>
+      <c r="AR10" s="594" t="n"/>
+      <c r="AS10" s="594" t="n"/>
+      <c r="AT10" s="594" t="n"/>
+      <c r="AU10" s="594" t="n"/>
+      <c r="AV10" s="594" t="n"/>
+      <c r="AW10" s="594" t="n"/>
+      <c r="AX10" s="594" t="n"/>
+      <c r="AY10" s="594" t="n"/>
+      <c r="AZ10" s="594" t="n"/>
+      <c r="BA10" s="594" t="n"/>
+      <c r="BB10" s="594" t="n"/>
+      <c r="BC10" s="594" t="n"/>
+      <c r="BD10" s="598" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="547" t="inlineStr">
+      <c r="A11" s="592" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="548" t="n"/>
-      <c r="L11" s="549" t="n"/>
-      <c r="M11" s="549" t="n"/>
-      <c r="N11" s="549" t="n"/>
-      <c r="O11" s="549" t="n"/>
-      <c r="P11" s="549" t="n"/>
-      <c r="Q11" s="549" t="n"/>
-      <c r="R11" s="549" t="n"/>
-      <c r="S11" s="549" t="n"/>
-      <c r="T11" s="549" t="n"/>
-      <c r="U11" s="549" t="n"/>
-      <c r="V11" s="549" t="n"/>
-      <c r="W11" s="549" t="n"/>
-      <c r="X11" s="549" t="n"/>
-      <c r="Y11" s="549" t="n"/>
-      <c r="Z11" s="549" t="n"/>
-      <c r="AA11" s="549" t="n"/>
-      <c r="AB11" s="550" t="n"/>
-      <c r="AC11" s="551" t="inlineStr">
+      <c r="B11" s="276" t="n"/>
+      <c r="C11" s="276" t="n"/>
+      <c r="D11" s="276" t="n"/>
+      <c r="E11" s="276" t="n"/>
+      <c r="F11" s="276" t="n"/>
+      <c r="G11" s="276" t="n"/>
+      <c r="H11" s="276" t="n"/>
+      <c r="I11" s="276" t="n"/>
+      <c r="J11" s="277" t="n"/>
+      <c r="K11" s="593" t="n"/>
+      <c r="L11" s="594" t="n"/>
+      <c r="M11" s="594" t="n"/>
+      <c r="N11" s="594" t="n"/>
+      <c r="O11" s="594" t="n"/>
+      <c r="P11" s="594" t="n"/>
+      <c r="Q11" s="594" t="n"/>
+      <c r="R11" s="594" t="n"/>
+      <c r="S11" s="594" t="n"/>
+      <c r="T11" s="594" t="n"/>
+      <c r="U11" s="594" t="n"/>
+      <c r="V11" s="594" t="n"/>
+      <c r="W11" s="594" t="n"/>
+      <c r="X11" s="594" t="n"/>
+      <c r="Y11" s="594" t="n"/>
+      <c r="Z11" s="594" t="n"/>
+      <c r="AA11" s="594" t="n"/>
+      <c r="AB11" s="595" t="n"/>
+      <c r="AC11" s="596" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="AD11" s="12" t="n"/>
-      <c r="AE11" s="12" t="n"/>
-      <c r="AF11" s="12" t="n"/>
-      <c r="AG11" s="12" t="n"/>
-      <c r="AH11" s="12" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="12" t="n"/>
-      <c r="AK11" s="12" t="n"/>
-      <c r="AL11" s="13" t="n"/>
-      <c r="AM11" s="548" t="n"/>
-      <c r="AN11" s="549" t="n"/>
-      <c r="AO11" s="549" t="n"/>
-      <c r="AP11" s="549" t="n"/>
-      <c r="AQ11" s="549" t="n"/>
-      <c r="AR11" s="549" t="n"/>
-      <c r="AS11" s="549" t="n"/>
-      <c r="AT11" s="549" t="n"/>
-      <c r="AU11" s="549" t="n"/>
-      <c r="AV11" s="549" t="n"/>
-      <c r="AW11" s="549" t="n"/>
-      <c r="AX11" s="549" t="n"/>
-      <c r="AY11" s="549" t="n"/>
-      <c r="AZ11" s="549" t="n"/>
-      <c r="BA11" s="549" t="n"/>
-      <c r="BB11" s="549" t="n"/>
-      <c r="BC11" s="549" t="n"/>
-      <c r="BD11" s="552" t="n"/>
+      <c r="AD11" s="276" t="n"/>
+      <c r="AE11" s="276" t="n"/>
+      <c r="AF11" s="276" t="n"/>
+      <c r="AG11" s="276" t="n"/>
+      <c r="AH11" s="276" t="n"/>
+      <c r="AI11" s="276" t="n"/>
+      <c r="AJ11" s="276" t="n"/>
+      <c r="AK11" s="276" t="n"/>
+      <c r="AL11" s="277" t="n"/>
+      <c r="AM11" s="597" t="n"/>
+      <c r="AN11" s="594" t="n"/>
+      <c r="AO11" s="594" t="n"/>
+      <c r="AP11" s="594" t="n"/>
+      <c r="AQ11" s="594" t="n"/>
+      <c r="AR11" s="594" t="n"/>
+      <c r="AS11" s="594" t="n"/>
+      <c r="AT11" s="594" t="n"/>
+      <c r="AU11" s="594" t="n"/>
+      <c r="AV11" s="594" t="n"/>
+      <c r="AW11" s="594" t="n"/>
+      <c r="AX11" s="594" t="n"/>
+      <c r="AY11" s="594" t="n"/>
+      <c r="AZ11" s="594" t="n"/>
+      <c r="BA11" s="594" t="n"/>
+      <c r="BB11" s="594" t="n"/>
+      <c r="BC11" s="594" t="n"/>
+      <c r="BD11" s="598" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="553" t="inlineStr">
+      <c r="A12" s="599" t="inlineStr">
         <is>
           <t>Method / Acceptance Ref</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="22" t="n"/>
-      <c r="K12" s="554" t="n"/>
-      <c r="L12" s="555" t="n"/>
-      <c r="M12" s="555" t="n"/>
-      <c r="N12" s="555" t="n"/>
-      <c r="O12" s="555" t="n"/>
-      <c r="P12" s="555" t="n"/>
-      <c r="Q12" s="555" t="n"/>
-      <c r="R12" s="555" t="n"/>
-      <c r="S12" s="555" t="n"/>
-      <c r="T12" s="555" t="n"/>
-      <c r="U12" s="555" t="n"/>
-      <c r="V12" s="555" t="n"/>
-      <c r="W12" s="555" t="n"/>
-      <c r="X12" s="555" t="n"/>
-      <c r="Y12" s="555" t="n"/>
-      <c r="Z12" s="555" t="n"/>
-      <c r="AA12" s="555" t="n"/>
-      <c r="AB12" s="556" t="n"/>
-      <c r="AC12" s="557" t="inlineStr">
+      <c r="B12" s="281" t="n"/>
+      <c r="C12" s="281" t="n"/>
+      <c r="D12" s="281" t="n"/>
+      <c r="E12" s="281" t="n"/>
+      <c r="F12" s="281" t="n"/>
+      <c r="G12" s="281" t="n"/>
+      <c r="H12" s="281" t="n"/>
+      <c r="I12" s="281" t="n"/>
+      <c r="J12" s="282" t="n"/>
+      <c r="K12" s="600" t="n"/>
+      <c r="L12" s="601" t="n"/>
+      <c r="M12" s="601" t="n"/>
+      <c r="N12" s="601" t="n"/>
+      <c r="O12" s="601" t="n"/>
+      <c r="P12" s="601" t="n"/>
+      <c r="Q12" s="601" t="n"/>
+      <c r="R12" s="601" t="n"/>
+      <c r="S12" s="601" t="n"/>
+      <c r="T12" s="601" t="n"/>
+      <c r="U12" s="601" t="n"/>
+      <c r="V12" s="601" t="n"/>
+      <c r="W12" s="601" t="n"/>
+      <c r="X12" s="601" t="n"/>
+      <c r="Y12" s="601" t="n"/>
+      <c r="Z12" s="601" t="n"/>
+      <c r="AA12" s="601" t="n"/>
+      <c r="AB12" s="602" t="n"/>
+      <c r="AC12" s="603" t="inlineStr">
         <is>
           <t>Affected Job Ref</t>
         </is>
       </c>
-      <c r="AD12" s="19" t="n"/>
-      <c r="AE12" s="19" t="n"/>
-      <c r="AF12" s="19" t="n"/>
-      <c r="AG12" s="19" t="n"/>
-      <c r="AH12" s="19" t="n"/>
-      <c r="AI12" s="19" t="n"/>
-      <c r="AJ12" s="19" t="n"/>
-      <c r="AK12" s="19" t="n"/>
-      <c r="AL12" s="22" t="n"/>
-      <c r="AM12" s="554" t="n"/>
-      <c r="AN12" s="555" t="n"/>
-      <c r="AO12" s="555" t="n"/>
-      <c r="AP12" s="555" t="n"/>
-      <c r="AQ12" s="555" t="n"/>
-      <c r="AR12" s="555" t="n"/>
-      <c r="AS12" s="555" t="n"/>
-      <c r="AT12" s="555" t="n"/>
-      <c r="AU12" s="555" t="n"/>
-      <c r="AV12" s="555" t="n"/>
-      <c r="AW12" s="555" t="n"/>
-      <c r="AX12" s="555" t="n"/>
-      <c r="AY12" s="555" t="n"/>
-      <c r="AZ12" s="555" t="n"/>
-      <c r="BA12" s="555" t="n"/>
-      <c r="BB12" s="555" t="n"/>
-      <c r="BC12" s="555" t="n"/>
-      <c r="BD12" s="558" t="n"/>
+      <c r="AD12" s="281" t="n"/>
+      <c r="AE12" s="281" t="n"/>
+      <c r="AF12" s="281" t="n"/>
+      <c r="AG12" s="281" t="n"/>
+      <c r="AH12" s="281" t="n"/>
+      <c r="AI12" s="281" t="n"/>
+      <c r="AJ12" s="281" t="n"/>
+      <c r="AK12" s="281" t="n"/>
+      <c r="AL12" s="282" t="n"/>
+      <c r="AM12" s="604" t="n"/>
+      <c r="AN12" s="601" t="n"/>
+      <c r="AO12" s="601" t="n"/>
+      <c r="AP12" s="601" t="n"/>
+      <c r="AQ12" s="601" t="n"/>
+      <c r="AR12" s="601" t="n"/>
+      <c r="AS12" s="601" t="n"/>
+      <c r="AT12" s="601" t="n"/>
+      <c r="AU12" s="601" t="n"/>
+      <c r="AV12" s="601" t="n"/>
+      <c r="AW12" s="601" t="n"/>
+      <c r="AX12" s="601" t="n"/>
+      <c r="AY12" s="601" t="n"/>
+      <c r="AZ12" s="601" t="n"/>
+      <c r="BA12" s="601" t="n"/>
+      <c r="BB12" s="601" t="n"/>
+      <c r="BC12" s="601" t="n"/>
+      <c r="BD12" s="605" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="559" t="n"/>
@@ -9510,864 +9601,864 @@
       <c r="BD13" s="559" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="540" t="inlineStr">
+      <c r="A14" s="589" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. REVIEW SNAPSHOT / LIVE ENTRY ON GAGE_DATA_LOG</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="27" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="27" t="n"/>
-      <c r="N14" s="27" t="n"/>
-      <c r="O14" s="27" t="n"/>
-      <c r="P14" s="27" t="n"/>
-      <c r="Q14" s="27" t="n"/>
-      <c r="R14" s="27" t="n"/>
-      <c r="S14" s="27" t="n"/>
-      <c r="T14" s="27" t="n"/>
-      <c r="U14" s="27" t="n"/>
-      <c r="V14" s="27" t="n"/>
-      <c r="W14" s="27" t="n"/>
-      <c r="X14" s="27" t="n"/>
-      <c r="Y14" s="27" t="n"/>
-      <c r="Z14" s="27" t="n"/>
-      <c r="AA14" s="27" t="n"/>
-      <c r="AB14" s="27" t="n"/>
-      <c r="AC14" s="27" t="n"/>
-      <c r="AD14" s="27" t="n"/>
-      <c r="AE14" s="27" t="n"/>
-      <c r="AF14" s="27" t="n"/>
-      <c r="AG14" s="27" t="n"/>
-      <c r="AH14" s="27" t="n"/>
-      <c r="AI14" s="27" t="n"/>
-      <c r="AJ14" s="27" t="n"/>
-      <c r="AK14" s="27" t="n"/>
-      <c r="AL14" s="27" t="n"/>
-      <c r="AM14" s="27" t="n"/>
-      <c r="AN14" s="27" t="n"/>
-      <c r="AO14" s="27" t="n"/>
-      <c r="AP14" s="27" t="n"/>
-      <c r="AQ14" s="27" t="n"/>
-      <c r="AR14" s="27" t="n"/>
-      <c r="AS14" s="27" t="n"/>
-      <c r="AT14" s="27" t="n"/>
-      <c r="AU14" s="27" t="n"/>
-      <c r="AV14" s="27" t="n"/>
-      <c r="AW14" s="27" t="n"/>
-      <c r="AX14" s="27" t="n"/>
-      <c r="AY14" s="27" t="n"/>
-      <c r="AZ14" s="27" t="n"/>
-      <c r="BA14" s="27" t="n"/>
-      <c r="BB14" s="27" t="n"/>
-      <c r="BC14" s="27" t="n"/>
-      <c r="BD14" s="28" t="n"/>
+      <c r="B14" s="285" t="n"/>
+      <c r="C14" s="285" t="n"/>
+      <c r="D14" s="285" t="n"/>
+      <c r="E14" s="285" t="n"/>
+      <c r="F14" s="285" t="n"/>
+      <c r="G14" s="285" t="n"/>
+      <c r="H14" s="285" t="n"/>
+      <c r="I14" s="285" t="n"/>
+      <c r="J14" s="285" t="n"/>
+      <c r="K14" s="285" t="n"/>
+      <c r="L14" s="285" t="n"/>
+      <c r="M14" s="285" t="n"/>
+      <c r="N14" s="285" t="n"/>
+      <c r="O14" s="285" t="n"/>
+      <c r="P14" s="285" t="n"/>
+      <c r="Q14" s="285" t="n"/>
+      <c r="R14" s="285" t="n"/>
+      <c r="S14" s="285" t="n"/>
+      <c r="T14" s="285" t="n"/>
+      <c r="U14" s="285" t="n"/>
+      <c r="V14" s="285" t="n"/>
+      <c r="W14" s="285" t="n"/>
+      <c r="X14" s="285" t="n"/>
+      <c r="Y14" s="285" t="n"/>
+      <c r="Z14" s="285" t="n"/>
+      <c r="AA14" s="285" t="n"/>
+      <c r="AB14" s="285" t="n"/>
+      <c r="AC14" s="285" t="n"/>
+      <c r="AD14" s="285" t="n"/>
+      <c r="AE14" s="285" t="n"/>
+      <c r="AF14" s="285" t="n"/>
+      <c r="AG14" s="285" t="n"/>
+      <c r="AH14" s="285" t="n"/>
+      <c r="AI14" s="285" t="n"/>
+      <c r="AJ14" s="285" t="n"/>
+      <c r="AK14" s="285" t="n"/>
+      <c r="AL14" s="285" t="n"/>
+      <c r="AM14" s="285" t="n"/>
+      <c r="AN14" s="285" t="n"/>
+      <c r="AO14" s="285" t="n"/>
+      <c r="AP14" s="285" t="n"/>
+      <c r="AQ14" s="285" t="n"/>
+      <c r="AR14" s="285" t="n"/>
+      <c r="AS14" s="285" t="n"/>
+      <c r="AT14" s="285" t="n"/>
+      <c r="AU14" s="285" t="n"/>
+      <c r="AV14" s="285" t="n"/>
+      <c r="AW14" s="285" t="n"/>
+      <c r="AX14" s="285" t="n"/>
+      <c r="AY14" s="285" t="n"/>
+      <c r="AZ14" s="285" t="n"/>
+      <c r="BA14" s="285" t="n"/>
+      <c r="BB14" s="285" t="n"/>
+      <c r="BC14" s="285" t="n"/>
+      <c r="BD14" s="286" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="308" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="37" t="inlineStr">
+      <c r="B15" s="271" t="n"/>
+      <c r="C15" s="272" t="n"/>
+      <c r="D15" s="299" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="37" t="inlineStr">
+      <c r="E15" s="271" t="n"/>
+      <c r="F15" s="271" t="n"/>
+      <c r="G15" s="271" t="n"/>
+      <c r="H15" s="272" t="n"/>
+      <c r="I15" s="299" t="inlineStr">
         <is>
           <t>Gage ID</t>
         </is>
       </c>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="6" t="n"/>
-      <c r="N15" s="37" t="inlineStr">
+      <c r="J15" s="271" t="n"/>
+      <c r="K15" s="271" t="n"/>
+      <c r="L15" s="271" t="n"/>
+      <c r="M15" s="272" t="n"/>
+      <c r="N15" s="299" t="inlineStr">
         <is>
           <t>Verification Type</t>
         </is>
       </c>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="6" t="n"/>
-      <c r="U15" s="37" t="inlineStr">
+      <c r="O15" s="271" t="n"/>
+      <c r="P15" s="271" t="n"/>
+      <c r="Q15" s="271" t="n"/>
+      <c r="R15" s="271" t="n"/>
+      <c r="S15" s="271" t="n"/>
+      <c r="T15" s="272" t="n"/>
+      <c r="U15" s="299" t="inlineStr">
         <is>
           <t>Check Artifact / Master</t>
         </is>
       </c>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-      <c r="Y15" s="5" t="n"/>
-      <c r="Z15" s="6" t="n"/>
-      <c r="AA15" s="37" t="inlineStr">
+      <c r="V15" s="271" t="n"/>
+      <c r="W15" s="271" t="n"/>
+      <c r="X15" s="271" t="n"/>
+      <c r="Y15" s="271" t="n"/>
+      <c r="Z15" s="272" t="n"/>
+      <c r="AA15" s="299" t="inlineStr">
         <is>
           <t>Criteria</t>
         </is>
       </c>
-      <c r="AB15" s="5" t="n"/>
-      <c r="AC15" s="5" t="n"/>
-      <c r="AD15" s="5" t="n"/>
-      <c r="AE15" s="5" t="n"/>
-      <c r="AF15" s="5" t="n"/>
-      <c r="AG15" s="6" t="n"/>
-      <c r="AH15" s="37" t="inlineStr">
+      <c r="AB15" s="271" t="n"/>
+      <c r="AC15" s="271" t="n"/>
+      <c r="AD15" s="271" t="n"/>
+      <c r="AE15" s="271" t="n"/>
+      <c r="AF15" s="271" t="n"/>
+      <c r="AG15" s="272" t="n"/>
+      <c r="AH15" s="299" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AI15" s="5" t="n"/>
-      <c r="AJ15" s="5" t="n"/>
-      <c r="AK15" s="6" t="n"/>
-      <c r="AL15" s="37" t="inlineStr">
+      <c r="AI15" s="271" t="n"/>
+      <c r="AJ15" s="271" t="n"/>
+      <c r="AK15" s="272" t="n"/>
+      <c r="AL15" s="299" t="inlineStr">
         <is>
           <t>CAL Status</t>
         </is>
       </c>
-      <c r="AM15" s="5" t="n"/>
-      <c r="AN15" s="5" t="n"/>
-      <c r="AO15" s="6" t="n"/>
-      <c r="AP15" s="37" t="inlineStr">
+      <c r="AM15" s="271" t="n"/>
+      <c r="AN15" s="271" t="n"/>
+      <c r="AO15" s="272" t="n"/>
+      <c r="AP15" s="299" t="inlineStr">
         <is>
           <t>Use Stop (Y/N)</t>
         </is>
       </c>
-      <c r="AQ15" s="5" t="n"/>
-      <c r="AR15" s="5" t="n"/>
-      <c r="AS15" s="6" t="n"/>
-      <c r="AT15" s="37" t="inlineStr">
+      <c r="AQ15" s="271" t="n"/>
+      <c r="AR15" s="271" t="n"/>
+      <c r="AS15" s="272" t="n"/>
+      <c r="AT15" s="299" t="inlineStr">
         <is>
           <t>Owner Dept</t>
         </is>
       </c>
-      <c r="AU15" s="5" t="n"/>
-      <c r="AV15" s="5" t="n"/>
-      <c r="AW15" s="6" t="n"/>
-      <c r="AX15" s="37" t="inlineStr">
+      <c r="AU15" s="271" t="n"/>
+      <c r="AV15" s="271" t="n"/>
+      <c r="AW15" s="272" t="n"/>
+      <c r="AX15" s="300" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AY15" s="5" t="n"/>
-      <c r="AZ15" s="5" t="n"/>
-      <c r="BA15" s="5" t="n"/>
-      <c r="BB15" s="5" t="n"/>
-      <c r="BC15" s="5" t="n"/>
-      <c r="BD15" s="8" t="n"/>
+      <c r="AY15" s="271" t="n"/>
+      <c r="AZ15" s="271" t="n"/>
+      <c r="BA15" s="271" t="n"/>
+      <c r="BB15" s="271" t="n"/>
+      <c r="BC15" s="271" t="n"/>
+      <c r="BD15" s="274" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="560" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="561" t="n"/>
-      <c r="E16" s="543" t="n"/>
-      <c r="F16" s="543" t="n"/>
-      <c r="G16" s="543" t="n"/>
-      <c r="H16" s="544" t="n"/>
-      <c r="I16" s="561" t="n"/>
-      <c r="J16" s="543" t="n"/>
-      <c r="K16" s="543" t="n"/>
-      <c r="L16" s="543" t="n"/>
-      <c r="M16" s="544" t="n"/>
-      <c r="N16" s="561" t="n"/>
-      <c r="O16" s="543" t="n"/>
-      <c r="P16" s="543" t="n"/>
-      <c r="Q16" s="543" t="n"/>
-      <c r="R16" s="543" t="n"/>
-      <c r="S16" s="543" t="n"/>
-      <c r="T16" s="544" t="n"/>
-      <c r="U16" s="561" t="n"/>
-      <c r="V16" s="543" t="n"/>
-      <c r="W16" s="543" t="n"/>
-      <c r="X16" s="543" t="n"/>
-      <c r="Y16" s="543" t="n"/>
-      <c r="Z16" s="544" t="n"/>
-      <c r="AA16" s="561" t="n"/>
-      <c r="AB16" s="543" t="n"/>
-      <c r="AC16" s="543" t="n"/>
-      <c r="AD16" s="543" t="n"/>
-      <c r="AE16" s="543" t="n"/>
-      <c r="AF16" s="543" t="n"/>
-      <c r="AG16" s="544" t="n"/>
-      <c r="AH16" s="561" t="n"/>
-      <c r="AI16" s="543" t="n"/>
-      <c r="AJ16" s="543" t="n"/>
-      <c r="AK16" s="544" t="n"/>
-      <c r="AL16" s="561" t="n"/>
-      <c r="AM16" s="543" t="n"/>
-      <c r="AN16" s="543" t="n"/>
-      <c r="AO16" s="544" t="n"/>
-      <c r="AP16" s="561" t="n"/>
-      <c r="AQ16" s="543" t="n"/>
-      <c r="AR16" s="543" t="n"/>
-      <c r="AS16" s="544" t="n"/>
-      <c r="AT16" s="561" t="n"/>
-      <c r="AU16" s="543" t="n"/>
-      <c r="AV16" s="543" t="n"/>
-      <c r="AW16" s="544" t="n"/>
-      <c r="AX16" s="561" t="n"/>
-      <c r="AY16" s="543" t="n"/>
-      <c r="AZ16" s="543" t="n"/>
-      <c r="BA16" s="543" t="n"/>
-      <c r="BB16" s="543" t="n"/>
-      <c r="BC16" s="543" t="n"/>
-      <c r="BD16" s="546" t="n"/>
+      <c r="A16" s="606" t="n"/>
+      <c r="B16" s="271" t="n"/>
+      <c r="C16" s="272" t="n"/>
+      <c r="D16" s="607" t="n"/>
+      <c r="E16" s="319" t="n"/>
+      <c r="F16" s="319" t="n"/>
+      <c r="G16" s="319" t="n"/>
+      <c r="H16" s="320" t="n"/>
+      <c r="I16" s="607" t="n"/>
+      <c r="J16" s="319" t="n"/>
+      <c r="K16" s="319" t="n"/>
+      <c r="L16" s="319" t="n"/>
+      <c r="M16" s="320" t="n"/>
+      <c r="N16" s="607" t="n"/>
+      <c r="O16" s="319" t="n"/>
+      <c r="P16" s="319" t="n"/>
+      <c r="Q16" s="319" t="n"/>
+      <c r="R16" s="319" t="n"/>
+      <c r="S16" s="319" t="n"/>
+      <c r="T16" s="320" t="n"/>
+      <c r="U16" s="607" t="n"/>
+      <c r="V16" s="319" t="n"/>
+      <c r="W16" s="319" t="n"/>
+      <c r="X16" s="319" t="n"/>
+      <c r="Y16" s="319" t="n"/>
+      <c r="Z16" s="320" t="n"/>
+      <c r="AA16" s="607" t="n"/>
+      <c r="AB16" s="319" t="n"/>
+      <c r="AC16" s="319" t="n"/>
+      <c r="AD16" s="319" t="n"/>
+      <c r="AE16" s="319" t="n"/>
+      <c r="AF16" s="319" t="n"/>
+      <c r="AG16" s="320" t="n"/>
+      <c r="AH16" s="607" t="n"/>
+      <c r="AI16" s="319" t="n"/>
+      <c r="AJ16" s="319" t="n"/>
+      <c r="AK16" s="320" t="n"/>
+      <c r="AL16" s="607" t="n"/>
+      <c r="AM16" s="319" t="n"/>
+      <c r="AN16" s="319" t="n"/>
+      <c r="AO16" s="320" t="n"/>
+      <c r="AP16" s="607" t="n"/>
+      <c r="AQ16" s="319" t="n"/>
+      <c r="AR16" s="319" t="n"/>
+      <c r="AS16" s="320" t="n"/>
+      <c r="AT16" s="607" t="n"/>
+      <c r="AU16" s="319" t="n"/>
+      <c r="AV16" s="319" t="n"/>
+      <c r="AW16" s="320" t="n"/>
+      <c r="AX16" s="608" t="n"/>
+      <c r="AY16" s="319" t="n"/>
+      <c r="AZ16" s="319" t="n"/>
+      <c r="BA16" s="319" t="n"/>
+      <c r="BB16" s="319" t="n"/>
+      <c r="BC16" s="319" t="n"/>
+      <c r="BD16" s="321" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="562" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="563" t="n"/>
-      <c r="E17" s="549" t="n"/>
-      <c r="F17" s="549" t="n"/>
-      <c r="G17" s="549" t="n"/>
-      <c r="H17" s="550" t="n"/>
-      <c r="I17" s="563" t="n"/>
-      <c r="J17" s="549" t="n"/>
-      <c r="K17" s="549" t="n"/>
-      <c r="L17" s="549" t="n"/>
-      <c r="M17" s="550" t="n"/>
-      <c r="N17" s="563" t="n"/>
-      <c r="O17" s="549" t="n"/>
-      <c r="P17" s="549" t="n"/>
-      <c r="Q17" s="549" t="n"/>
-      <c r="R17" s="549" t="n"/>
-      <c r="S17" s="549" t="n"/>
-      <c r="T17" s="550" t="n"/>
-      <c r="U17" s="563" t="n"/>
-      <c r="V17" s="549" t="n"/>
-      <c r="W17" s="549" t="n"/>
-      <c r="X17" s="549" t="n"/>
-      <c r="Y17" s="549" t="n"/>
-      <c r="Z17" s="550" t="n"/>
-      <c r="AA17" s="563" t="n"/>
-      <c r="AB17" s="549" t="n"/>
-      <c r="AC17" s="549" t="n"/>
-      <c r="AD17" s="549" t="n"/>
-      <c r="AE17" s="549" t="n"/>
-      <c r="AF17" s="549" t="n"/>
-      <c r="AG17" s="550" t="n"/>
-      <c r="AH17" s="563" t="n"/>
-      <c r="AI17" s="549" t="n"/>
-      <c r="AJ17" s="549" t="n"/>
-      <c r="AK17" s="550" t="n"/>
-      <c r="AL17" s="563" t="n"/>
-      <c r="AM17" s="549" t="n"/>
-      <c r="AN17" s="549" t="n"/>
-      <c r="AO17" s="550" t="n"/>
-      <c r="AP17" s="563" t="n"/>
-      <c r="AQ17" s="549" t="n"/>
-      <c r="AR17" s="549" t="n"/>
-      <c r="AS17" s="550" t="n"/>
-      <c r="AT17" s="563" t="n"/>
-      <c r="AU17" s="549" t="n"/>
-      <c r="AV17" s="549" t="n"/>
-      <c r="AW17" s="550" t="n"/>
-      <c r="AX17" s="563" t="n"/>
-      <c r="AY17" s="549" t="n"/>
-      <c r="AZ17" s="549" t="n"/>
-      <c r="BA17" s="549" t="n"/>
-      <c r="BB17" s="549" t="n"/>
-      <c r="BC17" s="549" t="n"/>
-      <c r="BD17" s="552" t="n"/>
+      <c r="A17" s="609" t="n"/>
+      <c r="B17" s="276" t="n"/>
+      <c r="C17" s="277" t="n"/>
+      <c r="D17" s="610" t="n"/>
+      <c r="E17" s="594" t="n"/>
+      <c r="F17" s="594" t="n"/>
+      <c r="G17" s="594" t="n"/>
+      <c r="H17" s="595" t="n"/>
+      <c r="I17" s="610" t="n"/>
+      <c r="J17" s="594" t="n"/>
+      <c r="K17" s="594" t="n"/>
+      <c r="L17" s="594" t="n"/>
+      <c r="M17" s="595" t="n"/>
+      <c r="N17" s="610" t="n"/>
+      <c r="O17" s="594" t="n"/>
+      <c r="P17" s="594" t="n"/>
+      <c r="Q17" s="594" t="n"/>
+      <c r="R17" s="594" t="n"/>
+      <c r="S17" s="594" t="n"/>
+      <c r="T17" s="595" t="n"/>
+      <c r="U17" s="610" t="n"/>
+      <c r="V17" s="594" t="n"/>
+      <c r="W17" s="594" t="n"/>
+      <c r="X17" s="594" t="n"/>
+      <c r="Y17" s="594" t="n"/>
+      <c r="Z17" s="595" t="n"/>
+      <c r="AA17" s="610" t="n"/>
+      <c r="AB17" s="594" t="n"/>
+      <c r="AC17" s="594" t="n"/>
+      <c r="AD17" s="594" t="n"/>
+      <c r="AE17" s="594" t="n"/>
+      <c r="AF17" s="594" t="n"/>
+      <c r="AG17" s="595" t="n"/>
+      <c r="AH17" s="610" t="n"/>
+      <c r="AI17" s="594" t="n"/>
+      <c r="AJ17" s="594" t="n"/>
+      <c r="AK17" s="595" t="n"/>
+      <c r="AL17" s="610" t="n"/>
+      <c r="AM17" s="594" t="n"/>
+      <c r="AN17" s="594" t="n"/>
+      <c r="AO17" s="595" t="n"/>
+      <c r="AP17" s="610" t="n"/>
+      <c r="AQ17" s="594" t="n"/>
+      <c r="AR17" s="594" t="n"/>
+      <c r="AS17" s="595" t="n"/>
+      <c r="AT17" s="610" t="n"/>
+      <c r="AU17" s="594" t="n"/>
+      <c r="AV17" s="594" t="n"/>
+      <c r="AW17" s="595" t="n"/>
+      <c r="AX17" s="611" t="n"/>
+      <c r="AY17" s="594" t="n"/>
+      <c r="AZ17" s="594" t="n"/>
+      <c r="BA17" s="594" t="n"/>
+      <c r="BB17" s="594" t="n"/>
+      <c r="BC17" s="594" t="n"/>
+      <c r="BD17" s="598" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="562" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="563" t="n"/>
-      <c r="E18" s="549" t="n"/>
-      <c r="F18" s="549" t="n"/>
-      <c r="G18" s="549" t="n"/>
-      <c r="H18" s="550" t="n"/>
-      <c r="I18" s="563" t="n"/>
-      <c r="J18" s="549" t="n"/>
-      <c r="K18" s="549" t="n"/>
-      <c r="L18" s="549" t="n"/>
-      <c r="M18" s="550" t="n"/>
-      <c r="N18" s="563" t="n"/>
-      <c r="O18" s="549" t="n"/>
-      <c r="P18" s="549" t="n"/>
-      <c r="Q18" s="549" t="n"/>
-      <c r="R18" s="549" t="n"/>
-      <c r="S18" s="549" t="n"/>
-      <c r="T18" s="550" t="n"/>
-      <c r="U18" s="563" t="n"/>
-      <c r="V18" s="549" t="n"/>
-      <c r="W18" s="549" t="n"/>
-      <c r="X18" s="549" t="n"/>
-      <c r="Y18" s="549" t="n"/>
-      <c r="Z18" s="550" t="n"/>
-      <c r="AA18" s="563" t="n"/>
-      <c r="AB18" s="549" t="n"/>
-      <c r="AC18" s="549" t="n"/>
-      <c r="AD18" s="549" t="n"/>
-      <c r="AE18" s="549" t="n"/>
-      <c r="AF18" s="549" t="n"/>
-      <c r="AG18" s="550" t="n"/>
-      <c r="AH18" s="563" t="n"/>
-      <c r="AI18" s="549" t="n"/>
-      <c r="AJ18" s="549" t="n"/>
-      <c r="AK18" s="550" t="n"/>
-      <c r="AL18" s="563" t="n"/>
-      <c r="AM18" s="549" t="n"/>
-      <c r="AN18" s="549" t="n"/>
-      <c r="AO18" s="550" t="n"/>
-      <c r="AP18" s="563" t="n"/>
-      <c r="AQ18" s="549" t="n"/>
-      <c r="AR18" s="549" t="n"/>
-      <c r="AS18" s="550" t="n"/>
-      <c r="AT18" s="563" t="n"/>
-      <c r="AU18" s="549" t="n"/>
-      <c r="AV18" s="549" t="n"/>
-      <c r="AW18" s="550" t="n"/>
-      <c r="AX18" s="563" t="n"/>
-      <c r="AY18" s="549" t="n"/>
-      <c r="AZ18" s="549" t="n"/>
-      <c r="BA18" s="549" t="n"/>
-      <c r="BB18" s="549" t="n"/>
-      <c r="BC18" s="549" t="n"/>
-      <c r="BD18" s="552" t="n"/>
+      <c r="A18" s="609" t="n"/>
+      <c r="B18" s="276" t="n"/>
+      <c r="C18" s="277" t="n"/>
+      <c r="D18" s="610" t="n"/>
+      <c r="E18" s="594" t="n"/>
+      <c r="F18" s="594" t="n"/>
+      <c r="G18" s="594" t="n"/>
+      <c r="H18" s="595" t="n"/>
+      <c r="I18" s="610" t="n"/>
+      <c r="J18" s="594" t="n"/>
+      <c r="K18" s="594" t="n"/>
+      <c r="L18" s="594" t="n"/>
+      <c r="M18" s="595" t="n"/>
+      <c r="N18" s="610" t="n"/>
+      <c r="O18" s="594" t="n"/>
+      <c r="P18" s="594" t="n"/>
+      <c r="Q18" s="594" t="n"/>
+      <c r="R18" s="594" t="n"/>
+      <c r="S18" s="594" t="n"/>
+      <c r="T18" s="595" t="n"/>
+      <c r="U18" s="610" t="n"/>
+      <c r="V18" s="594" t="n"/>
+      <c r="W18" s="594" t="n"/>
+      <c r="X18" s="594" t="n"/>
+      <c r="Y18" s="594" t="n"/>
+      <c r="Z18" s="595" t="n"/>
+      <c r="AA18" s="610" t="n"/>
+      <c r="AB18" s="594" t="n"/>
+      <c r="AC18" s="594" t="n"/>
+      <c r="AD18" s="594" t="n"/>
+      <c r="AE18" s="594" t="n"/>
+      <c r="AF18" s="594" t="n"/>
+      <c r="AG18" s="595" t="n"/>
+      <c r="AH18" s="610" t="n"/>
+      <c r="AI18" s="594" t="n"/>
+      <c r="AJ18" s="594" t="n"/>
+      <c r="AK18" s="595" t="n"/>
+      <c r="AL18" s="610" t="n"/>
+      <c r="AM18" s="594" t="n"/>
+      <c r="AN18" s="594" t="n"/>
+      <c r="AO18" s="595" t="n"/>
+      <c r="AP18" s="610" t="n"/>
+      <c r="AQ18" s="594" t="n"/>
+      <c r="AR18" s="594" t="n"/>
+      <c r="AS18" s="595" t="n"/>
+      <c r="AT18" s="610" t="n"/>
+      <c r="AU18" s="594" t="n"/>
+      <c r="AV18" s="594" t="n"/>
+      <c r="AW18" s="595" t="n"/>
+      <c r="AX18" s="611" t="n"/>
+      <c r="AY18" s="594" t="n"/>
+      <c r="AZ18" s="594" t="n"/>
+      <c r="BA18" s="594" t="n"/>
+      <c r="BB18" s="594" t="n"/>
+      <c r="BC18" s="594" t="n"/>
+      <c r="BD18" s="598" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="562" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="563" t="n"/>
-      <c r="E19" s="549" t="n"/>
-      <c r="F19" s="549" t="n"/>
-      <c r="G19" s="549" t="n"/>
-      <c r="H19" s="550" t="n"/>
-      <c r="I19" s="563" t="n"/>
-      <c r="J19" s="549" t="n"/>
-      <c r="K19" s="549" t="n"/>
-      <c r="L19" s="549" t="n"/>
-      <c r="M19" s="550" t="n"/>
-      <c r="N19" s="563" t="n"/>
-      <c r="O19" s="549" t="n"/>
-      <c r="P19" s="549" t="n"/>
-      <c r="Q19" s="549" t="n"/>
-      <c r="R19" s="549" t="n"/>
-      <c r="S19" s="549" t="n"/>
-      <c r="T19" s="550" t="n"/>
-      <c r="U19" s="563" t="n"/>
-      <c r="V19" s="549" t="n"/>
-      <c r="W19" s="549" t="n"/>
-      <c r="X19" s="549" t="n"/>
-      <c r="Y19" s="549" t="n"/>
-      <c r="Z19" s="550" t="n"/>
-      <c r="AA19" s="563" t="n"/>
-      <c r="AB19" s="549" t="n"/>
-      <c r="AC19" s="549" t="n"/>
-      <c r="AD19" s="549" t="n"/>
-      <c r="AE19" s="549" t="n"/>
-      <c r="AF19" s="549" t="n"/>
-      <c r="AG19" s="550" t="n"/>
-      <c r="AH19" s="563" t="n"/>
-      <c r="AI19" s="549" t="n"/>
-      <c r="AJ19" s="549" t="n"/>
-      <c r="AK19" s="550" t="n"/>
-      <c r="AL19" s="563" t="n"/>
-      <c r="AM19" s="549" t="n"/>
-      <c r="AN19" s="549" t="n"/>
-      <c r="AO19" s="550" t="n"/>
-      <c r="AP19" s="563" t="n"/>
-      <c r="AQ19" s="549" t="n"/>
-      <c r="AR19" s="549" t="n"/>
-      <c r="AS19" s="550" t="n"/>
-      <c r="AT19" s="563" t="n"/>
-      <c r="AU19" s="549" t="n"/>
-      <c r="AV19" s="549" t="n"/>
-      <c r="AW19" s="550" t="n"/>
-      <c r="AX19" s="563" t="n"/>
-      <c r="AY19" s="549" t="n"/>
-      <c r="AZ19" s="549" t="n"/>
-      <c r="BA19" s="549" t="n"/>
-      <c r="BB19" s="549" t="n"/>
-      <c r="BC19" s="549" t="n"/>
-      <c r="BD19" s="552" t="n"/>
+      <c r="A19" s="609" t="n"/>
+      <c r="B19" s="276" t="n"/>
+      <c r="C19" s="277" t="n"/>
+      <c r="D19" s="610" t="n"/>
+      <c r="E19" s="594" t="n"/>
+      <c r="F19" s="594" t="n"/>
+      <c r="G19" s="594" t="n"/>
+      <c r="H19" s="595" t="n"/>
+      <c r="I19" s="610" t="n"/>
+      <c r="J19" s="594" t="n"/>
+      <c r="K19" s="594" t="n"/>
+      <c r="L19" s="594" t="n"/>
+      <c r="M19" s="595" t="n"/>
+      <c r="N19" s="610" t="n"/>
+      <c r="O19" s="594" t="n"/>
+      <c r="P19" s="594" t="n"/>
+      <c r="Q19" s="594" t="n"/>
+      <c r="R19" s="594" t="n"/>
+      <c r="S19" s="594" t="n"/>
+      <c r="T19" s="595" t="n"/>
+      <c r="U19" s="610" t="n"/>
+      <c r="V19" s="594" t="n"/>
+      <c r="W19" s="594" t="n"/>
+      <c r="X19" s="594" t="n"/>
+      <c r="Y19" s="594" t="n"/>
+      <c r="Z19" s="595" t="n"/>
+      <c r="AA19" s="610" t="n"/>
+      <c r="AB19" s="594" t="n"/>
+      <c r="AC19" s="594" t="n"/>
+      <c r="AD19" s="594" t="n"/>
+      <c r="AE19" s="594" t="n"/>
+      <c r="AF19" s="594" t="n"/>
+      <c r="AG19" s="595" t="n"/>
+      <c r="AH19" s="610" t="n"/>
+      <c r="AI19" s="594" t="n"/>
+      <c r="AJ19" s="594" t="n"/>
+      <c r="AK19" s="595" t="n"/>
+      <c r="AL19" s="610" t="n"/>
+      <c r="AM19" s="594" t="n"/>
+      <c r="AN19" s="594" t="n"/>
+      <c r="AO19" s="595" t="n"/>
+      <c r="AP19" s="610" t="n"/>
+      <c r="AQ19" s="594" t="n"/>
+      <c r="AR19" s="594" t="n"/>
+      <c r="AS19" s="595" t="n"/>
+      <c r="AT19" s="610" t="n"/>
+      <c r="AU19" s="594" t="n"/>
+      <c r="AV19" s="594" t="n"/>
+      <c r="AW19" s="595" t="n"/>
+      <c r="AX19" s="611" t="n"/>
+      <c r="AY19" s="594" t="n"/>
+      <c r="AZ19" s="594" t="n"/>
+      <c r="BA19" s="594" t="n"/>
+      <c r="BB19" s="594" t="n"/>
+      <c r="BC19" s="594" t="n"/>
+      <c r="BD19" s="598" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="562" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="563" t="n"/>
-      <c r="E20" s="549" t="n"/>
-      <c r="F20" s="549" t="n"/>
-      <c r="G20" s="549" t="n"/>
-      <c r="H20" s="550" t="n"/>
-      <c r="I20" s="563" t="n"/>
-      <c r="J20" s="549" t="n"/>
-      <c r="K20" s="549" t="n"/>
-      <c r="L20" s="549" t="n"/>
-      <c r="M20" s="550" t="n"/>
-      <c r="N20" s="563" t="n"/>
-      <c r="O20" s="549" t="n"/>
-      <c r="P20" s="549" t="n"/>
-      <c r="Q20" s="549" t="n"/>
-      <c r="R20" s="549" t="n"/>
-      <c r="S20" s="549" t="n"/>
-      <c r="T20" s="550" t="n"/>
-      <c r="U20" s="563" t="n"/>
-      <c r="V20" s="549" t="n"/>
-      <c r="W20" s="549" t="n"/>
-      <c r="X20" s="549" t="n"/>
-      <c r="Y20" s="549" t="n"/>
-      <c r="Z20" s="550" t="n"/>
-      <c r="AA20" s="563" t="n"/>
-      <c r="AB20" s="549" t="n"/>
-      <c r="AC20" s="549" t="n"/>
-      <c r="AD20" s="549" t="n"/>
-      <c r="AE20" s="549" t="n"/>
-      <c r="AF20" s="549" t="n"/>
-      <c r="AG20" s="550" t="n"/>
-      <c r="AH20" s="563" t="n"/>
-      <c r="AI20" s="549" t="n"/>
-      <c r="AJ20" s="549" t="n"/>
-      <c r="AK20" s="550" t="n"/>
-      <c r="AL20" s="563" t="n"/>
-      <c r="AM20" s="549" t="n"/>
-      <c r="AN20" s="549" t="n"/>
-      <c r="AO20" s="550" t="n"/>
-      <c r="AP20" s="563" t="n"/>
-      <c r="AQ20" s="549" t="n"/>
-      <c r="AR20" s="549" t="n"/>
-      <c r="AS20" s="550" t="n"/>
-      <c r="AT20" s="563" t="n"/>
-      <c r="AU20" s="549" t="n"/>
-      <c r="AV20" s="549" t="n"/>
-      <c r="AW20" s="550" t="n"/>
-      <c r="AX20" s="563" t="n"/>
-      <c r="AY20" s="549" t="n"/>
-      <c r="AZ20" s="549" t="n"/>
-      <c r="BA20" s="549" t="n"/>
-      <c r="BB20" s="549" t="n"/>
-      <c r="BC20" s="549" t="n"/>
-      <c r="BD20" s="552" t="n"/>
+      <c r="A20" s="609" t="n"/>
+      <c r="B20" s="276" t="n"/>
+      <c r="C20" s="277" t="n"/>
+      <c r="D20" s="610" t="n"/>
+      <c r="E20" s="594" t="n"/>
+      <c r="F20" s="594" t="n"/>
+      <c r="G20" s="594" t="n"/>
+      <c r="H20" s="595" t="n"/>
+      <c r="I20" s="610" t="n"/>
+      <c r="J20" s="594" t="n"/>
+      <c r="K20" s="594" t="n"/>
+      <c r="L20" s="594" t="n"/>
+      <c r="M20" s="595" t="n"/>
+      <c r="N20" s="610" t="n"/>
+      <c r="O20" s="594" t="n"/>
+      <c r="P20" s="594" t="n"/>
+      <c r="Q20" s="594" t="n"/>
+      <c r="R20" s="594" t="n"/>
+      <c r="S20" s="594" t="n"/>
+      <c r="T20" s="595" t="n"/>
+      <c r="U20" s="610" t="n"/>
+      <c r="V20" s="594" t="n"/>
+      <c r="W20" s="594" t="n"/>
+      <c r="X20" s="594" t="n"/>
+      <c r="Y20" s="594" t="n"/>
+      <c r="Z20" s="595" t="n"/>
+      <c r="AA20" s="610" t="n"/>
+      <c r="AB20" s="594" t="n"/>
+      <c r="AC20" s="594" t="n"/>
+      <c r="AD20" s="594" t="n"/>
+      <c r="AE20" s="594" t="n"/>
+      <c r="AF20" s="594" t="n"/>
+      <c r="AG20" s="595" t="n"/>
+      <c r="AH20" s="610" t="n"/>
+      <c r="AI20" s="594" t="n"/>
+      <c r="AJ20" s="594" t="n"/>
+      <c r="AK20" s="595" t="n"/>
+      <c r="AL20" s="610" t="n"/>
+      <c r="AM20" s="594" t="n"/>
+      <c r="AN20" s="594" t="n"/>
+      <c r="AO20" s="595" t="n"/>
+      <c r="AP20" s="610" t="n"/>
+      <c r="AQ20" s="594" t="n"/>
+      <c r="AR20" s="594" t="n"/>
+      <c r="AS20" s="595" t="n"/>
+      <c r="AT20" s="610" t="n"/>
+      <c r="AU20" s="594" t="n"/>
+      <c r="AV20" s="594" t="n"/>
+      <c r="AW20" s="595" t="n"/>
+      <c r="AX20" s="611" t="n"/>
+      <c r="AY20" s="594" t="n"/>
+      <c r="AZ20" s="594" t="n"/>
+      <c r="BA20" s="594" t="n"/>
+      <c r="BB20" s="594" t="n"/>
+      <c r="BC20" s="594" t="n"/>
+      <c r="BD20" s="598" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="562" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="563" t="n"/>
-      <c r="E21" s="549" t="n"/>
-      <c r="F21" s="549" t="n"/>
-      <c r="G21" s="549" t="n"/>
-      <c r="H21" s="550" t="n"/>
-      <c r="I21" s="563" t="n"/>
-      <c r="J21" s="549" t="n"/>
-      <c r="K21" s="549" t="n"/>
-      <c r="L21" s="549" t="n"/>
-      <c r="M21" s="550" t="n"/>
-      <c r="N21" s="563" t="n"/>
-      <c r="O21" s="549" t="n"/>
-      <c r="P21" s="549" t="n"/>
-      <c r="Q21" s="549" t="n"/>
-      <c r="R21" s="549" t="n"/>
-      <c r="S21" s="549" t="n"/>
-      <c r="T21" s="550" t="n"/>
-      <c r="U21" s="563" t="n"/>
-      <c r="V21" s="549" t="n"/>
-      <c r="W21" s="549" t="n"/>
-      <c r="X21" s="549" t="n"/>
-      <c r="Y21" s="549" t="n"/>
-      <c r="Z21" s="550" t="n"/>
-      <c r="AA21" s="563" t="n"/>
-      <c r="AB21" s="549" t="n"/>
-      <c r="AC21" s="549" t="n"/>
-      <c r="AD21" s="549" t="n"/>
-      <c r="AE21" s="549" t="n"/>
-      <c r="AF21" s="549" t="n"/>
-      <c r="AG21" s="550" t="n"/>
-      <c r="AH21" s="563" t="n"/>
-      <c r="AI21" s="549" t="n"/>
-      <c r="AJ21" s="549" t="n"/>
-      <c r="AK21" s="550" t="n"/>
-      <c r="AL21" s="563" t="n"/>
-      <c r="AM21" s="549" t="n"/>
-      <c r="AN21" s="549" t="n"/>
-      <c r="AO21" s="550" t="n"/>
-      <c r="AP21" s="563" t="n"/>
-      <c r="AQ21" s="549" t="n"/>
-      <c r="AR21" s="549" t="n"/>
-      <c r="AS21" s="550" t="n"/>
-      <c r="AT21" s="563" t="n"/>
-      <c r="AU21" s="549" t="n"/>
-      <c r="AV21" s="549" t="n"/>
-      <c r="AW21" s="550" t="n"/>
-      <c r="AX21" s="563" t="n"/>
-      <c r="AY21" s="549" t="n"/>
-      <c r="AZ21" s="549" t="n"/>
-      <c r="BA21" s="549" t="n"/>
-      <c r="BB21" s="549" t="n"/>
-      <c r="BC21" s="549" t="n"/>
-      <c r="BD21" s="552" t="n"/>
+      <c r="A21" s="609" t="n"/>
+      <c r="B21" s="276" t="n"/>
+      <c r="C21" s="277" t="n"/>
+      <c r="D21" s="610" t="n"/>
+      <c r="E21" s="594" t="n"/>
+      <c r="F21" s="594" t="n"/>
+      <c r="G21" s="594" t="n"/>
+      <c r="H21" s="595" t="n"/>
+      <c r="I21" s="610" t="n"/>
+      <c r="J21" s="594" t="n"/>
+      <c r="K21" s="594" t="n"/>
+      <c r="L21" s="594" t="n"/>
+      <c r="M21" s="595" t="n"/>
+      <c r="N21" s="610" t="n"/>
+      <c r="O21" s="594" t="n"/>
+      <c r="P21" s="594" t="n"/>
+      <c r="Q21" s="594" t="n"/>
+      <c r="R21" s="594" t="n"/>
+      <c r="S21" s="594" t="n"/>
+      <c r="T21" s="595" t="n"/>
+      <c r="U21" s="610" t="n"/>
+      <c r="V21" s="594" t="n"/>
+      <c r="W21" s="594" t="n"/>
+      <c r="X21" s="594" t="n"/>
+      <c r="Y21" s="594" t="n"/>
+      <c r="Z21" s="595" t="n"/>
+      <c r="AA21" s="610" t="n"/>
+      <c r="AB21" s="594" t="n"/>
+      <c r="AC21" s="594" t="n"/>
+      <c r="AD21" s="594" t="n"/>
+      <c r="AE21" s="594" t="n"/>
+      <c r="AF21" s="594" t="n"/>
+      <c r="AG21" s="595" t="n"/>
+      <c r="AH21" s="610" t="n"/>
+      <c r="AI21" s="594" t="n"/>
+      <c r="AJ21" s="594" t="n"/>
+      <c r="AK21" s="595" t="n"/>
+      <c r="AL21" s="610" t="n"/>
+      <c r="AM21" s="594" t="n"/>
+      <c r="AN21" s="594" t="n"/>
+      <c r="AO21" s="595" t="n"/>
+      <c r="AP21" s="610" t="n"/>
+      <c r="AQ21" s="594" t="n"/>
+      <c r="AR21" s="594" t="n"/>
+      <c r="AS21" s="595" t="n"/>
+      <c r="AT21" s="610" t="n"/>
+      <c r="AU21" s="594" t="n"/>
+      <c r="AV21" s="594" t="n"/>
+      <c r="AW21" s="595" t="n"/>
+      <c r="AX21" s="611" t="n"/>
+      <c r="AY21" s="594" t="n"/>
+      <c r="AZ21" s="594" t="n"/>
+      <c r="BA21" s="594" t="n"/>
+      <c r="BB21" s="594" t="n"/>
+      <c r="BC21" s="594" t="n"/>
+      <c r="BD21" s="598" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="562" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="563" t="n"/>
-      <c r="E22" s="549" t="n"/>
-      <c r="F22" s="549" t="n"/>
-      <c r="G22" s="549" t="n"/>
-      <c r="H22" s="550" t="n"/>
-      <c r="I22" s="563" t="n"/>
-      <c r="J22" s="549" t="n"/>
-      <c r="K22" s="549" t="n"/>
-      <c r="L22" s="549" t="n"/>
-      <c r="M22" s="550" t="n"/>
-      <c r="N22" s="563" t="n"/>
-      <c r="O22" s="549" t="n"/>
-      <c r="P22" s="549" t="n"/>
-      <c r="Q22" s="549" t="n"/>
-      <c r="R22" s="549" t="n"/>
-      <c r="S22" s="549" t="n"/>
-      <c r="T22" s="550" t="n"/>
-      <c r="U22" s="563" t="n"/>
-      <c r="V22" s="549" t="n"/>
-      <c r="W22" s="549" t="n"/>
-      <c r="X22" s="549" t="n"/>
-      <c r="Y22" s="549" t="n"/>
-      <c r="Z22" s="550" t="n"/>
-      <c r="AA22" s="563" t="n"/>
-      <c r="AB22" s="549" t="n"/>
-      <c r="AC22" s="549" t="n"/>
-      <c r="AD22" s="549" t="n"/>
-      <c r="AE22" s="549" t="n"/>
-      <c r="AF22" s="549" t="n"/>
-      <c r="AG22" s="550" t="n"/>
-      <c r="AH22" s="563" t="n"/>
-      <c r="AI22" s="549" t="n"/>
-      <c r="AJ22" s="549" t="n"/>
-      <c r="AK22" s="550" t="n"/>
-      <c r="AL22" s="563" t="n"/>
-      <c r="AM22" s="549" t="n"/>
-      <c r="AN22" s="549" t="n"/>
-      <c r="AO22" s="550" t="n"/>
-      <c r="AP22" s="563" t="n"/>
-      <c r="AQ22" s="549" t="n"/>
-      <c r="AR22" s="549" t="n"/>
-      <c r="AS22" s="550" t="n"/>
-      <c r="AT22" s="563" t="n"/>
-      <c r="AU22" s="549" t="n"/>
-      <c r="AV22" s="549" t="n"/>
-      <c r="AW22" s="550" t="n"/>
-      <c r="AX22" s="563" t="n"/>
-      <c r="AY22" s="549" t="n"/>
-      <c r="AZ22" s="549" t="n"/>
-      <c r="BA22" s="549" t="n"/>
-      <c r="BB22" s="549" t="n"/>
-      <c r="BC22" s="549" t="n"/>
-      <c r="BD22" s="552" t="n"/>
+      <c r="A22" s="609" t="n"/>
+      <c r="B22" s="276" t="n"/>
+      <c r="C22" s="277" t="n"/>
+      <c r="D22" s="610" t="n"/>
+      <c r="E22" s="594" t="n"/>
+      <c r="F22" s="594" t="n"/>
+      <c r="G22" s="594" t="n"/>
+      <c r="H22" s="595" t="n"/>
+      <c r="I22" s="610" t="n"/>
+      <c r="J22" s="594" t="n"/>
+      <c r="K22" s="594" t="n"/>
+      <c r="L22" s="594" t="n"/>
+      <c r="M22" s="595" t="n"/>
+      <c r="N22" s="610" t="n"/>
+      <c r="O22" s="594" t="n"/>
+      <c r="P22" s="594" t="n"/>
+      <c r="Q22" s="594" t="n"/>
+      <c r="R22" s="594" t="n"/>
+      <c r="S22" s="594" t="n"/>
+      <c r="T22" s="595" t="n"/>
+      <c r="U22" s="610" t="n"/>
+      <c r="V22" s="594" t="n"/>
+      <c r="W22" s="594" t="n"/>
+      <c r="X22" s="594" t="n"/>
+      <c r="Y22" s="594" t="n"/>
+      <c r="Z22" s="595" t="n"/>
+      <c r="AA22" s="610" t="n"/>
+      <c r="AB22" s="594" t="n"/>
+      <c r="AC22" s="594" t="n"/>
+      <c r="AD22" s="594" t="n"/>
+      <c r="AE22" s="594" t="n"/>
+      <c r="AF22" s="594" t="n"/>
+      <c r="AG22" s="595" t="n"/>
+      <c r="AH22" s="610" t="n"/>
+      <c r="AI22" s="594" t="n"/>
+      <c r="AJ22" s="594" t="n"/>
+      <c r="AK22" s="595" t="n"/>
+      <c r="AL22" s="610" t="n"/>
+      <c r="AM22" s="594" t="n"/>
+      <c r="AN22" s="594" t="n"/>
+      <c r="AO22" s="595" t="n"/>
+      <c r="AP22" s="610" t="n"/>
+      <c r="AQ22" s="594" t="n"/>
+      <c r="AR22" s="594" t="n"/>
+      <c r="AS22" s="595" t="n"/>
+      <c r="AT22" s="610" t="n"/>
+      <c r="AU22" s="594" t="n"/>
+      <c r="AV22" s="594" t="n"/>
+      <c r="AW22" s="595" t="n"/>
+      <c r="AX22" s="611" t="n"/>
+      <c r="AY22" s="594" t="n"/>
+      <c r="AZ22" s="594" t="n"/>
+      <c r="BA22" s="594" t="n"/>
+      <c r="BB22" s="594" t="n"/>
+      <c r="BC22" s="594" t="n"/>
+      <c r="BD22" s="598" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="562" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="563" t="n"/>
-      <c r="E23" s="549" t="n"/>
-      <c r="F23" s="549" t="n"/>
-      <c r="G23" s="549" t="n"/>
-      <c r="H23" s="550" t="n"/>
-      <c r="I23" s="563" t="n"/>
-      <c r="J23" s="549" t="n"/>
-      <c r="K23" s="549" t="n"/>
-      <c r="L23" s="549" t="n"/>
-      <c r="M23" s="550" t="n"/>
-      <c r="N23" s="563" t="n"/>
-      <c r="O23" s="549" t="n"/>
-      <c r="P23" s="549" t="n"/>
-      <c r="Q23" s="549" t="n"/>
-      <c r="R23" s="549" t="n"/>
-      <c r="S23" s="549" t="n"/>
-      <c r="T23" s="550" t="n"/>
-      <c r="U23" s="563" t="n"/>
-      <c r="V23" s="549" t="n"/>
-      <c r="W23" s="549" t="n"/>
-      <c r="X23" s="549" t="n"/>
-      <c r="Y23" s="549" t="n"/>
-      <c r="Z23" s="550" t="n"/>
-      <c r="AA23" s="563" t="n"/>
-      <c r="AB23" s="549" t="n"/>
-      <c r="AC23" s="549" t="n"/>
-      <c r="AD23" s="549" t="n"/>
-      <c r="AE23" s="549" t="n"/>
-      <c r="AF23" s="549" t="n"/>
-      <c r="AG23" s="550" t="n"/>
-      <c r="AH23" s="563" t="n"/>
-      <c r="AI23" s="549" t="n"/>
-      <c r="AJ23" s="549" t="n"/>
-      <c r="AK23" s="550" t="n"/>
-      <c r="AL23" s="563" t="n"/>
-      <c r="AM23" s="549" t="n"/>
-      <c r="AN23" s="549" t="n"/>
-      <c r="AO23" s="550" t="n"/>
-      <c r="AP23" s="563" t="n"/>
-      <c r="AQ23" s="549" t="n"/>
-      <c r="AR23" s="549" t="n"/>
-      <c r="AS23" s="550" t="n"/>
-      <c r="AT23" s="563" t="n"/>
-      <c r="AU23" s="549" t="n"/>
-      <c r="AV23" s="549" t="n"/>
-      <c r="AW23" s="550" t="n"/>
-      <c r="AX23" s="563" t="n"/>
-      <c r="AY23" s="549" t="n"/>
-      <c r="AZ23" s="549" t="n"/>
-      <c r="BA23" s="549" t="n"/>
-      <c r="BB23" s="549" t="n"/>
-      <c r="BC23" s="549" t="n"/>
-      <c r="BD23" s="552" t="n"/>
+      <c r="A23" s="609" t="n"/>
+      <c r="B23" s="276" t="n"/>
+      <c r="C23" s="277" t="n"/>
+      <c r="D23" s="610" t="n"/>
+      <c r="E23" s="594" t="n"/>
+      <c r="F23" s="594" t="n"/>
+      <c r="G23" s="594" t="n"/>
+      <c r="H23" s="595" t="n"/>
+      <c r="I23" s="610" t="n"/>
+      <c r="J23" s="594" t="n"/>
+      <c r="K23" s="594" t="n"/>
+      <c r="L23" s="594" t="n"/>
+      <c r="M23" s="595" t="n"/>
+      <c r="N23" s="610" t="n"/>
+      <c r="O23" s="594" t="n"/>
+      <c r="P23" s="594" t="n"/>
+      <c r="Q23" s="594" t="n"/>
+      <c r="R23" s="594" t="n"/>
+      <c r="S23" s="594" t="n"/>
+      <c r="T23" s="595" t="n"/>
+      <c r="U23" s="610" t="n"/>
+      <c r="V23" s="594" t="n"/>
+      <c r="W23" s="594" t="n"/>
+      <c r="X23" s="594" t="n"/>
+      <c r="Y23" s="594" t="n"/>
+      <c r="Z23" s="595" t="n"/>
+      <c r="AA23" s="610" t="n"/>
+      <c r="AB23" s="594" t="n"/>
+      <c r="AC23" s="594" t="n"/>
+      <c r="AD23" s="594" t="n"/>
+      <c r="AE23" s="594" t="n"/>
+      <c r="AF23" s="594" t="n"/>
+      <c r="AG23" s="595" t="n"/>
+      <c r="AH23" s="610" t="n"/>
+      <c r="AI23" s="594" t="n"/>
+      <c r="AJ23" s="594" t="n"/>
+      <c r="AK23" s="595" t="n"/>
+      <c r="AL23" s="610" t="n"/>
+      <c r="AM23" s="594" t="n"/>
+      <c r="AN23" s="594" t="n"/>
+      <c r="AO23" s="595" t="n"/>
+      <c r="AP23" s="610" t="n"/>
+      <c r="AQ23" s="594" t="n"/>
+      <c r="AR23" s="594" t="n"/>
+      <c r="AS23" s="595" t="n"/>
+      <c r="AT23" s="610" t="n"/>
+      <c r="AU23" s="594" t="n"/>
+      <c r="AV23" s="594" t="n"/>
+      <c r="AW23" s="595" t="n"/>
+      <c r="AX23" s="611" t="n"/>
+      <c r="AY23" s="594" t="n"/>
+      <c r="AZ23" s="594" t="n"/>
+      <c r="BA23" s="594" t="n"/>
+      <c r="BB23" s="594" t="n"/>
+      <c r="BC23" s="594" t="n"/>
+      <c r="BD23" s="598" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="562" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="563" t="n"/>
-      <c r="E24" s="549" t="n"/>
-      <c r="F24" s="549" t="n"/>
-      <c r="G24" s="549" t="n"/>
-      <c r="H24" s="550" t="n"/>
-      <c r="I24" s="563" t="n"/>
-      <c r="J24" s="549" t="n"/>
-      <c r="K24" s="549" t="n"/>
-      <c r="L24" s="549" t="n"/>
-      <c r="M24" s="550" t="n"/>
-      <c r="N24" s="563" t="n"/>
-      <c r="O24" s="549" t="n"/>
-      <c r="P24" s="549" t="n"/>
-      <c r="Q24" s="549" t="n"/>
-      <c r="R24" s="549" t="n"/>
-      <c r="S24" s="549" t="n"/>
-      <c r="T24" s="550" t="n"/>
-      <c r="U24" s="563" t="n"/>
-      <c r="V24" s="549" t="n"/>
-      <c r="W24" s="549" t="n"/>
-      <c r="X24" s="549" t="n"/>
-      <c r="Y24" s="549" t="n"/>
-      <c r="Z24" s="550" t="n"/>
-      <c r="AA24" s="563" t="n"/>
-      <c r="AB24" s="549" t="n"/>
-      <c r="AC24" s="549" t="n"/>
-      <c r="AD24" s="549" t="n"/>
-      <c r="AE24" s="549" t="n"/>
-      <c r="AF24" s="549" t="n"/>
-      <c r="AG24" s="550" t="n"/>
-      <c r="AH24" s="563" t="n"/>
-      <c r="AI24" s="549" t="n"/>
-      <c r="AJ24" s="549" t="n"/>
-      <c r="AK24" s="550" t="n"/>
-      <c r="AL24" s="563" t="n"/>
-      <c r="AM24" s="549" t="n"/>
-      <c r="AN24" s="549" t="n"/>
-      <c r="AO24" s="550" t="n"/>
-      <c r="AP24" s="563" t="n"/>
-      <c r="AQ24" s="549" t="n"/>
-      <c r="AR24" s="549" t="n"/>
-      <c r="AS24" s="550" t="n"/>
-      <c r="AT24" s="563" t="n"/>
-      <c r="AU24" s="549" t="n"/>
-      <c r="AV24" s="549" t="n"/>
-      <c r="AW24" s="550" t="n"/>
-      <c r="AX24" s="563" t="n"/>
-      <c r="AY24" s="549" t="n"/>
-      <c r="AZ24" s="549" t="n"/>
-      <c r="BA24" s="549" t="n"/>
-      <c r="BB24" s="549" t="n"/>
-      <c r="BC24" s="549" t="n"/>
-      <c r="BD24" s="552" t="n"/>
+      <c r="A24" s="609" t="n"/>
+      <c r="B24" s="276" t="n"/>
+      <c r="C24" s="277" t="n"/>
+      <c r="D24" s="610" t="n"/>
+      <c r="E24" s="594" t="n"/>
+      <c r="F24" s="594" t="n"/>
+      <c r="G24" s="594" t="n"/>
+      <c r="H24" s="595" t="n"/>
+      <c r="I24" s="610" t="n"/>
+      <c r="J24" s="594" t="n"/>
+      <c r="K24" s="594" t="n"/>
+      <c r="L24" s="594" t="n"/>
+      <c r="M24" s="595" t="n"/>
+      <c r="N24" s="610" t="n"/>
+      <c r="O24" s="594" t="n"/>
+      <c r="P24" s="594" t="n"/>
+      <c r="Q24" s="594" t="n"/>
+      <c r="R24" s="594" t="n"/>
+      <c r="S24" s="594" t="n"/>
+      <c r="T24" s="595" t="n"/>
+      <c r="U24" s="610" t="n"/>
+      <c r="V24" s="594" t="n"/>
+      <c r="W24" s="594" t="n"/>
+      <c r="X24" s="594" t="n"/>
+      <c r="Y24" s="594" t="n"/>
+      <c r="Z24" s="595" t="n"/>
+      <c r="AA24" s="610" t="n"/>
+      <c r="AB24" s="594" t="n"/>
+      <c r="AC24" s="594" t="n"/>
+      <c r="AD24" s="594" t="n"/>
+      <c r="AE24" s="594" t="n"/>
+      <c r="AF24" s="594" t="n"/>
+      <c r="AG24" s="595" t="n"/>
+      <c r="AH24" s="610" t="n"/>
+      <c r="AI24" s="594" t="n"/>
+      <c r="AJ24" s="594" t="n"/>
+      <c r="AK24" s="595" t="n"/>
+      <c r="AL24" s="610" t="n"/>
+      <c r="AM24" s="594" t="n"/>
+      <c r="AN24" s="594" t="n"/>
+      <c r="AO24" s="595" t="n"/>
+      <c r="AP24" s="610" t="n"/>
+      <c r="AQ24" s="594" t="n"/>
+      <c r="AR24" s="594" t="n"/>
+      <c r="AS24" s="595" t="n"/>
+      <c r="AT24" s="610" t="n"/>
+      <c r="AU24" s="594" t="n"/>
+      <c r="AV24" s="594" t="n"/>
+      <c r="AW24" s="595" t="n"/>
+      <c r="AX24" s="611" t="n"/>
+      <c r="AY24" s="594" t="n"/>
+      <c r="AZ24" s="594" t="n"/>
+      <c r="BA24" s="594" t="n"/>
+      <c r="BB24" s="594" t="n"/>
+      <c r="BC24" s="594" t="n"/>
+      <c r="BD24" s="598" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="562" t="n"/>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="563" t="n"/>
-      <c r="E25" s="549" t="n"/>
-      <c r="F25" s="549" t="n"/>
-      <c r="G25" s="549" t="n"/>
-      <c r="H25" s="550" t="n"/>
-      <c r="I25" s="563" t="n"/>
-      <c r="J25" s="549" t="n"/>
-      <c r="K25" s="549" t="n"/>
-      <c r="L25" s="549" t="n"/>
-      <c r="M25" s="550" t="n"/>
-      <c r="N25" s="563" t="n"/>
-      <c r="O25" s="549" t="n"/>
-      <c r="P25" s="549" t="n"/>
-      <c r="Q25" s="549" t="n"/>
-      <c r="R25" s="549" t="n"/>
-      <c r="S25" s="549" t="n"/>
-      <c r="T25" s="550" t="n"/>
-      <c r="U25" s="563" t="n"/>
-      <c r="V25" s="549" t="n"/>
-      <c r="W25" s="549" t="n"/>
-      <c r="X25" s="549" t="n"/>
-      <c r="Y25" s="549" t="n"/>
-      <c r="Z25" s="550" t="n"/>
-      <c r="AA25" s="563" t="n"/>
-      <c r="AB25" s="549" t="n"/>
-      <c r="AC25" s="549" t="n"/>
-      <c r="AD25" s="549" t="n"/>
-      <c r="AE25" s="549" t="n"/>
-      <c r="AF25" s="549" t="n"/>
-      <c r="AG25" s="550" t="n"/>
-      <c r="AH25" s="563" t="n"/>
-      <c r="AI25" s="549" t="n"/>
-      <c r="AJ25" s="549" t="n"/>
-      <c r="AK25" s="550" t="n"/>
-      <c r="AL25" s="563" t="n"/>
-      <c r="AM25" s="549" t="n"/>
-      <c r="AN25" s="549" t="n"/>
-      <c r="AO25" s="550" t="n"/>
-      <c r="AP25" s="563" t="n"/>
-      <c r="AQ25" s="549" t="n"/>
-      <c r="AR25" s="549" t="n"/>
-      <c r="AS25" s="550" t="n"/>
-      <c r="AT25" s="563" t="n"/>
-      <c r="AU25" s="549" t="n"/>
-      <c r="AV25" s="549" t="n"/>
-      <c r="AW25" s="550" t="n"/>
-      <c r="AX25" s="563" t="n"/>
-      <c r="AY25" s="549" t="n"/>
-      <c r="AZ25" s="549" t="n"/>
-      <c r="BA25" s="549" t="n"/>
-      <c r="BB25" s="549" t="n"/>
-      <c r="BC25" s="549" t="n"/>
-      <c r="BD25" s="552" t="n"/>
+      <c r="A25" s="609" t="n"/>
+      <c r="B25" s="276" t="n"/>
+      <c r="C25" s="277" t="n"/>
+      <c r="D25" s="610" t="n"/>
+      <c r="E25" s="594" t="n"/>
+      <c r="F25" s="594" t="n"/>
+      <c r="G25" s="594" t="n"/>
+      <c r="H25" s="595" t="n"/>
+      <c r="I25" s="610" t="n"/>
+      <c r="J25" s="594" t="n"/>
+      <c r="K25" s="594" t="n"/>
+      <c r="L25" s="594" t="n"/>
+      <c r="M25" s="595" t="n"/>
+      <c r="N25" s="610" t="n"/>
+      <c r="O25" s="594" t="n"/>
+      <c r="P25" s="594" t="n"/>
+      <c r="Q25" s="594" t="n"/>
+      <c r="R25" s="594" t="n"/>
+      <c r="S25" s="594" t="n"/>
+      <c r="T25" s="595" t="n"/>
+      <c r="U25" s="610" t="n"/>
+      <c r="V25" s="594" t="n"/>
+      <c r="W25" s="594" t="n"/>
+      <c r="X25" s="594" t="n"/>
+      <c r="Y25" s="594" t="n"/>
+      <c r="Z25" s="595" t="n"/>
+      <c r="AA25" s="610" t="n"/>
+      <c r="AB25" s="594" t="n"/>
+      <c r="AC25" s="594" t="n"/>
+      <c r="AD25" s="594" t="n"/>
+      <c r="AE25" s="594" t="n"/>
+      <c r="AF25" s="594" t="n"/>
+      <c r="AG25" s="595" t="n"/>
+      <c r="AH25" s="610" t="n"/>
+      <c r="AI25" s="594" t="n"/>
+      <c r="AJ25" s="594" t="n"/>
+      <c r="AK25" s="595" t="n"/>
+      <c r="AL25" s="610" t="n"/>
+      <c r="AM25" s="594" t="n"/>
+      <c r="AN25" s="594" t="n"/>
+      <c r="AO25" s="595" t="n"/>
+      <c r="AP25" s="610" t="n"/>
+      <c r="AQ25" s="594" t="n"/>
+      <c r="AR25" s="594" t="n"/>
+      <c r="AS25" s="595" t="n"/>
+      <c r="AT25" s="610" t="n"/>
+      <c r="AU25" s="594" t="n"/>
+      <c r="AV25" s="594" t="n"/>
+      <c r="AW25" s="595" t="n"/>
+      <c r="AX25" s="611" t="n"/>
+      <c r="AY25" s="594" t="n"/>
+      <c r="AZ25" s="594" t="n"/>
+      <c r="BA25" s="594" t="n"/>
+      <c r="BB25" s="594" t="n"/>
+      <c r="BC25" s="594" t="n"/>
+      <c r="BD25" s="598" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="562" t="n"/>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="563" t="n"/>
-      <c r="E26" s="549" t="n"/>
-      <c r="F26" s="549" t="n"/>
-      <c r="G26" s="549" t="n"/>
-      <c r="H26" s="550" t="n"/>
-      <c r="I26" s="563" t="n"/>
-      <c r="J26" s="549" t="n"/>
-      <c r="K26" s="549" t="n"/>
-      <c r="L26" s="549" t="n"/>
-      <c r="M26" s="550" t="n"/>
-      <c r="N26" s="563" t="n"/>
-      <c r="O26" s="549" t="n"/>
-      <c r="P26" s="549" t="n"/>
-      <c r="Q26" s="549" t="n"/>
-      <c r="R26" s="549" t="n"/>
-      <c r="S26" s="549" t="n"/>
-      <c r="T26" s="550" t="n"/>
-      <c r="U26" s="563" t="n"/>
-      <c r="V26" s="549" t="n"/>
-      <c r="W26" s="549" t="n"/>
-      <c r="X26" s="549" t="n"/>
-      <c r="Y26" s="549" t="n"/>
-      <c r="Z26" s="550" t="n"/>
-      <c r="AA26" s="563" t="n"/>
-      <c r="AB26" s="549" t="n"/>
-      <c r="AC26" s="549" t="n"/>
-      <c r="AD26" s="549" t="n"/>
-      <c r="AE26" s="549" t="n"/>
-      <c r="AF26" s="549" t="n"/>
-      <c r="AG26" s="550" t="n"/>
-      <c r="AH26" s="563" t="n"/>
-      <c r="AI26" s="549" t="n"/>
-      <c r="AJ26" s="549" t="n"/>
-      <c r="AK26" s="550" t="n"/>
-      <c r="AL26" s="563" t="n"/>
-      <c r="AM26" s="549" t="n"/>
-      <c r="AN26" s="549" t="n"/>
-      <c r="AO26" s="550" t="n"/>
-      <c r="AP26" s="563" t="n"/>
-      <c r="AQ26" s="549" t="n"/>
-      <c r="AR26" s="549" t="n"/>
-      <c r="AS26" s="550" t="n"/>
-      <c r="AT26" s="563" t="n"/>
-      <c r="AU26" s="549" t="n"/>
-      <c r="AV26" s="549" t="n"/>
-      <c r="AW26" s="550" t="n"/>
-      <c r="AX26" s="563" t="n"/>
-      <c r="AY26" s="549" t="n"/>
-      <c r="AZ26" s="549" t="n"/>
-      <c r="BA26" s="549" t="n"/>
-      <c r="BB26" s="549" t="n"/>
-      <c r="BC26" s="549" t="n"/>
-      <c r="BD26" s="552" t="n"/>
+      <c r="A26" s="609" t="n"/>
+      <c r="B26" s="276" t="n"/>
+      <c r="C26" s="277" t="n"/>
+      <c r="D26" s="610" t="n"/>
+      <c r="E26" s="594" t="n"/>
+      <c r="F26" s="594" t="n"/>
+      <c r="G26" s="594" t="n"/>
+      <c r="H26" s="595" t="n"/>
+      <c r="I26" s="610" t="n"/>
+      <c r="J26" s="594" t="n"/>
+      <c r="K26" s="594" t="n"/>
+      <c r="L26" s="594" t="n"/>
+      <c r="M26" s="595" t="n"/>
+      <c r="N26" s="610" t="n"/>
+      <c r="O26" s="594" t="n"/>
+      <c r="P26" s="594" t="n"/>
+      <c r="Q26" s="594" t="n"/>
+      <c r="R26" s="594" t="n"/>
+      <c r="S26" s="594" t="n"/>
+      <c r="T26" s="595" t="n"/>
+      <c r="U26" s="610" t="n"/>
+      <c r="V26" s="594" t="n"/>
+      <c r="W26" s="594" t="n"/>
+      <c r="X26" s="594" t="n"/>
+      <c r="Y26" s="594" t="n"/>
+      <c r="Z26" s="595" t="n"/>
+      <c r="AA26" s="610" t="n"/>
+      <c r="AB26" s="594" t="n"/>
+      <c r="AC26" s="594" t="n"/>
+      <c r="AD26" s="594" t="n"/>
+      <c r="AE26" s="594" t="n"/>
+      <c r="AF26" s="594" t="n"/>
+      <c r="AG26" s="595" t="n"/>
+      <c r="AH26" s="610" t="n"/>
+      <c r="AI26" s="594" t="n"/>
+      <c r="AJ26" s="594" t="n"/>
+      <c r="AK26" s="595" t="n"/>
+      <c r="AL26" s="610" t="n"/>
+      <c r="AM26" s="594" t="n"/>
+      <c r="AN26" s="594" t="n"/>
+      <c r="AO26" s="595" t="n"/>
+      <c r="AP26" s="610" t="n"/>
+      <c r="AQ26" s="594" t="n"/>
+      <c r="AR26" s="594" t="n"/>
+      <c r="AS26" s="595" t="n"/>
+      <c r="AT26" s="610" t="n"/>
+      <c r="AU26" s="594" t="n"/>
+      <c r="AV26" s="594" t="n"/>
+      <c r="AW26" s="595" t="n"/>
+      <c r="AX26" s="611" t="n"/>
+      <c r="AY26" s="594" t="n"/>
+      <c r="AZ26" s="594" t="n"/>
+      <c r="BA26" s="594" t="n"/>
+      <c r="BB26" s="594" t="n"/>
+      <c r="BC26" s="594" t="n"/>
+      <c r="BD26" s="598" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="564" t="n"/>
-      <c r="B27" s="19" t="n"/>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="565" t="n"/>
-      <c r="E27" s="555" t="n"/>
-      <c r="F27" s="555" t="n"/>
-      <c r="G27" s="555" t="n"/>
-      <c r="H27" s="556" t="n"/>
-      <c r="I27" s="565" t="n"/>
-      <c r="J27" s="555" t="n"/>
-      <c r="K27" s="555" t="n"/>
-      <c r="L27" s="555" t="n"/>
-      <c r="M27" s="556" t="n"/>
-      <c r="N27" s="565" t="n"/>
-      <c r="O27" s="555" t="n"/>
-      <c r="P27" s="555" t="n"/>
-      <c r="Q27" s="555" t="n"/>
-      <c r="R27" s="555" t="n"/>
-      <c r="S27" s="555" t="n"/>
-      <c r="T27" s="556" t="n"/>
-      <c r="U27" s="565" t="n"/>
-      <c r="V27" s="555" t="n"/>
-      <c r="W27" s="555" t="n"/>
-      <c r="X27" s="555" t="n"/>
-      <c r="Y27" s="555" t="n"/>
-      <c r="Z27" s="556" t="n"/>
-      <c r="AA27" s="565" t="n"/>
-      <c r="AB27" s="555" t="n"/>
-      <c r="AC27" s="555" t="n"/>
-      <c r="AD27" s="555" t="n"/>
-      <c r="AE27" s="555" t="n"/>
-      <c r="AF27" s="555" t="n"/>
-      <c r="AG27" s="556" t="n"/>
-      <c r="AH27" s="565" t="n"/>
-      <c r="AI27" s="555" t="n"/>
-      <c r="AJ27" s="555" t="n"/>
-      <c r="AK27" s="556" t="n"/>
-      <c r="AL27" s="565" t="n"/>
-      <c r="AM27" s="555" t="n"/>
-      <c r="AN27" s="555" t="n"/>
-      <c r="AO27" s="556" t="n"/>
-      <c r="AP27" s="565" t="n"/>
-      <c r="AQ27" s="555" t="n"/>
-      <c r="AR27" s="555" t="n"/>
-      <c r="AS27" s="556" t="n"/>
-      <c r="AT27" s="565" t="n"/>
-      <c r="AU27" s="555" t="n"/>
-      <c r="AV27" s="555" t="n"/>
-      <c r="AW27" s="556" t="n"/>
-      <c r="AX27" s="565" t="n"/>
-      <c r="AY27" s="555" t="n"/>
-      <c r="AZ27" s="555" t="n"/>
-      <c r="BA27" s="555" t="n"/>
-      <c r="BB27" s="555" t="n"/>
-      <c r="BC27" s="555" t="n"/>
-      <c r="BD27" s="558" t="n"/>
+      <c r="A27" s="612" t="n"/>
+      <c r="B27" s="281" t="n"/>
+      <c r="C27" s="282" t="n"/>
+      <c r="D27" s="613" t="n"/>
+      <c r="E27" s="601" t="n"/>
+      <c r="F27" s="601" t="n"/>
+      <c r="G27" s="601" t="n"/>
+      <c r="H27" s="602" t="n"/>
+      <c r="I27" s="613" t="n"/>
+      <c r="J27" s="601" t="n"/>
+      <c r="K27" s="601" t="n"/>
+      <c r="L27" s="601" t="n"/>
+      <c r="M27" s="602" t="n"/>
+      <c r="N27" s="613" t="n"/>
+      <c r="O27" s="601" t="n"/>
+      <c r="P27" s="601" t="n"/>
+      <c r="Q27" s="601" t="n"/>
+      <c r="R27" s="601" t="n"/>
+      <c r="S27" s="601" t="n"/>
+      <c r="T27" s="602" t="n"/>
+      <c r="U27" s="613" t="n"/>
+      <c r="V27" s="601" t="n"/>
+      <c r="W27" s="601" t="n"/>
+      <c r="X27" s="601" t="n"/>
+      <c r="Y27" s="601" t="n"/>
+      <c r="Z27" s="602" t="n"/>
+      <c r="AA27" s="613" t="n"/>
+      <c r="AB27" s="601" t="n"/>
+      <c r="AC27" s="601" t="n"/>
+      <c r="AD27" s="601" t="n"/>
+      <c r="AE27" s="601" t="n"/>
+      <c r="AF27" s="601" t="n"/>
+      <c r="AG27" s="602" t="n"/>
+      <c r="AH27" s="613" t="n"/>
+      <c r="AI27" s="601" t="n"/>
+      <c r="AJ27" s="601" t="n"/>
+      <c r="AK27" s="602" t="n"/>
+      <c r="AL27" s="613" t="n"/>
+      <c r="AM27" s="601" t="n"/>
+      <c r="AN27" s="601" t="n"/>
+      <c r="AO27" s="602" t="n"/>
+      <c r="AP27" s="613" t="n"/>
+      <c r="AQ27" s="601" t="n"/>
+      <c r="AR27" s="601" t="n"/>
+      <c r="AS27" s="602" t="n"/>
+      <c r="AT27" s="613" t="n"/>
+      <c r="AU27" s="601" t="n"/>
+      <c r="AV27" s="601" t="n"/>
+      <c r="AW27" s="602" t="n"/>
+      <c r="AX27" s="614" t="n"/>
+      <c r="AY27" s="601" t="n"/>
+      <c r="AZ27" s="601" t="n"/>
+      <c r="BA27" s="601" t="n"/>
+      <c r="BB27" s="601" t="n"/>
+      <c r="BC27" s="601" t="n"/>
+      <c r="BD27" s="605" t="n"/>
     </row>
     <row r="28" ht="3" customHeight="1">
       <c r="A28" s="566" t="n"/>
@@ -10428,198 +10519,198 @@
       <c r="BD28" s="559" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="540" t="inlineStr">
+      <c r="A29" s="589" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. PERIODIC REVIEW / CLOSEOUT</t>
         </is>
       </c>
-      <c r="B29" s="27" t="n"/>
-      <c r="C29" s="27" t="n"/>
-      <c r="D29" s="27" t="n"/>
-      <c r="E29" s="27" t="n"/>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
-      <c r="H29" s="27" t="n"/>
-      <c r="I29" s="27" t="n"/>
-      <c r="J29" s="27" t="n"/>
-      <c r="K29" s="27" t="n"/>
-      <c r="L29" s="27" t="n"/>
-      <c r="M29" s="27" t="n"/>
-      <c r="N29" s="27" t="n"/>
-      <c r="O29" s="27" t="n"/>
-      <c r="P29" s="27" t="n"/>
-      <c r="Q29" s="27" t="n"/>
-      <c r="R29" s="27" t="n"/>
-      <c r="S29" s="27" t="n"/>
-      <c r="T29" s="27" t="n"/>
-      <c r="U29" s="27" t="n"/>
-      <c r="V29" s="27" t="n"/>
-      <c r="W29" s="27" t="n"/>
-      <c r="X29" s="27" t="n"/>
-      <c r="Y29" s="27" t="n"/>
-      <c r="Z29" s="27" t="n"/>
-      <c r="AA29" s="27" t="n"/>
-      <c r="AB29" s="27" t="n"/>
-      <c r="AC29" s="27" t="n"/>
-      <c r="AD29" s="27" t="n"/>
-      <c r="AE29" s="27" t="n"/>
-      <c r="AF29" s="27" t="n"/>
-      <c r="AG29" s="27" t="n"/>
-      <c r="AH29" s="27" t="n"/>
-      <c r="AI29" s="27" t="n"/>
-      <c r="AJ29" s="27" t="n"/>
-      <c r="AK29" s="27" t="n"/>
-      <c r="AL29" s="27" t="n"/>
-      <c r="AM29" s="27" t="n"/>
-      <c r="AN29" s="27" t="n"/>
-      <c r="AO29" s="27" t="n"/>
-      <c r="AP29" s="27" t="n"/>
-      <c r="AQ29" s="27" t="n"/>
-      <c r="AR29" s="27" t="n"/>
-      <c r="AS29" s="27" t="n"/>
-      <c r="AT29" s="27" t="n"/>
-      <c r="AU29" s="27" t="n"/>
-      <c r="AV29" s="27" t="n"/>
-      <c r="AW29" s="27" t="n"/>
-      <c r="AX29" s="27" t="n"/>
-      <c r="AY29" s="27" t="n"/>
-      <c r="AZ29" s="27" t="n"/>
-      <c r="BA29" s="27" t="n"/>
-      <c r="BB29" s="27" t="n"/>
-      <c r="BC29" s="27" t="n"/>
-      <c r="BD29" s="28" t="n"/>
+      <c r="B29" s="285" t="n"/>
+      <c r="C29" s="285" t="n"/>
+      <c r="D29" s="285" t="n"/>
+      <c r="E29" s="285" t="n"/>
+      <c r="F29" s="285" t="n"/>
+      <c r="G29" s="285" t="n"/>
+      <c r="H29" s="285" t="n"/>
+      <c r="I29" s="285" t="n"/>
+      <c r="J29" s="285" t="n"/>
+      <c r="K29" s="285" t="n"/>
+      <c r="L29" s="285" t="n"/>
+      <c r="M29" s="285" t="n"/>
+      <c r="N29" s="285" t="n"/>
+      <c r="O29" s="285" t="n"/>
+      <c r="P29" s="285" t="n"/>
+      <c r="Q29" s="285" t="n"/>
+      <c r="R29" s="285" t="n"/>
+      <c r="S29" s="285" t="n"/>
+      <c r="T29" s="285" t="n"/>
+      <c r="U29" s="285" t="n"/>
+      <c r="V29" s="285" t="n"/>
+      <c r="W29" s="285" t="n"/>
+      <c r="X29" s="285" t="n"/>
+      <c r="Y29" s="285" t="n"/>
+      <c r="Z29" s="285" t="n"/>
+      <c r="AA29" s="285" t="n"/>
+      <c r="AB29" s="285" t="n"/>
+      <c r="AC29" s="285" t="n"/>
+      <c r="AD29" s="285" t="n"/>
+      <c r="AE29" s="285" t="n"/>
+      <c r="AF29" s="285" t="n"/>
+      <c r="AG29" s="285" t="n"/>
+      <c r="AH29" s="285" t="n"/>
+      <c r="AI29" s="285" t="n"/>
+      <c r="AJ29" s="285" t="n"/>
+      <c r="AK29" s="285" t="n"/>
+      <c r="AL29" s="285" t="n"/>
+      <c r="AM29" s="285" t="n"/>
+      <c r="AN29" s="285" t="n"/>
+      <c r="AO29" s="285" t="n"/>
+      <c r="AP29" s="285" t="n"/>
+      <c r="AQ29" s="285" t="n"/>
+      <c r="AR29" s="285" t="n"/>
+      <c r="AS29" s="285" t="n"/>
+      <c r="AT29" s="285" t="n"/>
+      <c r="AU29" s="285" t="n"/>
+      <c r="AV29" s="285" t="n"/>
+      <c r="AW29" s="285" t="n"/>
+      <c r="AX29" s="285" t="n"/>
+      <c r="AY29" s="285" t="n"/>
+      <c r="AZ29" s="285" t="n"/>
+      <c r="BA29" s="285" t="n"/>
+      <c r="BB29" s="285" t="n"/>
+      <c r="BC29" s="285" t="n"/>
+      <c r="BD29" s="286" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="541" t="inlineStr">
+      <c r="A30" s="590" t="inlineStr">
         <is>
           <t>Periodic Review Date</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="542" t="n"/>
-      <c r="L30" s="543" t="n"/>
-      <c r="M30" s="543" t="n"/>
-      <c r="N30" s="543" t="n"/>
-      <c r="O30" s="543" t="n"/>
-      <c r="P30" s="543" t="n"/>
-      <c r="Q30" s="543" t="n"/>
-      <c r="R30" s="543" t="n"/>
-      <c r="S30" s="543" t="n"/>
-      <c r="T30" s="543" t="n"/>
-      <c r="U30" s="543" t="n"/>
-      <c r="V30" s="543" t="n"/>
-      <c r="W30" s="543" t="n"/>
-      <c r="X30" s="543" t="n"/>
-      <c r="Y30" s="543" t="n"/>
-      <c r="Z30" s="543" t="n"/>
-      <c r="AA30" s="543" t="n"/>
-      <c r="AB30" s="544" t="n"/>
-      <c r="AC30" s="545" t="inlineStr">
+      <c r="B30" s="271" t="n"/>
+      <c r="C30" s="271" t="n"/>
+      <c r="D30" s="271" t="n"/>
+      <c r="E30" s="271" t="n"/>
+      <c r="F30" s="271" t="n"/>
+      <c r="G30" s="271" t="n"/>
+      <c r="H30" s="271" t="n"/>
+      <c r="I30" s="271" t="n"/>
+      <c r="J30" s="272" t="n"/>
+      <c r="K30" s="288" t="n"/>
+      <c r="L30" s="319" t="n"/>
+      <c r="M30" s="319" t="n"/>
+      <c r="N30" s="319" t="n"/>
+      <c r="O30" s="319" t="n"/>
+      <c r="P30" s="319" t="n"/>
+      <c r="Q30" s="319" t="n"/>
+      <c r="R30" s="319" t="n"/>
+      <c r="S30" s="319" t="n"/>
+      <c r="T30" s="319" t="n"/>
+      <c r="U30" s="319" t="n"/>
+      <c r="V30" s="319" t="n"/>
+      <c r="W30" s="319" t="n"/>
+      <c r="X30" s="319" t="n"/>
+      <c r="Y30" s="319" t="n"/>
+      <c r="Z30" s="319" t="n"/>
+      <c r="AA30" s="319" t="n"/>
+      <c r="AB30" s="320" t="n"/>
+      <c r="AC30" s="591" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="AD30" s="5" t="n"/>
-      <c r="AE30" s="5" t="n"/>
-      <c r="AF30" s="5" t="n"/>
-      <c r="AG30" s="5" t="n"/>
-      <c r="AH30" s="5" t="n"/>
-      <c r="AI30" s="5" t="n"/>
-      <c r="AJ30" s="5" t="n"/>
-      <c r="AK30" s="5" t="n"/>
-      <c r="AL30" s="6" t="n"/>
-      <c r="AM30" s="542" t="n"/>
-      <c r="AN30" s="543" t="n"/>
-      <c r="AO30" s="543" t="n"/>
-      <c r="AP30" s="543" t="n"/>
-      <c r="AQ30" s="543" t="n"/>
-      <c r="AR30" s="543" t="n"/>
-      <c r="AS30" s="543" t="n"/>
-      <c r="AT30" s="543" t="n"/>
-      <c r="AU30" s="543" t="n"/>
-      <c r="AV30" s="543" t="n"/>
-      <c r="AW30" s="543" t="n"/>
-      <c r="AX30" s="543" t="n"/>
-      <c r="AY30" s="543" t="n"/>
-      <c r="AZ30" s="543" t="n"/>
-      <c r="BA30" s="543" t="n"/>
-      <c r="BB30" s="543" t="n"/>
-      <c r="BC30" s="543" t="n"/>
-      <c r="BD30" s="546" t="n"/>
+      <c r="AD30" s="271" t="n"/>
+      <c r="AE30" s="271" t="n"/>
+      <c r="AF30" s="271" t="n"/>
+      <c r="AG30" s="271" t="n"/>
+      <c r="AH30" s="271" t="n"/>
+      <c r="AI30" s="271" t="n"/>
+      <c r="AJ30" s="271" t="n"/>
+      <c r="AK30" s="271" t="n"/>
+      <c r="AL30" s="272" t="n"/>
+      <c r="AM30" s="290" t="n"/>
+      <c r="AN30" s="319" t="n"/>
+      <c r="AO30" s="319" t="n"/>
+      <c r="AP30" s="319" t="n"/>
+      <c r="AQ30" s="319" t="n"/>
+      <c r="AR30" s="319" t="n"/>
+      <c r="AS30" s="319" t="n"/>
+      <c r="AT30" s="319" t="n"/>
+      <c r="AU30" s="319" t="n"/>
+      <c r="AV30" s="319" t="n"/>
+      <c r="AW30" s="319" t="n"/>
+      <c r="AX30" s="319" t="n"/>
+      <c r="AY30" s="319" t="n"/>
+      <c r="AZ30" s="319" t="n"/>
+      <c r="BA30" s="319" t="n"/>
+      <c r="BB30" s="319" t="n"/>
+      <c r="BC30" s="319" t="n"/>
+      <c r="BD30" s="321" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="553" t="inlineStr">
+      <c r="A31" s="599" t="inlineStr">
         <is>
           <t>Suspect / Hold Items</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="22" t="n"/>
-      <c r="K31" s="554" t="n"/>
-      <c r="L31" s="555" t="n"/>
-      <c r="M31" s="555" t="n"/>
-      <c r="N31" s="555" t="n"/>
-      <c r="O31" s="555" t="n"/>
-      <c r="P31" s="555" t="n"/>
-      <c r="Q31" s="555" t="n"/>
-      <c r="R31" s="555" t="n"/>
-      <c r="S31" s="555" t="n"/>
-      <c r="T31" s="555" t="n"/>
-      <c r="U31" s="555" t="n"/>
-      <c r="V31" s="555" t="n"/>
-      <c r="W31" s="555" t="n"/>
-      <c r="X31" s="555" t="n"/>
-      <c r="Y31" s="555" t="n"/>
-      <c r="Z31" s="555" t="n"/>
-      <c r="AA31" s="555" t="n"/>
-      <c r="AB31" s="556" t="n"/>
-      <c r="AC31" s="557" t="inlineStr">
+      <c r="B31" s="281" t="n"/>
+      <c r="C31" s="281" t="n"/>
+      <c r="D31" s="281" t="n"/>
+      <c r="E31" s="281" t="n"/>
+      <c r="F31" s="281" t="n"/>
+      <c r="G31" s="281" t="n"/>
+      <c r="H31" s="281" t="n"/>
+      <c r="I31" s="281" t="n"/>
+      <c r="J31" s="282" t="n"/>
+      <c r="K31" s="600" t="n"/>
+      <c r="L31" s="601" t="n"/>
+      <c r="M31" s="601" t="n"/>
+      <c r="N31" s="601" t="n"/>
+      <c r="O31" s="601" t="n"/>
+      <c r="P31" s="601" t="n"/>
+      <c r="Q31" s="601" t="n"/>
+      <c r="R31" s="601" t="n"/>
+      <c r="S31" s="601" t="n"/>
+      <c r="T31" s="601" t="n"/>
+      <c r="U31" s="601" t="n"/>
+      <c r="V31" s="601" t="n"/>
+      <c r="W31" s="601" t="n"/>
+      <c r="X31" s="601" t="n"/>
+      <c r="Y31" s="601" t="n"/>
+      <c r="Z31" s="601" t="n"/>
+      <c r="AA31" s="601" t="n"/>
+      <c r="AB31" s="602" t="n"/>
+      <c r="AC31" s="603" t="inlineStr">
         <is>
           <t>Final Status</t>
         </is>
       </c>
-      <c r="AD31" s="19" t="n"/>
-      <c r="AE31" s="19" t="n"/>
-      <c r="AF31" s="19" t="n"/>
-      <c r="AG31" s="19" t="n"/>
-      <c r="AH31" s="19" t="n"/>
-      <c r="AI31" s="19" t="n"/>
-      <c r="AJ31" s="19" t="n"/>
-      <c r="AK31" s="19" t="n"/>
-      <c r="AL31" s="22" t="n"/>
-      <c r="AM31" s="554" t="n"/>
-      <c r="AN31" s="555" t="n"/>
-      <c r="AO31" s="555" t="n"/>
-      <c r="AP31" s="555" t="n"/>
-      <c r="AQ31" s="555" t="n"/>
-      <c r="AR31" s="555" t="n"/>
-      <c r="AS31" s="555" t="n"/>
-      <c r="AT31" s="555" t="n"/>
-      <c r="AU31" s="555" t="n"/>
-      <c r="AV31" s="555" t="n"/>
-      <c r="AW31" s="555" t="n"/>
-      <c r="AX31" s="555" t="n"/>
-      <c r="AY31" s="555" t="n"/>
-      <c r="AZ31" s="555" t="n"/>
-      <c r="BA31" s="555" t="n"/>
-      <c r="BB31" s="555" t="n"/>
-      <c r="BC31" s="555" t="n"/>
-      <c r="BD31" s="558" t="n"/>
+      <c r="AD31" s="281" t="n"/>
+      <c r="AE31" s="281" t="n"/>
+      <c r="AF31" s="281" t="n"/>
+      <c r="AG31" s="281" t="n"/>
+      <c r="AH31" s="281" t="n"/>
+      <c r="AI31" s="281" t="n"/>
+      <c r="AJ31" s="281" t="n"/>
+      <c r="AK31" s="281" t="n"/>
+      <c r="AL31" s="282" t="n"/>
+      <c r="AM31" s="604" t="n"/>
+      <c r="AN31" s="601" t="n"/>
+      <c r="AO31" s="601" t="n"/>
+      <c r="AP31" s="601" t="n"/>
+      <c r="AQ31" s="601" t="n"/>
+      <c r="AR31" s="601" t="n"/>
+      <c r="AS31" s="601" t="n"/>
+      <c r="AT31" s="601" t="n"/>
+      <c r="AU31" s="601" t="n"/>
+      <c r="AV31" s="601" t="n"/>
+      <c r="AW31" s="601" t="n"/>
+      <c r="AX31" s="601" t="n"/>
+      <c r="AY31" s="601" t="n"/>
+      <c r="AZ31" s="601" t="n"/>
+      <c r="BA31" s="601" t="n"/>
+      <c r="BB31" s="601" t="n"/>
+      <c r="BC31" s="601" t="n"/>
+      <c r="BD31" s="605" t="n"/>
     </row>
     <row r="32" ht="3" customHeight="1">
       <c r="A32" s="559" t="n"/>
@@ -10680,66 +10771,66 @@
       <c r="BD32" s="559" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="572" t="inlineStr">
+      <c r="A33" s="615" t="inlineStr">
         <is>
           <t>NOTICE: Review face only. Complete row-level entry, filters and frozen-header operations on sheet GAGE_DATA_LOG. Keep English only, preserve history, record owner and evidence reference, and follow controlled dropdowns / gate rules.</t>
         </is>
       </c>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="27" t="n"/>
-      <c r="J33" s="27" t="n"/>
-      <c r="K33" s="27" t="n"/>
-      <c r="L33" s="27" t="n"/>
-      <c r="M33" s="27" t="n"/>
-      <c r="N33" s="27" t="n"/>
-      <c r="O33" s="27" t="n"/>
-      <c r="P33" s="27" t="n"/>
-      <c r="Q33" s="27" t="n"/>
-      <c r="R33" s="27" t="n"/>
-      <c r="S33" s="27" t="n"/>
-      <c r="T33" s="27" t="n"/>
-      <c r="U33" s="27" t="n"/>
-      <c r="V33" s="27" t="n"/>
-      <c r="W33" s="27" t="n"/>
-      <c r="X33" s="27" t="n"/>
-      <c r="Y33" s="27" t="n"/>
-      <c r="Z33" s="27" t="n"/>
-      <c r="AA33" s="27" t="n"/>
-      <c r="AB33" s="27" t="n"/>
-      <c r="AC33" s="27" t="n"/>
-      <c r="AD33" s="27" t="n"/>
-      <c r="AE33" s="27" t="n"/>
-      <c r="AF33" s="27" t="n"/>
-      <c r="AG33" s="27" t="n"/>
-      <c r="AH33" s="27" t="n"/>
-      <c r="AI33" s="27" t="n"/>
-      <c r="AJ33" s="27" t="n"/>
-      <c r="AK33" s="27" t="n"/>
-      <c r="AL33" s="27" t="n"/>
-      <c r="AM33" s="27" t="n"/>
-      <c r="AN33" s="27" t="n"/>
-      <c r="AO33" s="27" t="n"/>
-      <c r="AP33" s="27" t="n"/>
-      <c r="AQ33" s="27" t="n"/>
-      <c r="AR33" s="27" t="n"/>
-      <c r="AS33" s="27" t="n"/>
-      <c r="AT33" s="27" t="n"/>
-      <c r="AU33" s="27" t="n"/>
-      <c r="AV33" s="27" t="n"/>
-      <c r="AW33" s="27" t="n"/>
-      <c r="AX33" s="27" t="n"/>
-      <c r="AY33" s="27" t="n"/>
-      <c r="AZ33" s="27" t="n"/>
-      <c r="BA33" s="27" t="n"/>
-      <c r="BB33" s="27" t="n"/>
-      <c r="BC33" s="27" t="n"/>
-      <c r="BD33" s="28" t="n"/>
+      <c r="B33" s="285" t="n"/>
+      <c r="C33" s="285" t="n"/>
+      <c r="D33" s="285" t="n"/>
+      <c r="E33" s="285" t="n"/>
+      <c r="F33" s="285" t="n"/>
+      <c r="G33" s="285" t="n"/>
+      <c r="H33" s="285" t="n"/>
+      <c r="I33" s="285" t="n"/>
+      <c r="J33" s="285" t="n"/>
+      <c r="K33" s="285" t="n"/>
+      <c r="L33" s="285" t="n"/>
+      <c r="M33" s="285" t="n"/>
+      <c r="N33" s="285" t="n"/>
+      <c r="O33" s="285" t="n"/>
+      <c r="P33" s="285" t="n"/>
+      <c r="Q33" s="285" t="n"/>
+      <c r="R33" s="285" t="n"/>
+      <c r="S33" s="285" t="n"/>
+      <c r="T33" s="285" t="n"/>
+      <c r="U33" s="285" t="n"/>
+      <c r="V33" s="285" t="n"/>
+      <c r="W33" s="285" t="n"/>
+      <c r="X33" s="285" t="n"/>
+      <c r="Y33" s="285" t="n"/>
+      <c r="Z33" s="285" t="n"/>
+      <c r="AA33" s="285" t="n"/>
+      <c r="AB33" s="285" t="n"/>
+      <c r="AC33" s="285" t="n"/>
+      <c r="AD33" s="285" t="n"/>
+      <c r="AE33" s="285" t="n"/>
+      <c r="AF33" s="285" t="n"/>
+      <c r="AG33" s="285" t="n"/>
+      <c r="AH33" s="285" t="n"/>
+      <c r="AI33" s="285" t="n"/>
+      <c r="AJ33" s="285" t="n"/>
+      <c r="AK33" s="285" t="n"/>
+      <c r="AL33" s="285" t="n"/>
+      <c r="AM33" s="285" t="n"/>
+      <c r="AN33" s="285" t="n"/>
+      <c r="AO33" s="285" t="n"/>
+      <c r="AP33" s="285" t="n"/>
+      <c r="AQ33" s="285" t="n"/>
+      <c r="AR33" s="285" t="n"/>
+      <c r="AS33" s="285" t="n"/>
+      <c r="AT33" s="285" t="n"/>
+      <c r="AU33" s="285" t="n"/>
+      <c r="AV33" s="285" t="n"/>
+      <c r="AW33" s="285" t="n"/>
+      <c r="AX33" s="285" t="n"/>
+      <c r="AY33" s="285" t="n"/>
+      <c r="AZ33" s="285" t="n"/>
+      <c r="BA33" s="285" t="n"/>
+      <c r="BB33" s="285" t="n"/>
+      <c r="BC33" s="285" t="n"/>
+      <c r="BD33" s="286" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1"/>
     <row r="35" ht="20" customHeight="1"/>
@@ -10968,7 +11059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11303,7 +11394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU9"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -11799,7 +11890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -12642,7 +12733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAGE_DATA_LOG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAGE_VERIFY_LOG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAGE_VERIFY_LOG" sheetId="2" state="veryHidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW_SUMMARY" sheetId="4" state="veryHidden" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
@@ -10851,9 +10851,9 @@
   <mergeCells count="189">
     <mergeCell ref="AP27:AS27"/>
     <mergeCell ref="AH26:AK26"/>
+    <mergeCell ref="AW2:BD2"/>
+    <mergeCell ref="AL17:AO17"/>
     <mergeCell ref="AA18:AG18"/>
-    <mergeCell ref="AL17:AO17"/>
-    <mergeCell ref="AW2:BD2"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="AP17:AS17"/>
     <mergeCell ref="A21:C21"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
@@ -10851,9 +10851,9 @@
   <mergeCells count="189">
     <mergeCell ref="AP27:AS27"/>
     <mergeCell ref="AH26:AK26"/>
+    <mergeCell ref="AA18:AG18"/>
+    <mergeCell ref="AL17:AO17"/>
     <mergeCell ref="AW2:BD2"/>
-    <mergeCell ref="AL17:AO17"/>
-    <mergeCell ref="AA18:AG18"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="AP17:AS17"/>
     <mergeCell ref="A21:C21"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
@@ -24,10 +24,456 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+  <si>
+    <t>  1. ACTIVE LOG TABLE</t>
+  </si>
+  <si>
+    <t>  1. SCOPE / REVIEW CONTEXT</t>
+  </si>
+  <si>
+    <t>  2. PERIODIC REVIEW / CLOSEOUT</t>
+  </si>
+  <si>
+    <t>  2. REVIEW SNAPSHOT / LIVE ENTRY ON GAGE_DATA_LOG</t>
+  </si>
+  <si>
+    <t>  3. PERIODIC REVIEW / CLOSEOUT</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$7)+1</t>
+  </si>
+  <si>
+    <t>ACTION_STATUS</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-001</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-002</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-003</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-004</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-006</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-007</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QMS-020</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
+  </si>
+  <si>
+    <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>Affected Job Ref</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>CAL STATUS ISSUE</t>
+  </si>
+  <si>
+    <t>CAL Status</t>
+  </si>
+  <si>
+    <t>CAL_STATUS_LIST</t>
+  </si>
+  <si>
+    <t>CERT MISMATCH</t>
+  </si>
+  <si>
+    <t>CLEANLINESS RISK</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>CLOSEOUT_STATE</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>Calibration / QA file + M365 evidence</t>
+  </si>
+  <si>
+    <t>Check Artifact / Master</t>
+  </si>
+  <si>
+    <t>Controlled row-level entry. Use approved dropdowns only. Do not delete history. Refer to the FACE sheet for review context and sign-off.</t>
+  </si>
+  <si>
+    <t>Count from main log where status remains open or in progress.</t>
+  </si>
+  <si>
+    <t>Criteria</t>
+  </si>
+  <si>
+    <t>Cross-Reference Boundary</t>
+  </si>
+  <si>
+    <t>DAMAGE</t>
+  </si>
+  <si>
+    <t>DISPOSITION_GATE</t>
+  </si>
+  <si>
+    <t>DOC GAP</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Define the review cycle for this log.</t>
+  </si>
+  <si>
+    <t>Do not duplicate ERP/M365/ANNEX master data.</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>EXPIRED</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Equipment ID / Description</t>
+  </si>
+  <si>
+    <t>Escalated / Blocked Items</t>
+  </si>
+  <si>
+    <t>Evidence Package Ref</t>
+  </si>
+  <si>
+    <t>Evidence Reference / Attachment Guidance</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FRM-602</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Final Status</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>Gage ID</t>
+  </si>
+  <si>
+    <t>Gage Verification Log</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>INEFFECTIVE</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Import / Reference Guidance</t>
+  </si>
+  <si>
+    <t>Import or reference keys from Epicor / M365 / calibration master rather than re-keying duplicates.</t>
+  </si>
+  <si>
+    <t>LATE DELIVERY</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>Method / Acceptance Ref</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NOT CLOSED</t>
+  </si>
+  <si>
+    <t>NOTICE: Complete in English. Do not back-date, delete history, or overwrite a closed row without a controlled supplemental entry. Review / sign-off context remains on sheet GAGE_VERIFY_LOG.</t>
+  </si>
+  <si>
+    <t>NOTICE: Review face only. Complete row-level entry, filters and frozen-header operations on sheet GAGE_DATA_LOG. Keep English only, preserve history, record owner and evidence reference, and follow controlled dropdowns / gate rules.</t>
+  </si>
+  <si>
+    <t>No per-row release signature is required unless a row contains an explicit disposition or escalation. A named owner shall review the register or log at the defined cadence, and any formal period-end review shall be signed or e-signed by the responsible owner.</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>OVERDUE</t>
+  </si>
+  <si>
+    <t>OWNER_DEPT</t>
+  </si>
+  <si>
+    <t>Open Items</t>
+  </si>
+  <si>
+    <t>Open Items / Exceptions</t>
+  </si>
+  <si>
+    <t>Operational Data Sheet · FRM-602 · Owner: QA</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Owner Dept</t>
+  </si>
+  <si>
+    <t>PACKAGING ISSUE</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>PUR</t>
+  </si>
+  <si>
+    <t>Periodic Review Date</t>
+  </si>
+  <si>
+    <t>Periodic Review Summary</t>
+  </si>
+  <si>
+    <t>Pre-use gage-verification gate before FRM-621/631/641 inspection execution and before Pack A first-piece/release decisions. Formal MSA remains in FRM-611/612/613.</t>
+  </si>
+  <si>
+    <t>Prepared by / Date-Time</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>REASON_CODE_LIST</t>
+  </si>
+  <si>
+    <t>REJECT</t>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>Reference abnormal findings that require management attention.</t>
+  </si>
+  <si>
+    <t>Responsible Owner</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Review Conclusion</t>
+  </si>
+  <si>
+    <t>Review Date</t>
+  </si>
+  <si>
+    <t>Review Period</t>
+  </si>
+  <si>
+    <t>Reviewer</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SOP SOP-601</t>
+  </si>
+  <si>
+    <t>SOP-601 — Hiệu chuẩn và kiểm soát dụng cụ đo | HESEM QMS</t>
+  </si>
+  <si>
+    <t>SPEC DEVIATION</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>SUSPECT</t>
+  </si>
+  <si>
+    <t>Source of Truth</t>
+  </si>
+  <si>
+    <t>Suspect / Hold Items</t>
+  </si>
+  <si>
+    <t>TRACEABILITY BREAK</t>
+  </si>
+  <si>
+    <t>This form does not replace SOP-601; it records the evidence, data or decision required by that SOP.
+Detailed task execution belongs in WI-602; this form captures results, checks, decisions or exceptions only.
+Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-001/002/003/004/006/007 + ANNEX-QMS-020; do not copy ANNEX content into the live data-entry body.
+System-of-record / source-of-truth boundary: Calibration / QA file + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
+  </si>
+  <si>
+    <t>Use Stop (Y/N)</t>
+  </si>
+  <si>
+    <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
+  </si>
+  <si>
+    <t>Use final status field on the main sheet for period closeout.</t>
+  </si>
+  <si>
+    <t>User / Area</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VALID</t>
+  </si>
+  <si>
+    <t>VERIFIED</t>
+  </si>
+  <si>
+    <t>Value / Reference</t>
+  </si>
+  <si>
+    <t>Verification ID</t>
+  </si>
+  <si>
+    <t>Verification Result</t>
+  </si>
+  <si>
+    <t>Verification Type</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>WI WI-602</t>
+  </si>
+  <si>
+    <t>WI-602 — Kiểm trước khi dùng dụng cụ đo, trạng thái CAL và xử lý nghi ngờ</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>YES_NO</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-601-calibration-and-gage-control.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-602-gage-pre-use-verification-and-status-control.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="86">
+  <fonts count="87">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -514,8 +960,13 @@
       <color rgb="001B3A6B"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="52">
+  <fills count="53">
     <fill>
       <patternFill/>
     </fill>
@@ -772,8 +1223,13 @@
         <fgColor rgb="002C9CD7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="367">
+  <borders count="370">
     <border>
       <left/>
       <right/>
@@ -4736,11 +5192,45 @@
       </top>
       <bottom/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="616">
+  <cellXfs count="619">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6245,6 +6735,15 @@
     </xf>
     <xf numFmtId="0" fontId="85" fillId="4" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8713,51 +9212,51 @@
       <c r="AM41" s="464" t="n"/>
       <c r="AN41" s="465" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="466" t="inlineStr">
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="616" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. Do not back-date, delete history, or overwrite a closed row without a controlled supplemental entry. Review / sign-off context remains on sheet GAGE_VERIFY_LOG.</t>
         </is>
       </c>
-      <c r="B42" s="522" t="n"/>
-      <c r="C42" s="522" t="n"/>
-      <c r="D42" s="522" t="n"/>
-      <c r="E42" s="522" t="n"/>
-      <c r="F42" s="522" t="n"/>
-      <c r="G42" s="522" t="n"/>
-      <c r="H42" s="522" t="n"/>
-      <c r="I42" s="522" t="n"/>
-      <c r="J42" s="522" t="n"/>
-      <c r="K42" s="522" t="n"/>
-      <c r="L42" s="467" t="n"/>
-      <c r="M42" s="467" t="n"/>
-      <c r="N42" s="467" t="n"/>
-      <c r="O42" s="467" t="n"/>
-      <c r="P42" s="467" t="n"/>
-      <c r="Q42" s="467" t="n"/>
-      <c r="R42" s="467" t="n"/>
-      <c r="S42" s="467" t="n"/>
-      <c r="T42" s="467" t="n"/>
-      <c r="U42" s="467" t="n"/>
-      <c r="V42" s="467" t="n"/>
-      <c r="W42" s="467" t="n"/>
-      <c r="X42" s="467" t="n"/>
-      <c r="Y42" s="467" t="n"/>
-      <c r="Z42" s="467" t="n"/>
-      <c r="AA42" s="467" t="n"/>
-      <c r="AB42" s="467" t="n"/>
-      <c r="AC42" s="467" t="n"/>
-      <c r="AD42" s="467" t="n"/>
-      <c r="AE42" s="467" t="n"/>
-      <c r="AF42" s="467" t="n"/>
-      <c r="AG42" s="467" t="n"/>
-      <c r="AH42" s="467" t="n"/>
-      <c r="AI42" s="467" t="n"/>
-      <c r="AJ42" s="467" t="n"/>
-      <c r="AK42" s="467" t="n"/>
-      <c r="AL42" s="467" t="n"/>
-      <c r="AM42" s="467" t="n"/>
-      <c r="AN42" s="468" t="n"/>
+      <c r="B42" s="617" t="n"/>
+      <c r="C42" s="617" t="n"/>
+      <c r="D42" s="617" t="n"/>
+      <c r="E42" s="617" t="n"/>
+      <c r="F42" s="617" t="n"/>
+      <c r="G42" s="617" t="n"/>
+      <c r="H42" s="617" t="n"/>
+      <c r="I42" s="617" t="n"/>
+      <c r="J42" s="617" t="n"/>
+      <c r="K42" s="617" t="n"/>
+      <c r="L42" s="617" t="n"/>
+      <c r="M42" s="617" t="n"/>
+      <c r="N42" s="617" t="n"/>
+      <c r="O42" s="617" t="n"/>
+      <c r="P42" s="617" t="n"/>
+      <c r="Q42" s="617" t="n"/>
+      <c r="R42" s="617" t="n"/>
+      <c r="S42" s="617" t="n"/>
+      <c r="T42" s="617" t="n"/>
+      <c r="U42" s="617" t="n"/>
+      <c r="V42" s="617" t="n"/>
+      <c r="W42" s="617" t="n"/>
+      <c r="X42" s="617" t="n"/>
+      <c r="Y42" s="617" t="n"/>
+      <c r="Z42" s="617" t="n"/>
+      <c r="AA42" s="617" t="n"/>
+      <c r="AB42" s="617" t="n"/>
+      <c r="AC42" s="617" t="n"/>
+      <c r="AD42" s="617" t="n"/>
+      <c r="AE42" s="617" t="n"/>
+      <c r="AF42" s="617" t="n"/>
+      <c r="AG42" s="617" t="n"/>
+      <c r="AH42" s="617" t="n"/>
+      <c r="AI42" s="617" t="n"/>
+      <c r="AJ42" s="617" t="n"/>
+      <c r="AK42" s="617" t="n"/>
+      <c r="AL42" s="617" t="n"/>
+      <c r="AM42" s="617" t="n"/>
+      <c r="AN42" s="618" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -10851,9 +11350,9 @@
   <mergeCells count="189">
     <mergeCell ref="AP27:AS27"/>
     <mergeCell ref="AH26:AK26"/>
+    <mergeCell ref="AW2:BD2"/>
+    <mergeCell ref="AL17:AO17"/>
     <mergeCell ref="AA18:AG18"/>
-    <mergeCell ref="AL17:AO17"/>
-    <mergeCell ref="AW2:BD2"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="AP17:AS17"/>
     <mergeCell ref="A21:C21"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
@@ -1229,7 +1229,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="370">
+  <borders count="372">
     <border>
       <left/>
       <right/>
@@ -5225,6 +5225,26 @@
       <bottom style="thin">
         <color rgb="00F9A825"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">

--- a/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
@@ -4513,6 +4513,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4576,6 +4579,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4606,6 +4612,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4636,6 +4645,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5586,6 +5598,7 @@
       <c r="J36" s="333" t="n"/>
       <c r="K36" s="333" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="331" t="inlineStr">
         <is>
@@ -5645,6 +5658,7 @@
       <c r="J40" s="285" t="n"/>
       <c r="K40" s="286" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="336" t="inlineStr">
         <is>
@@ -7563,13 +7577,12 @@
     <row r="46" ht="4" customHeight="1"/>
     <row r="47" ht="24" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="190">
     <mergeCell ref="AP27:AS27"/>
     <mergeCell ref="AH26:AK26"/>
+    <mergeCell ref="AA18:AG18"/>
+    <mergeCell ref="AL17:AO17"/>
     <mergeCell ref="AW2:BD2"/>
-    <mergeCell ref="AL17:AO17"/>
-    <mergeCell ref="AA18:AG18"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="AP17:AS17"/>
     <mergeCell ref="A21:C21"/>
@@ -8143,6 +8156,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="291" t="inlineStr">
         <is>
@@ -8226,7 +8240,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <autoFilter ref="A4:C9"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
@@ -8275,6 +8288,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="291" t="inlineStr">
         <is>
@@ -8483,7 +8497,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <autoFilter ref="A4:C15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
@@ -8532,6 +8545,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="291" t="inlineStr">
         <is>

--- a/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAGE_DATA_LOG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAGE_VERIFY_LOG" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW_SUMMARY" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_REF" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAGE_VERIFY_LOG" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="3" state="veryHidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW_SUMMARY" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="6" state="veryHidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'GAGE_DATA_LOG'!$A$1:$K$42</definedName>
@@ -5598,7 +5598,6 @@
       <c r="J36" s="333" t="n"/>
       <c r="K36" s="333" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="331" t="inlineStr">
         <is>
@@ -5658,7 +5657,6 @@
       <c r="J40" s="285" t="n"/>
       <c r="K40" s="286" t="n"/>
     </row>
-    <row r="41"/>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="336" t="inlineStr">
         <is>
@@ -8156,7 +8154,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="291" t="inlineStr">
         <is>
@@ -8288,7 +8285,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="291" t="inlineStr">
         <is>
@@ -8545,7 +8541,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="291" t="inlineStr">
         <is>

--- a/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
@@ -17,8 +17,6 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'GAGE_DATA_LOG'!$A$1:$K$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'GAGE_VERIFY_LOG'!$A$1:$BD$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REVIEW_SUMMARY'!$A$4:$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'IMPORT_REF'!$A$4:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7578,9 +7576,9 @@
   <mergeCells count="190">
     <mergeCell ref="AP27:AS27"/>
     <mergeCell ref="AH26:AK26"/>
+    <mergeCell ref="AW2:BD2"/>
+    <mergeCell ref="AL17:AO17"/>
     <mergeCell ref="AA18:AG18"/>
-    <mergeCell ref="AL17:AO17"/>
-    <mergeCell ref="AW2:BD2"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="AP17:AS17"/>
     <mergeCell ref="A21:C21"/>
@@ -8237,7 +8235,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C9"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -8493,7 +8490,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
@@ -8,15 +8,18 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAGE_DATA_LOG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAGE_VERIFY_LOG" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="3" state="veryHidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW_SUMMARY" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="6" state="veryHidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAGE_VERIFY_LOG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW_SUMMARY" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'GAGE_DATA_LOG'!$A$1:$K$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'GAGE_VERIFY_LOG'!$A$1:$BD$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REVIEW_SUMMARY'!$A$4:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'IMPORT_REF'!$A$4:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4493,11 +4496,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>161925</colOff>
+      <colOff>0</colOff>
       <row>0</row>
-      <rowOff>314325</rowOff>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1123950" cy="323850"/>
+    <ext cx="5238750" cy="1514475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -4531,105 +4534,6 @@
       <rowOff>257175</rowOff>
     </from>
     <ext cx="1552575" cy="438150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -4962,7 +4866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:AW42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5581,9 +5485,10 @@
       <c r="K35" s="333" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="338">
-        <f>ROW()-ROW($A$7)+1</f>
-        <v/>
+      <c r="A36" s="338" t="inlineStr">
+        <is>
+          <t>Linked FRM-601 / FRM-525</t>
+        </is>
       </c>
       <c r="B36" s="333" t="n"/>
       <c r="C36" s="333" t="n"/>
@@ -5596,6 +5501,7 @@
       <c r="J36" s="333" t="n"/>
       <c r="K36" s="333" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="331" t="inlineStr">
         <is>
@@ -5655,6 +5561,7 @@
       <c r="J40" s="285" t="n"/>
       <c r="K40" s="286" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="336" t="inlineStr">
         <is>
@@ -7573,6 +7480,7 @@
     <row r="46" ht="4" customHeight="1"/>
     <row r="47" ht="24" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="190">
     <mergeCell ref="AP27:AS27"/>
     <mergeCell ref="AH26:AK26"/>
@@ -8235,12 +8143,13 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <autoFilter ref="A4:C9"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8490,12 +8399,13 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <autoFilter ref="A4:C15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8750,6 +8660,85 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-601, FRM-525; Parent ref: SOP-601</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-602_Gage_Verification_Log.xlsx
@@ -757,7 +757,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="245">
+  <borders count="246">
     <border>
       <left/>
       <right/>
@@ -3511,12 +3511,16 @@
         <color rgb="000078D4"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="494">
+  <cellXfs count="495">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4707,6 +4711,7 @@
     <xf numFmtId="0" fontId="82" fillId="48" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4783,6 +4788,48 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="E9" authorId="0" shapeId="0">
+      <text>
+        <t>Mã dụng cụ
+ID từ FRM-525.</t>
+      </text>
+    </comment>
+    <comment ref="O9" authorId="0" shapeId="0">
+      <text>
+        <t>Ngày kiểm tra
+Ngày verify giữa 2 lần hiệu chuẩn.</t>
+      </text>
+    </comment>
+    <comment ref="W9" authorId="0" shapeId="0">
+      <text>
+        <t>Phương pháp
+Mô tả cách verify.
+Ví dụ: Check with gage block set, Compare with reference standard.</t>
+      </text>
+    </comment>
+    <comment ref="AI9" authorId="0" shapeId="0">
+      <text>
+        <t>Kết quả
+PASS = trong giới hạn cho phép.
+FAIL = cần gửi hiệu chuẩn lại.</t>
+      </text>
+    </comment>
+    <comment ref="AS9" authorId="0" shapeId="0">
+      <text>
+        <t>Người kiểm tra
+Tên người thực hiện verification.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -4806,6 +4853,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5417,7 +5467,7 @@
       <c r="BD6" s="30" t="n"/>
     </row>
     <row r="7" ht="4" customHeight="1" s="264">
-      <c r="A7" s="469" t="n"/>
+      <c r="A7" s="494" t="n"/>
       <c r="B7" s="26" t="n"/>
       <c r="C7" s="26" t="n"/>
       <c r="D7" s="26" t="n"/>
@@ -7119,7 +7169,7 @@
       <c r="BD34" s="492" t="n"/>
     </row>
     <row r="35" ht="4" customHeight="1" s="264">
-      <c r="A35" s="469" t="n"/>
+      <c r="A35" s="494" t="n"/>
       <c r="B35" s="26" t="n"/>
       <c r="C35" s="26" t="n"/>
       <c r="D35" s="26" t="n"/>
@@ -7179,7 +7229,7 @@
     <row r="36" ht="24" customHeight="1" s="264">
       <c r="A36" s="493" t="inlineStr">
         <is>
-          <t>NOTICE — Interim verification between calibrations. Ref: SOP-601. Retain: 10 years.</t>
+          <t>NOTICE — Interim check between calibrations. If FAIL → remove from use, send for calibration. Ref: SOP-601. Retain: 10 years.</t>
         </is>
       </c>
       <c r="B36" s="471" t="n"/>
@@ -7243,8 +7293,8 @@
     <mergeCell ref="AS12:BD12"/>
     <mergeCell ref="E26:N26"/>
     <mergeCell ref="O10:V10"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="AW2:BD2"/>
-    <mergeCell ref="A20:D20"/>
     <mergeCell ref="O19:V19"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="W32:AH32"/>
@@ -7418,6 +7468,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
